--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF3AAB6-2C16-4E8C-9CAD-98CED59E10D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335A1093-0C71-41E8-A23B-C4533CEC55F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -659,9 +659,6 @@
     <t>TAM</t>
   </si>
   <si>
-    <t>COR NOVA</t>
-  </si>
-  <si>
     <t>LANÇAMENTO</t>
   </si>
   <si>
@@ -1452,6 +1449,9 @@
   </si>
   <si>
     <t>PREÇO</t>
+  </si>
+  <si>
+    <t>NOVA COR</t>
   </si>
 </sst>
 </file>
@@ -1863,6 +1863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K259"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1900,21 +1901,21 @@
         <v>3</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
@@ -1944,12 +1945,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>9</v>
@@ -1979,12 +1980,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
@@ -2014,12 +2015,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>9</v>
@@ -2049,12 +2050,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
@@ -2084,12 +2085,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>9</v>
@@ -2119,12 +2120,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>9</v>
@@ -2154,12 +2155,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>9</v>
@@ -2189,12 +2190,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
@@ -2224,12 +2225,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>9</v>
@@ -2259,12 +2260,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>9</v>
@@ -2294,12 +2295,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>9</v>
@@ -2329,12 +2330,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
@@ -2364,12 +2365,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>9</v>
@@ -2399,12 +2400,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>9</v>
@@ -2434,12 +2435,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>9</v>
@@ -2469,12 +2470,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
@@ -2504,12 +2505,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>9</v>
@@ -2539,12 +2540,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>9</v>
@@ -2574,12 +2575,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>9</v>
@@ -2609,12 +2610,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>9</v>
@@ -2644,12 +2645,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>9</v>
@@ -2679,12 +2680,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>9</v>
@@ -2716,10 +2717,10 @@
     </row>
     <row r="25" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>9</v>
@@ -2751,10 +2752,10 @@
     </row>
     <row r="26" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>9</v>
@@ -2786,10 +2787,10 @@
     </row>
     <row r="27" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>9</v>
@@ -2821,10 +2822,10 @@
     </row>
     <row r="28" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>9</v>
@@ -2856,10 +2857,10 @@
     </row>
     <row r="29" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>9</v>
@@ -2891,10 +2892,10 @@
     </row>
     <row r="30" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>9</v>
@@ -2924,12 +2925,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>9</v>
@@ -2959,12 +2960,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>9</v>
@@ -2994,12 +2995,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>9</v>
@@ -3029,12 +3030,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>51</v>
@@ -3064,12 +3065,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>51</v>
@@ -3099,12 +3100,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>51</v>
@@ -3134,12 +3135,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>51</v>
@@ -3169,12 +3170,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>51</v>
@@ -3204,12 +3205,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>51</v>
@@ -3239,12 +3240,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>51</v>
@@ -3274,12 +3275,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>58</v>
@@ -3309,12 +3310,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>58</v>
@@ -3344,12 +3345,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>58</v>
@@ -3379,12 +3380,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>58</v>
@@ -3414,12 +3415,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>58</v>
@@ -3449,12 +3450,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>58</v>
@@ -3484,12 +3485,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>58</v>
@@ -3519,12 +3520,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>58</v>
@@ -3554,12 +3555,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>58</v>
@@ -3589,12 +3590,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>58</v>
@@ -3624,12 +3625,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>58</v>
@@ -3659,12 +3660,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>58</v>
@@ -3694,12 +3695,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>58</v>
@@ -3729,12 +3730,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>58</v>
@@ -3764,12 +3765,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>58</v>
@@ -3799,12 +3800,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>58</v>
@@ -3834,12 +3835,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>58</v>
@@ -3869,12 +3870,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>58</v>
@@ -3904,12 +3905,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>58</v>
@@ -3939,12 +3940,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>58</v>
@@ -3974,12 +3975,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>58</v>
@@ -4009,12 +4010,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>58</v>
@@ -4044,12 +4045,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>58</v>
@@ -4079,12 +4080,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>58</v>
@@ -4114,12 +4115,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>58</v>
@@ -4149,12 +4150,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>58</v>
@@ -4184,12 +4185,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>58</v>
@@ -4219,12 +4220,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>58</v>
@@ -4254,12 +4255,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>58</v>
@@ -4289,12 +4290,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>58</v>
@@ -4324,12 +4325,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>58</v>
@@ -4359,12 +4360,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>58</v>
@@ -4394,12 +4395,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>58</v>
@@ -4429,12 +4430,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>58</v>
@@ -4464,12 +4465,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>58</v>
@@ -4499,12 +4500,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>58</v>
@@ -4534,12 +4535,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>58</v>
@@ -4569,12 +4570,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>58</v>
@@ -4604,12 +4605,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>58</v>
@@ -4639,12 +4640,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>58</v>
@@ -4674,12 +4675,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>58</v>
@@ -4709,12 +4710,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>58</v>
@@ -4744,12 +4745,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>58</v>
@@ -4779,12 +4780,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>58</v>
@@ -4814,12 +4815,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>58</v>
@@ -4849,12 +4850,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>58</v>
@@ -4884,12 +4885,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>58</v>
@@ -4919,12 +4920,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>58</v>
@@ -4954,12 +4955,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>58</v>
@@ -4989,12 +4990,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>58</v>
@@ -5024,12 +5025,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>58</v>
@@ -5059,12 +5060,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>58</v>
@@ -5094,12 +5095,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>58</v>
@@ -5129,12 +5130,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>58</v>
@@ -5164,12 +5165,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>58</v>
@@ -5199,12 +5200,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>58</v>
@@ -5234,12 +5235,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>58</v>
@@ -5269,12 +5270,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>58</v>
@@ -5304,12 +5305,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>58</v>
@@ -5339,12 +5340,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>58</v>
@@ -5374,12 +5375,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>58</v>
@@ -5409,12 +5410,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>58</v>
@@ -5444,12 +5445,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>58</v>
@@ -5479,12 +5480,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>58</v>
@@ -5514,12 +5515,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>58</v>
@@ -5549,12 +5550,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>58</v>
@@ -5584,12 +5585,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>58</v>
@@ -5619,12 +5620,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>58</v>
@@ -5654,12 +5655,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>58</v>
@@ -5689,12 +5690,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>58</v>
@@ -5724,12 +5725,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>58</v>
@@ -5759,12 +5760,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>58</v>
@@ -5794,12 +5795,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>58</v>
@@ -5829,12 +5830,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>58</v>
@@ -5864,12 +5865,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>58</v>
@@ -5899,12 +5900,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>58</v>
@@ -5934,12 +5935,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>58</v>
@@ -5969,12 +5970,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>58</v>
@@ -6004,12 +6005,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>58</v>
@@ -6039,12 +6040,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>58</v>
@@ -6074,12 +6075,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>58</v>
@@ -6109,12 +6110,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>58</v>
@@ -6144,12 +6145,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>58</v>
@@ -6179,12 +6180,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>58</v>
@@ -6214,12 +6215,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>58</v>
@@ -6249,12 +6250,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>58</v>
@@ -6284,12 +6285,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>58</v>
@@ -6319,12 +6320,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>58</v>
@@ -6354,12 +6355,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>58</v>
@@ -6389,12 +6390,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>58</v>
@@ -6424,12 +6425,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>58</v>
@@ -6459,12 +6460,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>58</v>
@@ -6494,12 +6495,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>58</v>
@@ -6529,12 +6530,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>58</v>
@@ -6564,12 +6565,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>58</v>
@@ -6599,12 +6600,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>58</v>
@@ -6634,12 +6635,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>58</v>
@@ -6669,12 +6670,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>58</v>
@@ -6704,12 +6705,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>58</v>
@@ -6739,12 +6740,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>58</v>
@@ -6774,12 +6775,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>58</v>
@@ -6809,12 +6810,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>58</v>
@@ -6844,12 +6845,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>58</v>
@@ -6879,12 +6880,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>58</v>
@@ -6914,12 +6915,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>58</v>
@@ -6949,12 +6950,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>58</v>
@@ -6984,12 +6985,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>58</v>
@@ -7019,12 +7020,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>58</v>
@@ -7054,12 +7055,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>58</v>
@@ -7089,12 +7090,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>58</v>
@@ -7124,12 +7125,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>58</v>
@@ -7159,12 +7160,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C152" s="4" t="s">
         <v>58</v>
@@ -7194,12 +7195,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>58</v>
@@ -7229,12 +7230,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>58</v>
@@ -7264,12 +7265,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>58</v>
@@ -7299,12 +7300,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="156" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>58</v>
@@ -7334,12 +7335,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>58</v>
@@ -7369,12 +7370,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>58</v>
@@ -7404,12 +7405,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>58</v>
@@ -7439,12 +7440,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>58</v>
@@ -7474,12 +7475,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="161" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>58</v>
@@ -7509,12 +7510,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>58</v>
@@ -7544,12 +7545,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>58</v>
@@ -7579,12 +7580,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>58</v>
@@ -7614,12 +7615,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>58</v>
@@ -7649,12 +7650,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>58</v>
@@ -7684,12 +7685,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>58</v>
@@ -7719,12 +7720,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>58</v>
@@ -7754,12 +7755,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>58</v>
@@ -7789,12 +7790,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>58</v>
@@ -7824,12 +7825,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>58</v>
@@ -7859,12 +7860,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>58</v>
@@ -7894,12 +7895,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>58</v>
@@ -7929,12 +7930,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>58</v>
@@ -7964,12 +7965,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>58</v>
@@ -7999,12 +8000,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>58</v>
@@ -8034,12 +8035,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>58</v>
@@ -8069,12 +8070,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>58</v>
@@ -8104,12 +8105,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>58</v>
@@ -8139,12 +8140,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>58</v>
@@ -8174,12 +8175,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>58</v>
@@ -8209,12 +8210,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>58</v>
@@ -8244,12 +8245,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>58</v>
@@ -8279,12 +8280,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>58</v>
@@ -8314,12 +8315,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>58</v>
@@ -8349,12 +8350,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>58</v>
@@ -8384,12 +8385,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>58</v>
@@ -8419,15 +8420,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D188" s="4">
         <v>43752263</v>
@@ -8454,15 +8455,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D189" s="2">
         <v>43752263</v>
@@ -8489,15 +8490,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D190" s="4">
         <v>43752263</v>
@@ -8524,15 +8525,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D191" s="2">
         <v>43752263</v>
@@ -8559,15 +8560,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D192" s="4">
         <v>43752263</v>
@@ -8594,15 +8595,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D193" s="2">
         <v>43752263</v>
@@ -8629,15 +8630,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="194" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D194" s="4" t="s">
         <v>172</v>
@@ -8664,15 +8665,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>172</v>
@@ -8699,15 +8700,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D196" s="4">
         <v>43489502</v>
@@ -8734,15 +8735,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="197" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D197" s="2">
         <v>43489502</v>
@@ -8769,15 +8770,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D198" s="4">
         <v>43489502</v>
@@ -8804,15 +8805,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="199" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D199" s="2">
         <v>43489502</v>
@@ -8839,15 +8840,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="200" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D200" s="4">
         <v>43489502</v>
@@ -8874,15 +8875,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D201" s="2">
         <v>43489502</v>
@@ -8909,15 +8910,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="202" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D202" s="4">
         <v>43409454</v>
@@ -8944,15 +8945,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="203" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D203" s="2">
         <v>43409454</v>
@@ -8979,15 +8980,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D204" s="4">
         <v>43409454</v>
@@ -9014,15 +9015,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="205" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D205" s="2">
         <v>43409454</v>
@@ -9049,15 +9050,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="206" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D206" s="4">
         <v>43409454</v>
@@ -9084,15 +9085,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="207" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D207" s="2">
         <v>43409454</v>
@@ -9119,12 +9120,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="208" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>58</v>
@@ -9154,12 +9155,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>58</v>
@@ -9189,12 +9190,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="210" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>58</v>
@@ -9224,12 +9225,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>58</v>
@@ -9259,12 +9260,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>58</v>
@@ -9294,12 +9295,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="213" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>58</v>
@@ -9329,12 +9330,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="214" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C214" s="4" t="s">
         <v>58</v>
@@ -9364,12 +9365,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>58</v>
@@ -9399,12 +9400,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="216" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>58</v>
@@ -9434,12 +9435,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>58</v>
@@ -9469,12 +9470,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="218" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>58</v>
@@ -9504,12 +9505,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="219" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>58</v>
@@ -9539,12 +9540,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="220" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>58</v>
@@ -9574,12 +9575,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="221" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>58</v>
@@ -9609,12 +9610,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>58</v>
@@ -9644,12 +9645,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="223" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>58</v>
@@ -9679,15 +9680,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="224" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D224" s="4">
         <v>43406455</v>
@@ -9714,15 +9715,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="225" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D225" s="2">
         <v>43406455</v>
@@ -9749,15 +9750,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="226" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D226" s="4">
         <v>43406455</v>
@@ -9784,15 +9785,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="227" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D227" s="2">
         <v>43406455</v>
@@ -9819,15 +9820,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="228" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D228" s="4">
         <v>43406455</v>
@@ -9854,15 +9855,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="229" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D229" s="2">
         <v>43406455</v>
@@ -9889,12 +9890,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="230" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C230" s="4" t="s">
         <v>58</v>
@@ -9924,12 +9925,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="231" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>58</v>
@@ -9959,12 +9960,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="232" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>58</v>
@@ -9994,12 +9995,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="233" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>58</v>
@@ -10029,12 +10030,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="234" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>58</v>
@@ -10064,15 +10065,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="235" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B235" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C235" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D235" s="2">
         <v>54113468</v>
@@ -10099,15 +10100,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="236" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B236" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C236" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D236" s="4">
         <v>54113468</v>
@@ -10134,15 +10135,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="237" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B237" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C237" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D237" s="2">
         <v>54113468</v>
@@ -10169,15 +10170,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="238" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B238" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C238" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D238" s="4">
         <v>54113468</v>
@@ -10204,15 +10205,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="239" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B239" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C239" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D239" s="2">
         <v>54113468</v>
@@ -10239,15 +10240,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="240" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B240" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C240" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D240" s="4">
         <v>54113468</v>
@@ -10274,15 +10275,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="241" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B241" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C241" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D241" s="2">
         <v>54112479</v>
@@ -10309,15 +10310,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="242" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B242" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C242" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D242" s="4">
         <v>54112479</v>
@@ -10344,15 +10345,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="243" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B243" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C243" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D243" s="2">
         <v>54112479</v>
@@ -10379,15 +10380,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="244" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B244" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C244" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D244" s="4">
         <v>54112479</v>
@@ -10414,15 +10415,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="245" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B245" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C245" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C245" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D245" s="2">
         <v>54107376</v>
@@ -10449,15 +10450,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="246" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B246" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C246" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D246" s="4">
         <v>54107376</v>
@@ -10484,15 +10485,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="247" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B247" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C247" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D247" s="2">
         <v>54107376</v>
@@ -10519,15 +10520,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="248" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B248" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C248" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D248" s="4">
         <v>54107376</v>
@@ -10554,15 +10555,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="249" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B249" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C249" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D249" s="2">
         <v>54107376</v>
@@ -10589,15 +10590,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="250" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B250" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C250" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D250" s="4">
         <v>54104269</v>
@@ -10624,15 +10625,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="251" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B251" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C251" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D251" s="2">
         <v>54104269</v>
@@ -10659,15 +10660,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="252" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B252" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C252" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D252" s="4">
         <v>54104269</v>
@@ -10694,15 +10695,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="253" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B253" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C253" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D253" s="2">
         <v>54104269</v>
@@ -10729,15 +10730,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="254" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B254" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C254" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D254" s="4">
         <v>54110438</v>
@@ -10764,15 +10765,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="255" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B255" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C255" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D255" s="2">
         <v>54110438</v>
@@ -10799,15 +10800,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="256" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B256" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C256" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D256" s="4">
         <v>54110438</v>
@@ -10834,15 +10835,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="257" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B257" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C257" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D257" s="2">
         <v>54110438</v>
@@ -10869,15 +10870,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="258" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:11" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B258" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C258" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D258" s="4">
         <v>54110438</v>
@@ -10904,16 +10905,22 @@
         <v>6</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B259" s="2"/>
       <c r="D259" s="5"/>
       <c r="E259" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K259" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K259" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="CHALLENGER 6"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C420C5A-14E2-401B-8927-7194F891583B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F6703B-B7A1-4880-97F4-A8304D0C9958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4895,7 +4895,7 @@
     <t>OBMSR241922_BFCBPO</t>
   </si>
   <si>
-    <t>OIWSC26601_TAPTRY</t>
+    <t>OIWSC26601_PTPRT</t>
   </si>
 </sst>
 </file>
@@ -48004,7 +48004,7 @@
     </row>
     <row r="900" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="2" t="s">
-        <v>1396</v>
+        <v>1517</v>
       </c>
       <c r="B900" s="2" t="s">
         <v>565</v>
@@ -48048,7 +48048,7 @@
     </row>
     <row r="901" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="2" t="s">
-        <v>1399</v>
+        <v>1520</v>
       </c>
       <c r="B901" s="2" t="s">
         <v>565</v>
@@ -48092,7 +48092,7 @@
     </row>
     <row r="902" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="2" t="s">
-        <v>1400</v>
+        <v>1521</v>
       </c>
       <c r="B902" s="2" t="s">
         <v>565</v>
@@ -48136,7 +48136,7 @@
     </row>
     <row r="903" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="2" t="s">
-        <v>1403</v>
+        <v>1524</v>
       </c>
       <c r="B903" s="2" t="s">
         <v>565</v>
@@ -48180,7 +48180,7 @@
     </row>
     <row r="904" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="2" t="s">
-        <v>1406</v>
+        <v>1525</v>
       </c>
       <c r="B904" s="2" t="s">
         <v>565</v>
@@ -48224,7 +48224,7 @@
     </row>
     <row r="905" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="2" t="s">
-        <v>1407</v>
+        <v>1528</v>
       </c>
       <c r="B905" s="2" t="s">
         <v>565</v>
@@ -48268,7 +48268,7 @@
     </row>
     <row r="906" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="2" t="s">
-        <v>1409</v>
+        <v>1529</v>
       </c>
       <c r="B906" s="2" t="s">
         <v>565</v>
@@ -48312,7 +48312,7 @@
     </row>
     <row r="907" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="2" t="s">
-        <v>1411</v>
+        <v>1532</v>
       </c>
       <c r="B907" s="2" t="s">
         <v>565</v>
@@ -48356,7 +48356,7 @@
     </row>
     <row r="908" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="2" t="s">
-        <v>1619</v>
+        <v>1535</v>
       </c>
       <c r="B908" s="2" t="s">
         <v>565</v>
@@ -48400,7 +48400,7 @@
     </row>
     <row r="909" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="2" t="s">
-        <v>1414</v>
+        <v>1538</v>
       </c>
       <c r="B909" s="2" t="s">
         <v>565</v>
@@ -48444,7 +48444,7 @@
     </row>
     <row r="910" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="2" t="s">
-        <v>1416</v>
+        <v>1539</v>
       </c>
       <c r="B910" s="2" t="s">
         <v>565</v>
@@ -48488,7 +48488,7 @@
     </row>
     <row r="911" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="2" t="s">
-        <v>1418</v>
+        <v>1542</v>
       </c>
       <c r="B911" s="2" t="s">
         <v>565</v>
@@ -48532,7 +48532,7 @@
     </row>
     <row r="912" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="2" t="s">
-        <v>1420</v>
+        <v>1544</v>
       </c>
       <c r="B912" s="2" t="s">
         <v>565</v>
@@ -48576,7 +48576,7 @@
     </row>
     <row r="913" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
-        <v>1423</v>
+        <v>1547</v>
       </c>
       <c r="B913" s="2" t="s">
         <v>565</v>
@@ -48620,7 +48620,7 @@
     </row>
     <row r="914" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="2" t="s">
-        <v>1425</v>
+        <v>1548</v>
       </c>
       <c r="B914" s="2" t="s">
         <v>565</v>
@@ -48664,7 +48664,7 @@
     </row>
     <row r="915" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="2" t="s">
-        <v>1426</v>
+        <v>1551</v>
       </c>
       <c r="B915" s="2" t="s">
         <v>565</v>
@@ -48708,7 +48708,7 @@
     </row>
     <row r="916" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="2" t="s">
-        <v>1427</v>
+        <v>1552</v>
       </c>
       <c r="B916" s="2" t="s">
         <v>565</v>
@@ -48752,7 +48752,7 @@
     </row>
     <row r="917" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="2" t="s">
-        <v>1428</v>
+        <v>1553</v>
       </c>
       <c r="B917" s="2" t="s">
         <v>565</v>
@@ -48796,7 +48796,7 @@
     </row>
     <row r="918" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="2" t="s">
-        <v>1431</v>
+        <v>1556</v>
       </c>
       <c r="B918" s="2" t="s">
         <v>565</v>
@@ -48840,7 +48840,7 @@
     </row>
     <row r="919" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="2" t="s">
-        <v>1432</v>
+        <v>1565</v>
       </c>
       <c r="B919" s="2" t="s">
         <v>565</v>
@@ -48884,7 +48884,7 @@
     </row>
     <row r="920" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="2" t="s">
-        <v>1433</v>
+        <v>1568</v>
       </c>
       <c r="B920" s="2" t="s">
         <v>565</v>
@@ -48928,7 +48928,7 @@
     </row>
     <row r="921" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="2" t="s">
-        <v>1434</v>
+        <v>1571</v>
       </c>
       <c r="B921" s="2" t="s">
         <v>565</v>
@@ -48972,7 +48972,7 @@
     </row>
     <row r="922" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A922" s="2" t="s">
-        <v>1436</v>
+        <v>1574</v>
       </c>
       <c r="B922" s="2" t="s">
         <v>565</v>
@@ -49016,7 +49016,7 @@
     </row>
     <row r="923" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A923" s="2" t="s">
-        <v>1439</v>
+        <v>1575</v>
       </c>
       <c r="B923" s="2" t="s">
         <v>565</v>
@@ -49060,7 +49060,7 @@
     </row>
     <row r="924" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A924" s="2" t="s">
-        <v>1441</v>
+        <v>1579</v>
       </c>
       <c r="B924" s="2" t="s">
         <v>565</v>
@@ -49104,7 +49104,7 @@
     </row>
     <row r="925" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="2" t="s">
-        <v>1444</v>
+        <v>1581</v>
       </c>
       <c r="B925" s="2" t="s">
         <v>565</v>
@@ -49148,7 +49148,7 @@
     </row>
     <row r="926" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A926" s="2" t="s">
-        <v>1445</v>
+        <v>1582</v>
       </c>
       <c r="B926" s="2" t="s">
         <v>565</v>
@@ -49192,7 +49192,7 @@
     </row>
     <row r="927" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A927" s="2" t="s">
-        <v>1446</v>
+        <v>1586</v>
       </c>
       <c r="B927" s="2" t="s">
         <v>565</v>
@@ -49236,7 +49236,7 @@
     </row>
     <row r="928" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A928" s="2" t="s">
-        <v>1448</v>
+        <v>1595</v>
       </c>
       <c r="B928" s="2" t="s">
         <v>565</v>
@@ -49280,7 +49280,7 @@
     </row>
     <row r="929" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A929" s="2" t="s">
-        <v>1451</v>
+        <v>1596</v>
       </c>
       <c r="B929" s="2" t="s">
         <v>565</v>
@@ -49324,7 +49324,7 @@
     </row>
     <row r="930" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="2" t="s">
-        <v>1452</v>
+        <v>1605</v>
       </c>
       <c r="B930" s="2" t="s">
         <v>666</v>
@@ -49368,7 +49368,7 @@
     </row>
     <row r="931" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A931" s="2" t="s">
-        <v>1455</v>
+        <v>1606</v>
       </c>
       <c r="B931" s="2" t="s">
         <v>666</v>
@@ -49412,7 +49412,7 @@
     </row>
     <row r="932" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A932" s="2" t="s">
-        <v>1457</v>
+        <v>1609</v>
       </c>
       <c r="B932" s="2" t="s">
         <v>666</v>
@@ -49456,7 +49456,7 @@
     </row>
     <row r="933" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A933" s="2" t="s">
-        <v>1460</v>
+        <v>1610</v>
       </c>
       <c r="B933" s="2" t="s">
         <v>666</v>
@@ -49500,7 +49500,7 @@
     </row>
     <row r="934" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A934" s="2" t="s">
-        <v>1462</v>
+        <v>1611</v>
       </c>
       <c r="B934" s="2" t="s">
         <v>666</v>
@@ -49544,7 +49544,7 @@
     </row>
     <row r="935" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A935" s="2" t="s">
-        <v>1464</v>
+        <v>1614</v>
       </c>
       <c r="B935" s="2" t="s">
         <v>666</v>
@@ -49588,7 +49588,7 @@
     </row>
     <row r="936" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A936" s="2" t="s">
-        <v>1465</v>
+        <v>1615</v>
       </c>
       <c r="B936" s="2" t="s">
         <v>666</v>
@@ -49632,7 +49632,7 @@
     </row>
     <row r="937" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A937" s="2" t="s">
-        <v>1468</v>
+        <v>1618</v>
       </c>
       <c r="B937" s="2" t="s">
         <v>666</v>
@@ -49676,7 +49676,7 @@
     </row>
     <row r="938" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A938" s="2" t="s">
-        <v>1469</v>
+        <v>1396</v>
       </c>
       <c r="B938" s="2" t="s">
         <v>565</v>
@@ -49720,7 +49720,7 @@
     </row>
     <row r="939" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A939" s="2" t="s">
-        <v>1473</v>
+        <v>1399</v>
       </c>
       <c r="B939" s="2" t="s">
         <v>565</v>
@@ -49764,7 +49764,7 @@
     </row>
     <row r="940" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A940" s="2" t="s">
-        <v>1474</v>
+        <v>1400</v>
       </c>
       <c r="B940" s="2" t="s">
         <v>565</v>
@@ -49808,7 +49808,7 @@
     </row>
     <row r="941" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A941" s="2" t="s">
-        <v>1477</v>
+        <v>1403</v>
       </c>
       <c r="B941" s="2" t="s">
         <v>565</v>
@@ -49852,7 +49852,7 @@
     </row>
     <row r="942" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A942" s="2" t="s">
-        <v>1479</v>
+        <v>1406</v>
       </c>
       <c r="B942" s="2" t="s">
         <v>565</v>
@@ -49896,7 +49896,7 @@
     </row>
     <row r="943" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A943" s="2" t="s">
-        <v>1482</v>
+        <v>1407</v>
       </c>
       <c r="B943" s="2" t="s">
         <v>565</v>
@@ -49940,7 +49940,7 @@
     </row>
     <row r="944" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A944" s="2" t="s">
-        <v>1483</v>
+        <v>1409</v>
       </c>
       <c r="B944" s="2" t="s">
         <v>565</v>
@@ -49984,7 +49984,7 @@
     </row>
     <row r="945" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A945" s="2" t="s">
-        <v>1487</v>
+        <v>1411</v>
       </c>
       <c r="B945" s="2" t="s">
         <v>565</v>
@@ -50028,7 +50028,7 @@
     </row>
     <row r="946" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A946" s="2" t="s">
-        <v>1488</v>
+        <v>1619</v>
       </c>
       <c r="B946" s="2" t="s">
         <v>565</v>
@@ -50072,7 +50072,7 @@
     </row>
     <row r="947" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A947" s="2" t="s">
-        <v>1491</v>
+        <v>1414</v>
       </c>
       <c r="B947" s="2" t="s">
         <v>565</v>
@@ -50116,7 +50116,7 @@
     </row>
     <row r="948" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A948" s="2" t="s">
-        <v>1492</v>
+        <v>1416</v>
       </c>
       <c r="B948" s="2" t="s">
         <v>565</v>
@@ -50160,7 +50160,7 @@
     </row>
     <row r="949" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A949" s="2" t="s">
-        <v>1493</v>
+        <v>1418</v>
       </c>
       <c r="B949" s="2" t="s">
         <v>565</v>
@@ -50204,7 +50204,7 @@
     </row>
     <row r="950" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A950" s="2" t="s">
-        <v>1496</v>
+        <v>1420</v>
       </c>
       <c r="B950" s="2" t="s">
         <v>565</v>
@@ -50248,7 +50248,7 @@
     </row>
     <row r="951" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="2" t="s">
-        <v>1497</v>
+        <v>1423</v>
       </c>
       <c r="B951" s="2" t="s">
         <v>565</v>
@@ -50292,7 +50292,7 @@
     </row>
     <row r="952" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="2" t="s">
-        <v>1500</v>
+        <v>1425</v>
       </c>
       <c r="B952" s="2" t="s">
         <v>565</v>
@@ -50336,7 +50336,7 @@
     </row>
     <row r="953" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A953" s="2" t="s">
-        <v>1501</v>
+        <v>1426</v>
       </c>
       <c r="B953" s="2" t="s">
         <v>565</v>
@@ -50380,7 +50380,7 @@
     </row>
     <row r="954" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="2" t="s">
-        <v>1504</v>
+        <v>1427</v>
       </c>
       <c r="B954" s="2" t="s">
         <v>565</v>
@@ -50424,7 +50424,7 @@
     </row>
     <row r="955" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A955" s="2" t="s">
-        <v>1505</v>
+        <v>1428</v>
       </c>
       <c r="B955" s="2" t="s">
         <v>565</v>
@@ -50468,7 +50468,7 @@
     </row>
     <row r="956" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A956" s="2" t="s">
-        <v>1508</v>
+        <v>1431</v>
       </c>
       <c r="B956" s="2" t="s">
         <v>565</v>
@@ -50512,7 +50512,7 @@
     </row>
     <row r="957" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A957" s="2" t="s">
-        <v>1511</v>
+        <v>1432</v>
       </c>
       <c r="B957" s="2" t="s">
         <v>565</v>
@@ -50556,7 +50556,7 @@
     </row>
     <row r="958" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A958" s="2" t="s">
-        <v>1512</v>
+        <v>1433</v>
       </c>
       <c r="B958" s="2" t="s">
         <v>565</v>
@@ -50600,7 +50600,7 @@
     </row>
     <row r="959" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A959" s="2" t="s">
-        <v>1515</v>
+        <v>1434</v>
       </c>
       <c r="B959" s="2" t="s">
         <v>565</v>
@@ -50644,7 +50644,7 @@
     </row>
     <row r="960" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A960" s="2" t="s">
-        <v>1516</v>
+        <v>1436</v>
       </c>
       <c r="B960" s="2" t="s">
         <v>565</v>
@@ -50688,7 +50688,7 @@
     </row>
     <row r="961" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A961" s="2" t="s">
-        <v>1517</v>
+        <v>1439</v>
       </c>
       <c r="B961" s="2" t="s">
         <v>565</v>
@@ -50732,7 +50732,7 @@
     </row>
     <row r="962" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A962" s="2" t="s">
-        <v>1520</v>
+        <v>1441</v>
       </c>
       <c r="B962" s="2" t="s">
         <v>565</v>
@@ -50776,7 +50776,7 @@
     </row>
     <row r="963" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A963" s="2" t="s">
-        <v>1521</v>
+        <v>1444</v>
       </c>
       <c r="B963" s="2" t="s">
         <v>565</v>
@@ -50820,7 +50820,7 @@
     </row>
     <row r="964" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A964" s="2" t="s">
-        <v>1524</v>
+        <v>1445</v>
       </c>
       <c r="B964" s="2" t="s">
         <v>565</v>
@@ -50864,7 +50864,7 @@
     </row>
     <row r="965" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A965" s="2" t="s">
-        <v>1525</v>
+        <v>1446</v>
       </c>
       <c r="B965" s="2" t="s">
         <v>565</v>
@@ -50908,7 +50908,7 @@
     </row>
     <row r="966" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A966" s="2" t="s">
-        <v>1528</v>
+        <v>1448</v>
       </c>
       <c r="B966" s="2" t="s">
         <v>565</v>
@@ -50952,7 +50952,7 @@
     </row>
     <row r="967" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A967" s="2" t="s">
-        <v>1529</v>
+        <v>1451</v>
       </c>
       <c r="B967" s="2" t="s">
         <v>565</v>
@@ -50996,7 +50996,7 @@
     </row>
     <row r="968" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A968" s="2" t="s">
-        <v>1532</v>
+        <v>1452</v>
       </c>
       <c r="B968" s="2" t="s">
         <v>565</v>
@@ -51040,7 +51040,7 @@
     </row>
     <row r="969" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A969" s="2" t="s">
-        <v>1535</v>
+        <v>1455</v>
       </c>
       <c r="B969" s="2" t="s">
         <v>565</v>
@@ -51084,7 +51084,7 @@
     </row>
     <row r="970" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A970" s="2" t="s">
-        <v>1538</v>
+        <v>1457</v>
       </c>
       <c r="B970" s="2" t="s">
         <v>565</v>
@@ -51128,7 +51128,7 @@
     </row>
     <row r="971" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A971" s="2" t="s">
-        <v>1539</v>
+        <v>1460</v>
       </c>
       <c r="B971" s="2" t="s">
         <v>565</v>
@@ -51172,7 +51172,7 @@
     </row>
     <row r="972" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A972" s="2" t="s">
-        <v>1542</v>
+        <v>1462</v>
       </c>
       <c r="B972" s="2" t="s">
         <v>565</v>
@@ -51216,7 +51216,7 @@
     </row>
     <row r="973" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A973" s="2" t="s">
-        <v>1544</v>
+        <v>1464</v>
       </c>
       <c r="B973" s="2" t="s">
         <v>565</v>
@@ -51260,7 +51260,7 @@
     </row>
     <row r="974" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A974" s="2" t="s">
-        <v>1547</v>
+        <v>1465</v>
       </c>
       <c r="B974" s="2" t="s">
         <v>565</v>
@@ -51304,7 +51304,7 @@
     </row>
     <row r="975" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A975" s="2" t="s">
-        <v>1548</v>
+        <v>1468</v>
       </c>
       <c r="B975" s="2" t="s">
         <v>565</v>
@@ -51348,7 +51348,7 @@
     </row>
     <row r="976" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A976" s="2" t="s">
-        <v>1551</v>
+        <v>1469</v>
       </c>
       <c r="B976" s="2" t="s">
         <v>565</v>
@@ -51392,7 +51392,7 @@
     </row>
     <row r="977" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A977" s="2" t="s">
-        <v>1552</v>
+        <v>1473</v>
       </c>
       <c r="B977" s="2" t="s">
         <v>565</v>
@@ -51436,7 +51436,7 @@
     </row>
     <row r="978" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A978" s="2" t="s">
-        <v>1553</v>
+        <v>1474</v>
       </c>
       <c r="B978" s="2" t="s">
         <v>565</v>
@@ -51480,7 +51480,7 @@
     </row>
     <row r="979" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A979" s="2" t="s">
-        <v>1556</v>
+        <v>1477</v>
       </c>
       <c r="B979" s="2" t="s">
         <v>565</v>
@@ -51524,7 +51524,7 @@
     </row>
     <row r="980" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A980" s="2" t="s">
-        <v>1557</v>
+        <v>1479</v>
       </c>
       <c r="B980" s="2" t="s">
         <v>565</v>
@@ -51568,7 +51568,7 @@
     </row>
     <row r="981" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A981" s="2" t="s">
-        <v>1560</v>
+        <v>1482</v>
       </c>
       <c r="B981" s="2" t="s">
         <v>565</v>
@@ -51612,7 +51612,7 @@
     </row>
     <row r="982" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A982" s="2" t="s">
-        <v>1561</v>
+        <v>1483</v>
       </c>
       <c r="B982" s="2" t="s">
         <v>565</v>
@@ -51656,7 +51656,7 @@
     </row>
     <row r="983" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A983" s="2" t="s">
-        <v>1564</v>
+        <v>1487</v>
       </c>
       <c r="B983" s="2" t="s">
         <v>565</v>
@@ -51700,7 +51700,7 @@
     </row>
     <row r="984" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A984" s="2" t="s">
-        <v>1565</v>
+        <v>1488</v>
       </c>
       <c r="B984" s="2" t="s">
         <v>600</v>
@@ -51744,7 +51744,7 @@
     </row>
     <row r="985" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A985" s="2" t="s">
-        <v>1568</v>
+        <v>1491</v>
       </c>
       <c r="B985" s="2" t="s">
         <v>1569</v>
@@ -51788,7 +51788,7 @@
     </row>
     <row r="986" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A986" s="2" t="s">
-        <v>1571</v>
+        <v>1492</v>
       </c>
       <c r="B986" s="2" t="s">
         <v>565</v>
@@ -51832,7 +51832,7 @@
     </row>
     <row r="987" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A987" s="2" t="s">
-        <v>1574</v>
+        <v>1493</v>
       </c>
       <c r="B987" s="2" t="s">
         <v>565</v>
@@ -51876,7 +51876,7 @@
     </row>
     <row r="988" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A988" s="2" t="s">
-        <v>1575</v>
+        <v>1496</v>
       </c>
       <c r="B988" s="2" t="s">
         <v>666</v>
@@ -51920,7 +51920,7 @@
     </row>
     <row r="989" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A989" s="2" t="s">
-        <v>1579</v>
+        <v>1497</v>
       </c>
       <c r="B989" s="2" t="s">
         <v>666</v>
@@ -51964,7 +51964,7 @@
     </row>
     <row r="990" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A990" s="2" t="s">
-        <v>1581</v>
+        <v>1500</v>
       </c>
       <c r="B990" s="2" t="s">
         <v>666</v>
@@ -52008,7 +52008,7 @@
     </row>
     <row r="991" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A991" s="2" t="s">
-        <v>1582</v>
+        <v>1501</v>
       </c>
       <c r="B991" s="2" t="s">
         <v>666</v>
@@ -52052,7 +52052,7 @@
     </row>
     <row r="992" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A992" s="2" t="s">
-        <v>1586</v>
+        <v>1504</v>
       </c>
       <c r="B992" s="2" t="s">
         <v>666</v>
@@ -52096,7 +52096,7 @@
     </row>
     <row r="993" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="2" t="s">
-        <v>1588</v>
+        <v>1505</v>
       </c>
       <c r="B993" s="2" t="s">
         <v>666</v>
@@ -52140,7 +52140,7 @@
     </row>
     <row r="994" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A994" s="2" t="s">
-        <v>1590</v>
+        <v>1508</v>
       </c>
       <c r="B994" s="2" t="s">
         <v>666</v>
@@ -52184,7 +52184,7 @@
     </row>
     <row r="995" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A995" s="2" t="s">
-        <v>1592</v>
+        <v>1511</v>
       </c>
       <c r="B995" s="2" t="s">
         <v>666</v>
@@ -52228,7 +52228,7 @@
     </row>
     <row r="996" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A996" s="2" t="s">
-        <v>1595</v>
+        <v>1512</v>
       </c>
       <c r="B996" s="2" t="s">
         <v>666</v>
@@ -52272,7 +52272,7 @@
     </row>
     <row r="997" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A997" s="2" t="s">
-        <v>1596</v>
+        <v>1515</v>
       </c>
       <c r="B997" s="2" t="s">
         <v>666</v>
@@ -52316,7 +52316,7 @@
     </row>
     <row r="998" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A998" s="2" t="s">
-        <v>1597</v>
+        <v>1516</v>
       </c>
       <c r="B998" s="2" t="s">
         <v>666</v>
@@ -52360,7 +52360,7 @@
     </row>
     <row r="999" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A999" s="2" t="s">
-        <v>1598</v>
+        <v>1557</v>
       </c>
       <c r="B999" s="2" t="s">
         <v>565</v>
@@ -52404,7 +52404,7 @@
     </row>
     <row r="1000" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1000" s="2" t="s">
-        <v>1601</v>
+        <v>1560</v>
       </c>
       <c r="B1000" s="2" t="s">
         <v>565</v>
@@ -52448,7 +52448,7 @@
     </row>
     <row r="1001" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1001" s="2" t="s">
-        <v>1602</v>
+        <v>1561</v>
       </c>
       <c r="B1001" s="2" t="s">
         <v>565</v>
@@ -52492,7 +52492,7 @@
     </row>
     <row r="1002" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1002" s="2" t="s">
-        <v>1605</v>
+        <v>1564</v>
       </c>
       <c r="B1002" s="2" t="s">
         <v>565</v>
@@ -52536,7 +52536,7 @@
     </row>
     <row r="1003" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1003" s="2" t="s">
-        <v>1606</v>
+        <v>1588</v>
       </c>
       <c r="B1003" s="2" t="s">
         <v>565</v>
@@ -52580,7 +52580,7 @@
     </row>
     <row r="1004" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="2" t="s">
-        <v>1609</v>
+        <v>1590</v>
       </c>
       <c r="B1004" s="2" t="s">
         <v>565</v>
@@ -52624,7 +52624,7 @@
     </row>
     <row r="1005" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="2" t="s">
-        <v>1610</v>
+        <v>1592</v>
       </c>
       <c r="B1005" s="2" t="s">
         <v>565</v>
@@ -52668,7 +52668,7 @@
     </row>
     <row r="1006" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="2" t="s">
-        <v>1611</v>
+        <v>1597</v>
       </c>
       <c r="B1006" s="2" t="s">
         <v>565</v>
@@ -52712,7 +52712,7 @@
     </row>
     <row r="1007" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1007" s="2" t="s">
-        <v>1614</v>
+        <v>1598</v>
       </c>
       <c r="B1007" s="2" t="s">
         <v>565</v>
@@ -52756,7 +52756,7 @@
     </row>
     <row r="1008" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1008" s="2" t="s">
-        <v>1615</v>
+        <v>1601</v>
       </c>
       <c r="B1008" s="2" t="s">
         <v>565</v>
@@ -52800,7 +52800,7 @@
     </row>
     <row r="1009" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1009" s="2" t="s">
-        <v>1618</v>
+        <v>1602</v>
       </c>
       <c r="B1009" s="2" t="s">
         <v>565</v>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781841F3-4BED-4FCE-80B2-4325F3F6BE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F5C307-9828-4521-920E-15FA9798C364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13103" uniqueCount="1679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13155" uniqueCount="1699">
   <si>
     <t>IMAGEM</t>
   </si>
@@ -5074,13 +5074,73 @@
   </si>
   <si>
     <t>43540500_PTO_LM</t>
+  </si>
+  <si>
+    <t>SHORT CORRE FOCO 2EM1 3 F</t>
+  </si>
+  <si>
+    <t>TOP CORRE FOCO A IMPAC F</t>
+  </si>
+  <si>
+    <t>BERM BOLSO CORRE FOCO 7 F</t>
+  </si>
+  <si>
+    <t>TOP CORRE FOCO M IMPAC F</t>
+  </si>
+  <si>
+    <t>BERM CORRE FOCO 2EM1 5 M</t>
+  </si>
+  <si>
+    <t>BERM BOLSO CORRE FOCO 8 M</t>
+  </si>
+  <si>
+    <t>BONE CORRE FOCO</t>
+  </si>
+  <si>
+    <t>OIWSC26701_PT_BCO</t>
+  </si>
+  <si>
+    <t>OIWSC26801_PT_PRT</t>
+  </si>
+  <si>
+    <t>OIWSC26802_PT_PRT</t>
+  </si>
+  <si>
+    <t>OIWSC26101_PT_PRT</t>
+  </si>
+  <si>
+    <t>OIWSC26103_PT_PRT</t>
+  </si>
+  <si>
+    <t>OIWSC26301_PT_PRT</t>
+  </si>
+  <si>
+    <t>OIWSC26102_PT_PRT</t>
+  </si>
+  <si>
+    <t>OIWSC26601_PT_PRT</t>
+  </si>
+  <si>
+    <t>OIMSC26704_PT_BCO</t>
+  </si>
+  <si>
+    <t>OIMSC26806_PT_PRT</t>
+  </si>
+  <si>
+    <t>OIMSC26805_PT_PRT</t>
+  </si>
+  <si>
+    <t>OIMSC26303_PT_PRT</t>
+  </si>
+  <si>
+    <t>OICR261714_PT_PRT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5107,8 +5167,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5147,6 +5214,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4ADE80"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFEFF6FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -5189,10 +5262,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5216,9 +5290,13 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 4 2 2 2 2" xfId="1" xr:uid="{7A960E73-CD2E-4168-980B-749B14AF9817}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -5518,8 +5596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:AI1026"/>
+  <dimension ref="A1:AI1040"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" style="6" customWidth="1"/>
@@ -5640,7 +5717,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
@@ -5854,7 +5931,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>47</v>
       </c>
@@ -5961,7 +6038,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>49</v>
       </c>
@@ -6068,7 +6145,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>51</v>
       </c>
@@ -6175,7 +6252,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>53</v>
       </c>
@@ -6282,7 +6359,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>56</v>
       </c>
@@ -6389,7 +6466,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>58</v>
       </c>
@@ -6496,7 +6573,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>60</v>
       </c>
@@ -6710,7 +6787,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>64</v>
       </c>
@@ -6817,7 +6894,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>67</v>
       </c>
@@ -6924,7 +7001,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>69</v>
       </c>
@@ -7031,7 +7108,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>71</v>
       </c>
@@ -7138,7 +7215,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>73</v>
       </c>
@@ -7245,7 +7322,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>75</v>
       </c>
@@ -7459,7 +7536,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>79</v>
       </c>
@@ -7566,7 +7643,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>82</v>
       </c>
@@ -7673,7 +7750,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>83</v>
       </c>
@@ -7780,7 +7857,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>85</v>
       </c>
@@ -7887,7 +7964,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>87</v>
       </c>
@@ -8101,7 +8178,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>89</v>
       </c>
@@ -8208,7 +8285,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>93</v>
       </c>
@@ -8315,7 +8392,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>96</v>
       </c>
@@ -8422,7 +8499,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>98</v>
       </c>
@@ -8636,7 +8713,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>101</v>
       </c>
@@ -8743,7 +8820,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>103</v>
       </c>
@@ -8850,7 +8927,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>105</v>
       </c>
@@ -8957,7 +9034,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="33" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>106</v>
       </c>
@@ -9064,7 +9141,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>108</v>
       </c>
@@ -9171,7 +9248,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>113</v>
       </c>
@@ -9278,7 +9355,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>114</v>
       </c>
@@ -9385,7 +9462,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="37" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>116</v>
       </c>
@@ -9492,7 +9569,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="38" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>117</v>
       </c>
@@ -9599,7 +9676,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="39" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>118</v>
       </c>
@@ -9706,7 +9783,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="40" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>120</v>
       </c>
@@ -9813,7 +9890,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="41" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>122</v>
       </c>
@@ -9920,7 +9997,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>126</v>
       </c>
@@ -10027,7 +10104,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="43" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>128</v>
       </c>
@@ -10134,7 +10211,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>129</v>
       </c>
@@ -10348,7 +10425,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="46" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>132</v>
       </c>
@@ -10455,7 +10532,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>134</v>
       </c>
@@ -10562,7 +10639,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>136</v>
       </c>
@@ -10669,7 +10746,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="49" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>138</v>
       </c>
@@ -10883,7 +10960,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>141</v>
       </c>
@@ -10990,7 +11067,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="52" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>145</v>
       </c>
@@ -11097,7 +11174,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>146</v>
       </c>
@@ -11204,7 +11281,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="54" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>147</v>
       </c>
@@ -11311,7 +11388,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="55" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>149</v>
       </c>
@@ -11418,7 +11495,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="56" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>150</v>
       </c>
@@ -11525,7 +11602,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="57" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>152</v>
       </c>
@@ -11739,7 +11816,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>156</v>
       </c>
@@ -11846,7 +11923,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>158</v>
       </c>
@@ -11953,7 +12030,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>160</v>
       </c>
@@ -12060,7 +12137,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>161</v>
       </c>
@@ -12167,7 +12244,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>163</v>
       </c>
@@ -12274,7 +12351,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="64" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>166</v>
       </c>
@@ -12381,7 +12458,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>168</v>
       </c>
@@ -12488,7 +12565,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="66" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>170</v>
       </c>
@@ -12702,7 +12779,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="68" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>173</v>
       </c>
@@ -12809,7 +12886,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>175</v>
       </c>
@@ -12916,7 +12993,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="70" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>178</v>
       </c>
@@ -13023,7 +13100,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="71" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>179</v>
       </c>
@@ -13237,7 +13314,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="73" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>181</v>
       </c>
@@ -13344,7 +13421,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>184</v>
       </c>
@@ -13451,7 +13528,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>186</v>
       </c>
@@ -13558,7 +13635,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>188</v>
       </c>
@@ -13772,7 +13849,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>191</v>
       </c>
@@ -13879,7 +13956,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>194</v>
       </c>
@@ -14093,7 +14170,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>197</v>
       </c>
@@ -14200,7 +14277,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="82" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>200</v>
       </c>
@@ -14414,7 +14491,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="84" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>202</v>
       </c>
@@ -14628,7 +14705,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="86" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>206</v>
       </c>
@@ -14735,7 +14812,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="87" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>208</v>
       </c>
@@ -14842,7 +14919,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="88" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>210</v>
       </c>
@@ -14949,7 +15026,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="89" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>213</v>
       </c>
@@ -15056,7 +15133,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="90" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>215</v>
       </c>
@@ -15163,7 +15240,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="91" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>216</v>
       </c>
@@ -15270,7 +15347,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="92" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>217</v>
       </c>
@@ -15377,7 +15454,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="93" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>220</v>
       </c>
@@ -15484,7 +15561,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="94" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>221</v>
       </c>
@@ -15591,7 +15668,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="95" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>223</v>
       </c>
@@ -15698,7 +15775,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="96" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>225</v>
       </c>
@@ -15805,7 +15882,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>229</v>
       </c>
@@ -15912,7 +15989,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>231</v>
       </c>
@@ -16126,7 +16203,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>234</v>
       </c>
@@ -16233,7 +16310,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>237</v>
       </c>
@@ -16340,7 +16417,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>239</v>
       </c>
@@ -16554,7 +16631,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>241</v>
       </c>
@@ -16661,7 +16738,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>243</v>
       </c>
@@ -16768,7 +16845,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>245</v>
       </c>
@@ -16875,7 +16952,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="107" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>248</v>
       </c>
@@ -16982,7 +17059,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="108" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>249</v>
       </c>
@@ -17089,7 +17166,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="109" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>250</v>
       </c>
@@ -17303,7 +17380,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="111" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>253</v>
       </c>
@@ -17410,7 +17487,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="112" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>255</v>
       </c>
@@ -17517,7 +17594,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="113" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>257</v>
       </c>
@@ -17624,7 +17701,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="114" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>259</v>
       </c>
@@ -17731,7 +17808,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="115" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>260</v>
       </c>
@@ -17838,7 +17915,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="116" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>262</v>
       </c>
@@ -17945,7 +18022,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="117" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>264</v>
       </c>
@@ -18052,7 +18129,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="118" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>266</v>
       </c>
@@ -18159,7 +18236,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="119" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>268</v>
       </c>
@@ -18266,7 +18343,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="120" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>270</v>
       </c>
@@ -18373,7 +18450,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="121" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>271</v>
       </c>
@@ -18480,7 +18557,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>273</v>
       </c>
@@ -18587,7 +18664,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>275</v>
       </c>
@@ -18694,7 +18771,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="124" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>277</v>
       </c>
@@ -18801,7 +18878,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>278</v>
       </c>
@@ -18908,7 +18985,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="126" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>281</v>
       </c>
@@ -19015,7 +19092,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="127" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>282</v>
       </c>
@@ -19122,7 +19199,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="128" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>283</v>
       </c>
@@ -19229,7 +19306,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>284</v>
       </c>
@@ -19336,7 +19413,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>286</v>
       </c>
@@ -19443,7 +19520,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>288</v>
       </c>
@@ -19550,7 +19627,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="132" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>290</v>
       </c>
@@ -19657,7 +19734,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="133" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>291</v>
       </c>
@@ -19764,7 +19841,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="134" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>293</v>
       </c>
@@ -19871,7 +19948,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="135" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>294</v>
       </c>
@@ -20085,7 +20162,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="137" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>296</v>
       </c>
@@ -20192,7 +20269,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="138" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>299</v>
       </c>
@@ -20299,7 +20376,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="139" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>300</v>
       </c>
@@ -20513,7 +20590,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>302</v>
       </c>
@@ -20620,7 +20697,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="142" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>305</v>
       </c>
@@ -20834,7 +20911,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="144" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>308</v>
       </c>
@@ -20941,7 +21018,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="145" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>310</v>
       </c>
@@ -21048,7 +21125,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="146" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>312</v>
       </c>
@@ -21262,7 +21339,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="148" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>314</v>
       </c>
@@ -21369,7 +21446,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="149" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>316</v>
       </c>
@@ -21476,7 +21553,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="150" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>317</v>
       </c>
@@ -21583,7 +21660,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="151" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>318</v>
       </c>
@@ -21690,7 +21767,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="152" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>321</v>
       </c>
@@ -21797,7 +21874,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="153" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>322</v>
       </c>
@@ -21904,7 +21981,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="154" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>324</v>
       </c>
@@ -22011,7 +22088,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="155" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>325</v>
       </c>
@@ -22118,7 +22195,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="156" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>327</v>
       </c>
@@ -22225,7 +22302,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="157" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>328</v>
       </c>
@@ -22332,7 +22409,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="158" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>329</v>
       </c>
@@ -22439,7 +22516,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="159" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>330</v>
       </c>
@@ -22546,7 +22623,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="160" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>332</v>
       </c>
@@ -22653,7 +22730,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="161" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>334</v>
       </c>
@@ -22760,7 +22837,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="162" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>336</v>
       </c>
@@ -22867,7 +22944,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="163" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>337</v>
       </c>
@@ -22974,7 +23051,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="164" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>340</v>
       </c>
@@ -23081,7 +23158,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="165" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>342</v>
       </c>
@@ -23188,7 +23265,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="166" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>344</v>
       </c>
@@ -23295,7 +23372,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="167" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>346</v>
       </c>
@@ -23402,7 +23479,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="168" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>348</v>
       </c>
@@ -23509,7 +23586,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="169" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>349</v>
       </c>
@@ -23616,7 +23693,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="170" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>351</v>
       </c>
@@ -23723,7 +23800,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="171" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>352</v>
       </c>
@@ -23830,7 +23907,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="172" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>355</v>
       </c>
@@ -23937,7 +24014,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="173" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>356</v>
       </c>
@@ -24151,7 +24228,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="175" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>358</v>
       </c>
@@ -24258,7 +24335,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="176" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>360</v>
       </c>
@@ -24472,7 +24549,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="178" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>362</v>
       </c>
@@ -24579,7 +24656,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="179" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>365</v>
       </c>
@@ -24686,7 +24763,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="180" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>367</v>
       </c>
@@ -24900,7 +24977,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="182" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>369</v>
       </c>
@@ -25007,7 +25084,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="183" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>372</v>
       </c>
@@ -25114,7 +25191,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="184" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>374</v>
       </c>
@@ -25221,7 +25298,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="185" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>376</v>
       </c>
@@ -25328,7 +25405,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="186" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>379</v>
       </c>
@@ -25435,7 +25512,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="187" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>380</v>
       </c>
@@ -25542,7 +25619,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="188" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>381</v>
       </c>
@@ -25649,7 +25726,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="189" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>385</v>
       </c>
@@ -25756,7 +25833,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="190" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>387</v>
       </c>
@@ -25863,7 +25940,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="191" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>389</v>
       </c>
@@ -25970,7 +26047,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="192" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>391</v>
       </c>
@@ -26184,7 +26261,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="194" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>393</v>
       </c>
@@ -26291,7 +26368,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>396</v>
       </c>
@@ -26398,7 +26475,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>397</v>
       </c>
@@ -26505,7 +26582,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>400</v>
       </c>
@@ -26612,7 +26689,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>401</v>
       </c>
@@ -26719,7 +26796,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>402</v>
       </c>
@@ -27040,7 +27117,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="202" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>406</v>
       </c>
@@ -27147,7 +27224,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="203" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>408</v>
       </c>
@@ -27254,7 +27331,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="204" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>409</v>
       </c>
@@ -27361,7 +27438,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="205" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>410</v>
       </c>
@@ -27468,7 +27545,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="206" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>411</v>
       </c>
@@ -27682,7 +27759,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="208" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>413</v>
       </c>
@@ -27789,7 +27866,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="209" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>417</v>
       </c>
@@ -27896,7 +27973,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="210" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>418</v>
       </c>
@@ -28003,7 +28080,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="211" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>419</v>
       </c>
@@ -28217,7 +28294,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="213" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>421</v>
       </c>
@@ -28324,7 +28401,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="214" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>423</v>
       </c>
@@ -28431,7 +28508,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="215" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>424</v>
       </c>
@@ -28645,7 +28722,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="217" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>426</v>
       </c>
@@ -28752,7 +28829,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="218" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>427</v>
       </c>
@@ -28859,7 +28936,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="219" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>428</v>
       </c>
@@ -28966,7 +29043,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="220" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>430</v>
       </c>
@@ -29073,7 +29150,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="221" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>432</v>
       </c>
@@ -29180,7 +29257,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="222" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>434</v>
       </c>
@@ -29287,7 +29364,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="223" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>435</v>
       </c>
@@ -29394,7 +29471,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="224" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>436</v>
       </c>
@@ -29501,7 +29578,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="225" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>438</v>
       </c>
@@ -29608,7 +29685,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="226" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>439</v>
       </c>
@@ -29715,7 +29792,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="227" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>440</v>
       </c>
@@ -29822,7 +29899,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="228" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>441</v>
       </c>
@@ -30036,7 +30113,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="230" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>443</v>
       </c>
@@ -30143,7 +30220,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="231" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>445</v>
       </c>
@@ -30250,7 +30327,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="232" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>446</v>
       </c>
@@ -30357,7 +30434,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="233" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>447</v>
       </c>
@@ -30464,7 +30541,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="234" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>448</v>
       </c>
@@ -30571,7 +30648,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="235" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>449</v>
       </c>
@@ -30678,7 +30755,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="236" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>455</v>
       </c>
@@ -30785,7 +30862,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="237" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>456</v>
       </c>
@@ -30892,7 +30969,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="238" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>458</v>
       </c>
@@ -30999,7 +31076,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="239" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>460</v>
       </c>
@@ -31213,7 +31290,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="241" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>462</v>
       </c>
@@ -31320,7 +31397,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="242" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>465</v>
       </c>
@@ -31641,7 +31718,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="245" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>469</v>
       </c>
@@ -31748,7 +31825,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="246" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>471</v>
       </c>
@@ -31962,7 +32039,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="248" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>473</v>
       </c>
@@ -32176,7 +32253,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="250" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>475</v>
       </c>
@@ -32283,7 +32360,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="251" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>478</v>
       </c>
@@ -32390,7 +32467,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="252" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>479</v>
       </c>
@@ -32497,7 +32574,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="253" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>481</v>
       </c>
@@ -32604,7 +32681,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="254" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>482</v>
       </c>
@@ -32711,7 +32788,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="255" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>485</v>
       </c>
@@ -32818,7 +32895,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="256" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>487</v>
       </c>
@@ -32925,7 +33002,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="257" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>489</v>
       </c>
@@ -33032,7 +33109,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="258" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>490</v>
       </c>
@@ -33234,7 +33311,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="260" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>495</v>
       </c>
@@ -33329,7 +33406,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="261" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>496</v>
       </c>
@@ -33424,7 +33501,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="262" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>498</v>
       </c>
@@ -33519,7 +33596,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="263" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>499</v>
       </c>
@@ -33614,7 +33691,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="264" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>501</v>
       </c>
@@ -33709,7 +33786,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="265" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>503</v>
       </c>
@@ -33804,7 +33881,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="266" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>505</v>
       </c>
@@ -33899,7 +33976,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="267" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>506</v>
       </c>
@@ -33994,7 +34071,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="268" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>507</v>
       </c>
@@ -34089,7 +34166,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="269" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>508</v>
       </c>
@@ -34184,7 +34261,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="270" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>510</v>
       </c>
@@ -34279,7 +34356,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="271" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>511</v>
       </c>
@@ -34374,7 +34451,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="272" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>512</v>
       </c>
@@ -34469,7 +34546,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="273" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>513</v>
       </c>
@@ -34530,7 +34607,7 @@
       <c r="AH273" s="4"/>
       <c r="AI273" s="4"/>
     </row>
-    <row r="274" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>515</v>
       </c>
@@ -34591,7 +34668,7 @@
       <c r="AH274" s="4"/>
       <c r="AI274" s="4"/>
     </row>
-    <row r="275" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>516</v>
       </c>
@@ -34652,7 +34729,7 @@
       <c r="AH275" s="4"/>
       <c r="AI275" s="4"/>
     </row>
-    <row r="276" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>517</v>
       </c>
@@ -34713,7 +34790,7 @@
       <c r="AH276" s="4"/>
       <c r="AI276" s="4"/>
     </row>
-    <row r="277" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>518</v>
       </c>
@@ -34869,7 +34946,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="279" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>522</v>
       </c>
@@ -34964,7 +35041,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="280" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>524</v>
       </c>
@@ -35059,7 +35136,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="281" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>525</v>
       </c>
@@ -35249,7 +35326,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="283" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>179</v>
       </c>
@@ -35344,7 +35421,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="284" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>178</v>
       </c>
@@ -35439,7 +35516,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="285" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>175</v>
       </c>
@@ -35629,7 +35706,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>526</v>
       </c>
@@ -35724,7 +35801,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="288" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>186</v>
       </c>
@@ -35819,7 +35896,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="289" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>181</v>
       </c>
@@ -35914,7 +35991,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="290" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>184</v>
       </c>
@@ -36009,7 +36086,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="291" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>528</v>
       </c>
@@ -36199,7 +36276,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="293" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>531</v>
       </c>
@@ -36294,7 +36371,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="294" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>533</v>
       </c>
@@ -36416,7 +36493,7 @@
       <c r="AH295" s="4"/>
       <c r="AI295" s="4"/>
     </row>
-    <row r="296" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>536</v>
       </c>
@@ -36477,7 +36554,7 @@
       <c r="AH296" s="4"/>
       <c r="AI296" s="4"/>
     </row>
-    <row r="297" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>220</v>
       </c>
@@ -36572,7 +36649,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="298" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>221</v>
       </c>
@@ -36667,7 +36744,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="299" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>217</v>
       </c>
@@ -36762,7 +36839,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="300" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>223</v>
       </c>
@@ -36952,7 +37029,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="302" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>202</v>
       </c>
@@ -37047,7 +37124,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="303" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>537</v>
       </c>
@@ -37142,7 +37219,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="304" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>539</v>
       </c>
@@ -37237,7 +37314,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="305" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>541</v>
       </c>
@@ -37427,7 +37504,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="307" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>250</v>
       </c>
@@ -37522,7 +37599,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="308" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>248</v>
       </c>
@@ -37617,7 +37694,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="309" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>245</v>
       </c>
@@ -37712,7 +37789,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="310" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>249</v>
       </c>
@@ -37807,7 +37884,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="311" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>257</v>
       </c>
@@ -37902,7 +37979,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="312" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>259</v>
       </c>
@@ -37997,7 +38074,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="313" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>255</v>
       </c>
@@ -38092,7 +38169,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="314" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>253</v>
       </c>
@@ -38187,7 +38264,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="315" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>543</v>
       </c>
@@ -38282,7 +38359,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="316" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>282</v>
       </c>
@@ -38377,7 +38454,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="317" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>281</v>
       </c>
@@ -38472,7 +38549,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="318" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>278</v>
       </c>
@@ -38567,7 +38644,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="319" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>290</v>
       </c>
@@ -38662,7 +38739,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="320" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>286</v>
       </c>
@@ -38757,7 +38834,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="321" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>284</v>
       </c>
@@ -38852,7 +38929,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="322" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>288</v>
       </c>
@@ -39042,7 +39119,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="324" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>546</v>
       </c>
@@ -39137,7 +39214,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="325" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>548</v>
       </c>
@@ -39232,7 +39309,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="326" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>550</v>
       </c>
@@ -39327,7 +39404,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="327" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>551</v>
       </c>
@@ -39422,7 +39499,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="328" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>554</v>
       </c>
@@ -39517,7 +39594,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="329" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>555</v>
       </c>
@@ -39612,7 +39689,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="330" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>294</v>
       </c>
@@ -39707,7 +39784,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="331" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>293</v>
       </c>
@@ -39802,7 +39879,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="332" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>291</v>
       </c>
@@ -39992,7 +40069,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="334" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>329</v>
       </c>
@@ -40087,7 +40164,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="335" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>327</v>
       </c>
@@ -40182,7 +40259,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="336" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>325</v>
       </c>
@@ -40277,7 +40354,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="337" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>328</v>
       </c>
@@ -40372,7 +40449,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="338" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>318</v>
       </c>
@@ -40467,7 +40544,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="339" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>322</v>
       </c>
@@ -40562,7 +40639,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="340" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>321</v>
       </c>
@@ -40657,7 +40734,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="341" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>324</v>
       </c>
@@ -40752,7 +40829,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="342" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>330</v>
       </c>
@@ -40847,7 +40924,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="343" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>336</v>
       </c>
@@ -40942,7 +41019,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="344" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>332</v>
       </c>
@@ -41037,7 +41114,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="345" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>557</v>
       </c>
@@ -41132,7 +41209,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="346" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>340</v>
       </c>
@@ -41227,7 +41304,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="347" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>344</v>
       </c>
@@ -41322,7 +41399,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="348" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>342</v>
       </c>
@@ -41417,7 +41494,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="349" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>337</v>
       </c>
@@ -41512,7 +41589,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="350" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>559</v>
       </c>
@@ -41619,7 +41696,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="351" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>561</v>
       </c>
@@ -41726,7 +41803,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="352" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>562</v>
       </c>
@@ -41833,7 +41910,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="353" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>564</v>
       </c>
@@ -41928,7 +42005,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="354" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>369</v>
       </c>
@@ -42023,7 +42100,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="355" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>372</v>
       </c>
@@ -42118,7 +42195,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="356" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>565</v>
       </c>
@@ -42213,7 +42290,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="357" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>365</v>
       </c>
@@ -42308,7 +42385,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="358" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>566</v>
       </c>
@@ -42403,7 +42480,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="359" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>362</v>
       </c>
@@ -42498,7 +42575,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="360" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>567</v>
       </c>
@@ -42593,7 +42670,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="361" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>568</v>
       </c>
@@ -42688,7 +42765,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="362" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>376</v>
       </c>
@@ -42783,7 +42860,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="363" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>147</v>
       </c>
@@ -42878,7 +42955,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="364" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>570</v>
       </c>
@@ -42973,7 +43050,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="365" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>150</v>
       </c>
@@ -43068,7 +43145,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="366" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>149</v>
       </c>
@@ -43163,7 +43240,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="367" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>141</v>
       </c>
@@ -43258,7 +43335,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="368" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>145</v>
       </c>
@@ -43353,7 +43430,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="369" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>146</v>
       </c>
@@ -43543,7 +43620,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="371" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>571</v>
       </c>
@@ -43638,7 +43715,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="372" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>572</v>
       </c>
@@ -43733,7 +43810,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="373" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>573</v>
       </c>
@@ -43828,7 +43905,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="374" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>575</v>
       </c>
@@ -43923,7 +44000,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="375" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>229</v>
       </c>
@@ -44113,7 +44190,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="377" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
         <v>225</v>
       </c>
@@ -44208,7 +44285,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="378" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>231</v>
       </c>
@@ -44303,7 +44380,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="379" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>312</v>
       </c>
@@ -44493,7 +44570,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="381" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>310</v>
       </c>
@@ -44588,7 +44665,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="382" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>308</v>
       </c>
@@ -44778,7 +44855,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="384" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>579</v>
       </c>
@@ -44873,7 +44950,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="385" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>581</v>
       </c>
@@ -44968,7 +45045,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="386" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>583</v>
       </c>
@@ -45063,7 +45140,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="387" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>434</v>
       </c>
@@ -45158,7 +45235,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="388" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>432</v>
       </c>
@@ -45253,7 +45330,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="389" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>435</v>
       </c>
@@ -45348,7 +45425,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="390" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
         <v>428</v>
       </c>
@@ -45443,7 +45520,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="391" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
         <v>430</v>
       </c>
@@ -45538,7 +45615,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="392" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>447</v>
       </c>
@@ -45633,7 +45710,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="393" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>445</v>
       </c>
@@ -45728,7 +45805,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="394" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
         <v>443</v>
       </c>
@@ -45823,7 +45900,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="395" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
         <v>585</v>
       </c>
@@ -46013,7 +46090,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="397" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>588</v>
       </c>
@@ -46108,7 +46185,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="398" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>589</v>
       </c>
@@ -46203,7 +46280,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="399" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
         <v>590</v>
       </c>
@@ -46264,7 +46341,7 @@
       <c r="AH399" s="4"/>
       <c r="AI399" s="4"/>
     </row>
-    <row r="400" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>594</v>
       </c>
@@ -46325,7 +46402,7 @@
       <c r="AH400" s="4"/>
       <c r="AI400" s="4"/>
     </row>
-    <row r="401" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>596</v>
       </c>
@@ -46386,7 +46463,7 @@
       <c r="AH401" s="4"/>
       <c r="AI401" s="4"/>
     </row>
-    <row r="402" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
         <v>598</v>
       </c>
@@ -46447,7 +46524,7 @@
       <c r="AH402" s="4"/>
       <c r="AI402" s="4"/>
     </row>
-    <row r="403" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>381</v>
       </c>
@@ -46637,7 +46714,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="405" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
         <v>391</v>
       </c>
@@ -46732,7 +46809,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="406" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>389</v>
       </c>
@@ -46827,7 +46904,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="407" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>385</v>
       </c>
@@ -46922,7 +46999,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="408" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>387</v>
       </c>
@@ -47112,7 +47189,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="410" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>191</v>
       </c>
@@ -47207,7 +47284,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>194</v>
       </c>
@@ -47397,7 +47474,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="413" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
         <v>602</v>
       </c>
@@ -47492,7 +47569,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="414" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>603</v>
       </c>
@@ -47587,7 +47664,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="415" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>604</v>
       </c>
@@ -47777,7 +47854,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="417" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>607</v>
       </c>
@@ -47872,7 +47949,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="418" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>608</v>
       </c>
@@ -47967,7 +48044,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="419" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>609</v>
       </c>
@@ -48157,7 +48234,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="421" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>360</v>
       </c>
@@ -48252,7 +48329,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="422" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>358</v>
       </c>
@@ -48442,7 +48519,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="424" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>356</v>
       </c>
@@ -48537,7 +48614,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="425" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>355</v>
       </c>
@@ -48632,7 +48709,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="426" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>352</v>
       </c>
@@ -48727,7 +48804,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="427" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>610</v>
       </c>
@@ -48822,7 +48899,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="428" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
         <v>613</v>
       </c>
@@ -48917,7 +48994,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="429" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>614</v>
       </c>
@@ -49012,7 +49089,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="430" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>616</v>
       </c>
@@ -49107,7 +49184,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="431" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>406</v>
       </c>
@@ -49297,7 +49374,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="433" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>411</v>
       </c>
@@ -49392,7 +49469,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="434" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>409</v>
       </c>
@@ -49487,7 +49564,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="435" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>617</v>
       </c>
@@ -49582,7 +49659,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="436" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>410</v>
       </c>
@@ -49677,7 +49754,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="437" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>396</v>
       </c>
@@ -49772,7 +49849,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="438" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>393</v>
       </c>
@@ -49867,7 +49944,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="439" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>436</v>
       </c>
@@ -50057,7 +50134,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="441" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>441</v>
       </c>
@@ -50152,7 +50229,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="442" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>439</v>
       </c>
@@ -50247,7 +50324,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="443" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>440</v>
       </c>
@@ -50342,7 +50419,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="444" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>490</v>
       </c>
@@ -50437,7 +50514,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="445" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>489</v>
       </c>
@@ -50532,7 +50609,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="446" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
         <v>487</v>
       </c>
@@ -50627,7 +50704,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="447" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>485</v>
       </c>
@@ -50722,7 +50799,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="448" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>482</v>
       </c>
@@ -50912,7 +50989,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="450" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
         <v>460</v>
       </c>
@@ -51007,7 +51084,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="451" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>458</v>
       </c>
@@ -51102,7 +51179,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="452" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>455</v>
       </c>
@@ -51197,7 +51274,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="453" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>456</v>
       </c>
@@ -51292,7 +51369,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="454" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>449</v>
       </c>
@@ -51448,7 +51525,7 @@
       <c r="AH455" s="4"/>
       <c r="AI455" s="4"/>
     </row>
-    <row r="456" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>623</v>
       </c>
@@ -51509,7 +51586,7 @@
       <c r="AH456" s="4"/>
       <c r="AI456" s="4"/>
     </row>
-    <row r="457" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>625</v>
       </c>
@@ -51570,7 +51647,7 @@
       <c r="AH457" s="4"/>
       <c r="AI457" s="4"/>
     </row>
-    <row r="458" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>627</v>
       </c>
@@ -51726,7 +51803,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="460" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>473</v>
       </c>
@@ -51821,7 +51898,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="461" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>469</v>
       </c>
@@ -51916,7 +51993,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="462" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>471</v>
       </c>
@@ -52106,7 +52183,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="464" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>628</v>
       </c>
@@ -52201,7 +52278,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="465" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>475</v>
       </c>
@@ -52296,7 +52373,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="466" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>630</v>
       </c>
@@ -52391,7 +52468,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="467" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>631</v>
       </c>
@@ -52486,7 +52563,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="468" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
         <v>632</v>
       </c>
@@ -52676,7 +52753,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="470" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>635</v>
       </c>
@@ -52771,7 +52848,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="471" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
         <v>637</v>
       </c>
@@ -52866,7 +52943,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="472" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
         <v>639</v>
       </c>
@@ -52961,7 +53038,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="473" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
         <v>641</v>
       </c>
@@ -53022,7 +53099,7 @@
       <c r="AH473" s="4"/>
       <c r="AI473" s="4"/>
     </row>
-    <row r="474" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
         <v>644</v>
       </c>
@@ -53083,7 +53160,7 @@
       <c r="AH474" s="4"/>
       <c r="AI474" s="4"/>
     </row>
-    <row r="475" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
         <v>645</v>
       </c>
@@ -53266,7 +53343,7 @@
       <c r="AH477" s="4"/>
       <c r="AI477" s="4"/>
     </row>
-    <row r="478" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
         <v>650</v>
       </c>
@@ -53327,7 +53404,7 @@
       <c r="AH478" s="4"/>
       <c r="AI478" s="4"/>
     </row>
-    <row r="479" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
         <v>654</v>
       </c>
@@ -53449,7 +53526,7 @@
       <c r="AH480" s="4"/>
       <c r="AI480" s="4"/>
     </row>
-    <row r="481" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
         <v>659</v>
       </c>
@@ -53571,7 +53648,7 @@
       <c r="AH482" s="4"/>
       <c r="AI482" s="4"/>
     </row>
-    <row r="483" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
         <v>662</v>
       </c>
@@ -53727,7 +53804,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="485" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
         <v>75</v>
       </c>
@@ -53822,7 +53899,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="486" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
         <v>73</v>
       </c>
@@ -53917,7 +53994,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="487" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
         <v>69</v>
       </c>
@@ -54012,7 +54089,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="488" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
         <v>64</v>
       </c>
@@ -54107,7 +54184,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="489" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
         <v>71</v>
       </c>
@@ -54202,7 +54279,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="490" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
         <v>67</v>
       </c>
@@ -54297,7 +54374,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="491" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
         <v>663</v>
       </c>
@@ -54358,7 +54435,7 @@
       <c r="AH491" s="4"/>
       <c r="AI491" s="4"/>
     </row>
-    <row r="492" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
         <v>665</v>
       </c>
@@ -54419,7 +54496,7 @@
       <c r="AH492" s="4"/>
       <c r="AI492" s="4"/>
     </row>
-    <row r="493" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
         <v>667</v>
       </c>
@@ -54480,7 +54557,7 @@
       <c r="AH493" s="4"/>
       <c r="AI493" s="4"/>
     </row>
-    <row r="494" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
         <v>668</v>
       </c>
@@ -54602,7 +54679,7 @@
       <c r="AH495" s="4"/>
       <c r="AI495" s="4"/>
     </row>
-    <row r="496" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
         <v>670</v>
       </c>
@@ -54724,7 +54801,7 @@
       <c r="AH497" s="4"/>
       <c r="AI497" s="4"/>
     </row>
-    <row r="498" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
         <v>673</v>
       </c>
@@ -54785,7 +54862,7 @@
       <c r="AH498" s="4"/>
       <c r="AI498" s="4"/>
     </row>
-    <row r="499" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
         <v>674</v>
       </c>
@@ -54846,7 +54923,7 @@
       <c r="AH499" s="4"/>
       <c r="AI499" s="4"/>
     </row>
-    <row r="500" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
         <v>675</v>
       </c>
@@ -54907,7 +54984,7 @@
       <c r="AH500" s="4"/>
       <c r="AI500" s="4"/>
     </row>
-    <row r="501" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
         <v>270</v>
       </c>
@@ -55002,7 +55079,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="502" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
         <v>266</v>
       </c>
@@ -55097,7 +55174,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="503" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
         <v>268</v>
       </c>
@@ -55192,7 +55269,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="504" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
         <v>262</v>
       </c>
@@ -55287,7 +55364,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="505" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
         <v>264</v>
       </c>
@@ -55477,7 +55554,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="507" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
         <v>93</v>
       </c>
@@ -55572,7 +55649,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="508" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
         <v>89</v>
       </c>
@@ -55667,7 +55744,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="509" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
         <v>677</v>
       </c>
@@ -55762,7 +55839,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="510" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
         <v>679</v>
       </c>
@@ -55952,7 +56029,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="512" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
         <v>681</v>
       </c>
@@ -56047,7 +56124,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="513" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
         <v>683</v>
       </c>
@@ -56142,7 +56219,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="514" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
         <v>685</v>
       </c>
@@ -56237,7 +56314,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="515" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
         <v>687</v>
       </c>
@@ -56332,7 +56409,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="516" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
         <v>688</v>
       </c>
@@ -56522,7 +56599,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="518" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
         <v>691</v>
       </c>
@@ -56617,7 +56694,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="519" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
         <v>692</v>
       </c>
@@ -56807,7 +56884,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="521" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
         <v>695</v>
       </c>
@@ -56902,7 +56979,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="522" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
         <v>697</v>
       </c>
@@ -56963,7 +57040,7 @@
       <c r="AH522" s="4"/>
       <c r="AI522" s="4"/>
     </row>
-    <row r="523" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
         <v>703</v>
       </c>
@@ -57024,7 +57101,7 @@
       <c r="AH523" s="4"/>
       <c r="AI523" s="4"/>
     </row>
-    <row r="524" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
         <v>705</v>
       </c>
@@ -57085,7 +57162,7 @@
       <c r="AH524" s="4"/>
       <c r="AI524" s="4"/>
     </row>
-    <row r="525" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
         <v>710</v>
       </c>
@@ -57146,7 +57223,7 @@
       <c r="AH525" s="4"/>
       <c r="AI525" s="4"/>
     </row>
-    <row r="526" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
         <v>711</v>
       </c>
@@ -57207,7 +57284,7 @@
       <c r="AH526" s="4"/>
       <c r="AI526" s="4"/>
     </row>
-    <row r="527" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
         <v>712</v>
       </c>
@@ -57268,7 +57345,7 @@
       <c r="AH527" s="4"/>
       <c r="AI527" s="4"/>
     </row>
-    <row r="528" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
         <v>715</v>
       </c>
@@ -57329,7 +57406,7 @@
       <c r="AH528" s="4"/>
       <c r="AI528" s="4"/>
     </row>
-    <row r="529" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
         <v>716</v>
       </c>
@@ -57390,7 +57467,7 @@
       <c r="AH529" s="4"/>
       <c r="AI529" s="4"/>
     </row>
-    <row r="530" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
         <v>719</v>
       </c>
@@ -57451,7 +57528,7 @@
       <c r="AH530" s="4"/>
       <c r="AI530" s="4"/>
     </row>
-    <row r="531" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
         <v>720</v>
       </c>
@@ -57512,7 +57589,7 @@
       <c r="AH531" s="4"/>
       <c r="AI531" s="4"/>
     </row>
-    <row r="532" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
         <v>722</v>
       </c>
@@ -57573,7 +57650,7 @@
       <c r="AH532" s="4"/>
       <c r="AI532" s="4"/>
     </row>
-    <row r="533" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
         <v>723</v>
       </c>
@@ -57634,7 +57711,7 @@
       <c r="AH533" s="4"/>
       <c r="AI533" s="4"/>
     </row>
-    <row r="534" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
         <v>726</v>
       </c>
@@ -57695,7 +57772,7 @@
       <c r="AH534" s="4"/>
       <c r="AI534" s="4"/>
     </row>
-    <row r="535" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
         <v>727</v>
       </c>
@@ -57756,7 +57833,7 @@
       <c r="AH535" s="4"/>
       <c r="AI535" s="4"/>
     </row>
-    <row r="536" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
         <v>728</v>
       </c>
@@ -57817,7 +57894,7 @@
       <c r="AH536" s="4"/>
       <c r="AI536" s="4"/>
     </row>
-    <row r="537" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
         <v>1541</v>
       </c>
@@ -57878,7 +57955,7 @@
       <c r="AH537" s="4"/>
       <c r="AI537" s="4"/>
     </row>
-    <row r="538" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
         <v>734</v>
       </c>
@@ -57939,7 +58016,7 @@
       <c r="AH538" s="4"/>
       <c r="AI538" s="4"/>
     </row>
-    <row r="539" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
         <v>735</v>
       </c>
@@ -58000,7 +58077,7 @@
       <c r="AH539" s="4"/>
       <c r="AI539" s="4"/>
     </row>
-    <row r="540" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
         <v>739</v>
       </c>
@@ -58061,7 +58138,7 @@
       <c r="AH540" s="4"/>
       <c r="AI540" s="4"/>
     </row>
-    <row r="541" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
         <v>742</v>
       </c>
@@ -58122,7 +58199,7 @@
       <c r="AH541" s="4"/>
       <c r="AI541" s="4"/>
     </row>
-    <row r="542" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
         <v>744</v>
       </c>
@@ -58183,7 +58260,7 @@
       <c r="AH542" s="4"/>
       <c r="AI542" s="4"/>
     </row>
-    <row r="543" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
         <v>746</v>
       </c>
@@ -58244,7 +58321,7 @@
       <c r="AH543" s="4"/>
       <c r="AI543" s="4"/>
     </row>
-    <row r="544" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
         <v>748</v>
       </c>
@@ -58305,7 +58382,7 @@
       <c r="AH544" s="4"/>
       <c r="AI544" s="4"/>
     </row>
-    <row r="545" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
         <v>749</v>
       </c>
@@ -58366,7 +58443,7 @@
       <c r="AH545" s="4"/>
       <c r="AI545" s="4"/>
     </row>
-    <row r="546" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
         <v>750</v>
       </c>
@@ -58427,7 +58504,7 @@
       <c r="AH546" s="4"/>
       <c r="AI546" s="4"/>
     </row>
-    <row r="547" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
         <v>753</v>
       </c>
@@ -58488,7 +58565,7 @@
       <c r="AH547" s="4"/>
       <c r="AI547" s="4"/>
     </row>
-    <row r="548" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
         <v>754</v>
       </c>
@@ -58549,7 +58626,7 @@
       <c r="AH548" s="4"/>
       <c r="AI548" s="4"/>
     </row>
-    <row r="549" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
         <v>756</v>
       </c>
@@ -58610,7 +58687,7 @@
       <c r="AH549" s="4"/>
       <c r="AI549" s="4"/>
     </row>
-    <row r="550" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
         <v>758</v>
       </c>
@@ -58671,7 +58748,7 @@
       <c r="AH550" s="4"/>
       <c r="AI550" s="4"/>
     </row>
-    <row r="551" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
         <v>759</v>
       </c>
@@ -58732,7 +58809,7 @@
       <c r="AH551" s="4"/>
       <c r="AI551" s="4"/>
     </row>
-    <row r="552" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
         <v>761</v>
       </c>
@@ -58793,7 +58870,7 @@
       <c r="AH552" s="4"/>
       <c r="AI552" s="4"/>
     </row>
-    <row r="553" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
         <v>763</v>
       </c>
@@ -58854,7 +58931,7 @@
       <c r="AH553" s="4"/>
       <c r="AI553" s="4"/>
     </row>
-    <row r="554" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
         <v>766</v>
       </c>
@@ -58915,7 +58992,7 @@
       <c r="AH554" s="4"/>
       <c r="AI554" s="4"/>
     </row>
-    <row r="555" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
         <v>768</v>
       </c>
@@ -58976,7 +59053,7 @@
       <c r="AH555" s="4"/>
       <c r="AI555" s="4"/>
     </row>
-    <row r="556" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
         <v>769</v>
       </c>
@@ -59037,7 +59114,7 @@
       <c r="AH556" s="4"/>
       <c r="AI556" s="4"/>
     </row>
-    <row r="557" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
         <v>772</v>
       </c>
@@ -59098,7 +59175,7 @@
       <c r="AH557" s="4"/>
       <c r="AI557" s="4"/>
     </row>
-    <row r="558" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
         <v>773</v>
       </c>
@@ -59159,7 +59236,7 @@
       <c r="AH558" s="4"/>
       <c r="AI558" s="4"/>
     </row>
-    <row r="559" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
         <v>776</v>
       </c>
@@ -59220,7 +59297,7 @@
       <c r="AH559" s="4"/>
       <c r="AI559" s="4"/>
     </row>
-    <row r="560" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
         <v>777</v>
       </c>
@@ -59281,7 +59358,7 @@
       <c r="AH560" s="4"/>
       <c r="AI560" s="4"/>
     </row>
-    <row r="561" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
         <v>779</v>
       </c>
@@ -59342,7 +59419,7 @@
       <c r="AH561" s="4"/>
       <c r="AI561" s="4"/>
     </row>
-    <row r="562" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
         <v>782</v>
       </c>
@@ -59403,7 +59480,7 @@
       <c r="AH562" s="4"/>
       <c r="AI562" s="4"/>
     </row>
-    <row r="563" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
         <v>783</v>
       </c>
@@ -59464,7 +59541,7 @@
       <c r="AH563" s="4"/>
       <c r="AI563" s="4"/>
     </row>
-    <row r="564" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
         <v>786</v>
       </c>
@@ -59525,7 +59602,7 @@
       <c r="AH564" s="4"/>
       <c r="AI564" s="4"/>
     </row>
-    <row r="565" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
         <v>787</v>
       </c>
@@ -59586,7 +59663,7 @@
       <c r="AH565" s="4"/>
       <c r="AI565" s="4"/>
     </row>
-    <row r="566" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
         <v>791</v>
       </c>
@@ -59647,7 +59724,7 @@
       <c r="AH566" s="4"/>
       <c r="AI566" s="4"/>
     </row>
-    <row r="567" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
         <v>794</v>
       </c>
@@ -59769,7 +59846,7 @@
       <c r="AH568" s="4"/>
       <c r="AI568" s="4"/>
     </row>
-    <row r="569" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
         <v>801</v>
       </c>
@@ -59830,7 +59907,7 @@
       <c r="AH569" s="4"/>
       <c r="AI569" s="4"/>
     </row>
-    <row r="570" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
         <v>803</v>
       </c>
@@ -59891,7 +59968,7 @@
       <c r="AH570" s="4"/>
       <c r="AI570" s="4"/>
     </row>
-    <row r="571" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
         <v>805</v>
       </c>
@@ -59952,7 +60029,7 @@
       <c r="AH571" s="4"/>
       <c r="AI571" s="4"/>
     </row>
-    <row r="572" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
         <v>807</v>
       </c>
@@ -60013,7 +60090,7 @@
       <c r="AH572" s="4"/>
       <c r="AI572" s="4"/>
     </row>
-    <row r="573" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
         <v>810</v>
       </c>
@@ -60074,7 +60151,7 @@
       <c r="AH573" s="4"/>
       <c r="AI573" s="4"/>
     </row>
-    <row r="574" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
         <v>811</v>
       </c>
@@ -60135,7 +60212,7 @@
       <c r="AH574" s="4"/>
       <c r="AI574" s="4"/>
     </row>
-    <row r="575" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
         <v>812</v>
       </c>
@@ -60196,7 +60273,7 @@
       <c r="AH575" s="4"/>
       <c r="AI575" s="4"/>
     </row>
-    <row r="576" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
         <v>815</v>
       </c>
@@ -60257,7 +60334,7 @@
       <c r="AH576" s="4"/>
       <c r="AI576" s="4"/>
     </row>
-    <row r="577" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
         <v>816</v>
       </c>
@@ -60318,7 +60395,7 @@
       <c r="AH577" s="4"/>
       <c r="AI577" s="4"/>
     </row>
-    <row r="578" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
         <v>817</v>
       </c>
@@ -60379,7 +60456,7 @@
       <c r="AH578" s="4"/>
       <c r="AI578" s="4"/>
     </row>
-    <row r="579" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
         <v>820</v>
       </c>
@@ -60440,7 +60517,7 @@
       <c r="AH579" s="4"/>
       <c r="AI579" s="4"/>
     </row>
-    <row r="580" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
         <v>821</v>
       </c>
@@ -60501,7 +60578,7 @@
       <c r="AH580" s="4"/>
       <c r="AI580" s="4"/>
     </row>
-    <row r="581" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
         <v>822</v>
       </c>
@@ -60562,7 +60639,7 @@
       <c r="AH581" s="4"/>
       <c r="AI581" s="4"/>
     </row>
-    <row r="582" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
         <v>825</v>
       </c>
@@ -60623,7 +60700,7 @@
       <c r="AH582" s="4"/>
       <c r="AI582" s="4"/>
     </row>
-    <row r="583" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
         <v>826</v>
       </c>
@@ -60684,7 +60761,7 @@
       <c r="AH583" s="4"/>
       <c r="AI583" s="4"/>
     </row>
-    <row r="584" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
         <v>827</v>
       </c>
@@ -60745,7 +60822,7 @@
       <c r="AH584" s="4"/>
       <c r="AI584" s="4"/>
     </row>
-    <row r="585" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
         <v>831</v>
       </c>
@@ -60806,7 +60883,7 @@
       <c r="AH585" s="4"/>
       <c r="AI585" s="4"/>
     </row>
-    <row r="586" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
         <v>832</v>
       </c>
@@ -60867,7 +60944,7 @@
       <c r="AH586" s="4"/>
       <c r="AI586" s="4"/>
     </row>
-    <row r="587" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
         <v>833</v>
       </c>
@@ -60928,7 +61005,7 @@
       <c r="AH587" s="4"/>
       <c r="AI587" s="4"/>
     </row>
-    <row r="588" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
         <v>836</v>
       </c>
@@ -60989,7 +61066,7 @@
       <c r="AH588" s="4"/>
       <c r="AI588" s="4"/>
     </row>
-    <row r="589" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
         <v>837</v>
       </c>
@@ -61050,7 +61127,7 @@
       <c r="AH589" s="4"/>
       <c r="AI589" s="4"/>
     </row>
-    <row r="590" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
         <v>838</v>
       </c>
@@ -61111,7 +61188,7 @@
       <c r="AH590" s="4"/>
       <c r="AI590" s="4"/>
     </row>
-    <row r="591" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
         <v>841</v>
       </c>
@@ -61172,7 +61249,7 @@
       <c r="AH591" s="4"/>
       <c r="AI591" s="4"/>
     </row>
-    <row r="592" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
         <v>842</v>
       </c>
@@ -61233,7 +61310,7 @@
       <c r="AH592" s="4"/>
       <c r="AI592" s="4"/>
     </row>
-    <row r="593" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
         <v>843</v>
       </c>
@@ -61294,7 +61371,7 @@
       <c r="AH593" s="4"/>
       <c r="AI593" s="4"/>
     </row>
-    <row r="594" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
         <v>846</v>
       </c>
@@ -61355,7 +61432,7 @@
       <c r="AH594" s="4"/>
       <c r="AI594" s="4"/>
     </row>
-    <row r="595" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
         <v>847</v>
       </c>
@@ -61416,7 +61493,7 @@
       <c r="AH595" s="4"/>
       <c r="AI595" s="4"/>
     </row>
-    <row r="596" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
         <v>848</v>
       </c>
@@ -61477,7 +61554,7 @@
       <c r="AH596" s="4"/>
       <c r="AI596" s="4"/>
     </row>
-    <row r="597" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
         <v>849</v>
       </c>
@@ -61599,7 +61676,7 @@
       <c r="AH598" s="4"/>
       <c r="AI598" s="4"/>
     </row>
-    <row r="599" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
         <v>854</v>
       </c>
@@ -61660,7 +61737,7 @@
       <c r="AH599" s="4"/>
       <c r="AI599" s="4"/>
     </row>
-    <row r="600" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
         <v>855</v>
       </c>
@@ -61721,7 +61798,7 @@
       <c r="AH600" s="4"/>
       <c r="AI600" s="4"/>
     </row>
-    <row r="601" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
         <v>856</v>
       </c>
@@ -61782,7 +61859,7 @@
       <c r="AH601" s="4"/>
       <c r="AI601" s="4"/>
     </row>
-    <row r="602" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
         <v>857</v>
       </c>
@@ -61843,7 +61920,7 @@
       <c r="AH602" s="4"/>
       <c r="AI602" s="4"/>
     </row>
-    <row r="603" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
         <v>860</v>
       </c>
@@ -61904,7 +61981,7 @@
       <c r="AH603" s="4"/>
       <c r="AI603" s="4"/>
     </row>
-    <row r="604" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
         <v>861</v>
       </c>
@@ -61965,7 +62042,7 @@
       <c r="AH604" s="4"/>
       <c r="AI604" s="4"/>
     </row>
-    <row r="605" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
         <v>862</v>
       </c>
@@ -62026,7 +62103,7 @@
       <c r="AH605" s="4"/>
       <c r="AI605" s="4"/>
     </row>
-    <row r="606" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
         <v>865</v>
       </c>
@@ -62087,7 +62164,7 @@
       <c r="AH606" s="4"/>
       <c r="AI606" s="4"/>
     </row>
-    <row r="607" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
         <v>866</v>
       </c>
@@ -62148,7 +62225,7 @@
       <c r="AH607" s="4"/>
       <c r="AI607" s="4"/>
     </row>
-    <row r="608" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
         <v>867</v>
       </c>
@@ -62209,7 +62286,7 @@
       <c r="AH608" s="4"/>
       <c r="AI608" s="4"/>
     </row>
-    <row r="609" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
         <v>870</v>
       </c>
@@ -62270,7 +62347,7 @@
       <c r="AH609" s="4"/>
       <c r="AI609" s="4"/>
     </row>
-    <row r="610" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
         <v>871</v>
       </c>
@@ -62331,7 +62408,7 @@
       <c r="AH610" s="4"/>
       <c r="AI610" s="4"/>
     </row>
-    <row r="611" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
         <v>872</v>
       </c>
@@ -62392,7 +62469,7 @@
       <c r="AH611" s="4"/>
       <c r="AI611" s="4"/>
     </row>
-    <row r="612" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
         <v>875</v>
       </c>
@@ -62453,7 +62530,7 @@
       <c r="AH612" s="4"/>
       <c r="AI612" s="4"/>
     </row>
-    <row r="613" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
         <v>876</v>
       </c>
@@ -62514,7 +62591,7 @@
       <c r="AH613" s="4"/>
       <c r="AI613" s="4"/>
     </row>
-    <row r="614" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
         <v>877</v>
       </c>
@@ -62575,7 +62652,7 @@
       <c r="AH614" s="4"/>
       <c r="AI614" s="4"/>
     </row>
-    <row r="615" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
         <v>880</v>
       </c>
@@ -62636,7 +62713,7 @@
       <c r="AH615" s="4"/>
       <c r="AI615" s="4"/>
     </row>
-    <row r="616" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
         <v>881</v>
       </c>
@@ -62697,7 +62774,7 @@
       <c r="AH616" s="4"/>
       <c r="AI616" s="4"/>
     </row>
-    <row r="617" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
         <v>882</v>
       </c>
@@ -62758,7 +62835,7 @@
       <c r="AH617" s="4"/>
       <c r="AI617" s="4"/>
     </row>
-    <row r="618" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
         <v>885</v>
       </c>
@@ -62819,7 +62896,7 @@
       <c r="AH618" s="4"/>
       <c r="AI618" s="4"/>
     </row>
-    <row r="619" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
         <v>886</v>
       </c>
@@ -62880,7 +62957,7 @@
       <c r="AH619" s="4"/>
       <c r="AI619" s="4"/>
     </row>
-    <row r="620" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
         <v>887</v>
       </c>
@@ -62941,7 +63018,7 @@
       <c r="AH620" s="4"/>
       <c r="AI620" s="4"/>
     </row>
-    <row r="621" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
         <v>890</v>
       </c>
@@ -63002,7 +63079,7 @@
       <c r="AH621" s="4"/>
       <c r="AI621" s="4"/>
     </row>
-    <row r="622" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
         <v>891</v>
       </c>
@@ -63063,7 +63140,7 @@
       <c r="AH622" s="4"/>
       <c r="AI622" s="4"/>
     </row>
-    <row r="623" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
         <v>892</v>
       </c>
@@ -63124,7 +63201,7 @@
       <c r="AH623" s="4"/>
       <c r="AI623" s="4"/>
     </row>
-    <row r="624" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
         <v>895</v>
       </c>
@@ -63185,7 +63262,7 @@
       <c r="AH624" s="4"/>
       <c r="AI624" s="4"/>
     </row>
-    <row r="625" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
         <v>896</v>
       </c>
@@ -63246,7 +63323,7 @@
       <c r="AH625" s="4"/>
       <c r="AI625" s="4"/>
     </row>
-    <row r="626" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
         <v>897</v>
       </c>
@@ -63307,7 +63384,7 @@
       <c r="AH626" s="4"/>
       <c r="AI626" s="4"/>
     </row>
-    <row r="627" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
         <v>898</v>
       </c>
@@ -63368,7 +63445,7 @@
       <c r="AH627" s="4"/>
       <c r="AI627" s="4"/>
     </row>
-    <row r="628" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
         <v>901</v>
       </c>
@@ -63429,7 +63506,7 @@
       <c r="AH628" s="4"/>
       <c r="AI628" s="4"/>
     </row>
-    <row r="629" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
         <v>903</v>
       </c>
@@ -63490,7 +63567,7 @@
       <c r="AH629" s="4"/>
       <c r="AI629" s="4"/>
     </row>
-    <row r="630" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
         <v>905</v>
       </c>
@@ -63551,7 +63628,7 @@
       <c r="AH630" s="4"/>
       <c r="AI630" s="4"/>
     </row>
-    <row r="631" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
         <v>907</v>
       </c>
@@ -63612,7 +63689,7 @@
       <c r="AH631" s="4"/>
       <c r="AI631" s="4"/>
     </row>
-    <row r="632" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
         <v>911</v>
       </c>
@@ -63673,7 +63750,7 @@
       <c r="AH632" s="4"/>
       <c r="AI632" s="4"/>
     </row>
-    <row r="633" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
         <v>913</v>
       </c>
@@ -63734,7 +63811,7 @@
       <c r="AH633" s="4"/>
       <c r="AI633" s="4"/>
     </row>
-    <row r="634" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
         <v>915</v>
       </c>
@@ -63795,7 +63872,7 @@
       <c r="AH634" s="4"/>
       <c r="AI634" s="4"/>
     </row>
-    <row r="635" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
         <v>917</v>
       </c>
@@ -63856,7 +63933,7 @@
       <c r="AH635" s="4"/>
       <c r="AI635" s="4"/>
     </row>
-    <row r="636" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
         <v>919</v>
       </c>
@@ -63917,7 +63994,7 @@
       <c r="AH636" s="4"/>
       <c r="AI636" s="4"/>
     </row>
-    <row r="637" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
         <v>922</v>
       </c>
@@ -63978,7 +64055,7 @@
       <c r="AH637" s="4"/>
       <c r="AI637" s="4"/>
     </row>
-    <row r="638" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
         <v>923</v>
       </c>
@@ -64039,7 +64116,7 @@
       <c r="AH638" s="4"/>
       <c r="AI638" s="4"/>
     </row>
-    <row r="639" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
         <v>924</v>
       </c>
@@ -64100,7 +64177,7 @@
       <c r="AH639" s="4"/>
       <c r="AI639" s="4"/>
     </row>
-    <row r="640" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
         <v>925</v>
       </c>
@@ -64161,7 +64238,7 @@
       <c r="AH640" s="4"/>
       <c r="AI640" s="4"/>
     </row>
-    <row r="641" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
         <v>926</v>
       </c>
@@ -64222,7 +64299,7 @@
       <c r="AH641" s="4"/>
       <c r="AI641" s="4"/>
     </row>
-    <row r="642" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
         <v>929</v>
       </c>
@@ -64283,7 +64360,7 @@
       <c r="AH642" s="4"/>
       <c r="AI642" s="4"/>
     </row>
-    <row r="643" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
         <v>933</v>
       </c>
@@ -64344,7 +64421,7 @@
       <c r="AH643" s="4"/>
       <c r="AI643" s="4"/>
     </row>
-    <row r="644" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
         <v>934</v>
       </c>
@@ -64405,7 +64482,7 @@
       <c r="AH644" s="4"/>
       <c r="AI644" s="4"/>
     </row>
-    <row r="645" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
         <v>937</v>
       </c>
@@ -64466,7 +64543,7 @@
       <c r="AH645" s="4"/>
       <c r="AI645" s="4"/>
     </row>
-    <row r="646" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
         <v>938</v>
       </c>
@@ -64527,7 +64604,7 @@
       <c r="AH646" s="4"/>
       <c r="AI646" s="4"/>
     </row>
-    <row r="647" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
         <v>941</v>
       </c>
@@ -64588,7 +64665,7 @@
       <c r="AH647" s="4"/>
       <c r="AI647" s="4"/>
     </row>
-    <row r="648" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
         <v>944</v>
       </c>
@@ -64649,7 +64726,7 @@
       <c r="AH648" s="4"/>
       <c r="AI648" s="4"/>
     </row>
-    <row r="649" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
         <v>946</v>
       </c>
@@ -64710,7 +64787,7 @@
       <c r="AH649" s="4"/>
       <c r="AI649" s="4"/>
     </row>
-    <row r="650" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
         <v>949</v>
       </c>
@@ -64771,7 +64848,7 @@
       <c r="AH650" s="4"/>
       <c r="AI650" s="4"/>
     </row>
-    <row r="651" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
         <v>952</v>
       </c>
@@ -64832,7 +64909,7 @@
       <c r="AH651" s="4"/>
       <c r="AI651" s="4"/>
     </row>
-    <row r="652" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
         <v>955</v>
       </c>
@@ -64893,7 +64970,7 @@
       <c r="AH652" s="4"/>
       <c r="AI652" s="4"/>
     </row>
-    <row r="653" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
         <v>956</v>
       </c>
@@ -64954,7 +65031,7 @@
       <c r="AH653" s="4"/>
       <c r="AI653" s="4"/>
     </row>
-    <row r="654" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
         <v>957</v>
       </c>
@@ -65015,7 +65092,7 @@
       <c r="AH654" s="4"/>
       <c r="AI654" s="4"/>
     </row>
-    <row r="655" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
         <v>960</v>
       </c>
@@ -65076,7 +65153,7 @@
       <c r="AH655" s="4"/>
       <c r="AI655" s="4"/>
     </row>
-    <row r="656" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
         <v>962</v>
       </c>
@@ -65137,7 +65214,7 @@
       <c r="AH656" s="4"/>
       <c r="AI656" s="4"/>
     </row>
-    <row r="657" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
         <v>963</v>
       </c>
@@ -65198,7 +65275,7 @@
       <c r="AH657" s="4"/>
       <c r="AI657" s="4"/>
     </row>
-    <row r="658" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
         <v>964</v>
       </c>
@@ -65259,7 +65336,7 @@
       <c r="AH658" s="4"/>
       <c r="AI658" s="4"/>
     </row>
-    <row r="659" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
         <v>965</v>
       </c>
@@ -65320,7 +65397,7 @@
       <c r="AH659" s="4"/>
       <c r="AI659" s="4"/>
     </row>
-    <row r="660" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
         <v>968</v>
       </c>
@@ -65381,7 +65458,7 @@
       <c r="AH660" s="4"/>
       <c r="AI660" s="4"/>
     </row>
-    <row r="661" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
         <v>969</v>
       </c>
@@ -65442,7 +65519,7 @@
       <c r="AH661" s="4"/>
       <c r="AI661" s="4"/>
     </row>
-    <row r="662" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
         <v>971</v>
       </c>
@@ -65503,7 +65580,7 @@
       <c r="AH662" s="4"/>
       <c r="AI662" s="4"/>
     </row>
-    <row r="663" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
         <v>972</v>
       </c>
@@ -65564,7 +65641,7 @@
       <c r="AH663" s="4"/>
       <c r="AI663" s="4"/>
     </row>
-    <row r="664" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
         <v>973</v>
       </c>
@@ -65625,7 +65702,7 @@
       <c r="AH664" s="4"/>
       <c r="AI664" s="4"/>
     </row>
-    <row r="665" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
         <v>976</v>
       </c>
@@ -65686,7 +65763,7 @@
       <c r="AH665" s="4"/>
       <c r="AI665" s="4"/>
     </row>
-    <row r="666" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
         <v>978</v>
       </c>
@@ -65747,7 +65824,7 @@
       <c r="AH666" s="4"/>
       <c r="AI666" s="4"/>
     </row>
-    <row r="667" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
         <v>980</v>
       </c>
@@ -65808,7 +65885,7 @@
       <c r="AH667" s="4"/>
       <c r="AI667" s="4"/>
     </row>
-    <row r="668" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
         <v>983</v>
       </c>
@@ -65869,7 +65946,7 @@
       <c r="AH668" s="4"/>
       <c r="AI668" s="4"/>
     </row>
-    <row r="669" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
         <v>986</v>
       </c>
@@ -65930,7 +66007,7 @@
       <c r="AH669" s="4"/>
       <c r="AI669" s="4"/>
     </row>
-    <row r="670" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
         <v>989</v>
       </c>
@@ -65991,7 +66068,7 @@
       <c r="AH670" s="4"/>
       <c r="AI670" s="4"/>
     </row>
-    <row r="671" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
         <v>990</v>
       </c>
@@ -66052,7 +66129,7 @@
       <c r="AH671" s="4"/>
       <c r="AI671" s="4"/>
     </row>
-    <row r="672" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
         <v>993</v>
       </c>
@@ -66113,7 +66190,7 @@
       <c r="AH672" s="4"/>
       <c r="AI672" s="4"/>
     </row>
-    <row r="673" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
         <v>994</v>
       </c>
@@ -66174,7 +66251,7 @@
       <c r="AH673" s="4"/>
       <c r="AI673" s="4"/>
     </row>
-    <row r="674" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
         <v>995</v>
       </c>
@@ -66235,7 +66312,7 @@
       <c r="AH674" s="4"/>
       <c r="AI674" s="4"/>
     </row>
-    <row r="675" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
         <v>996</v>
       </c>
@@ -66296,7 +66373,7 @@
       <c r="AH675" s="4"/>
       <c r="AI675" s="4"/>
     </row>
-    <row r="676" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
         <v>999</v>
       </c>
@@ -66357,7 +66434,7 @@
       <c r="AH676" s="4"/>
       <c r="AI676" s="4"/>
     </row>
-    <row r="677" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
         <v>1000</v>
       </c>
@@ -66418,7 +66495,7 @@
       <c r="AH677" s="4"/>
       <c r="AI677" s="4"/>
     </row>
-    <row r="678" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
         <v>1001</v>
       </c>
@@ -66479,7 +66556,7 @@
       <c r="AH678" s="4"/>
       <c r="AI678" s="4"/>
     </row>
-    <row r="679" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
         <v>1002</v>
       </c>
@@ -66540,7 +66617,7 @@
       <c r="AH679" s="4"/>
       <c r="AI679" s="4"/>
     </row>
-    <row r="680" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
         <v>1005</v>
       </c>
@@ -66601,7 +66678,7 @@
       <c r="AH680" s="4"/>
       <c r="AI680" s="4"/>
     </row>
-    <row r="681" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
         <v>1008</v>
       </c>
@@ -66662,7 +66739,7 @@
       <c r="AH681" s="4"/>
       <c r="AI681" s="4"/>
     </row>
-    <row r="682" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
         <v>1009</v>
       </c>
@@ -66723,7 +66800,7 @@
       <c r="AH682" s="4"/>
       <c r="AI682" s="4"/>
     </row>
-    <row r="683" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
         <v>1010</v>
       </c>
@@ -66784,7 +66861,7 @@
       <c r="AH683" s="4"/>
       <c r="AI683" s="4"/>
     </row>
-    <row r="684" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
         <v>1011</v>
       </c>
@@ -66845,7 +66922,7 @@
       <c r="AH684" s="4"/>
       <c r="AI684" s="4"/>
     </row>
-    <row r="685" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
         <v>1012</v>
       </c>
@@ -66906,7 +66983,7 @@
       <c r="AH685" s="4"/>
       <c r="AI685" s="4"/>
     </row>
-    <row r="686" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
         <v>1015</v>
       </c>
@@ -66967,7 +67044,7 @@
       <c r="AH686" s="4"/>
       <c r="AI686" s="4"/>
     </row>
-    <row r="687" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
         <v>1016</v>
       </c>
@@ -67028,7 +67105,7 @@
       <c r="AH687" s="4"/>
       <c r="AI687" s="4"/>
     </row>
-    <row r="688" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
         <v>1019</v>
       </c>
@@ -67089,7 +67166,7 @@
       <c r="AH688" s="4"/>
       <c r="AI688" s="4"/>
     </row>
-    <row r="689" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
         <v>1020</v>
       </c>
@@ -67150,7 +67227,7 @@
       <c r="AH689" s="4"/>
       <c r="AI689" s="4"/>
     </row>
-    <row r="690" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
         <v>1022</v>
       </c>
@@ -67211,7 +67288,7 @@
       <c r="AH690" s="4"/>
       <c r="AI690" s="4"/>
     </row>
-    <row r="691" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
         <v>1027</v>
       </c>
@@ -67272,7 +67349,7 @@
       <c r="AH691" s="4"/>
       <c r="AI691" s="4"/>
     </row>
-    <row r="692" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
         <v>1029</v>
       </c>
@@ -67333,7 +67410,7 @@
       <c r="AH692" s="4"/>
       <c r="AI692" s="4"/>
     </row>
-    <row r="693" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
         <v>1033</v>
       </c>
@@ -67394,7 +67471,7 @@
       <c r="AH693" s="4"/>
       <c r="AI693" s="4"/>
     </row>
-    <row r="694" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
         <v>1034</v>
       </c>
@@ -67455,7 +67532,7 @@
       <c r="AH694" s="4"/>
       <c r="AI694" s="4"/>
     </row>
-    <row r="695" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
         <v>1036</v>
       </c>
@@ -67516,7 +67593,7 @@
       <c r="AH695" s="4"/>
       <c r="AI695" s="4"/>
     </row>
-    <row r="696" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
         <v>1039</v>
       </c>
@@ -67577,7 +67654,7 @@
       <c r="AH696" s="4"/>
       <c r="AI696" s="4"/>
     </row>
-    <row r="697" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
         <v>1040</v>
       </c>
@@ -67638,7 +67715,7 @@
       <c r="AH697" s="4"/>
       <c r="AI697" s="4"/>
     </row>
-    <row r="698" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
         <v>1041</v>
       </c>
@@ -67699,7 +67776,7 @@
       <c r="AH698" s="4"/>
       <c r="AI698" s="4"/>
     </row>
-    <row r="699" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
         <v>1043</v>
       </c>
@@ -67760,7 +67837,7 @@
       <c r="AH699" s="4"/>
       <c r="AI699" s="4"/>
     </row>
-    <row r="700" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
         <v>1047</v>
       </c>
@@ -67821,7 +67898,7 @@
       <c r="AH700" s="4"/>
       <c r="AI700" s="4"/>
     </row>
-    <row r="701" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
         <v>1049</v>
       </c>
@@ -67882,7 +67959,7 @@
       <c r="AH701" s="4"/>
       <c r="AI701" s="4"/>
     </row>
-    <row r="702" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
         <v>1052</v>
       </c>
@@ -67943,7 +68020,7 @@
       <c r="AH702" s="4"/>
       <c r="AI702" s="4"/>
     </row>
-    <row r="703" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
         <v>1053</v>
       </c>
@@ -68004,7 +68081,7 @@
       <c r="AH703" s="4"/>
       <c r="AI703" s="4"/>
     </row>
-    <row r="704" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
         <v>1056</v>
       </c>
@@ -68065,7 +68142,7 @@
       <c r="AH704" s="4"/>
       <c r="AI704" s="4"/>
     </row>
-    <row r="705" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
         <v>1057</v>
       </c>
@@ -68126,7 +68203,7 @@
       <c r="AH705" s="4"/>
       <c r="AI705" s="4"/>
     </row>
-    <row r="706" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
         <v>1058</v>
       </c>
@@ -68187,7 +68264,7 @@
       <c r="AH706" s="4"/>
       <c r="AI706" s="4"/>
     </row>
-    <row r="707" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
         <v>1060</v>
       </c>
@@ -68248,7 +68325,7 @@
       <c r="AH707" s="4"/>
       <c r="AI707" s="4"/>
     </row>
-    <row r="708" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
         <v>1061</v>
       </c>
@@ -68309,7 +68386,7 @@
       <c r="AH708" s="4"/>
       <c r="AI708" s="4"/>
     </row>
-    <row r="709" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
         <v>1062</v>
       </c>
@@ -68370,7 +68447,7 @@
       <c r="AH709" s="4"/>
       <c r="AI709" s="4"/>
     </row>
-    <row r="710" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
         <v>1066</v>
       </c>
@@ -68431,7 +68508,7 @@
       <c r="AH710" s="4"/>
       <c r="AI710" s="4"/>
     </row>
-    <row r="711" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
         <v>1068</v>
       </c>
@@ -68492,7 +68569,7 @@
       <c r="AH711" s="4"/>
       <c r="AI711" s="4"/>
     </row>
-    <row r="712" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
         <v>1070</v>
       </c>
@@ -68553,7 +68630,7 @@
       <c r="AH712" s="4"/>
       <c r="AI712" s="4"/>
     </row>
-    <row r="713" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
         <v>1071</v>
       </c>
@@ -68614,7 +68691,7 @@
       <c r="AH713" s="4"/>
       <c r="AI713" s="4"/>
     </row>
-    <row r="714" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
         <v>1074</v>
       </c>
@@ -68675,7 +68752,7 @@
       <c r="AH714" s="4"/>
       <c r="AI714" s="4"/>
     </row>
-    <row r="715" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
         <v>1077</v>
       </c>
@@ -68736,7 +68813,7 @@
       <c r="AH715" s="4"/>
       <c r="AI715" s="4"/>
     </row>
-    <row r="716" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
         <v>1078</v>
       </c>
@@ -68797,7 +68874,7 @@
       <c r="AH716" s="4"/>
       <c r="AI716" s="4"/>
     </row>
-    <row r="717" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
         <v>1081</v>
       </c>
@@ -68858,7 +68935,7 @@
       <c r="AH717" s="4"/>
       <c r="AI717" s="4"/>
     </row>
-    <row r="718" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
         <v>1085</v>
       </c>
@@ -68919,7 +68996,7 @@
       <c r="AH718" s="4"/>
       <c r="AI718" s="4"/>
     </row>
-    <row r="719" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
         <v>1086</v>
       </c>
@@ -68980,7 +69057,7 @@
       <c r="AH719" s="4"/>
       <c r="AI719" s="4"/>
     </row>
-    <row r="720" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
         <v>1087</v>
       </c>
@@ -69041,7 +69118,7 @@
       <c r="AH720" s="4"/>
       <c r="AI720" s="4"/>
     </row>
-    <row r="721" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
         <v>1089</v>
       </c>
@@ -69102,7 +69179,7 @@
       <c r="AH721" s="4"/>
       <c r="AI721" s="4"/>
     </row>
-    <row r="722" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
         <v>1092</v>
       </c>
@@ -69163,7 +69240,7 @@
       <c r="AH722" s="4"/>
       <c r="AI722" s="4"/>
     </row>
-    <row r="723" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
         <v>1093</v>
       </c>
@@ -69224,7 +69301,7 @@
       <c r="AH723" s="4"/>
       <c r="AI723" s="4"/>
     </row>
-    <row r="724" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
         <v>1094</v>
       </c>
@@ -69285,7 +69362,7 @@
       <c r="AH724" s="4"/>
       <c r="AI724" s="4"/>
     </row>
-    <row r="725" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
         <v>1096</v>
       </c>
@@ -69346,7 +69423,7 @@
       <c r="AH725" s="4"/>
       <c r="AI725" s="4"/>
     </row>
-    <row r="726" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
         <v>1097</v>
       </c>
@@ -69407,7 +69484,7 @@
       <c r="AH726" s="4"/>
       <c r="AI726" s="4"/>
     </row>
-    <row r="727" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
         <v>1098</v>
       </c>
@@ -69468,7 +69545,7 @@
       <c r="AH727" s="4"/>
       <c r="AI727" s="4"/>
     </row>
-    <row r="728" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="s">
         <v>1099</v>
       </c>
@@ -69529,7 +69606,7 @@
       <c r="AH728" s="4"/>
       <c r="AI728" s="4"/>
     </row>
-    <row r="729" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
         <v>1100</v>
       </c>
@@ -69590,7 +69667,7 @@
       <c r="AH729" s="4"/>
       <c r="AI729" s="4"/>
     </row>
-    <row r="730" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
         <v>1103</v>
       </c>
@@ -69651,7 +69728,7 @@
       <c r="AH730" s="4"/>
       <c r="AI730" s="4"/>
     </row>
-    <row r="731" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
         <v>1104</v>
       </c>
@@ -69712,7 +69789,7 @@
       <c r="AH731" s="4"/>
       <c r="AI731" s="4"/>
     </row>
-    <row r="732" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
         <v>1105</v>
       </c>
@@ -69773,7 +69850,7 @@
       <c r="AH732" s="4"/>
       <c r="AI732" s="4"/>
     </row>
-    <row r="733" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
         <v>1108</v>
       </c>
@@ -69834,7 +69911,7 @@
       <c r="AH733" s="4"/>
       <c r="AI733" s="4"/>
     </row>
-    <row r="734" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
         <v>1110</v>
       </c>
@@ -69895,7 +69972,7 @@
       <c r="AH734" s="4"/>
       <c r="AI734" s="4"/>
     </row>
-    <row r="735" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
         <v>1111</v>
       </c>
@@ -69956,7 +70033,7 @@
       <c r="AH735" s="4"/>
       <c r="AI735" s="4"/>
     </row>
-    <row r="736" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
         <v>1114</v>
       </c>
@@ -70017,7 +70094,7 @@
       <c r="AH736" s="4"/>
       <c r="AI736" s="4"/>
     </row>
-    <row r="737" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
         <v>1116</v>
       </c>
@@ -70078,7 +70155,7 @@
       <c r="AH737" s="4"/>
       <c r="AI737" s="4"/>
     </row>
-    <row r="738" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
         <v>1117</v>
       </c>
@@ -70139,7 +70216,7 @@
       <c r="AH738" s="4"/>
       <c r="AI738" s="4"/>
     </row>
-    <row r="739" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
         <v>1118</v>
       </c>
@@ -70200,7 +70277,7 @@
       <c r="AH739" s="4"/>
       <c r="AI739" s="4"/>
     </row>
-    <row r="740" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
         <v>1121</v>
       </c>
@@ -70261,7 +70338,7 @@
       <c r="AH740" s="4"/>
       <c r="AI740" s="4"/>
     </row>
-    <row r="741" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
         <v>1122</v>
       </c>
@@ -70322,7 +70399,7 @@
       <c r="AH741" s="4"/>
       <c r="AI741" s="4"/>
     </row>
-    <row r="742" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
         <v>1125</v>
       </c>
@@ -70383,7 +70460,7 @@
       <c r="AH742" s="4"/>
       <c r="AI742" s="4"/>
     </row>
-    <row r="743" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
         <v>1126</v>
       </c>
@@ -70444,7 +70521,7 @@
       <c r="AH743" s="4"/>
       <c r="AI743" s="4"/>
     </row>
-    <row r="744" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
         <v>1129</v>
       </c>
@@ -70505,7 +70582,7 @@
       <c r="AH744" s="4"/>
       <c r="AI744" s="4"/>
     </row>
-    <row r="745" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
         <v>1131</v>
       </c>
@@ -70566,7 +70643,7 @@
       <c r="AH745" s="4"/>
       <c r="AI745" s="4"/>
     </row>
-    <row r="746" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
         <v>1134</v>
       </c>
@@ -70627,7 +70704,7 @@
       <c r="AH746" s="4"/>
       <c r="AI746" s="4"/>
     </row>
-    <row r="747" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
         <v>1135</v>
       </c>
@@ -70688,7 +70765,7 @@
       <c r="AH747" s="4"/>
       <c r="AI747" s="4"/>
     </row>
-    <row r="748" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
         <v>1138</v>
       </c>
@@ -70749,7 +70826,7 @@
       <c r="AH748" s="4"/>
       <c r="AI748" s="4"/>
     </row>
-    <row r="749" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
         <v>1139</v>
       </c>
@@ -70810,7 +70887,7 @@
       <c r="AH749" s="4"/>
       <c r="AI749" s="4"/>
     </row>
-    <row r="750" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
         <v>1143</v>
       </c>
@@ -70871,7 +70948,7 @@
       <c r="AH750" s="4"/>
       <c r="AI750" s="4"/>
     </row>
-    <row r="751" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
         <v>1144</v>
       </c>
@@ -70932,7 +71009,7 @@
       <c r="AH751" s="4"/>
       <c r="AI751" s="4"/>
     </row>
-    <row r="752" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
         <v>1145</v>
       </c>
@@ -70993,7 +71070,7 @@
       <c r="AH752" s="4"/>
       <c r="AI752" s="4"/>
     </row>
-    <row r="753" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
         <v>1147</v>
       </c>
@@ -71054,7 +71131,7 @@
       <c r="AH753" s="4"/>
       <c r="AI753" s="4"/>
     </row>
-    <row r="754" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
         <v>1148</v>
       </c>
@@ -71115,7 +71192,7 @@
       <c r="AH754" s="4"/>
       <c r="AI754" s="4"/>
     </row>
-    <row r="755" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
         <v>1150</v>
       </c>
@@ -71176,7 +71253,7 @@
       <c r="AH755" s="4"/>
       <c r="AI755" s="4"/>
     </row>
-    <row r="756" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
         <v>1151</v>
       </c>
@@ -71237,7 +71314,7 @@
       <c r="AH756" s="4"/>
       <c r="AI756" s="4"/>
     </row>
-    <row r="757" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
         <v>1154</v>
       </c>
@@ -71298,7 +71375,7 @@
       <c r="AH757" s="4"/>
       <c r="AI757" s="4"/>
     </row>
-    <row r="758" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
         <v>1156</v>
       </c>
@@ -71359,7 +71436,7 @@
       <c r="AH758" s="4"/>
       <c r="AI758" s="4"/>
     </row>
-    <row r="759" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
         <v>1157</v>
       </c>
@@ -71420,7 +71497,7 @@
       <c r="AH759" s="4"/>
       <c r="AI759" s="4"/>
     </row>
-    <row r="760" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
         <v>1160</v>
       </c>
@@ -71481,7 +71558,7 @@
       <c r="AH760" s="4"/>
       <c r="AI760" s="4"/>
     </row>
-    <row r="761" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
         <v>1161</v>
       </c>
@@ -71542,7 +71619,7 @@
       <c r="AH761" s="4"/>
       <c r="AI761" s="4"/>
     </row>
-    <row r="762" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
         <v>1162</v>
       </c>
@@ -71603,7 +71680,7 @@
       <c r="AH762" s="4"/>
       <c r="AI762" s="4"/>
     </row>
-    <row r="763" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
         <v>1164</v>
       </c>
@@ -71664,7 +71741,7 @@
       <c r="AH763" s="4"/>
       <c r="AI763" s="4"/>
     </row>
-    <row r="764" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
         <v>1165</v>
       </c>
@@ -71725,7 +71802,7 @@
       <c r="AH764" s="4"/>
       <c r="AI764" s="4"/>
     </row>
-    <row r="765" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
         <v>1168</v>
       </c>
@@ -71786,7 +71863,7 @@
       <c r="AH765" s="4"/>
       <c r="AI765" s="4"/>
     </row>
-    <row r="766" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
         <v>1169</v>
       </c>
@@ -71847,7 +71924,7 @@
       <c r="AH766" s="4"/>
       <c r="AI766" s="4"/>
     </row>
-    <row r="767" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
         <v>1170</v>
       </c>
@@ -71908,7 +71985,7 @@
       <c r="AH767" s="4"/>
       <c r="AI767" s="4"/>
     </row>
-    <row r="768" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="s">
         <v>1172</v>
       </c>
@@ -71969,7 +72046,7 @@
       <c r="AH768" s="4"/>
       <c r="AI768" s="4"/>
     </row>
-    <row r="769" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
         <v>1173</v>
       </c>
@@ -72030,7 +72107,7 @@
       <c r="AH769" s="4"/>
       <c r="AI769" s="4"/>
     </row>
-    <row r="770" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
         <v>1174</v>
       </c>
@@ -72091,7 +72168,7 @@
       <c r="AH770" s="4"/>
       <c r="AI770" s="4"/>
     </row>
-    <row r="771" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
         <v>1177</v>
       </c>
@@ -72152,7 +72229,7 @@
       <c r="AH771" s="4"/>
       <c r="AI771" s="4"/>
     </row>
-    <row r="772" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
         <v>1178</v>
       </c>
@@ -72213,7 +72290,7 @@
       <c r="AH772" s="4"/>
       <c r="AI772" s="4"/>
     </row>
-    <row r="773" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
         <v>1179</v>
       </c>
@@ -72274,7 +72351,7 @@
       <c r="AH773" s="4"/>
       <c r="AI773" s="4"/>
     </row>
-    <row r="774" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
         <v>1180</v>
       </c>
@@ -72335,7 +72412,7 @@
       <c r="AH774" s="4"/>
       <c r="AI774" s="4"/>
     </row>
-    <row r="775" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
         <v>1183</v>
       </c>
@@ -72396,7 +72473,7 @@
       <c r="AH775" s="4"/>
       <c r="AI775" s="4"/>
     </row>
-    <row r="776" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
         <v>1184</v>
       </c>
@@ -72457,7 +72534,7 @@
       <c r="AH776" s="4"/>
       <c r="AI776" s="4"/>
     </row>
-    <row r="777" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
         <v>1185</v>
       </c>
@@ -72518,7 +72595,7 @@
       <c r="AH777" s="4"/>
       <c r="AI777" s="4"/>
     </row>
-    <row r="778" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
         <v>1186</v>
       </c>
@@ -72579,7 +72656,7 @@
       <c r="AH778" s="4"/>
       <c r="AI778" s="4"/>
     </row>
-    <row r="779" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
         <v>1187</v>
       </c>
@@ -72640,7 +72717,7 @@
       <c r="AH779" s="4"/>
       <c r="AI779" s="4"/>
     </row>
-    <row r="780" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
         <v>1188</v>
       </c>
@@ -72701,7 +72778,7 @@
       <c r="AH780" s="4"/>
       <c r="AI780" s="4"/>
     </row>
-    <row r="781" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
         <v>1191</v>
       </c>
@@ -72762,7 +72839,7 @@
       <c r="AH781" s="4"/>
       <c r="AI781" s="4"/>
     </row>
-    <row r="782" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
         <v>1194</v>
       </c>
@@ -72823,7 +72900,7 @@
       <c r="AH782" s="4"/>
       <c r="AI782" s="4"/>
     </row>
-    <row r="783" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
         <v>1195</v>
       </c>
@@ -72884,7 +72961,7 @@
       <c r="AH783" s="4"/>
       <c r="AI783" s="4"/>
     </row>
-    <row r="784" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784" s="2" t="s">
         <v>1196</v>
       </c>
@@ -72945,7 +73022,7 @@
       <c r="AH784" s="4"/>
       <c r="AI784" s="4"/>
     </row>
-    <row r="785" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
         <v>1197</v>
       </c>
@@ -73006,7 +73083,7 @@
       <c r="AH785" s="4"/>
       <c r="AI785" s="4"/>
     </row>
-    <row r="786" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
         <v>1200</v>
       </c>
@@ -73067,7 +73144,7 @@
       <c r="AH786" s="4"/>
       <c r="AI786" s="4"/>
     </row>
-    <row r="787" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
         <v>1201</v>
       </c>
@@ -73128,7 +73205,7 @@
       <c r="AH787" s="4"/>
       <c r="AI787" s="4"/>
     </row>
-    <row r="788" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="s">
         <v>1202</v>
       </c>
@@ -73189,7 +73266,7 @@
       <c r="AH788" s="4"/>
       <c r="AI788" s="4"/>
     </row>
-    <row r="789" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
         <v>1203</v>
       </c>
@@ -73250,7 +73327,7 @@
       <c r="AH789" s="4"/>
       <c r="AI789" s="4"/>
     </row>
-    <row r="790" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="s">
         <v>1206</v>
       </c>
@@ -73311,7 +73388,7 @@
       <c r="AH790" s="4"/>
       <c r="AI790" s="4"/>
     </row>
-    <row r="791" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="2" t="s">
         <v>1207</v>
       </c>
@@ -73372,7 +73449,7 @@
       <c r="AH791" s="4"/>
       <c r="AI791" s="4"/>
     </row>
-    <row r="792" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="2" t="s">
         <v>1210</v>
       </c>
@@ -73433,7 +73510,7 @@
       <c r="AH792" s="4"/>
       <c r="AI792" s="4"/>
     </row>
-    <row r="793" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="2" t="s">
         <v>1211</v>
       </c>
@@ -73494,7 +73571,7 @@
       <c r="AH793" s="4"/>
       <c r="AI793" s="4"/>
     </row>
-    <row r="794" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794" s="2" t="s">
         <v>1214</v>
       </c>
@@ -73555,7 +73632,7 @@
       <c r="AH794" s="4"/>
       <c r="AI794" s="4"/>
     </row>
-    <row r="795" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="2" t="s">
         <v>1217</v>
       </c>
@@ -73616,7 +73693,7 @@
       <c r="AH795" s="4"/>
       <c r="AI795" s="4"/>
     </row>
-    <row r="796" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796" s="2" t="s">
         <v>1218</v>
       </c>
@@ -73738,7 +73815,7 @@
       <c r="AH797" s="4"/>
       <c r="AI797" s="4"/>
     </row>
-    <row r="798" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="2" t="s">
         <v>1223</v>
       </c>
@@ -73799,7 +73876,7 @@
       <c r="AH798" s="4"/>
       <c r="AI798" s="4"/>
     </row>
-    <row r="799" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="2" t="s">
         <v>1225</v>
       </c>
@@ -73860,7 +73937,7 @@
       <c r="AH799" s="4"/>
       <c r="AI799" s="4"/>
     </row>
-    <row r="800" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800" s="2" t="s">
         <v>1228</v>
       </c>
@@ -73921,7 +73998,7 @@
       <c r="AH800" s="4"/>
       <c r="AI800" s="4"/>
     </row>
-    <row r="801" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801" s="2" t="s">
         <v>1229</v>
       </c>
@@ -73982,7 +74059,7 @@
       <c r="AH801" s="4"/>
       <c r="AI801" s="4"/>
     </row>
-    <row r="802" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A802" s="2" t="s">
         <v>1230</v>
       </c>
@@ -74043,7 +74120,7 @@
       <c r="AH802" s="4"/>
       <c r="AI802" s="4"/>
     </row>
-    <row r="803" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803" s="2" t="s">
         <v>1231</v>
       </c>
@@ -74104,7 +74181,7 @@
       <c r="AH803" s="4"/>
       <c r="AI803" s="4"/>
     </row>
-    <row r="804" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="2" t="s">
         <v>1234</v>
       </c>
@@ -74165,7 +74242,7 @@
       <c r="AH804" s="4"/>
       <c r="AI804" s="4"/>
     </row>
-    <row r="805" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A805" s="2" t="s">
         <v>1235</v>
       </c>
@@ -74226,7 +74303,7 @@
       <c r="AH805" s="4"/>
       <c r="AI805" s="4"/>
     </row>
-    <row r="806" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806" s="2" t="s">
         <v>1236</v>
       </c>
@@ -74287,7 +74364,7 @@
       <c r="AH806" s="4"/>
       <c r="AI806" s="4"/>
     </row>
-    <row r="807" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807" s="2" t="s">
         <v>1239</v>
       </c>
@@ -74348,7 +74425,7 @@
       <c r="AH807" s="4"/>
       <c r="AI807" s="4"/>
     </row>
-    <row r="808" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A808" s="2" t="s">
         <v>1240</v>
       </c>
@@ -74409,7 +74486,7 @@
       <c r="AH808" s="4"/>
       <c r="AI808" s="4"/>
     </row>
-    <row r="809" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A809" s="2" t="s">
         <v>1241</v>
       </c>
@@ -74470,7 +74547,7 @@
       <c r="AH809" s="4"/>
       <c r="AI809" s="4"/>
     </row>
-    <row r="810" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A810" s="2" t="s">
         <v>1244</v>
       </c>
@@ -74531,7 +74608,7 @@
       <c r="AH810" s="4"/>
       <c r="AI810" s="4"/>
     </row>
-    <row r="811" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A811" s="2" t="s">
         <v>1245</v>
       </c>
@@ -74592,7 +74669,7 @@
       <c r="AH811" s="4"/>
       <c r="AI811" s="4"/>
     </row>
-    <row r="812" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A812" s="2" t="s">
         <v>1247</v>
       </c>
@@ -74653,7 +74730,7 @@
       <c r="AH812" s="4"/>
       <c r="AI812" s="4"/>
     </row>
-    <row r="813" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A813" s="2" t="s">
         <v>1248</v>
       </c>
@@ -74714,7 +74791,7 @@
       <c r="AH813" s="4"/>
       <c r="AI813" s="4"/>
     </row>
-    <row r="814" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A814" s="2" t="s">
         <v>1252</v>
       </c>
@@ -74775,7 +74852,7 @@
       <c r="AH814" s="4"/>
       <c r="AI814" s="4"/>
     </row>
-    <row r="815" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A815" s="2" t="s">
         <v>1253</v>
       </c>
@@ -74836,7 +74913,7 @@
       <c r="AH815" s="4"/>
       <c r="AI815" s="4"/>
     </row>
-    <row r="816" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="2" t="s">
         <v>1255</v>
       </c>
@@ -74897,7 +74974,7 @@
       <c r="AH816" s="4"/>
       <c r="AI816" s="4"/>
     </row>
-    <row r="817" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817" s="2" t="s">
         <v>1256</v>
       </c>
@@ -74958,7 +75035,7 @@
       <c r="AH817" s="4"/>
       <c r="AI817" s="4"/>
     </row>
-    <row r="818" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="2" t="s">
         <v>1257</v>
       </c>
@@ -75019,7 +75096,7 @@
       <c r="AH818" s="4"/>
       <c r="AI818" s="4"/>
     </row>
-    <row r="819" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A819" s="2" t="s">
         <v>1258</v>
       </c>
@@ -75080,7 +75157,7 @@
       <c r="AH819" s="4"/>
       <c r="AI819" s="4"/>
     </row>
-    <row r="820" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A820" s="2" t="s">
         <v>1261</v>
       </c>
@@ -75141,7 +75218,7 @@
       <c r="AH820" s="4"/>
       <c r="AI820" s="4"/>
     </row>
-    <row r="821" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A821" s="2" t="s">
         <v>1262</v>
       </c>
@@ -75263,7 +75340,7 @@
       <c r="AH822" s="4"/>
       <c r="AI822" s="4"/>
     </row>
-    <row r="823" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="2" t="s">
         <v>1266</v>
       </c>
@@ -75324,7 +75401,7 @@
       <c r="AH823" s="4"/>
       <c r="AI823" s="4"/>
     </row>
-    <row r="824" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A824" s="2" t="s">
         <v>1268</v>
       </c>
@@ -75385,7 +75462,7 @@
       <c r="AH824" s="4"/>
       <c r="AI824" s="4"/>
     </row>
-    <row r="825" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A825" s="2" t="s">
         <v>1269</v>
       </c>
@@ -75446,7 +75523,7 @@
       <c r="AH825" s="4"/>
       <c r="AI825" s="4"/>
     </row>
-    <row r="826" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826" s="2" t="s">
         <v>1272</v>
       </c>
@@ -75507,7 +75584,7 @@
       <c r="AH826" s="4"/>
       <c r="AI826" s="4"/>
     </row>
-    <row r="827" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="2" t="s">
         <v>1273</v>
       </c>
@@ -75568,7 +75645,7 @@
       <c r="AH827" s="4"/>
       <c r="AI827" s="4"/>
     </row>
-    <row r="828" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="2" t="s">
         <v>1276</v>
       </c>
@@ -75629,7 +75706,7 @@
       <c r="AH828" s="4"/>
       <c r="AI828" s="4"/>
     </row>
-    <row r="829" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="2" t="s">
         <v>1277</v>
       </c>
@@ -75690,7 +75767,7 @@
       <c r="AH829" s="4"/>
       <c r="AI829" s="4"/>
     </row>
-    <row r="830" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830" s="2" t="s">
         <v>1279</v>
       </c>
@@ -75751,7 +75828,7 @@
       <c r="AH830" s="4"/>
       <c r="AI830" s="4"/>
     </row>
-    <row r="831" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A831" s="2" t="s">
         <v>1280</v>
       </c>
@@ -75812,7 +75889,7 @@
       <c r="AH831" s="4"/>
       <c r="AI831" s="4"/>
     </row>
-    <row r="832" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A832" s="2" t="s">
         <v>1281</v>
       </c>
@@ -75873,7 +75950,7 @@
       <c r="AH832" s="4"/>
       <c r="AI832" s="4"/>
     </row>
-    <row r="833" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A833" s="2" t="s">
         <v>1282</v>
       </c>
@@ -75934,7 +76011,7 @@
       <c r="AH833" s="4"/>
       <c r="AI833" s="4"/>
     </row>
-    <row r="834" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A834" s="2" t="s">
         <v>1283</v>
       </c>
@@ -75995,7 +76072,7 @@
       <c r="AH834" s="4"/>
       <c r="AI834" s="4"/>
     </row>
-    <row r="835" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835" s="2" t="s">
         <v>1286</v>
       </c>
@@ -76056,7 +76133,7 @@
       <c r="AH835" s="4"/>
       <c r="AI835" s="4"/>
     </row>
-    <row r="836" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A836" s="2" t="s">
         <v>1289</v>
       </c>
@@ -76117,7 +76194,7 @@
       <c r="AH836" s="4"/>
       <c r="AI836" s="4"/>
     </row>
-    <row r="837" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A837" s="2" t="s">
         <v>1290</v>
       </c>
@@ -76178,7 +76255,7 @@
       <c r="AH837" s="4"/>
       <c r="AI837" s="4"/>
     </row>
-    <row r="838" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="2" t="s">
         <v>1291</v>
       </c>
@@ -76239,7 +76316,7 @@
       <c r="AH838" s="4"/>
       <c r="AI838" s="4"/>
     </row>
-    <row r="839" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="2" t="s">
         <v>1292</v>
       </c>
@@ -76300,7 +76377,7 @@
       <c r="AH839" s="4"/>
       <c r="AI839" s="4"/>
     </row>
-    <row r="840" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="2" t="s">
         <v>1293</v>
       </c>
@@ -76361,7 +76438,7 @@
       <c r="AH840" s="4"/>
       <c r="AI840" s="4"/>
     </row>
-    <row r="841" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="2" t="s">
         <v>1297</v>
       </c>
@@ -76422,7 +76499,7 @@
       <c r="AH841" s="4"/>
       <c r="AI841" s="4"/>
     </row>
-    <row r="842" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="2" t="s">
         <v>1298</v>
       </c>
@@ -76483,7 +76560,7 @@
       <c r="AH842" s="4"/>
       <c r="AI842" s="4"/>
     </row>
-    <row r="843" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A843" s="2" t="s">
         <v>1299</v>
       </c>
@@ -76544,7 +76621,7 @@
       <c r="AH843" s="4"/>
       <c r="AI843" s="4"/>
     </row>
-    <row r="844" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A844" s="2" t="s">
         <v>1300</v>
       </c>
@@ -76605,7 +76682,7 @@
       <c r="AH844" s="4"/>
       <c r="AI844" s="4"/>
     </row>
-    <row r="845" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A845" s="2" t="s">
         <v>1301</v>
       </c>
@@ -76666,7 +76743,7 @@
       <c r="AH845" s="4"/>
       <c r="AI845" s="4"/>
     </row>
-    <row r="846" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="2" t="s">
         <v>1302</v>
       </c>
@@ -76727,7 +76804,7 @@
       <c r="AH846" s="4"/>
       <c r="AI846" s="4"/>
     </row>
-    <row r="847" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A847" s="2" t="s">
         <v>1303</v>
       </c>
@@ -76788,7 +76865,7 @@
       <c r="AH847" s="4"/>
       <c r="AI847" s="4"/>
     </row>
-    <row r="848" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A848" s="2" t="s">
         <v>1306</v>
       </c>
@@ -76849,7 +76926,7 @@
       <c r="AH848" s="4"/>
       <c r="AI848" s="4"/>
     </row>
-    <row r="849" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A849" s="2" t="s">
         <v>1308</v>
       </c>
@@ -76910,7 +76987,7 @@
       <c r="AH849" s="4"/>
       <c r="AI849" s="4"/>
     </row>
-    <row r="850" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850" s="2" t="s">
         <v>1309</v>
       </c>
@@ -76971,7 +77048,7 @@
       <c r="AH850" s="4"/>
       <c r="AI850" s="4"/>
     </row>
-    <row r="851" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A851" s="2" t="s">
         <v>1311</v>
       </c>
@@ -77032,7 +77109,7 @@
       <c r="AH851" s="4"/>
       <c r="AI851" s="4"/>
     </row>
-    <row r="852" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A852" s="2" t="s">
         <v>1312</v>
       </c>
@@ -77093,7 +77170,7 @@
       <c r="AH852" s="4"/>
       <c r="AI852" s="4"/>
     </row>
-    <row r="853" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A853" s="2" t="s">
         <v>1314</v>
       </c>
@@ -77154,7 +77231,7 @@
       <c r="AH853" s="4"/>
       <c r="AI853" s="4"/>
     </row>
-    <row r="854" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A854" s="2" t="s">
         <v>1315</v>
       </c>
@@ -77215,7 +77292,7 @@
       <c r="AH854" s="4"/>
       <c r="AI854" s="4"/>
     </row>
-    <row r="855" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A855" s="2" t="s">
         <v>1317</v>
       </c>
@@ -77276,7 +77353,7 @@
       <c r="AH855" s="4"/>
       <c r="AI855" s="4"/>
     </row>
-    <row r="856" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A856" s="2" t="s">
         <v>1319</v>
       </c>
@@ -77337,7 +77414,7 @@
       <c r="AH856" s="4"/>
       <c r="AI856" s="4"/>
     </row>
-    <row r="857" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A857" s="2" t="s">
         <v>1322</v>
       </c>
@@ -77459,7 +77536,7 @@
       <c r="AH858" s="4"/>
       <c r="AI858" s="4"/>
     </row>
-    <row r="859" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859" s="2" t="s">
         <v>1326</v>
       </c>
@@ -77520,7 +77597,7 @@
       <c r="AH859" s="4"/>
       <c r="AI859" s="4"/>
     </row>
-    <row r="860" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860" s="2" t="s">
         <v>1327</v>
       </c>
@@ -77581,7 +77658,7 @@
       <c r="AH860" s="4"/>
       <c r="AI860" s="4"/>
     </row>
-    <row r="861" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A861" s="2" t="s">
         <v>1329</v>
       </c>
@@ -77642,7 +77719,7 @@
       <c r="AH861" s="4"/>
       <c r="AI861" s="4"/>
     </row>
-    <row r="862" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A862" s="2" t="s">
         <v>1330</v>
       </c>
@@ -77703,7 +77780,7 @@
       <c r="AH862" s="4"/>
       <c r="AI862" s="4"/>
     </row>
-    <row r="863" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A863" s="2" t="s">
         <v>1332</v>
       </c>
@@ -77764,7 +77841,7 @@
       <c r="AH863" s="4"/>
       <c r="AI863" s="4"/>
     </row>
-    <row r="864" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A864" s="2" t="s">
         <v>1334</v>
       </c>
@@ -77825,7 +77902,7 @@
       <c r="AH864" s="4"/>
       <c r="AI864" s="4"/>
     </row>
-    <row r="865" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865" s="2" t="s">
         <v>1337</v>
       </c>
@@ -77886,7 +77963,7 @@
       <c r="AH865" s="4"/>
       <c r="AI865" s="4"/>
     </row>
-    <row r="866" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A866" s="2" t="s">
         <v>1338</v>
       </c>
@@ -77947,7 +78024,7 @@
       <c r="AH866" s="4"/>
       <c r="AI866" s="4"/>
     </row>
-    <row r="867" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867" s="2" t="s">
         <v>1341</v>
       </c>
@@ -78008,7 +78085,7 @@
       <c r="AH867" s="4"/>
       <c r="AI867" s="4"/>
     </row>
-    <row r="868" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868" s="2" t="s">
         <v>1344</v>
       </c>
@@ -78069,7 +78146,7 @@
       <c r="AH868" s="4"/>
       <c r="AI868" s="4"/>
     </row>
-    <row r="869" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869" s="2" t="s">
         <v>1345</v>
       </c>
@@ -78130,7 +78207,7 @@
       <c r="AH869" s="4"/>
       <c r="AI869" s="4"/>
     </row>
-    <row r="870" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870" s="2" t="s">
         <v>1347</v>
       </c>
@@ -78191,7 +78268,7 @@
       <c r="AH870" s="4"/>
       <c r="AI870" s="4"/>
     </row>
-    <row r="871" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="2" t="s">
         <v>1349</v>
       </c>
@@ -78252,7 +78329,7 @@
       <c r="AH871" s="4"/>
       <c r="AI871" s="4"/>
     </row>
-    <row r="872" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872" s="2" t="s">
         <v>1352</v>
       </c>
@@ -78313,7 +78390,7 @@
       <c r="AH872" s="4"/>
       <c r="AI872" s="4"/>
     </row>
-    <row r="873" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873" s="2" t="s">
         <v>1353</v>
       </c>
@@ -78374,7 +78451,7 @@
       <c r="AH873" s="4"/>
       <c r="AI873" s="4"/>
     </row>
-    <row r="874" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A874" s="2" t="s">
         <v>1355</v>
       </c>
@@ -78435,7 +78512,7 @@
       <c r="AH874" s="4"/>
       <c r="AI874" s="4"/>
     </row>
-    <row r="875" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A875" s="2" t="s">
         <v>1357</v>
       </c>
@@ -78496,7 +78573,7 @@
       <c r="AH875" s="4"/>
       <c r="AI875" s="4"/>
     </row>
-    <row r="876" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876" s="2" t="s">
         <v>1359</v>
       </c>
@@ -78557,7 +78634,7 @@
       <c r="AH876" s="4"/>
       <c r="AI876" s="4"/>
     </row>
-    <row r="877" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="2" t="s">
         <v>1362</v>
       </c>
@@ -78618,7 +78695,7 @@
       <c r="AH877" s="4"/>
       <c r="AI877" s="4"/>
     </row>
-    <row r="878" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878" s="2" t="s">
         <v>1364</v>
       </c>
@@ -78679,7 +78756,7 @@
       <c r="AH878" s="4"/>
       <c r="AI878" s="4"/>
     </row>
-    <row r="879" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879" s="2" t="s">
         <v>1365</v>
       </c>
@@ -78740,7 +78817,7 @@
       <c r="AH879" s="4"/>
       <c r="AI879" s="4"/>
     </row>
-    <row r="880" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880" s="2" t="s">
         <v>1366</v>
       </c>
@@ -78801,7 +78878,7 @@
       <c r="AH880" s="4"/>
       <c r="AI880" s="4"/>
     </row>
-    <row r="881" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881" s="2" t="s">
         <v>1367</v>
       </c>
@@ -78862,7 +78939,7 @@
       <c r="AH881" s="4"/>
       <c r="AI881" s="4"/>
     </row>
-    <row r="882" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882" s="2" t="s">
         <v>1370</v>
       </c>
@@ -78923,7 +79000,7 @@
       <c r="AH882" s="4"/>
       <c r="AI882" s="4"/>
     </row>
-    <row r="883" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="2" t="s">
         <v>1371</v>
       </c>
@@ -78984,7 +79061,7 @@
       <c r="AH883" s="4"/>
       <c r="AI883" s="4"/>
     </row>
-    <row r="884" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A884" s="2" t="s">
         <v>1372</v>
       </c>
@@ -79045,7 +79122,7 @@
       <c r="AH884" s="4"/>
       <c r="AI884" s="4"/>
     </row>
-    <row r="885" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A885" s="2" t="s">
         <v>1373</v>
       </c>
@@ -79106,7 +79183,7 @@
       <c r="AH885" s="4"/>
       <c r="AI885" s="4"/>
     </row>
-    <row r="886" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="2" t="s">
         <v>1375</v>
       </c>
@@ -79167,7 +79244,7 @@
       <c r="AH886" s="4"/>
       <c r="AI886" s="4"/>
     </row>
-    <row r="887" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="2" t="s">
         <v>1378</v>
       </c>
@@ -79228,7 +79305,7 @@
       <c r="AH887" s="4"/>
       <c r="AI887" s="4"/>
     </row>
-    <row r="888" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="2" t="s">
         <v>1380</v>
       </c>
@@ -79289,7 +79366,7 @@
       <c r="AH888" s="4"/>
       <c r="AI888" s="4"/>
     </row>
-    <row r="889" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="2" t="s">
         <v>1383</v>
       </c>
@@ -79350,7 +79427,7 @@
       <c r="AH889" s="4"/>
       <c r="AI889" s="4"/>
     </row>
-    <row r="890" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A890" s="2" t="s">
         <v>1384</v>
       </c>
@@ -79411,7 +79488,7 @@
       <c r="AH890" s="4"/>
       <c r="AI890" s="4"/>
     </row>
-    <row r="891" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A891" s="2" t="s">
         <v>1385</v>
       </c>
@@ -79472,7 +79549,7 @@
       <c r="AH891" s="4"/>
       <c r="AI891" s="4"/>
     </row>
-    <row r="892" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892" s="2" t="s">
         <v>1387</v>
       </c>
@@ -79533,7 +79610,7 @@
       <c r="AH892" s="4"/>
       <c r="AI892" s="4"/>
     </row>
-    <row r="893" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893" s="2" t="s">
         <v>1390</v>
       </c>
@@ -79594,7 +79671,7 @@
       <c r="AH893" s="4"/>
       <c r="AI893" s="4"/>
     </row>
-    <row r="894" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894" s="2" t="s">
         <v>1391</v>
       </c>
@@ -79655,7 +79732,7 @@
       <c r="AH894" s="4"/>
       <c r="AI894" s="4"/>
     </row>
-    <row r="895" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895" s="2" t="s">
         <v>1394</v>
       </c>
@@ -79716,7 +79793,7 @@
       <c r="AH895" s="4"/>
       <c r="AI895" s="4"/>
     </row>
-    <row r="896" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896" s="2" t="s">
         <v>1396</v>
       </c>
@@ -79777,7 +79854,7 @@
       <c r="AH896" s="4"/>
       <c r="AI896" s="4"/>
     </row>
-    <row r="897" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897" s="2" t="s">
         <v>1399</v>
       </c>
@@ -79838,7 +79915,7 @@
       <c r="AH897" s="4"/>
       <c r="AI897" s="4"/>
     </row>
-    <row r="898" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898" s="2" t="s">
         <v>1401</v>
       </c>
@@ -79899,7 +79976,7 @@
       <c r="AH898" s="4"/>
       <c r="AI898" s="4"/>
     </row>
-    <row r="899" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="2" t="s">
         <v>1403</v>
       </c>
@@ -79960,7 +80037,7 @@
       <c r="AH899" s="4"/>
       <c r="AI899" s="4"/>
     </row>
-    <row r="900" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="2" t="s">
         <v>1404</v>
       </c>
@@ -80021,7 +80098,7 @@
       <c r="AH900" s="4"/>
       <c r="AI900" s="4"/>
     </row>
-    <row r="901" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="2" t="s">
         <v>1407</v>
       </c>
@@ -80082,7 +80159,7 @@
       <c r="AH901" s="4"/>
       <c r="AI901" s="4"/>
     </row>
-    <row r="902" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="2" t="s">
         <v>1408</v>
       </c>
@@ -80143,7 +80220,7 @@
       <c r="AH902" s="4"/>
       <c r="AI902" s="4"/>
     </row>
-    <row r="903" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="2" t="s">
         <v>1412</v>
       </c>
@@ -80204,7 +80281,7 @@
       <c r="AH903" s="4"/>
       <c r="AI903" s="4"/>
     </row>
-    <row r="904" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="2" t="s">
         <v>1414</v>
       </c>
@@ -80265,7 +80342,7 @@
       <c r="AH904" s="4"/>
       <c r="AI904" s="4"/>
     </row>
-    <row r="905" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="2" t="s">
         <v>1418</v>
       </c>
@@ -80326,7 +80403,7 @@
       <c r="AH905" s="4"/>
       <c r="AI905" s="4"/>
     </row>
-    <row r="906" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="2" t="s">
         <v>1420</v>
       </c>
@@ -80387,7 +80464,7 @@
       <c r="AH906" s="4"/>
       <c r="AI906" s="4"/>
     </row>
-    <row r="907" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="2" t="s">
         <v>1422</v>
       </c>
@@ -80448,7 +80525,7 @@
       <c r="AH907" s="4"/>
       <c r="AI907" s="4"/>
     </row>
-    <row r="908" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="2" t="s">
         <v>1426</v>
       </c>
@@ -80509,7 +80586,7 @@
       <c r="AH908" s="4"/>
       <c r="AI908" s="4"/>
     </row>
-    <row r="909" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="2" t="s">
         <v>1428</v>
       </c>
@@ -80570,7 +80647,7 @@
       <c r="AH909" s="4"/>
       <c r="AI909" s="4"/>
     </row>
-    <row r="910" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="2" t="s">
         <v>1430</v>
       </c>
@@ -80631,7 +80708,7 @@
       <c r="AH910" s="4"/>
       <c r="AI910" s="4"/>
     </row>
-    <row r="911" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="2" t="s">
         <v>1432</v>
       </c>
@@ -80692,7 +80769,7 @@
       <c r="AH911" s="4"/>
       <c r="AI911" s="4"/>
     </row>
-    <row r="912" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="2" t="s">
         <v>1435</v>
       </c>
@@ -80753,7 +80830,7 @@
       <c r="AH912" s="4"/>
       <c r="AI912" s="4"/>
     </row>
-    <row r="913" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
         <v>1436</v>
       </c>
@@ -80814,7 +80891,7 @@
       <c r="AH913" s="4"/>
       <c r="AI913" s="4"/>
     </row>
-    <row r="914" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="2" t="s">
         <v>1437</v>
       </c>
@@ -80875,7 +80952,7 @@
       <c r="AH914" s="4"/>
       <c r="AI914" s="4"/>
     </row>
-    <row r="915" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="2" t="s">
         <v>1438</v>
       </c>
@@ -80936,7 +81013,7 @@
       <c r="AH915" s="4"/>
       <c r="AI915" s="4"/>
     </row>
-    <row r="916" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="2" t="s">
         <v>1441</v>
       </c>
@@ -80997,7 +81074,7 @@
       <c r="AH916" s="4"/>
       <c r="AI916" s="4"/>
     </row>
-    <row r="917" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="2" t="s">
         <v>1442</v>
       </c>
@@ -81058,7 +81135,7 @@
       <c r="AH917" s="4"/>
       <c r="AI917" s="4"/>
     </row>
-    <row r="918" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="2" t="s">
         <v>1445</v>
       </c>
@@ -81119,7 +81196,7 @@
       <c r="AH918" s="4"/>
       <c r="AI918" s="4"/>
     </row>
-    <row r="919" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="2" t="s">
         <v>1446</v>
       </c>
@@ -81180,7 +81257,7 @@
       <c r="AH919" s="4"/>
       <c r="AI919" s="4"/>
     </row>
-    <row r="920" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="2" t="s">
         <v>1449</v>
       </c>
@@ -81241,7 +81318,7 @@
       <c r="AH920" s="4"/>
       <c r="AI920" s="4"/>
     </row>
-    <row r="921" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="2" t="s">
         <v>1450</v>
       </c>
@@ -81302,7 +81379,7 @@
       <c r="AH921" s="4"/>
       <c r="AI921" s="4"/>
     </row>
-    <row r="922" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A922" s="2" t="s">
         <v>1542</v>
       </c>
@@ -81361,7 +81438,7 @@
       <c r="AH922" s="4"/>
       <c r="AI922" s="4"/>
     </row>
-    <row r="923" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A923" s="2" t="s">
         <v>1543</v>
       </c>
@@ -81420,7 +81497,7 @@
       <c r="AH923" s="4"/>
       <c r="AI923" s="4"/>
     </row>
-    <row r="924" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A924" s="2" t="s">
         <v>1544</v>
       </c>
@@ -81479,7 +81556,7 @@
       <c r="AH924" s="4"/>
       <c r="AI924" s="4"/>
     </row>
-    <row r="925" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="2" t="s">
         <v>1545</v>
       </c>
@@ -81538,7 +81615,7 @@
       <c r="AH925" s="4"/>
       <c r="AI925" s="4"/>
     </row>
-    <row r="926" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A926" s="2" t="s">
         <v>1546</v>
       </c>
@@ -81597,7 +81674,7 @@
       <c r="AH926" s="4"/>
       <c r="AI926" s="4"/>
     </row>
-    <row r="927" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A927" s="2" t="s">
         <v>1547</v>
       </c>
@@ -81656,7 +81733,7 @@
       <c r="AH927" s="4"/>
       <c r="AI927" s="4"/>
     </row>
-    <row r="928" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A928" s="2" t="s">
         <v>1548</v>
       </c>
@@ -81715,7 +81792,7 @@
       <c r="AH928" s="4"/>
       <c r="AI928" s="4"/>
     </row>
-    <row r="929" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A929" s="2" t="s">
         <v>1549</v>
       </c>
@@ -81774,7 +81851,7 @@
       <c r="AH929" s="4"/>
       <c r="AI929" s="4"/>
     </row>
-    <row r="930" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="2" t="s">
         <v>1550</v>
       </c>
@@ -81833,7 +81910,7 @@
       <c r="AH930" s="4"/>
       <c r="AI930" s="4"/>
     </row>
-    <row r="931" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A931" s="2" t="s">
         <v>1551</v>
       </c>
@@ -81892,7 +81969,7 @@
       <c r="AH931" s="4"/>
       <c r="AI931" s="4"/>
     </row>
-    <row r="932" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A932" s="2" t="s">
         <v>1552</v>
       </c>
@@ -81951,7 +82028,7 @@
       <c r="AH932" s="4"/>
       <c r="AI932" s="4"/>
     </row>
-    <row r="933" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A933" s="2" t="s">
         <v>1553</v>
       </c>
@@ -82010,7 +82087,7 @@
       <c r="AH933" s="4"/>
       <c r="AI933" s="4"/>
     </row>
-    <row r="934" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A934" s="2" t="s">
         <v>1554</v>
       </c>
@@ -82069,7 +82146,7 @@
       <c r="AH934" s="4"/>
       <c r="AI934" s="4"/>
     </row>
-    <row r="935" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A935" s="2" t="s">
         <v>1555</v>
       </c>
@@ -82128,7 +82205,7 @@
       <c r="AH935" s="4"/>
       <c r="AI935" s="4"/>
     </row>
-    <row r="936" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A936" s="2" t="s">
         <v>1556</v>
       </c>
@@ -82187,7 +82264,7 @@
       <c r="AH936" s="4"/>
       <c r="AI936" s="4"/>
     </row>
-    <row r="937" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A937" s="2" t="s">
         <v>1557</v>
       </c>
@@ -82246,7 +82323,7 @@
       <c r="AH937" s="4"/>
       <c r="AI937" s="4"/>
     </row>
-    <row r="938" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A938" s="2" t="s">
         <v>1558</v>
       </c>
@@ -82305,7 +82382,7 @@
       <c r="AH938" s="4"/>
       <c r="AI938" s="4"/>
     </row>
-    <row r="939" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A939" s="2" t="s">
         <v>1559</v>
       </c>
@@ -82364,7 +82441,7 @@
       <c r="AH939" s="4"/>
       <c r="AI939" s="4"/>
     </row>
-    <row r="940" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A940" s="2" t="s">
         <v>1560</v>
       </c>
@@ -82423,7 +82500,7 @@
       <c r="AH940" s="4"/>
       <c r="AI940" s="4"/>
     </row>
-    <row r="941" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A941" s="2" t="s">
         <v>1561</v>
       </c>
@@ -82482,7 +82559,7 @@
       <c r="AH941" s="4"/>
       <c r="AI941" s="4"/>
     </row>
-    <row r="942" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A942" s="2" t="s">
         <v>1562</v>
       </c>
@@ -82541,7 +82618,7 @@
       <c r="AH942" s="4"/>
       <c r="AI942" s="4"/>
     </row>
-    <row r="943" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A943" s="2" t="s">
         <v>1563</v>
       </c>
@@ -82600,7 +82677,7 @@
       <c r="AH943" s="4"/>
       <c r="AI943" s="4"/>
     </row>
-    <row r="944" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A944" s="2" t="s">
         <v>1564</v>
       </c>
@@ -82659,7 +82736,7 @@
       <c r="AH944" s="4"/>
       <c r="AI944" s="4"/>
     </row>
-    <row r="945" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A945" s="2" t="s">
         <v>1565</v>
       </c>
@@ -82718,7 +82795,7 @@
       <c r="AH945" s="4"/>
       <c r="AI945" s="4"/>
     </row>
-    <row r="946" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A946" s="2" t="s">
         <v>1566</v>
       </c>
@@ -82777,7 +82854,7 @@
       <c r="AH946" s="4"/>
       <c r="AI946" s="4"/>
     </row>
-    <row r="947" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A947" s="2" t="s">
         <v>1567</v>
       </c>
@@ -82836,7 +82913,7 @@
       <c r="AH947" s="4"/>
       <c r="AI947" s="4"/>
     </row>
-    <row r="948" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A948" s="2" t="s">
         <v>1568</v>
       </c>
@@ -82895,7 +82972,7 @@
       <c r="AH948" s="4"/>
       <c r="AI948" s="4"/>
     </row>
-    <row r="949" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A949" s="2" t="s">
         <v>1569</v>
       </c>
@@ -82954,7 +83031,7 @@
       <c r="AH949" s="4"/>
       <c r="AI949" s="4"/>
     </row>
-    <row r="950" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A950" s="2" t="s">
         <v>1570</v>
       </c>
@@ -83013,7 +83090,7 @@
       <c r="AH950" s="4"/>
       <c r="AI950" s="4"/>
     </row>
-    <row r="951" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="2" t="s">
         <v>1571</v>
       </c>
@@ -83072,7 +83149,7 @@
       <c r="AH951" s="4"/>
       <c r="AI951" s="4"/>
     </row>
-    <row r="952" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="2" t="s">
         <v>1572</v>
       </c>
@@ -83131,7 +83208,7 @@
       <c r="AH952" s="4"/>
       <c r="AI952" s="4"/>
     </row>
-    <row r="953" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A953" s="2" t="s">
         <v>1573</v>
       </c>
@@ -83190,7 +83267,7 @@
       <c r="AH953" s="4"/>
       <c r="AI953" s="4"/>
     </row>
-    <row r="954" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="2" t="s">
         <v>1574</v>
       </c>
@@ -83249,7 +83326,7 @@
       <c r="AH954" s="4"/>
       <c r="AI954" s="4"/>
     </row>
-    <row r="955" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A955" s="2" t="s">
         <v>1575</v>
       </c>
@@ -83308,7 +83385,7 @@
       <c r="AH955" s="4"/>
       <c r="AI955" s="4"/>
     </row>
-    <row r="956" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A956" s="2" t="s">
         <v>1576</v>
       </c>
@@ -83367,7 +83444,7 @@
       <c r="AH956" s="4"/>
       <c r="AI956" s="4"/>
     </row>
-    <row r="957" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A957" s="2" t="s">
         <v>1577</v>
       </c>
@@ -83426,7 +83503,7 @@
       <c r="AH957" s="4"/>
       <c r="AI957" s="4"/>
     </row>
-    <row r="958" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A958" s="2" t="s">
         <v>1578</v>
       </c>
@@ -83485,7 +83562,7 @@
       <c r="AH958" s="4"/>
       <c r="AI958" s="4"/>
     </row>
-    <row r="959" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A959" s="2" t="s">
         <v>1579</v>
       </c>
@@ -83544,7 +83621,7 @@
       <c r="AH959" s="4"/>
       <c r="AI959" s="4"/>
     </row>
-    <row r="960" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A960" s="2" t="s">
         <v>1580</v>
       </c>
@@ -83603,7 +83680,7 @@
       <c r="AH960" s="4"/>
       <c r="AI960" s="4"/>
     </row>
-    <row r="961" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A961" s="2" t="s">
         <v>1581</v>
       </c>
@@ -83662,7 +83739,7 @@
       <c r="AH961" s="4"/>
       <c r="AI961" s="4"/>
     </row>
-    <row r="962" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A962" s="2" t="s">
         <v>1582</v>
       </c>
@@ -83721,7 +83798,7 @@
       <c r="AH962" s="4"/>
       <c r="AI962" s="4"/>
     </row>
-    <row r="963" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A963" s="2" t="s">
         <v>1583</v>
       </c>
@@ -83780,7 +83857,7 @@
       <c r="AH963" s="4"/>
       <c r="AI963" s="4"/>
     </row>
-    <row r="964" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A964" s="2" t="s">
         <v>1584</v>
       </c>
@@ -83839,7 +83916,7 @@
       <c r="AH964" s="4"/>
       <c r="AI964" s="4"/>
     </row>
-    <row r="965" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A965" s="2" t="s">
         <v>1585</v>
       </c>
@@ -83898,7 +83975,7 @@
       <c r="AH965" s="4"/>
       <c r="AI965" s="4"/>
     </row>
-    <row r="966" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A966" s="2" t="s">
         <v>1586</v>
       </c>
@@ -83957,7 +84034,7 @@
       <c r="AH966" s="4"/>
       <c r="AI966" s="4"/>
     </row>
-    <row r="967" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A967" s="2" t="s">
         <v>1587</v>
       </c>
@@ -84016,7 +84093,7 @@
       <c r="AH967" s="4"/>
       <c r="AI967" s="4"/>
     </row>
-    <row r="968" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A968" s="2" t="s">
         <v>1588</v>
       </c>
@@ -84075,7 +84152,7 @@
       <c r="AH968" s="4"/>
       <c r="AI968" s="4"/>
     </row>
-    <row r="969" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A969" s="2" t="s">
         <v>1589</v>
       </c>
@@ -84134,7 +84211,7 @@
       <c r="AH969" s="4"/>
       <c r="AI969" s="4"/>
     </row>
-    <row r="970" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A970" s="2" t="s">
         <v>1590</v>
       </c>
@@ -84191,7 +84268,7 @@
       <c r="AH970" s="4"/>
       <c r="AI970" s="4"/>
     </row>
-    <row r="971" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A971" s="2" t="s">
         <v>1591</v>
       </c>
@@ -84248,7 +84325,7 @@
       <c r="AH971" s="4"/>
       <c r="AI971" s="4"/>
     </row>
-    <row r="972" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A972" s="2" t="s">
         <v>1592</v>
       </c>
@@ -84305,7 +84382,7 @@
       <c r="AH972" s="4"/>
       <c r="AI972" s="4"/>
     </row>
-    <row r="973" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A973" s="2" t="s">
         <v>1593</v>
       </c>
@@ -84362,7 +84439,7 @@
       <c r="AH973" s="4"/>
       <c r="AI973" s="4"/>
     </row>
-    <row r="974" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A974" s="2" t="s">
         <v>1595</v>
       </c>
@@ -84419,7 +84496,7 @@
       <c r="AH974" s="4"/>
       <c r="AI974" s="4"/>
     </row>
-    <row r="975" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A975" s="2" t="s">
         <v>1596</v>
       </c>
@@ -84476,7 +84553,7 @@
       <c r="AH975" s="4"/>
       <c r="AI975" s="4"/>
     </row>
-    <row r="976" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A976" s="2" t="s">
         <v>1597</v>
       </c>
@@ -84533,7 +84610,7 @@
       <c r="AH976" s="4"/>
       <c r="AI976" s="4"/>
     </row>
-    <row r="977" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A977" s="2" t="s">
         <v>1598</v>
       </c>
@@ -84590,7 +84667,7 @@
       <c r="AH977" s="4"/>
       <c r="AI977" s="4"/>
     </row>
-    <row r="978" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A978" s="2" t="s">
         <v>1599</v>
       </c>
@@ -84647,7 +84724,7 @@
       <c r="AH978" s="4"/>
       <c r="AI978" s="4"/>
     </row>
-    <row r="979" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A979" s="2" t="s">
         <v>1600</v>
       </c>
@@ -84704,7 +84781,7 @@
       <c r="AH979" s="4"/>
       <c r="AI979" s="4"/>
     </row>
-    <row r="980" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A980" s="2" t="s">
         <v>1601</v>
       </c>
@@ -84761,7 +84838,7 @@
       <c r="AH980" s="4"/>
       <c r="AI980" s="4"/>
     </row>
-    <row r="981" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A981" s="2" t="s">
         <v>1602</v>
       </c>
@@ -84818,7 +84895,7 @@
       <c r="AH981" s="4"/>
       <c r="AI981" s="4"/>
     </row>
-    <row r="982" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A982" s="2" t="s">
         <v>1604</v>
       </c>
@@ -84875,7 +84952,7 @@
       <c r="AH982" s="4"/>
       <c r="AI982" s="4"/>
     </row>
-    <row r="983" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A983" s="2" t="s">
         <v>1605</v>
       </c>
@@ -84932,7 +85009,7 @@
       <c r="AH983" s="4"/>
       <c r="AI983" s="4"/>
     </row>
-    <row r="984" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A984" s="2" t="s">
         <v>1606</v>
       </c>
@@ -84989,7 +85066,7 @@
       <c r="AH984" s="4"/>
       <c r="AI984" s="4"/>
     </row>
-    <row r="985" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A985" s="2" t="s">
         <v>1607</v>
       </c>
@@ -85046,7 +85123,7 @@
       <c r="AH985" s="4"/>
       <c r="AI985" s="4"/>
     </row>
-    <row r="986" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A986" s="2" t="s">
         <v>1608</v>
       </c>
@@ -85103,7 +85180,7 @@
       <c r="AH986" s="4"/>
       <c r="AI986" s="4"/>
     </row>
-    <row r="987" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A987" s="2" t="s">
         <v>1609</v>
       </c>
@@ -85160,7 +85237,7 @@
       <c r="AH987" s="4"/>
       <c r="AI987" s="4"/>
     </row>
-    <row r="988" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A988" s="2" t="s">
         <v>1610</v>
       </c>
@@ -85217,7 +85294,7 @@
       <c r="AH988" s="4"/>
       <c r="AI988" s="4"/>
     </row>
-    <row r="989" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A989" s="2" t="s">
         <v>1612</v>
       </c>
@@ -85274,7 +85351,7 @@
       <c r="AH989" s="4"/>
       <c r="AI989" s="4"/>
     </row>
-    <row r="990" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A990" s="2" t="s">
         <v>1613</v>
       </c>
@@ -85331,7 +85408,7 @@
       <c r="AH990" s="4"/>
       <c r="AI990" s="4"/>
     </row>
-    <row r="991" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A991" s="2" t="s">
         <v>1614</v>
       </c>
@@ -85388,7 +85465,7 @@
       <c r="AH991" s="4"/>
       <c r="AI991" s="4"/>
     </row>
-    <row r="992" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A992" s="2" t="s">
         <v>1616</v>
       </c>
@@ -85445,7 +85522,7 @@
       <c r="AH992" s="4"/>
       <c r="AI992" s="4"/>
     </row>
-    <row r="993" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="2" t="s">
         <v>1618</v>
       </c>
@@ -85502,7 +85579,7 @@
       <c r="AH993" s="4"/>
       <c r="AI993" s="4"/>
     </row>
-    <row r="994" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A994" s="2" t="s">
         <v>1620</v>
       </c>
@@ -85561,7 +85638,7 @@
       <c r="AH994" s="4"/>
       <c r="AI994" s="4"/>
     </row>
-    <row r="995" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A995" s="2" t="s">
         <v>1621</v>
       </c>
@@ -85620,7 +85697,7 @@
       <c r="AH995" s="4"/>
       <c r="AI995" s="4"/>
     </row>
-    <row r="996" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A996" s="2" t="s">
         <v>1622</v>
       </c>
@@ -85677,7 +85754,7 @@
       <c r="AH996" s="4"/>
       <c r="AI996" s="4"/>
     </row>
-    <row r="997" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A997" s="2" t="s">
         <v>1623</v>
       </c>
@@ -85734,7 +85811,7 @@
       <c r="AH997" s="4"/>
       <c r="AI997" s="4"/>
     </row>
-    <row r="998" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A998" s="2" t="s">
         <v>1626</v>
       </c>
@@ -85791,7 +85868,7 @@
       <c r="AH998" s="4"/>
       <c r="AI998" s="4"/>
     </row>
-    <row r="999" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A999" s="2" t="s">
         <v>1630</v>
       </c>
@@ -85848,7 +85925,7 @@
       <c r="AH999" s="4"/>
       <c r="AI999" s="4"/>
     </row>
-    <row r="1000" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1000" s="2" t="s">
         <v>1631</v>
       </c>
@@ -85905,7 +85982,7 @@
       <c r="AH1000" s="4"/>
       <c r="AI1000" s="4"/>
     </row>
-    <row r="1001" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1001" s="2" t="s">
         <v>1632</v>
       </c>
@@ -85962,7 +86039,7 @@
       <c r="AH1001" s="4"/>
       <c r="AI1001" s="4"/>
     </row>
-    <row r="1002" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1002" s="2" t="s">
         <v>1635</v>
       </c>
@@ -86019,7 +86096,7 @@
       <c r="AH1002" s="4"/>
       <c r="AI1002" s="4"/>
     </row>
-    <row r="1003" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1003" s="2" t="s">
         <v>1636</v>
       </c>
@@ -86076,7 +86153,7 @@
       <c r="AH1003" s="4"/>
       <c r="AI1003" s="4"/>
     </row>
-    <row r="1004" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="2" t="s">
         <v>1637</v>
       </c>
@@ -86133,7 +86210,7 @@
       <c r="AH1004" s="4"/>
       <c r="AI1004" s="4"/>
     </row>
-    <row r="1005" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="2" t="s">
         <v>1640</v>
       </c>
@@ -86190,7 +86267,7 @@
       <c r="AH1005" s="4"/>
       <c r="AI1005" s="4"/>
     </row>
-    <row r="1006" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="2" t="s">
         <v>1641</v>
       </c>
@@ -86247,7 +86324,7 @@
       <c r="AH1006" s="4"/>
       <c r="AI1006" s="4"/>
     </row>
-    <row r="1007" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1007" s="2" t="s">
         <v>1644</v>
       </c>
@@ -86304,7 +86381,7 @@
       <c r="AH1007" s="4"/>
       <c r="AI1007" s="4"/>
     </row>
-    <row r="1008" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1008" s="2" t="s">
         <v>1645</v>
       </c>
@@ -86361,7 +86438,7 @@
       <c r="AH1008" s="4"/>
       <c r="AI1008" s="4"/>
     </row>
-    <row r="1009" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1009" s="2" t="s">
         <v>1648</v>
       </c>
@@ -86418,7 +86495,7 @@
       <c r="AH1009" s="4"/>
       <c r="AI1009" s="4"/>
     </row>
-    <row r="1010" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1010" s="2" t="s">
         <v>1652</v>
       </c>
@@ -86475,7 +86552,7 @@
       <c r="AH1010" s="4"/>
       <c r="AI1010" s="4"/>
     </row>
-    <row r="1011" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1011" s="2" t="s">
         <v>1653</v>
       </c>
@@ -86532,7 +86609,7 @@
       <c r="AH1011" s="4"/>
       <c r="AI1011" s="4"/>
     </row>
-    <row r="1012" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1012" s="2" t="s">
         <v>1655</v>
       </c>
@@ -86591,7 +86668,7 @@
       <c r="AH1012" s="4"/>
       <c r="AI1012" s="4"/>
     </row>
-    <row r="1013" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1013" s="2" t="s">
         <v>1656</v>
       </c>
@@ -86650,7 +86727,7 @@
       <c r="AH1013" s="4"/>
       <c r="AI1013" s="4"/>
     </row>
-    <row r="1014" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1014" s="2" t="s">
         <v>1657</v>
       </c>
@@ -86707,7 +86784,7 @@
       <c r="AH1014" s="4"/>
       <c r="AI1014" s="4"/>
     </row>
-    <row r="1015" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1015" s="2" t="s">
         <v>1660</v>
       </c>
@@ -86764,7 +86841,7 @@
       <c r="AH1015" s="4"/>
       <c r="AI1015" s="4"/>
     </row>
-    <row r="1016" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1016" s="2" t="s">
         <v>1661</v>
       </c>
@@ -86821,7 +86898,7 @@
       <c r="AH1016" s="4"/>
       <c r="AI1016" s="4"/>
     </row>
-    <row r="1017" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1017" s="2" t="s">
         <v>1662</v>
       </c>
@@ -86878,7 +86955,7 @@
       <c r="AH1017" s="4"/>
       <c r="AI1017" s="4"/>
     </row>
-    <row r="1018" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1018" s="2" t="s">
         <v>1663</v>
       </c>
@@ -86935,7 +87012,7 @@
       <c r="AH1018" s="4"/>
       <c r="AI1018" s="4"/>
     </row>
-    <row r="1019" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1019" s="2" t="s">
         <v>1664</v>
       </c>
@@ -86992,7 +87069,7 @@
       <c r="AH1019" s="4"/>
       <c r="AI1019" s="4"/>
     </row>
-    <row r="1020" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1020" s="2" t="s">
         <v>1665</v>
       </c>
@@ -87049,7 +87126,7 @@
       <c r="AH1020" s="4"/>
       <c r="AI1020" s="4"/>
     </row>
-    <row r="1021" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1021" s="2" t="s">
         <v>1667</v>
       </c>
@@ -87106,7 +87183,7 @@
       <c r="AH1021" s="4"/>
       <c r="AI1021" s="4"/>
     </row>
-    <row r="1022" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1022" s="2" t="s">
         <v>1669</v>
       </c>
@@ -87163,7 +87240,7 @@
       <c r="AH1022" s="4"/>
       <c r="AI1022" s="4"/>
     </row>
-    <row r="1023" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1023" s="2" t="s">
         <v>1672</v>
       </c>
@@ -87220,7 +87297,7 @@
       <c r="AH1023" s="4"/>
       <c r="AI1023" s="4"/>
     </row>
-    <row r="1024" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1024" s="2" t="s">
         <v>1673</v>
       </c>
@@ -87277,7 +87354,7 @@
       <c r="AH1024" s="4"/>
       <c r="AI1024" s="4"/>
     </row>
-    <row r="1025" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1025" s="2" t="s">
         <v>1675</v>
       </c>
@@ -87334,7 +87411,7 @@
       <c r="AH1025" s="4"/>
       <c r="AI1025" s="4"/>
     </row>
-    <row r="1026" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1026" s="2" t="s">
         <v>1677</v>
       </c>
@@ -87391,19 +87468,630 @@
       <c r="AH1026" s="4"/>
       <c r="AI1026" s="4"/>
     </row>
+    <row r="1027" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1027" s="9" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B1027" s="2"/>
+      <c r="C1027" s="2"/>
+      <c r="D1027" s="4" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E1027" s="5" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F1027" s="4"/>
+      <c r="G1027" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H1027" s="4"/>
+      <c r="I1027" s="4"/>
+      <c r="J1027" s="4"/>
+      <c r="K1027" s="4"/>
+      <c r="L1027" s="4"/>
+      <c r="M1027" s="4"/>
+      <c r="N1027" s="4"/>
+      <c r="O1027" s="4"/>
+      <c r="P1027" s="4"/>
+      <c r="Q1027" s="4"/>
+      <c r="R1027" s="4"/>
+      <c r="S1027" s="4"/>
+      <c r="T1027" s="4"/>
+      <c r="U1027" s="4"/>
+      <c r="V1027" s="4"/>
+      <c r="W1027" s="4"/>
+      <c r="X1027" s="4"/>
+      <c r="Y1027" s="4"/>
+      <c r="Z1027" s="4"/>
+      <c r="AA1027" s="4"/>
+      <c r="AB1027" s="4"/>
+      <c r="AC1027" s="4"/>
+      <c r="AD1027" s="4"/>
+      <c r="AE1027" s="4"/>
+      <c r="AF1027" s="4"/>
+      <c r="AG1027" s="4"/>
+      <c r="AH1027" s="4"/>
+      <c r="AI1027" s="4"/>
+    </row>
+    <row r="1028" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1028" s="9" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B1028" s="2"/>
+      <c r="C1028" s="2"/>
+      <c r="D1028" s="4" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E1028" s="5" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F1028" s="4"/>
+      <c r="G1028" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1028" s="4"/>
+      <c r="I1028" s="4"/>
+      <c r="J1028" s="4"/>
+      <c r="K1028" s="4"/>
+      <c r="L1028" s="4"/>
+      <c r="M1028" s="4"/>
+      <c r="N1028" s="4"/>
+      <c r="O1028" s="4"/>
+      <c r="P1028" s="4"/>
+      <c r="Q1028" s="4"/>
+      <c r="R1028" s="4"/>
+      <c r="S1028" s="4"/>
+      <c r="T1028" s="4"/>
+      <c r="U1028" s="4"/>
+      <c r="V1028" s="4"/>
+      <c r="W1028" s="4"/>
+      <c r="X1028" s="4"/>
+      <c r="Y1028" s="4"/>
+      <c r="Z1028" s="4"/>
+      <c r="AA1028" s="4"/>
+      <c r="AB1028" s="4"/>
+      <c r="AC1028" s="4"/>
+      <c r="AD1028" s="4"/>
+      <c r="AE1028" s="4"/>
+      <c r="AF1028" s="4"/>
+      <c r="AG1028" s="4"/>
+      <c r="AH1028" s="4"/>
+      <c r="AI1028" s="4"/>
+    </row>
+    <row r="1029" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1029" s="9" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B1029" s="2"/>
+      <c r="C1029" s="2"/>
+      <c r="D1029" s="4" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E1029" s="5" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F1029" s="4"/>
+      <c r="G1029" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1029" s="4"/>
+      <c r="I1029" s="4"/>
+      <c r="J1029" s="4"/>
+      <c r="K1029" s="4"/>
+      <c r="L1029" s="4"/>
+      <c r="M1029" s="4"/>
+      <c r="N1029" s="4"/>
+      <c r="O1029" s="4"/>
+      <c r="P1029" s="4"/>
+      <c r="Q1029" s="4"/>
+      <c r="R1029" s="4"/>
+      <c r="S1029" s="4"/>
+      <c r="T1029" s="4"/>
+      <c r="U1029" s="4"/>
+      <c r="V1029" s="4"/>
+      <c r="W1029" s="4"/>
+      <c r="X1029" s="4"/>
+      <c r="Y1029" s="4"/>
+      <c r="Z1029" s="4"/>
+      <c r="AA1029" s="4"/>
+      <c r="AB1029" s="4"/>
+      <c r="AC1029" s="4"/>
+      <c r="AD1029" s="4"/>
+      <c r="AE1029" s="4"/>
+      <c r="AF1029" s="4"/>
+      <c r="AG1029" s="4"/>
+      <c r="AH1029" s="4"/>
+      <c r="AI1029" s="4"/>
+    </row>
+    <row r="1030" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1030" s="9" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B1030" s="2"/>
+      <c r="C1030" s="2"/>
+      <c r="D1030" s="4" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E1030" s="5" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F1030" s="4"/>
+      <c r="G1030" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1030" s="4"/>
+      <c r="I1030" s="4"/>
+      <c r="J1030" s="4"/>
+      <c r="K1030" s="4"/>
+      <c r="L1030" s="4"/>
+      <c r="M1030" s="4"/>
+      <c r="N1030" s="4"/>
+      <c r="O1030" s="4"/>
+      <c r="P1030" s="4"/>
+      <c r="Q1030" s="4"/>
+      <c r="R1030" s="4"/>
+      <c r="S1030" s="4"/>
+      <c r="T1030" s="4"/>
+      <c r="U1030" s="4"/>
+      <c r="V1030" s="4"/>
+      <c r="W1030" s="4"/>
+      <c r="X1030" s="4"/>
+      <c r="Y1030" s="4"/>
+      <c r="Z1030" s="4"/>
+      <c r="AA1030" s="4"/>
+      <c r="AB1030" s="4"/>
+      <c r="AC1030" s="4"/>
+      <c r="AD1030" s="4"/>
+      <c r="AE1030" s="4"/>
+      <c r="AF1030" s="4"/>
+      <c r="AG1030" s="4"/>
+      <c r="AH1030" s="4"/>
+      <c r="AI1030" s="4"/>
+    </row>
+    <row r="1031" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1031" s="9" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B1031" s="2"/>
+      <c r="C1031" s="2"/>
+      <c r="D1031" s="4" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E1031" s="5" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F1031" s="4"/>
+      <c r="G1031" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1031" s="4"/>
+      <c r="I1031" s="4"/>
+      <c r="J1031" s="4"/>
+      <c r="K1031" s="4"/>
+      <c r="L1031" s="4"/>
+      <c r="M1031" s="4"/>
+      <c r="N1031" s="4"/>
+      <c r="O1031" s="4"/>
+      <c r="P1031" s="4"/>
+      <c r="Q1031" s="4"/>
+      <c r="R1031" s="4"/>
+      <c r="S1031" s="4"/>
+      <c r="T1031" s="4"/>
+      <c r="U1031" s="4"/>
+      <c r="V1031" s="4"/>
+      <c r="W1031" s="4"/>
+      <c r="X1031" s="4"/>
+      <c r="Y1031" s="4"/>
+      <c r="Z1031" s="4"/>
+      <c r="AA1031" s="4"/>
+      <c r="AB1031" s="4"/>
+      <c r="AC1031" s="4"/>
+      <c r="AD1031" s="4"/>
+      <c r="AE1031" s="4"/>
+      <c r="AF1031" s="4"/>
+      <c r="AG1031" s="4"/>
+      <c r="AH1031" s="4"/>
+      <c r="AI1031" s="4"/>
+    </row>
+    <row r="1032" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1032" s="9" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B1032" s="2"/>
+      <c r="C1032" s="2"/>
+      <c r="D1032" s="4" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E1032" s="5" t="s">
+        <v>1681</v>
+      </c>
+      <c r="F1032" s="4"/>
+      <c r="G1032" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1032" s="4"/>
+      <c r="I1032" s="4"/>
+      <c r="J1032" s="4"/>
+      <c r="K1032" s="4"/>
+      <c r="L1032" s="4"/>
+      <c r="M1032" s="4"/>
+      <c r="N1032" s="4"/>
+      <c r="O1032" s="4"/>
+      <c r="P1032" s="4"/>
+      <c r="Q1032" s="4"/>
+      <c r="R1032" s="4"/>
+      <c r="S1032" s="4"/>
+      <c r="T1032" s="4"/>
+      <c r="U1032" s="4"/>
+      <c r="V1032" s="4"/>
+      <c r="W1032" s="4"/>
+      <c r="X1032" s="4"/>
+      <c r="Y1032" s="4"/>
+      <c r="Z1032" s="4"/>
+      <c r="AA1032" s="4"/>
+      <c r="AB1032" s="4"/>
+      <c r="AC1032" s="4"/>
+      <c r="AD1032" s="4"/>
+      <c r="AE1032" s="4"/>
+      <c r="AF1032" s="4"/>
+      <c r="AG1032" s="4"/>
+      <c r="AH1032" s="4"/>
+      <c r="AI1032" s="4"/>
+    </row>
+    <row r="1033" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1033" s="9" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B1033" s="2"/>
+      <c r="C1033" s="2"/>
+      <c r="D1033" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E1033" s="5" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F1033" s="4"/>
+      <c r="G1033" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1033" s="4"/>
+      <c r="I1033" s="4"/>
+      <c r="J1033" s="4"/>
+      <c r="K1033" s="4"/>
+      <c r="L1033" s="4"/>
+      <c r="M1033" s="4"/>
+      <c r="N1033" s="4"/>
+      <c r="O1033" s="4"/>
+      <c r="P1033" s="4"/>
+      <c r="Q1033" s="4"/>
+      <c r="R1033" s="4"/>
+      <c r="S1033" s="4"/>
+      <c r="T1033" s="4"/>
+      <c r="U1033" s="4"/>
+      <c r="V1033" s="4"/>
+      <c r="W1033" s="4"/>
+      <c r="X1033" s="4"/>
+      <c r="Y1033" s="4"/>
+      <c r="Z1033" s="4"/>
+      <c r="AA1033" s="4"/>
+      <c r="AB1033" s="4"/>
+      <c r="AC1033" s="4"/>
+      <c r="AD1033" s="4"/>
+      <c r="AE1033" s="4"/>
+      <c r="AF1033" s="4"/>
+      <c r="AG1033" s="4"/>
+      <c r="AH1033" s="4"/>
+      <c r="AI1033" s="4"/>
+    </row>
+    <row r="1034" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1034" s="9" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B1034" s="2"/>
+      <c r="C1034" s="2"/>
+      <c r="D1034" s="4" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E1034" s="5" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F1034" s="4"/>
+      <c r="G1034" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1034" s="4"/>
+      <c r="I1034" s="4"/>
+      <c r="J1034" s="4"/>
+      <c r="K1034" s="4"/>
+      <c r="L1034" s="4"/>
+      <c r="M1034" s="4"/>
+      <c r="N1034" s="4"/>
+      <c r="O1034" s="4"/>
+      <c r="P1034" s="4"/>
+      <c r="Q1034" s="4"/>
+      <c r="R1034" s="4"/>
+      <c r="S1034" s="4"/>
+      <c r="T1034" s="4"/>
+      <c r="U1034" s="4"/>
+      <c r="V1034" s="4"/>
+      <c r="W1034" s="4"/>
+      <c r="X1034" s="4"/>
+      <c r="Y1034" s="4"/>
+      <c r="Z1034" s="4"/>
+      <c r="AA1034" s="4"/>
+      <c r="AB1034" s="4"/>
+      <c r="AC1034" s="4"/>
+      <c r="AD1034" s="4"/>
+      <c r="AE1034" s="4"/>
+      <c r="AF1034" s="4"/>
+      <c r="AG1034" s="4"/>
+      <c r="AH1034" s="4"/>
+      <c r="AI1034" s="4"/>
+    </row>
+    <row r="1035" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1035" s="9" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B1035" s="2"/>
+      <c r="C1035" s="2"/>
+      <c r="D1035" s="4" t="s">
+        <v>1506</v>
+      </c>
+      <c r="E1035" s="5" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F1035" s="4"/>
+      <c r="G1035" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H1035" s="4"/>
+      <c r="I1035" s="4"/>
+      <c r="J1035" s="4"/>
+      <c r="K1035" s="4"/>
+      <c r="L1035" s="4"/>
+      <c r="M1035" s="4"/>
+      <c r="N1035" s="4"/>
+      <c r="O1035" s="4"/>
+      <c r="P1035" s="4"/>
+      <c r="Q1035" s="4"/>
+      <c r="R1035" s="4"/>
+      <c r="S1035" s="4"/>
+      <c r="T1035" s="4"/>
+      <c r="U1035" s="4"/>
+      <c r="V1035" s="4"/>
+      <c r="W1035" s="4"/>
+      <c r="X1035" s="4"/>
+      <c r="Y1035" s="4"/>
+      <c r="Z1035" s="4"/>
+      <c r="AA1035" s="4"/>
+      <c r="AB1035" s="4"/>
+      <c r="AC1035" s="4"/>
+      <c r="AD1035" s="4"/>
+      <c r="AE1035" s="4"/>
+      <c r="AF1035" s="4"/>
+      <c r="AG1035" s="4"/>
+      <c r="AH1035" s="4"/>
+      <c r="AI1035" s="4"/>
+    </row>
+    <row r="1036" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1036" s="9" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B1036" s="2"/>
+      <c r="C1036" s="2"/>
+      <c r="D1036" s="4" t="s">
+        <v>1512</v>
+      </c>
+      <c r="E1036" s="5" t="s">
+        <v>1683</v>
+      </c>
+      <c r="F1036" s="4"/>
+      <c r="G1036" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1036" s="4"/>
+      <c r="I1036" s="4"/>
+      <c r="J1036" s="4"/>
+      <c r="K1036" s="4"/>
+      <c r="L1036" s="4"/>
+      <c r="M1036" s="4"/>
+      <c r="N1036" s="4"/>
+      <c r="O1036" s="4"/>
+      <c r="P1036" s="4"/>
+      <c r="Q1036" s="4"/>
+      <c r="R1036" s="4"/>
+      <c r="S1036" s="4"/>
+      <c r="T1036" s="4"/>
+      <c r="U1036" s="4"/>
+      <c r="V1036" s="4"/>
+      <c r="W1036" s="4"/>
+      <c r="X1036" s="4"/>
+      <c r="Y1036" s="4"/>
+      <c r="Z1036" s="4"/>
+      <c r="AA1036" s="4"/>
+      <c r="AB1036" s="4"/>
+      <c r="AC1036" s="4"/>
+      <c r="AD1036" s="4"/>
+      <c r="AE1036" s="4"/>
+      <c r="AF1036" s="4"/>
+      <c r="AG1036" s="4"/>
+      <c r="AH1036" s="4"/>
+      <c r="AI1036" s="4"/>
+    </row>
+    <row r="1037" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1037" s="9" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B1037" s="2"/>
+      <c r="C1037" s="2"/>
+      <c r="D1037" s="4" t="s">
+        <v>1514</v>
+      </c>
+      <c r="E1037" s="5" t="s">
+        <v>1515</v>
+      </c>
+      <c r="F1037" s="4"/>
+      <c r="G1037" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1037" s="4"/>
+      <c r="I1037" s="4"/>
+      <c r="J1037" s="4"/>
+      <c r="K1037" s="4"/>
+      <c r="L1037" s="4"/>
+      <c r="M1037" s="4"/>
+      <c r="N1037" s="4"/>
+      <c r="O1037" s="4"/>
+      <c r="P1037" s="4"/>
+      <c r="Q1037" s="4"/>
+      <c r="R1037" s="4"/>
+      <c r="S1037" s="4"/>
+      <c r="T1037" s="4"/>
+      <c r="U1037" s="4"/>
+      <c r="V1037" s="4"/>
+      <c r="W1037" s="4"/>
+      <c r="X1037" s="4"/>
+      <c r="Y1037" s="4"/>
+      <c r="Z1037" s="4"/>
+      <c r="AA1037" s="4"/>
+      <c r="AB1037" s="4"/>
+      <c r="AC1037" s="4"/>
+      <c r="AD1037" s="4"/>
+      <c r="AE1037" s="4"/>
+      <c r="AF1037" s="4"/>
+      <c r="AG1037" s="4"/>
+      <c r="AH1037" s="4"/>
+      <c r="AI1037" s="4"/>
+    </row>
+    <row r="1038" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1038" s="9" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B1038" s="2"/>
+      <c r="C1038" s="2"/>
+      <c r="D1038" s="4" t="s">
+        <v>1516</v>
+      </c>
+      <c r="E1038" s="5" t="s">
+        <v>1684</v>
+      </c>
+      <c r="F1038" s="4"/>
+      <c r="G1038" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1038" s="4"/>
+      <c r="I1038" s="4"/>
+      <c r="J1038" s="4"/>
+      <c r="K1038" s="4"/>
+      <c r="L1038" s="4"/>
+      <c r="M1038" s="4"/>
+      <c r="N1038" s="4"/>
+      <c r="O1038" s="4"/>
+      <c r="P1038" s="4"/>
+      <c r="Q1038" s="4"/>
+      <c r="R1038" s="4"/>
+      <c r="S1038" s="4"/>
+      <c r="T1038" s="4"/>
+      <c r="U1038" s="4"/>
+      <c r="V1038" s="4"/>
+      <c r="W1038" s="4"/>
+      <c r="X1038" s="4"/>
+      <c r="Y1038" s="4"/>
+      <c r="Z1038" s="4"/>
+      <c r="AA1038" s="4"/>
+      <c r="AB1038" s="4"/>
+      <c r="AC1038" s="4"/>
+      <c r="AD1038" s="4"/>
+      <c r="AE1038" s="4"/>
+      <c r="AF1038" s="4"/>
+      <c r="AG1038" s="4"/>
+      <c r="AH1038" s="4"/>
+      <c r="AI1038" s="4"/>
+    </row>
+    <row r="1039" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1039" s="9" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B1039" s="2"/>
+      <c r="C1039" s="2"/>
+      <c r="D1039" s="4" t="s">
+        <v>1409</v>
+      </c>
+      <c r="E1039" s="5" t="s">
+        <v>1685</v>
+      </c>
+      <c r="F1039" s="4"/>
+      <c r="G1039" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H1039" s="4"/>
+      <c r="I1039" s="4"/>
+      <c r="J1039" s="4"/>
+      <c r="K1039" s="4"/>
+      <c r="L1039" s="4"/>
+      <c r="M1039" s="4"/>
+      <c r="N1039" s="4"/>
+      <c r="O1039" s="4"/>
+      <c r="P1039" s="4"/>
+      <c r="Q1039" s="4"/>
+      <c r="R1039" s="4"/>
+      <c r="S1039" s="4"/>
+      <c r="T1039" s="4"/>
+      <c r="U1039" s="4"/>
+      <c r="V1039" s="4"/>
+      <c r="W1039" s="4"/>
+      <c r="X1039" s="4"/>
+      <c r="Y1039" s="4"/>
+      <c r="Z1039" s="4"/>
+      <c r="AA1039" s="4"/>
+      <c r="AB1039" s="4"/>
+      <c r="AC1039" s="4"/>
+      <c r="AD1039" s="4"/>
+      <c r="AE1039" s="4"/>
+      <c r="AF1039" s="4"/>
+      <c r="AG1039" s="4"/>
+      <c r="AH1039" s="4"/>
+      <c r="AI1039" s="4"/>
+    </row>
+    <row r="1040" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1040" s="2"/>
+      <c r="B1040" s="2"/>
+      <c r="C1040" s="2"/>
+      <c r="D1040" s="4"/>
+      <c r="E1040" s="5"/>
+      <c r="F1040" s="4"/>
+      <c r="G1040" s="4"/>
+      <c r="H1040" s="4"/>
+      <c r="I1040" s="4"/>
+      <c r="J1040" s="4"/>
+      <c r="K1040" s="4"/>
+      <c r="L1040" s="4"/>
+      <c r="M1040" s="4"/>
+      <c r="N1040" s="4"/>
+      <c r="O1040" s="4"/>
+      <c r="P1040" s="4"/>
+      <c r="Q1040" s="4"/>
+      <c r="R1040" s="4"/>
+      <c r="S1040" s="4"/>
+      <c r="T1040" s="4"/>
+      <c r="U1040" s="4"/>
+      <c r="V1040" s="4"/>
+      <c r="W1040" s="4"/>
+      <c r="X1040" s="4"/>
+      <c r="Y1040" s="4"/>
+      <c r="Z1040" s="4"/>
+      <c r="AA1040" s="4"/>
+      <c r="AB1040" s="4"/>
+      <c r="AC1040" s="4"/>
+      <c r="AD1040" s="4"/>
+      <c r="AE1040" s="4"/>
+      <c r="AF1040" s="4"/>
+      <c r="AG1040" s="4"/>
+      <c r="AH1040" s="4"/>
+      <c r="AI1040" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R1026" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="PTO/BC"/>
-        <filter val="PTO/CH"/>
-        <filter val="PTO/GF"/>
-        <filter val="PTO/LM"/>
-        <filter val="PTO/PT"/>
-        <filter val="PTO/VD"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:R1026" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F5C307-9828-4521-920E-15FA9798C364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30820B18-C24C-42CD-896C-842EBB8A385F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30820B18-C24C-42CD-896C-842EBB8A385F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B444D32C-D776-48D3-A3A6-1ACE5F50728A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87485,7 +87485,9 @@
         <v>1026</v>
       </c>
       <c r="H1027" s="4"/>
-      <c r="I1027" s="4"/>
+      <c r="I1027" s="4">
+        <v>229.99</v>
+      </c>
       <c r="J1027" s="4"/>
       <c r="K1027" s="4"/>
       <c r="L1027" s="4"/>
@@ -87530,7 +87532,9 @@
         <v>1251</v>
       </c>
       <c r="H1028" s="4"/>
-      <c r="I1028" s="4"/>
+      <c r="I1028" s="4">
+        <v>259.99</v>
+      </c>
       <c r="J1028" s="4"/>
       <c r="K1028" s="4"/>
       <c r="L1028" s="4"/>
@@ -87575,7 +87579,9 @@
         <v>1251</v>
       </c>
       <c r="H1029" s="4"/>
-      <c r="I1029" s="4"/>
+      <c r="I1029" s="4">
+        <v>249.99</v>
+      </c>
       <c r="J1029" s="4"/>
       <c r="K1029" s="4"/>
       <c r="L1029" s="4"/>
@@ -87620,7 +87626,9 @@
         <v>1251</v>
       </c>
       <c r="H1030" s="4"/>
-      <c r="I1030" s="4"/>
+      <c r="I1030" s="4">
+        <v>229.99</v>
+      </c>
       <c r="J1030" s="4"/>
       <c r="K1030" s="4"/>
       <c r="L1030" s="4"/>
@@ -87665,7 +87673,9 @@
         <v>1251</v>
       </c>
       <c r="H1031" s="4"/>
-      <c r="I1031" s="4"/>
+      <c r="I1031" s="4">
+        <v>229.99</v>
+      </c>
       <c r="J1031" s="4"/>
       <c r="K1031" s="4"/>
       <c r="L1031" s="4"/>
@@ -87710,7 +87720,9 @@
         <v>1251</v>
       </c>
       <c r="H1032" s="4"/>
-      <c r="I1032" s="4"/>
+      <c r="I1032" s="4">
+        <v>229.99</v>
+      </c>
       <c r="J1032" s="4"/>
       <c r="K1032" s="4"/>
       <c r="L1032" s="4"/>
@@ -87755,7 +87767,9 @@
         <v>1251</v>
       </c>
       <c r="H1033" s="4"/>
-      <c r="I1033" s="4"/>
+      <c r="I1033" s="4">
+        <v>199.99</v>
+      </c>
       <c r="J1033" s="4"/>
       <c r="K1033" s="4"/>
       <c r="L1033" s="4"/>
@@ -87800,7 +87814,9 @@
         <v>1251</v>
       </c>
       <c r="H1034" s="4"/>
-      <c r="I1034" s="4"/>
+      <c r="I1034" s="4">
+        <v>199.99</v>
+      </c>
       <c r="J1034" s="4"/>
       <c r="K1034" s="4"/>
       <c r="L1034" s="4"/>
@@ -87845,7 +87861,9 @@
         <v>1026</v>
       </c>
       <c r="H1035" s="4"/>
-      <c r="I1035" s="4"/>
+      <c r="I1035" s="4">
+        <v>229.99</v>
+      </c>
       <c r="J1035" s="4"/>
       <c r="K1035" s="4"/>
       <c r="L1035" s="4"/>
@@ -87890,7 +87908,9 @@
         <v>1251</v>
       </c>
       <c r="H1036" s="4"/>
-      <c r="I1036" s="4"/>
+      <c r="I1036" s="4">
+        <v>249.99</v>
+      </c>
       <c r="J1036" s="4"/>
       <c r="K1036" s="4"/>
       <c r="L1036" s="4"/>
@@ -87935,7 +87955,9 @@
         <v>1251</v>
       </c>
       <c r="H1037" s="4"/>
-      <c r="I1037" s="4"/>
+      <c r="I1037" s="4">
+        <v>239.99</v>
+      </c>
       <c r="J1037" s="4"/>
       <c r="K1037" s="4"/>
       <c r="L1037" s="4"/>
@@ -87980,7 +88002,9 @@
         <v>1251</v>
       </c>
       <c r="H1038" s="4"/>
-      <c r="I1038" s="4"/>
+      <c r="I1038" s="4">
+        <v>219.99</v>
+      </c>
       <c r="J1038" s="4"/>
       <c r="K1038" s="4"/>
       <c r="L1038" s="4"/>
@@ -88025,7 +88049,9 @@
         <v>1251</v>
       </c>
       <c r="H1039" s="4"/>
-      <c r="I1039" s="4"/>
+      <c r="I1039" s="4">
+        <v>119.99</v>
+      </c>
       <c r="J1039" s="4"/>
       <c r="K1039" s="4"/>
       <c r="L1039" s="4"/>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B444D32C-D776-48D3-A3A6-1ACE5F50728A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF474D8F-B84D-4929-82CE-0BFC68E604F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="corre" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produtos!$A$1:$R$1026</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produtos!$A$1:$R$1048</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13155" uniqueCount="1699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12219" uniqueCount="1709">
   <si>
     <t>IMAGEM</t>
   </si>
@@ -5134,6 +5134,36 @@
   </si>
   <si>
     <t>OICR261714_PT_PRT</t>
+  </si>
+  <si>
+    <t>43206446_ALGMLT</t>
+  </si>
+  <si>
+    <t>43206446_LUNBEG</t>
+  </si>
+  <si>
+    <t>43206446_CHBMLT</t>
+  </si>
+  <si>
+    <t>43206446_PTO_PT</t>
+  </si>
+  <si>
+    <t>43206446_PTO_CH</t>
+  </si>
+  <si>
+    <t>PTOLM</t>
+  </si>
+  <si>
+    <t>54111405_ALGBEG</t>
+  </si>
+  <si>
+    <t>54111405_PTOLM</t>
+  </si>
+  <si>
+    <t>54111405_LUNAR</t>
+  </si>
+  <si>
+    <t>54111405_VDEMLT</t>
   </si>
 </sst>
 </file>
@@ -5596,7 +5626,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI1040"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:AI1048"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" style="6" customWidth="1"/>
@@ -5717,7 +5748,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
@@ -5824,7 +5855,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1678</v>
       </c>
@@ -5931,7 +5962,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>47</v>
       </c>
@@ -6038,7 +6069,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>49</v>
       </c>
@@ -6145,7 +6176,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>51</v>
       </c>
@@ -6252,7 +6283,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>53</v>
       </c>
@@ -6359,7 +6390,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>56</v>
       </c>
@@ -6466,7 +6497,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>58</v>
       </c>
@@ -6573,7 +6604,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>60</v>
       </c>
@@ -6680,7 +6711,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>62</v>
       </c>
@@ -6787,7 +6818,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>64</v>
       </c>
@@ -6894,7 +6925,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>67</v>
       </c>
@@ -7001,7 +7032,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>69</v>
       </c>
@@ -7108,7 +7139,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>71</v>
       </c>
@@ -7215,7 +7246,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>73</v>
       </c>
@@ -7322,7 +7353,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>75</v>
       </c>
@@ -7429,7 +7460,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>77</v>
       </c>
@@ -7536,7 +7567,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>79</v>
       </c>
@@ -7643,7 +7674,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>82</v>
       </c>
@@ -7750,7 +7781,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>83</v>
       </c>
@@ -7857,7 +7888,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>85</v>
       </c>
@@ -7964,7 +7995,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>87</v>
       </c>
@@ -8071,7 +8102,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>88</v>
       </c>
@@ -8178,7 +8209,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>89</v>
       </c>
@@ -8285,7 +8316,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>93</v>
       </c>
@@ -8392,7 +8423,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>96</v>
       </c>
@@ -8499,7 +8530,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>98</v>
       </c>
@@ -8606,7 +8637,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="29" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>100</v>
       </c>
@@ -8713,7 +8744,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>101</v>
       </c>
@@ -8820,7 +8851,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>103</v>
       </c>
@@ -8927,7 +8958,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>105</v>
       </c>
@@ -9034,7 +9065,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="33" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>106</v>
       </c>
@@ -9141,7 +9172,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>108</v>
       </c>
@@ -9248,7 +9279,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>113</v>
       </c>
@@ -9355,7 +9386,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>114</v>
       </c>
@@ -9462,7 +9493,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="37" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>116</v>
       </c>
@@ -9569,7 +9600,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="38" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>117</v>
       </c>
@@ -9676,7 +9707,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="39" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>118</v>
       </c>
@@ -9783,7 +9814,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="40" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>120</v>
       </c>
@@ -9890,7 +9921,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="41" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>122</v>
       </c>
@@ -9997,7 +10028,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>126</v>
       </c>
@@ -10104,7 +10135,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="43" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>128</v>
       </c>
@@ -10211,7 +10242,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>129</v>
       </c>
@@ -10318,7 +10349,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="45" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>131</v>
       </c>
@@ -10425,7 +10456,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="46" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>132</v>
       </c>
@@ -10532,7 +10563,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>134</v>
       </c>
@@ -10639,7 +10670,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>136</v>
       </c>
@@ -10746,7 +10777,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="49" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>138</v>
       </c>
@@ -10853,7 +10884,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="50" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>140</v>
       </c>
@@ -10960,7 +10991,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>141</v>
       </c>
@@ -11067,7 +11098,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="52" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>145</v>
       </c>
@@ -11174,7 +11205,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>146</v>
       </c>
@@ -11281,7 +11312,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="54" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>147</v>
       </c>
@@ -11388,7 +11419,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="55" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>149</v>
       </c>
@@ -11495,7 +11526,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="56" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>150</v>
       </c>
@@ -11602,7 +11633,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="57" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>152</v>
       </c>
@@ -11709,7 +11740,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="58" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>154</v>
       </c>
@@ -11816,7 +11847,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>156</v>
       </c>
@@ -11923,7 +11954,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>158</v>
       </c>
@@ -12030,7 +12061,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>160</v>
       </c>
@@ -12137,7 +12168,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>161</v>
       </c>
@@ -12244,7 +12275,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>163</v>
       </c>
@@ -12351,7 +12382,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="64" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>166</v>
       </c>
@@ -12458,7 +12489,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>168</v>
       </c>
@@ -12565,7 +12596,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="66" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>170</v>
       </c>
@@ -12672,7 +12703,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="67" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>172</v>
       </c>
@@ -12779,7 +12810,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="68" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>173</v>
       </c>
@@ -12886,7 +12917,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>175</v>
       </c>
@@ -12993,7 +13024,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="70" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>178</v>
       </c>
@@ -13100,7 +13131,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="71" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>179</v>
       </c>
@@ -13207,7 +13238,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="72" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>180</v>
       </c>
@@ -13314,7 +13345,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="73" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>181</v>
       </c>
@@ -13421,7 +13452,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>184</v>
       </c>
@@ -13528,7 +13559,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>186</v>
       </c>
@@ -13635,7 +13666,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>188</v>
       </c>
@@ -13742,7 +13773,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>190</v>
       </c>
@@ -13849,7 +13880,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>191</v>
       </c>
@@ -13956,7 +13987,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>194</v>
       </c>
@@ -14063,7 +14094,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>196</v>
       </c>
@@ -14170,7 +14201,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>197</v>
       </c>
@@ -14277,7 +14308,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="82" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>200</v>
       </c>
@@ -14384,7 +14415,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>201</v>
       </c>
@@ -14491,7 +14522,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="84" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>202</v>
       </c>
@@ -14598,7 +14629,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="85" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>205</v>
       </c>
@@ -14705,7 +14736,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="86" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>206</v>
       </c>
@@ -14812,7 +14843,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="87" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>208</v>
       </c>
@@ -14919,7 +14950,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="88" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>210</v>
       </c>
@@ -15026,7 +15057,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="89" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>213</v>
       </c>
@@ -15133,7 +15164,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="90" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>215</v>
       </c>
@@ -15240,7 +15271,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="91" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>216</v>
       </c>
@@ -15347,7 +15378,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="92" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>217</v>
       </c>
@@ -15454,7 +15485,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="93" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>220</v>
       </c>
@@ -15561,7 +15592,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="94" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>221</v>
       </c>
@@ -15668,7 +15699,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="95" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>223</v>
       </c>
@@ -15775,7 +15806,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="96" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>225</v>
       </c>
@@ -15882,7 +15913,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>229</v>
       </c>
@@ -15989,7 +16020,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>231</v>
       </c>
@@ -16096,7 +16127,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>233</v>
       </c>
@@ -16203,7 +16234,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>234</v>
       </c>
@@ -16310,7 +16341,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>237</v>
       </c>
@@ -16417,7 +16448,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>239</v>
       </c>
@@ -16524,7 +16555,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>240</v>
       </c>
@@ -16631,7 +16662,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>241</v>
       </c>
@@ -16738,7 +16769,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>243</v>
       </c>
@@ -16845,7 +16876,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>245</v>
       </c>
@@ -16952,7 +16983,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="107" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>248</v>
       </c>
@@ -17059,7 +17090,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="108" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>249</v>
       </c>
@@ -17166,7 +17197,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="109" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>250</v>
       </c>
@@ -17273,7 +17304,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="110" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>252</v>
       </c>
@@ -17380,7 +17411,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="111" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>253</v>
       </c>
@@ -17487,7 +17518,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="112" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>255</v>
       </c>
@@ -17594,7 +17625,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="113" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>257</v>
       </c>
@@ -17701,7 +17732,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="114" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>259</v>
       </c>
@@ -17808,7 +17839,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="115" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>260</v>
       </c>
@@ -17915,7 +17946,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="116" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>262</v>
       </c>
@@ -18022,7 +18053,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="117" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>264</v>
       </c>
@@ -18129,7 +18160,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="118" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>266</v>
       </c>
@@ -18236,7 +18267,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="119" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>268</v>
       </c>
@@ -18343,7 +18374,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="120" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>270</v>
       </c>
@@ -18450,7 +18481,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="121" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>271</v>
       </c>
@@ -18557,7 +18588,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>273</v>
       </c>
@@ -18664,7 +18695,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>275</v>
       </c>
@@ -18771,7 +18802,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="124" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>277</v>
       </c>
@@ -18878,7 +18909,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>278</v>
       </c>
@@ -18985,7 +19016,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="126" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>281</v>
       </c>
@@ -19092,7 +19123,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="127" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>282</v>
       </c>
@@ -19199,7 +19230,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="128" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>283</v>
       </c>
@@ -19306,7 +19337,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>284</v>
       </c>
@@ -19413,7 +19444,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>286</v>
       </c>
@@ -19520,7 +19551,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>288</v>
       </c>
@@ -19627,7 +19658,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="132" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>290</v>
       </c>
@@ -19734,7 +19765,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="133" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>291</v>
       </c>
@@ -19841,7 +19872,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="134" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>293</v>
       </c>
@@ -19948,7 +19979,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="135" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>294</v>
       </c>
@@ -20055,7 +20086,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="136" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>295</v>
       </c>
@@ -20162,7 +20193,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="137" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>296</v>
       </c>
@@ -20269,7 +20300,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="138" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>299</v>
       </c>
@@ -20376,7 +20407,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="139" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>300</v>
       </c>
@@ -20483,7 +20514,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="140" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>301</v>
       </c>
@@ -20590,7 +20621,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>302</v>
       </c>
@@ -20697,7 +20728,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="142" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>305</v>
       </c>
@@ -20804,7 +20835,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>307</v>
       </c>
@@ -20911,7 +20942,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="144" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>308</v>
       </c>
@@ -21018,7 +21049,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="145" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>310</v>
       </c>
@@ -21125,7 +21156,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="146" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>312</v>
       </c>
@@ -21232,7 +21263,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="147" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>313</v>
       </c>
@@ -21339,7 +21370,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="148" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>314</v>
       </c>
@@ -21446,7 +21477,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="149" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>316</v>
       </c>
@@ -21553,7 +21584,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="150" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>317</v>
       </c>
@@ -21660,7 +21691,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="151" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>318</v>
       </c>
@@ -21767,7 +21798,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="152" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>321</v>
       </c>
@@ -21874,7 +21905,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="153" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>322</v>
       </c>
@@ -21981,7 +22012,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="154" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>324</v>
       </c>
@@ -22088,7 +22119,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="155" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>325</v>
       </c>
@@ -22195,7 +22226,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="156" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>327</v>
       </c>
@@ -22302,7 +22333,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="157" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>328</v>
       </c>
@@ -22409,7 +22440,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="158" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>329</v>
       </c>
@@ -22516,7 +22547,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="159" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>330</v>
       </c>
@@ -22623,7 +22654,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="160" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>332</v>
       </c>
@@ -22730,7 +22761,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="161" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>334</v>
       </c>
@@ -22837,7 +22868,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="162" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>336</v>
       </c>
@@ -22944,7 +22975,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="163" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>337</v>
       </c>
@@ -23051,7 +23082,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="164" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>340</v>
       </c>
@@ -23158,7 +23189,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="165" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>342</v>
       </c>
@@ -23265,7 +23296,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="166" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>344</v>
       </c>
@@ -23372,7 +23403,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="167" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>346</v>
       </c>
@@ -23479,7 +23510,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="168" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>348</v>
       </c>
@@ -23586,7 +23617,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="169" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>349</v>
       </c>
@@ -23693,7 +23724,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="170" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>351</v>
       </c>
@@ -23800,7 +23831,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="171" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>352</v>
       </c>
@@ -23907,7 +23938,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="172" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>355</v>
       </c>
@@ -24014,7 +24045,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="173" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>356</v>
       </c>
@@ -24121,7 +24152,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="174" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>357</v>
       </c>
@@ -24228,7 +24259,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="175" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>358</v>
       </c>
@@ -24335,7 +24366,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="176" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>360</v>
       </c>
@@ -24442,7 +24473,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="177" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>361</v>
       </c>
@@ -24549,7 +24580,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="178" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>362</v>
       </c>
@@ -24656,7 +24687,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="179" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>365</v>
       </c>
@@ -24763,7 +24794,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="180" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>367</v>
       </c>
@@ -24870,7 +24901,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="181" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>368</v>
       </c>
@@ -24977,7 +25008,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="182" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>369</v>
       </c>
@@ -25084,7 +25115,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="183" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>372</v>
       </c>
@@ -25191,7 +25222,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="184" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>374</v>
       </c>
@@ -25298,7 +25329,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="185" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>376</v>
       </c>
@@ -25405,7 +25436,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="186" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>379</v>
       </c>
@@ -25512,7 +25543,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="187" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>380</v>
       </c>
@@ -25619,7 +25650,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="188" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>381</v>
       </c>
@@ -25726,7 +25757,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="189" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>385</v>
       </c>
@@ -25833,7 +25864,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="190" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>387</v>
       </c>
@@ -25940,7 +25971,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="191" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>389</v>
       </c>
@@ -26047,7 +26078,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="192" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>391</v>
       </c>
@@ -26154,7 +26185,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="193" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>392</v>
       </c>
@@ -26261,7 +26292,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="194" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>393</v>
       </c>
@@ -26368,7 +26399,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>396</v>
       </c>
@@ -26475,7 +26506,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>397</v>
       </c>
@@ -26582,7 +26613,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>400</v>
       </c>
@@ -26689,7 +26720,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>401</v>
       </c>
@@ -26796,7 +26827,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>402</v>
       </c>
@@ -26903,7 +26934,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="200" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>403</v>
       </c>
@@ -27010,7 +27041,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="201" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>404</v>
       </c>
@@ -27117,7 +27148,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="202" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>406</v>
       </c>
@@ -27224,7 +27255,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="203" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>408</v>
       </c>
@@ -27331,7 +27362,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="204" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>409</v>
       </c>
@@ -27438,7 +27469,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="205" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>410</v>
       </c>
@@ -27545,7 +27576,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="206" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>411</v>
       </c>
@@ -27652,7 +27683,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="207" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>412</v>
       </c>
@@ -27759,7 +27790,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="208" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>413</v>
       </c>
@@ -27866,7 +27897,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="209" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>417</v>
       </c>
@@ -27973,7 +28004,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="210" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>418</v>
       </c>
@@ -28080,7 +28111,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="211" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>419</v>
       </c>
@@ -28187,7 +28218,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="212" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>420</v>
       </c>
@@ -28294,7 +28325,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="213" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>421</v>
       </c>
@@ -28401,7 +28432,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="214" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>423</v>
       </c>
@@ -28508,7 +28539,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="215" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>424</v>
       </c>
@@ -28615,7 +28646,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="216" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>425</v>
       </c>
@@ -28722,7 +28753,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="217" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>426</v>
       </c>
@@ -28829,7 +28860,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="218" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>427</v>
       </c>
@@ -28936,7 +28967,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="219" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>428</v>
       </c>
@@ -29043,7 +29074,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="220" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>430</v>
       </c>
@@ -29150,7 +29181,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="221" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>432</v>
       </c>
@@ -29257,7 +29288,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="222" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>434</v>
       </c>
@@ -29364,7 +29395,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="223" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>435</v>
       </c>
@@ -29471,7 +29502,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="224" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>436</v>
       </c>
@@ -29578,7 +29609,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="225" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>438</v>
       </c>
@@ -29685,7 +29716,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="226" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>439</v>
       </c>
@@ -29792,7 +29823,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="227" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>440</v>
       </c>
@@ -29899,7 +29930,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="228" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>441</v>
       </c>
@@ -30006,7 +30037,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="229" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>442</v>
       </c>
@@ -30113,7 +30144,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="230" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>443</v>
       </c>
@@ -30220,7 +30251,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="231" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>445</v>
       </c>
@@ -30327,7 +30358,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="232" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>446</v>
       </c>
@@ -30434,7 +30465,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="233" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>447</v>
       </c>
@@ -30541,7 +30572,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="234" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>448</v>
       </c>
@@ -30648,7 +30679,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="235" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>449</v>
       </c>
@@ -30755,7 +30786,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="236" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>455</v>
       </c>
@@ -30862,7 +30893,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="237" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>456</v>
       </c>
@@ -30969,7 +31000,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="238" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>458</v>
       </c>
@@ -31076,7 +31107,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="239" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>460</v>
       </c>
@@ -31183,7 +31214,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="240" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>461</v>
       </c>
@@ -31290,7 +31321,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="241" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>462</v>
       </c>
@@ -31397,7 +31428,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="242" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>465</v>
       </c>
@@ -31504,7 +31535,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="243" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>466</v>
       </c>
@@ -31611,7 +31642,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="244" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>468</v>
       </c>
@@ -31718,7 +31749,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="245" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>469</v>
       </c>
@@ -31825,7 +31856,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="246" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>471</v>
       </c>
@@ -31932,7 +31963,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="247" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>472</v>
       </c>
@@ -32039,7 +32070,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="248" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>473</v>
       </c>
@@ -32146,7 +32177,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="249" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>474</v>
       </c>
@@ -32253,7 +32284,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="250" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>475</v>
       </c>
@@ -32360,7 +32391,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="251" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>478</v>
       </c>
@@ -32467,7 +32498,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="252" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>479</v>
       </c>
@@ -32574,7 +32605,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="253" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>481</v>
       </c>
@@ -32681,7 +32712,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="254" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>482</v>
       </c>
@@ -32788,7 +32819,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="255" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>485</v>
       </c>
@@ -32895,7 +32926,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="256" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>487</v>
       </c>
@@ -33002,7 +33033,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="257" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>489</v>
       </c>
@@ -33109,7 +33140,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="258" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>490</v>
       </c>
@@ -33216,7 +33247,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="259" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>492</v>
       </c>
@@ -33311,7 +33342,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="260" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>495</v>
       </c>
@@ -33406,7 +33437,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="261" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>496</v>
       </c>
@@ -33501,7 +33532,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="262" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>498</v>
       </c>
@@ -33596,7 +33627,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="263" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>499</v>
       </c>
@@ -33691,7 +33722,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="264" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>501</v>
       </c>
@@ -33786,7 +33817,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="265" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>503</v>
       </c>
@@ -33881,7 +33912,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="266" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>505</v>
       </c>
@@ -33976,7 +34007,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="267" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>506</v>
       </c>
@@ -34071,7 +34102,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="268" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>507</v>
       </c>
@@ -34166,7 +34197,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="269" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>508</v>
       </c>
@@ -34261,7 +34292,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="270" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>510</v>
       </c>
@@ -34356,7 +34387,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="271" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>511</v>
       </c>
@@ -34451,7 +34482,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="272" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>512</v>
       </c>
@@ -34546,7 +34577,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="273" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>513</v>
       </c>
@@ -34607,7 +34638,7 @@
       <c r="AH273" s="4"/>
       <c r="AI273" s="4"/>
     </row>
-    <row r="274" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>515</v>
       </c>
@@ -34668,7 +34699,7 @@
       <c r="AH274" s="4"/>
       <c r="AI274" s="4"/>
     </row>
-    <row r="275" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>516</v>
       </c>
@@ -34729,7 +34760,7 @@
       <c r="AH275" s="4"/>
       <c r="AI275" s="4"/>
     </row>
-    <row r="276" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>517</v>
       </c>
@@ -34790,7 +34821,7 @@
       <c r="AH276" s="4"/>
       <c r="AI276" s="4"/>
     </row>
-    <row r="277" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>518</v>
       </c>
@@ -34851,7 +34882,7 @@
       <c r="AH277" s="4"/>
       <c r="AI277" s="4"/>
     </row>
-    <row r="278" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>520</v>
       </c>
@@ -34946,7 +34977,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="279" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>522</v>
       </c>
@@ -35041,7 +35072,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="280" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>524</v>
       </c>
@@ -35136,7 +35167,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="281" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>525</v>
       </c>
@@ -35231,7 +35262,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="282" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>180</v>
       </c>
@@ -35326,7 +35357,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="283" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>179</v>
       </c>
@@ -35421,7 +35452,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="284" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>178</v>
       </c>
@@ -35516,7 +35547,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="285" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>175</v>
       </c>
@@ -35611,7 +35642,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="286" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>190</v>
       </c>
@@ -35706,7 +35737,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>526</v>
       </c>
@@ -35801,7 +35832,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="288" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>186</v>
       </c>
@@ -35896,7 +35927,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="289" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>181</v>
       </c>
@@ -35991,7 +36022,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="290" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>184</v>
       </c>
@@ -36086,7 +36117,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="291" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>528</v>
       </c>
@@ -36181,7 +36212,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="292" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>530</v>
       </c>
@@ -36276,7 +36307,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="293" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>531</v>
       </c>
@@ -36371,7 +36402,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="294" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>533</v>
       </c>
@@ -36432,7 +36463,7 @@
       <c r="AH294" s="4"/>
       <c r="AI294" s="4"/>
     </row>
-    <row r="295" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>535</v>
       </c>
@@ -36493,7 +36524,7 @@
       <c r="AH295" s="4"/>
       <c r="AI295" s="4"/>
     </row>
-    <row r="296" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>536</v>
       </c>
@@ -36554,7 +36585,7 @@
       <c r="AH296" s="4"/>
       <c r="AI296" s="4"/>
     </row>
-    <row r="297" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>220</v>
       </c>
@@ -36649,7 +36680,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="298" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>221</v>
       </c>
@@ -36744,7 +36775,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="299" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>217</v>
       </c>
@@ -36839,7 +36870,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="300" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>223</v>
       </c>
@@ -36934,7 +36965,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="301" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>205</v>
       </c>
@@ -37029,7 +37060,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="302" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>202</v>
       </c>
@@ -37124,7 +37155,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="303" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>537</v>
       </c>
@@ -37219,7 +37250,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="304" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>539</v>
       </c>
@@ -37314,7 +37345,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="305" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>541</v>
       </c>
@@ -37409,7 +37440,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="306" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>252</v>
       </c>
@@ -37504,7 +37535,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="307" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>250</v>
       </c>
@@ -37599,7 +37630,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="308" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>248</v>
       </c>
@@ -37694,7 +37725,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="309" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>245</v>
       </c>
@@ -37789,7 +37820,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="310" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>249</v>
       </c>
@@ -37884,7 +37915,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="311" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>257</v>
       </c>
@@ -37979,7 +38010,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="312" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>259</v>
       </c>
@@ -38074,7 +38105,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="313" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>255</v>
       </c>
@@ -38169,7 +38200,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="314" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>253</v>
       </c>
@@ -38264,7 +38295,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="315" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>543</v>
       </c>
@@ -38359,7 +38390,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="316" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>282</v>
       </c>
@@ -38454,7 +38485,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="317" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>281</v>
       </c>
@@ -38549,7 +38580,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="318" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>278</v>
       </c>
@@ -38644,7 +38675,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="319" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>290</v>
       </c>
@@ -38739,7 +38770,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="320" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>286</v>
       </c>
@@ -38834,7 +38865,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="321" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>284</v>
       </c>
@@ -38929,7 +38960,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="322" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>288</v>
       </c>
@@ -39024,7 +39055,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="323" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>544</v>
       </c>
@@ -39119,7 +39150,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="324" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>546</v>
       </c>
@@ -39214,7 +39245,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="325" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>548</v>
       </c>
@@ -39309,7 +39340,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="326" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>550</v>
       </c>
@@ -39404,7 +39435,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="327" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>551</v>
       </c>
@@ -39499,7 +39530,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="328" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>554</v>
       </c>
@@ -39594,7 +39625,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="329" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>555</v>
       </c>
@@ -39689,7 +39720,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="330" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>294</v>
       </c>
@@ -39784,7 +39815,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="331" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>293</v>
       </c>
@@ -39879,7 +39910,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="332" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>291</v>
       </c>
@@ -39974,7 +40005,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="333" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>295</v>
       </c>
@@ -40069,7 +40100,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="334" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>329</v>
       </c>
@@ -40164,7 +40195,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="335" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>327</v>
       </c>
@@ -40259,7 +40290,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="336" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>325</v>
       </c>
@@ -40354,7 +40385,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="337" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>328</v>
       </c>
@@ -40449,7 +40480,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="338" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>318</v>
       </c>
@@ -40544,7 +40575,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="339" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>322</v>
       </c>
@@ -40639,7 +40670,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="340" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>321</v>
       </c>
@@ -40734,7 +40765,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="341" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>324</v>
       </c>
@@ -40829,7 +40860,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="342" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>330</v>
       </c>
@@ -40924,7 +40955,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="343" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>336</v>
       </c>
@@ -41019,7 +41050,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="344" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>332</v>
       </c>
@@ -41114,7 +41145,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="345" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>557</v>
       </c>
@@ -41209,7 +41240,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="346" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>340</v>
       </c>
@@ -41304,7 +41335,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="347" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>344</v>
       </c>
@@ -41399,7 +41430,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="348" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>342</v>
       </c>
@@ -41494,7 +41525,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="349" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>337</v>
       </c>
@@ -41589,7 +41620,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="350" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>559</v>
       </c>
@@ -41696,7 +41727,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="351" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>561</v>
       </c>
@@ -41803,7 +41834,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="352" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>562</v>
       </c>
@@ -41910,7 +41941,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="353" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>564</v>
       </c>
@@ -42005,7 +42036,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="354" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>369</v>
       </c>
@@ -42100,7 +42131,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="355" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>372</v>
       </c>
@@ -42195,7 +42226,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="356" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>565</v>
       </c>
@@ -42290,7 +42321,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="357" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>365</v>
       </c>
@@ -42385,7 +42416,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="358" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>566</v>
       </c>
@@ -42480,7 +42511,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="359" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>362</v>
       </c>
@@ -42575,7 +42606,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="360" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>567</v>
       </c>
@@ -42670,7 +42701,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="361" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>568</v>
       </c>
@@ -42765,7 +42796,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="362" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>376</v>
       </c>
@@ -42860,7 +42891,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="363" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>147</v>
       </c>
@@ -42955,7 +42986,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="364" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>570</v>
       </c>
@@ -43050,7 +43081,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="365" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>150</v>
       </c>
@@ -43145,7 +43176,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="366" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>149</v>
       </c>
@@ -43240,7 +43271,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="367" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>141</v>
       </c>
@@ -43335,7 +43366,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="368" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>145</v>
       </c>
@@ -43430,7 +43461,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="369" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>146</v>
       </c>
@@ -43525,7 +43556,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="370" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>154</v>
       </c>
@@ -43620,7 +43651,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="371" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>571</v>
       </c>
@@ -43715,7 +43746,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="372" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>572</v>
       </c>
@@ -43810,7 +43841,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="373" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>573</v>
       </c>
@@ -43905,7 +43936,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="374" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>575</v>
       </c>
@@ -44000,7 +44031,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="375" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>229</v>
       </c>
@@ -44095,7 +44126,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="376" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
         <v>233</v>
       </c>
@@ -44190,7 +44221,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="377" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
         <v>225</v>
       </c>
@@ -44285,7 +44316,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="378" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>231</v>
       </c>
@@ -44380,7 +44411,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="379" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>312</v>
       </c>
@@ -44475,7 +44506,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="380" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>313</v>
       </c>
@@ -44570,7 +44601,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="381" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>310</v>
       </c>
@@ -44665,7 +44696,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="382" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>308</v>
       </c>
@@ -44760,7 +44791,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="383" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>577</v>
       </c>
@@ -44855,7 +44886,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="384" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>579</v>
       </c>
@@ -44950,7 +44981,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="385" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>581</v>
       </c>
@@ -45045,7 +45076,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="386" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>583</v>
       </c>
@@ -45140,7 +45171,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="387" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>434</v>
       </c>
@@ -45235,7 +45266,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="388" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>432</v>
       </c>
@@ -45330,7 +45361,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="389" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>435</v>
       </c>
@@ -45425,7 +45456,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="390" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
         <v>428</v>
       </c>
@@ -45520,7 +45551,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="391" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
         <v>430</v>
       </c>
@@ -45615,7 +45646,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="392" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>447</v>
       </c>
@@ -45710,7 +45741,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="393" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>445</v>
       </c>
@@ -45805,7 +45836,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="394" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
         <v>443</v>
       </c>
@@ -45900,7 +45931,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="395" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
         <v>585</v>
       </c>
@@ -45995,7 +46026,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="396" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
         <v>587</v>
       </c>
@@ -46090,7 +46121,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="397" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>588</v>
       </c>
@@ -46185,7 +46216,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="398" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>589</v>
       </c>
@@ -46280,7 +46311,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="399" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
         <v>590</v>
       </c>
@@ -46341,7 +46372,7 @@
       <c r="AH399" s="4"/>
       <c r="AI399" s="4"/>
     </row>
-    <row r="400" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>594</v>
       </c>
@@ -46402,7 +46433,7 @@
       <c r="AH400" s="4"/>
       <c r="AI400" s="4"/>
     </row>
-    <row r="401" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>596</v>
       </c>
@@ -46463,7 +46494,7 @@
       <c r="AH401" s="4"/>
       <c r="AI401" s="4"/>
     </row>
-    <row r="402" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
         <v>598</v>
       </c>
@@ -46524,7 +46555,7 @@
       <c r="AH402" s="4"/>
       <c r="AI402" s="4"/>
     </row>
-    <row r="403" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>381</v>
       </c>
@@ -46619,7 +46650,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="404" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
         <v>392</v>
       </c>
@@ -46714,7 +46745,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="405" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
         <v>391</v>
       </c>
@@ -46809,7 +46840,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="406" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>389</v>
       </c>
@@ -46904,7 +46935,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="407" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>385</v>
       </c>
@@ -46999,7 +47030,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="408" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>387</v>
       </c>
@@ -47094,7 +47125,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="409" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
         <v>196</v>
       </c>
@@ -47189,7 +47220,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="410" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>191</v>
       </c>
@@ -47284,7 +47315,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>194</v>
       </c>
@@ -47379,7 +47410,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="412" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
         <v>600</v>
       </c>
@@ -47474,7 +47505,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="413" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
         <v>602</v>
       </c>
@@ -47569,7 +47600,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="414" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>603</v>
       </c>
@@ -47664,7 +47695,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="415" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>604</v>
       </c>
@@ -47759,7 +47790,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="416" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
         <v>605</v>
       </c>
@@ -47854,7 +47885,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="417" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>607</v>
       </c>
@@ -47949,7 +47980,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="418" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>608</v>
       </c>
@@ -48044,7 +48075,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="419" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>609</v>
       </c>
@@ -48139,7 +48170,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="420" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
         <v>361</v>
       </c>
@@ -48234,7 +48265,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="421" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>360</v>
       </c>
@@ -48329,7 +48360,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="422" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>358</v>
       </c>
@@ -48424,7 +48455,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="423" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
         <v>357</v>
       </c>
@@ -48519,7 +48550,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="424" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>356</v>
       </c>
@@ -48614,7 +48645,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="425" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>355</v>
       </c>
@@ -48709,7 +48740,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="426" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>352</v>
       </c>
@@ -48804,7 +48835,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="427" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>610</v>
       </c>
@@ -48899,7 +48930,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="428" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
         <v>613</v>
       </c>
@@ -48994,7 +49025,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="429" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>614</v>
       </c>
@@ -49089,7 +49120,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="430" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>616</v>
       </c>
@@ -49184,7 +49215,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="431" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>406</v>
       </c>
@@ -49279,7 +49310,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="432" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
         <v>412</v>
       </c>
@@ -49374,7 +49405,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="433" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>411</v>
       </c>
@@ -49469,7 +49500,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="434" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>409</v>
       </c>
@@ -49564,7 +49595,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="435" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>617</v>
       </c>
@@ -49659,7 +49690,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="436" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>410</v>
       </c>
@@ -49754,7 +49785,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="437" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>396</v>
       </c>
@@ -49849,7 +49880,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="438" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>393</v>
       </c>
@@ -49944,7 +49975,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="439" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>436</v>
       </c>
@@ -50039,7 +50070,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="440" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
         <v>442</v>
       </c>
@@ -50134,7 +50165,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="441" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>441</v>
       </c>
@@ -50229,7 +50260,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="442" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>439</v>
       </c>
@@ -50324,7 +50355,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="443" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>440</v>
       </c>
@@ -50419,7 +50450,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="444" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>490</v>
       </c>
@@ -50514,7 +50545,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="445" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>489</v>
       </c>
@@ -50609,7 +50640,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="446" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
         <v>487</v>
       </c>
@@ -50704,7 +50735,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="447" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>485</v>
       </c>
@@ -50799,7 +50830,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="448" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>482</v>
       </c>
@@ -50894,7 +50925,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="449" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>461</v>
       </c>
@@ -50989,7 +51020,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="450" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
         <v>460</v>
       </c>
@@ -51084,7 +51115,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="451" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>458</v>
       </c>
@@ -51179,7 +51210,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="452" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>455</v>
       </c>
@@ -51274,7 +51305,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="453" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>456</v>
       </c>
@@ -51369,7 +51400,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="454" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>449</v>
       </c>
@@ -51464,7 +51495,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="455" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>620</v>
       </c>
@@ -51525,7 +51556,7 @@
       <c r="AH455" s="4"/>
       <c r="AI455" s="4"/>
     </row>
-    <row r="456" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>623</v>
       </c>
@@ -51586,7 +51617,7 @@
       <c r="AH456" s="4"/>
       <c r="AI456" s="4"/>
     </row>
-    <row r="457" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>625</v>
       </c>
@@ -51647,7 +51678,7 @@
       <c r="AH457" s="4"/>
       <c r="AI457" s="4"/>
     </row>
-    <row r="458" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>627</v>
       </c>
@@ -51708,7 +51739,7 @@
       <c r="AH458" s="4"/>
       <c r="AI458" s="4"/>
     </row>
-    <row r="459" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
         <v>474</v>
       </c>
@@ -51803,7 +51834,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="460" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>473</v>
       </c>
@@ -51898,7 +51929,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="461" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>469</v>
       </c>
@@ -51993,7 +52024,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="462" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>471</v>
       </c>
@@ -52088,7 +52119,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="463" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
         <v>472</v>
       </c>
@@ -52183,7 +52214,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="464" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>628</v>
       </c>
@@ -52278,7 +52309,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="465" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>475</v>
       </c>
@@ -52373,7 +52404,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="466" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>630</v>
       </c>
@@ -52468,7 +52499,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="467" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>631</v>
       </c>
@@ -52563,7 +52594,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="468" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
         <v>632</v>
       </c>
@@ -52658,7 +52689,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="469" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
         <v>633</v>
       </c>
@@ -52753,7 +52784,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="470" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>635</v>
       </c>
@@ -52848,7 +52879,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="471" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
         <v>637</v>
       </c>
@@ -52943,7 +52974,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="472" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
         <v>639</v>
       </c>
@@ -53038,7 +53069,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="473" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
         <v>641</v>
       </c>
@@ -53099,7 +53130,7 @@
       <c r="AH473" s="4"/>
       <c r="AI473" s="4"/>
     </row>
-    <row r="474" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
         <v>644</v>
       </c>
@@ -53160,7 +53191,7 @@
       <c r="AH474" s="4"/>
       <c r="AI474" s="4"/>
     </row>
-    <row r="475" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
         <v>645</v>
       </c>
@@ -53221,7 +53252,7 @@
       <c r="AH475" s="4"/>
       <c r="AI475" s="4"/>
     </row>
-    <row r="476" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
         <v>647</v>
       </c>
@@ -53282,7 +53313,7 @@
       <c r="AH476" s="4"/>
       <c r="AI476" s="4"/>
     </row>
-    <row r="477" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
         <v>649</v>
       </c>
@@ -53343,7 +53374,7 @@
       <c r="AH477" s="4"/>
       <c r="AI477" s="4"/>
     </row>
-    <row r="478" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
         <v>650</v>
       </c>
@@ -53404,7 +53435,7 @@
       <c r="AH478" s="4"/>
       <c r="AI478" s="4"/>
     </row>
-    <row r="479" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
         <v>654</v>
       </c>
@@ -53465,7 +53496,7 @@
       <c r="AH479" s="4"/>
       <c r="AI479" s="4"/>
     </row>
-    <row r="480" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
         <v>657</v>
       </c>
@@ -53526,7 +53557,7 @@
       <c r="AH480" s="4"/>
       <c r="AI480" s="4"/>
     </row>
-    <row r="481" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
         <v>659</v>
       </c>
@@ -53587,7 +53618,7 @@
       <c r="AH481" s="4"/>
       <c r="AI481" s="4"/>
     </row>
-    <row r="482" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
         <v>661</v>
       </c>
@@ -53648,7 +53679,7 @@
       <c r="AH482" s="4"/>
       <c r="AI482" s="4"/>
     </row>
-    <row r="483" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
         <v>662</v>
       </c>
@@ -53709,7 +53740,7 @@
       <c r="AH483" s="4"/>
       <c r="AI483" s="4"/>
     </row>
-    <row r="484" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
         <v>77</v>
       </c>
@@ -53804,7 +53835,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="485" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
         <v>75</v>
       </c>
@@ -53899,7 +53930,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="486" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
         <v>73</v>
       </c>
@@ -53994,7 +54025,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="487" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
         <v>69</v>
       </c>
@@ -54089,7 +54120,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="488" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
         <v>64</v>
       </c>
@@ -54184,7 +54215,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="489" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
         <v>71</v>
       </c>
@@ -54279,7 +54310,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="490" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
         <v>67</v>
       </c>
@@ -54374,7 +54405,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="491" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
         <v>663</v>
       </c>
@@ -54435,7 +54466,7 @@
       <c r="AH491" s="4"/>
       <c r="AI491" s="4"/>
     </row>
-    <row r="492" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
         <v>665</v>
       </c>
@@ -54496,7 +54527,7 @@
       <c r="AH492" s="4"/>
       <c r="AI492" s="4"/>
     </row>
-    <row r="493" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
         <v>667</v>
       </c>
@@ -54557,7 +54588,7 @@
       <c r="AH493" s="4"/>
       <c r="AI493" s="4"/>
     </row>
-    <row r="494" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
         <v>668</v>
       </c>
@@ -54618,7 +54649,7 @@
       <c r="AH494" s="4"/>
       <c r="AI494" s="4"/>
     </row>
-    <row r="495" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
         <v>669</v>
       </c>
@@ -54679,7 +54710,7 @@
       <c r="AH495" s="4"/>
       <c r="AI495" s="4"/>
     </row>
-    <row r="496" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
         <v>670</v>
       </c>
@@ -54740,7 +54771,7 @@
       <c r="AH496" s="4"/>
       <c r="AI496" s="4"/>
     </row>
-    <row r="497" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
         <v>671</v>
       </c>
@@ -54801,7 +54832,7 @@
       <c r="AH497" s="4"/>
       <c r="AI497" s="4"/>
     </row>
-    <row r="498" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
         <v>673</v>
       </c>
@@ -54862,7 +54893,7 @@
       <c r="AH498" s="4"/>
       <c r="AI498" s="4"/>
     </row>
-    <row r="499" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
         <v>674</v>
       </c>
@@ -54923,7 +54954,7 @@
       <c r="AH499" s="4"/>
       <c r="AI499" s="4"/>
     </row>
-    <row r="500" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
         <v>675</v>
       </c>
@@ -54984,7 +55015,7 @@
       <c r="AH500" s="4"/>
       <c r="AI500" s="4"/>
     </row>
-    <row r="501" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
         <v>270</v>
       </c>
@@ -55079,7 +55110,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="502" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
         <v>266</v>
       </c>
@@ -55174,7 +55205,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="503" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
         <v>268</v>
       </c>
@@ -55269,7 +55300,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="504" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
         <v>262</v>
       </c>
@@ -55364,7 +55395,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="505" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
         <v>264</v>
       </c>
@@ -55459,7 +55490,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="506" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
         <v>676</v>
       </c>
@@ -55554,7 +55585,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="507" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
         <v>93</v>
       </c>
@@ -55649,7 +55680,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="508" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
         <v>89</v>
       </c>
@@ -55744,7 +55775,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="509" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
         <v>677</v>
       </c>
@@ -55839,7 +55870,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="510" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
         <v>679</v>
       </c>
@@ -55934,7 +55965,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="511" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
         <v>680</v>
       </c>
@@ -56029,7 +56060,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="512" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
         <v>681</v>
       </c>
@@ -56124,7 +56155,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="513" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
         <v>683</v>
       </c>
@@ -56219,7 +56250,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="514" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
         <v>685</v>
       </c>
@@ -56314,7 +56345,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="515" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
         <v>687</v>
       </c>
@@ -56409,7 +56440,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="516" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
         <v>688</v>
       </c>
@@ -56504,7 +56535,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="517" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
         <v>689</v>
       </c>
@@ -56599,7 +56630,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="518" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
         <v>691</v>
       </c>
@@ -56694,7 +56725,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="519" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
         <v>692</v>
       </c>
@@ -56789,7 +56820,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="520" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
         <v>694</v>
       </c>
@@ -56884,7 +56915,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="521" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
         <v>695</v>
       </c>
@@ -56979,7 +57010,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="522" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
         <v>697</v>
       </c>
@@ -57040,7 +57071,7 @@
       <c r="AH522" s="4"/>
       <c r="AI522" s="4"/>
     </row>
-    <row r="523" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
         <v>703</v>
       </c>
@@ -57101,7 +57132,7 @@
       <c r="AH523" s="4"/>
       <c r="AI523" s="4"/>
     </row>
-    <row r="524" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
         <v>705</v>
       </c>
@@ -57162,7 +57193,7 @@
       <c r="AH524" s="4"/>
       <c r="AI524" s="4"/>
     </row>
-    <row r="525" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
         <v>710</v>
       </c>
@@ -57223,7 +57254,7 @@
       <c r="AH525" s="4"/>
       <c r="AI525" s="4"/>
     </row>
-    <row r="526" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
         <v>711</v>
       </c>
@@ -57284,7 +57315,7 @@
       <c r="AH526" s="4"/>
       <c r="AI526" s="4"/>
     </row>
-    <row r="527" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
         <v>712</v>
       </c>
@@ -57345,7 +57376,7 @@
       <c r="AH527" s="4"/>
       <c r="AI527" s="4"/>
     </row>
-    <row r="528" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
         <v>715</v>
       </c>
@@ -57406,7 +57437,7 @@
       <c r="AH528" s="4"/>
       <c r="AI528" s="4"/>
     </row>
-    <row r="529" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
         <v>716</v>
       </c>
@@ -57467,7 +57498,7 @@
       <c r="AH529" s="4"/>
       <c r="AI529" s="4"/>
     </row>
-    <row r="530" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
         <v>719</v>
       </c>
@@ -57528,7 +57559,7 @@
       <c r="AH530" s="4"/>
       <c r="AI530" s="4"/>
     </row>
-    <row r="531" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
         <v>720</v>
       </c>
@@ -57589,7 +57620,7 @@
       <c r="AH531" s="4"/>
       <c r="AI531" s="4"/>
     </row>
-    <row r="532" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
         <v>722</v>
       </c>
@@ -57650,7 +57681,7 @@
       <c r="AH532" s="4"/>
       <c r="AI532" s="4"/>
     </row>
-    <row r="533" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
         <v>723</v>
       </c>
@@ -57711,7 +57742,7 @@
       <c r="AH533" s="4"/>
       <c r="AI533" s="4"/>
     </row>
-    <row r="534" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
         <v>726</v>
       </c>
@@ -57772,7 +57803,7 @@
       <c r="AH534" s="4"/>
       <c r="AI534" s="4"/>
     </row>
-    <row r="535" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
         <v>727</v>
       </c>
@@ -57833,7 +57864,7 @@
       <c r="AH535" s="4"/>
       <c r="AI535" s="4"/>
     </row>
-    <row r="536" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
         <v>728</v>
       </c>
@@ -57894,7 +57925,7 @@
       <c r="AH536" s="4"/>
       <c r="AI536" s="4"/>
     </row>
-    <row r="537" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
         <v>1541</v>
       </c>
@@ -57955,7 +57986,7 @@
       <c r="AH537" s="4"/>
       <c r="AI537" s="4"/>
     </row>
-    <row r="538" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
         <v>734</v>
       </c>
@@ -58016,7 +58047,7 @@
       <c r="AH538" s="4"/>
       <c r="AI538" s="4"/>
     </row>
-    <row r="539" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
         <v>735</v>
       </c>
@@ -58077,7 +58108,7 @@
       <c r="AH539" s="4"/>
       <c r="AI539" s="4"/>
     </row>
-    <row r="540" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
         <v>739</v>
       </c>
@@ -58138,7 +58169,7 @@
       <c r="AH540" s="4"/>
       <c r="AI540" s="4"/>
     </row>
-    <row r="541" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
         <v>742</v>
       </c>
@@ -58199,7 +58230,7 @@
       <c r="AH541" s="4"/>
       <c r="AI541" s="4"/>
     </row>
-    <row r="542" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
         <v>744</v>
       </c>
@@ -58260,7 +58291,7 @@
       <c r="AH542" s="4"/>
       <c r="AI542" s="4"/>
     </row>
-    <row r="543" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
         <v>746</v>
       </c>
@@ -58321,7 +58352,7 @@
       <c r="AH543" s="4"/>
       <c r="AI543" s="4"/>
     </row>
-    <row r="544" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
         <v>748</v>
       </c>
@@ -58382,7 +58413,7 @@
       <c r="AH544" s="4"/>
       <c r="AI544" s="4"/>
     </row>
-    <row r="545" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
         <v>749</v>
       </c>
@@ -58443,7 +58474,7 @@
       <c r="AH545" s="4"/>
       <c r="AI545" s="4"/>
     </row>
-    <row r="546" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
         <v>750</v>
       </c>
@@ -58504,7 +58535,7 @@
       <c r="AH546" s="4"/>
       <c r="AI546" s="4"/>
     </row>
-    <row r="547" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
         <v>753</v>
       </c>
@@ -58565,7 +58596,7 @@
       <c r="AH547" s="4"/>
       <c r="AI547" s="4"/>
     </row>
-    <row r="548" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
         <v>754</v>
       </c>
@@ -58626,7 +58657,7 @@
       <c r="AH548" s="4"/>
       <c r="AI548" s="4"/>
     </row>
-    <row r="549" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
         <v>756</v>
       </c>
@@ -58687,7 +58718,7 @@
       <c r="AH549" s="4"/>
       <c r="AI549" s="4"/>
     </row>
-    <row r="550" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
         <v>758</v>
       </c>
@@ -58748,7 +58779,7 @@
       <c r="AH550" s="4"/>
       <c r="AI550" s="4"/>
     </row>
-    <row r="551" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
         <v>759</v>
       </c>
@@ -58809,7 +58840,7 @@
       <c r="AH551" s="4"/>
       <c r="AI551" s="4"/>
     </row>
-    <row r="552" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
         <v>761</v>
       </c>
@@ -58870,7 +58901,7 @@
       <c r="AH552" s="4"/>
       <c r="AI552" s="4"/>
     </row>
-    <row r="553" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
         <v>763</v>
       </c>
@@ -58931,7 +58962,7 @@
       <c r="AH553" s="4"/>
       <c r="AI553" s="4"/>
     </row>
-    <row r="554" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
         <v>766</v>
       </c>
@@ -58992,7 +59023,7 @@
       <c r="AH554" s="4"/>
       <c r="AI554" s="4"/>
     </row>
-    <row r="555" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
         <v>768</v>
       </c>
@@ -59053,7 +59084,7 @@
       <c r="AH555" s="4"/>
       <c r="AI555" s="4"/>
     </row>
-    <row r="556" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
         <v>769</v>
       </c>
@@ -59114,7 +59145,7 @@
       <c r="AH556" s="4"/>
       <c r="AI556" s="4"/>
     </row>
-    <row r="557" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
         <v>772</v>
       </c>
@@ -59175,7 +59206,7 @@
       <c r="AH557" s="4"/>
       <c r="AI557" s="4"/>
     </row>
-    <row r="558" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
         <v>773</v>
       </c>
@@ -59236,7 +59267,7 @@
       <c r="AH558" s="4"/>
       <c r="AI558" s="4"/>
     </row>
-    <row r="559" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
         <v>776</v>
       </c>
@@ -59297,7 +59328,7 @@
       <c r="AH559" s="4"/>
       <c r="AI559" s="4"/>
     </row>
-    <row r="560" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
         <v>777</v>
       </c>
@@ -59358,7 +59389,7 @@
       <c r="AH560" s="4"/>
       <c r="AI560" s="4"/>
     </row>
-    <row r="561" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
         <v>779</v>
       </c>
@@ -59419,7 +59450,7 @@
       <c r="AH561" s="4"/>
       <c r="AI561" s="4"/>
     </row>
-    <row r="562" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
         <v>782</v>
       </c>
@@ -59480,7 +59511,7 @@
       <c r="AH562" s="4"/>
       <c r="AI562" s="4"/>
     </row>
-    <row r="563" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
         <v>783</v>
       </c>
@@ -59541,7 +59572,7 @@
       <c r="AH563" s="4"/>
       <c r="AI563" s="4"/>
     </row>
-    <row r="564" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
         <v>786</v>
       </c>
@@ -59602,7 +59633,7 @@
       <c r="AH564" s="4"/>
       <c r="AI564" s="4"/>
     </row>
-    <row r="565" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
         <v>787</v>
       </c>
@@ -59663,7 +59694,7 @@
       <c r="AH565" s="4"/>
       <c r="AI565" s="4"/>
     </row>
-    <row r="566" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
         <v>791</v>
       </c>
@@ -59724,7 +59755,7 @@
       <c r="AH566" s="4"/>
       <c r="AI566" s="4"/>
     </row>
-    <row r="567" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
         <v>794</v>
       </c>
@@ -59785,7 +59816,7 @@
       <c r="AH567" s="4"/>
       <c r="AI567" s="4"/>
     </row>
-    <row r="568" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
         <v>800</v>
       </c>
@@ -59846,7 +59877,7 @@
       <c r="AH568" s="4"/>
       <c r="AI568" s="4"/>
     </row>
-    <row r="569" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
         <v>801</v>
       </c>
@@ -59907,7 +59938,7 @@
       <c r="AH569" s="4"/>
       <c r="AI569" s="4"/>
     </row>
-    <row r="570" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
         <v>803</v>
       </c>
@@ -59968,7 +59999,7 @@
       <c r="AH570" s="4"/>
       <c r="AI570" s="4"/>
     </row>
-    <row r="571" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
         <v>805</v>
       </c>
@@ -60029,7 +60060,7 @@
       <c r="AH571" s="4"/>
       <c r="AI571" s="4"/>
     </row>
-    <row r="572" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
         <v>807</v>
       </c>
@@ -60090,7 +60121,7 @@
       <c r="AH572" s="4"/>
       <c r="AI572" s="4"/>
     </row>
-    <row r="573" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
         <v>810</v>
       </c>
@@ -60151,7 +60182,7 @@
       <c r="AH573" s="4"/>
       <c r="AI573" s="4"/>
     </row>
-    <row r="574" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
         <v>811</v>
       </c>
@@ -60212,7 +60243,7 @@
       <c r="AH574" s="4"/>
       <c r="AI574" s="4"/>
     </row>
-    <row r="575" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
         <v>812</v>
       </c>
@@ -60273,7 +60304,7 @@
       <c r="AH575" s="4"/>
       <c r="AI575" s="4"/>
     </row>
-    <row r="576" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
         <v>815</v>
       </c>
@@ -60334,7 +60365,7 @@
       <c r="AH576" s="4"/>
       <c r="AI576" s="4"/>
     </row>
-    <row r="577" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
         <v>816</v>
       </c>
@@ -60395,7 +60426,7 @@
       <c r="AH577" s="4"/>
       <c r="AI577" s="4"/>
     </row>
-    <row r="578" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
         <v>817</v>
       </c>
@@ -60456,7 +60487,7 @@
       <c r="AH578" s="4"/>
       <c r="AI578" s="4"/>
     </row>
-    <row r="579" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
         <v>820</v>
       </c>
@@ -60517,7 +60548,7 @@
       <c r="AH579" s="4"/>
       <c r="AI579" s="4"/>
     </row>
-    <row r="580" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
         <v>821</v>
       </c>
@@ -60578,7 +60609,7 @@
       <c r="AH580" s="4"/>
       <c r="AI580" s="4"/>
     </row>
-    <row r="581" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
         <v>822</v>
       </c>
@@ -60639,7 +60670,7 @@
       <c r="AH581" s="4"/>
       <c r="AI581" s="4"/>
     </row>
-    <row r="582" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
         <v>825</v>
       </c>
@@ -60700,7 +60731,7 @@
       <c r="AH582" s="4"/>
       <c r="AI582" s="4"/>
     </row>
-    <row r="583" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
         <v>826</v>
       </c>
@@ -60761,7 +60792,7 @@
       <c r="AH583" s="4"/>
       <c r="AI583" s="4"/>
     </row>
-    <row r="584" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
         <v>827</v>
       </c>
@@ -60822,7 +60853,7 @@
       <c r="AH584" s="4"/>
       <c r="AI584" s="4"/>
     </row>
-    <row r="585" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
         <v>831</v>
       </c>
@@ -60883,7 +60914,7 @@
       <c r="AH585" s="4"/>
       <c r="AI585" s="4"/>
     </row>
-    <row r="586" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
         <v>832</v>
       </c>
@@ -60944,7 +60975,7 @@
       <c r="AH586" s="4"/>
       <c r="AI586" s="4"/>
     </row>
-    <row r="587" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
         <v>833</v>
       </c>
@@ -61005,7 +61036,7 @@
       <c r="AH587" s="4"/>
       <c r="AI587" s="4"/>
     </row>
-    <row r="588" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
         <v>836</v>
       </c>
@@ -61066,7 +61097,7 @@
       <c r="AH588" s="4"/>
       <c r="AI588" s="4"/>
     </row>
-    <row r="589" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
         <v>837</v>
       </c>
@@ -61127,7 +61158,7 @@
       <c r="AH589" s="4"/>
       <c r="AI589" s="4"/>
     </row>
-    <row r="590" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
         <v>838</v>
       </c>
@@ -61188,7 +61219,7 @@
       <c r="AH590" s="4"/>
       <c r="AI590" s="4"/>
     </row>
-    <row r="591" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
         <v>841</v>
       </c>
@@ -61249,7 +61280,7 @@
       <c r="AH591" s="4"/>
       <c r="AI591" s="4"/>
     </row>
-    <row r="592" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
         <v>842</v>
       </c>
@@ -61310,7 +61341,7 @@
       <c r="AH592" s="4"/>
       <c r="AI592" s="4"/>
     </row>
-    <row r="593" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
         <v>843</v>
       </c>
@@ -61371,7 +61402,7 @@
       <c r="AH593" s="4"/>
       <c r="AI593" s="4"/>
     </row>
-    <row r="594" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
         <v>846</v>
       </c>
@@ -61432,7 +61463,7 @@
       <c r="AH594" s="4"/>
       <c r="AI594" s="4"/>
     </row>
-    <row r="595" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
         <v>847</v>
       </c>
@@ -61493,7 +61524,7 @@
       <c r="AH595" s="4"/>
       <c r="AI595" s="4"/>
     </row>
-    <row r="596" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
         <v>848</v>
       </c>
@@ -61554,7 +61585,7 @@
       <c r="AH596" s="4"/>
       <c r="AI596" s="4"/>
     </row>
-    <row r="597" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
         <v>849</v>
       </c>
@@ -61615,7 +61646,7 @@
       <c r="AH597" s="4"/>
       <c r="AI597" s="4"/>
     </row>
-    <row r="598" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
         <v>853</v>
       </c>
@@ -61676,7 +61707,7 @@
       <c r="AH598" s="4"/>
       <c r="AI598" s="4"/>
     </row>
-    <row r="599" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
         <v>854</v>
       </c>
@@ -61737,7 +61768,7 @@
       <c r="AH599" s="4"/>
       <c r="AI599" s="4"/>
     </row>
-    <row r="600" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
         <v>855</v>
       </c>
@@ -61798,7 +61829,7 @@
       <c r="AH600" s="4"/>
       <c r="AI600" s="4"/>
     </row>
-    <row r="601" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
         <v>856</v>
       </c>
@@ -61859,7 +61890,7 @@
       <c r="AH601" s="4"/>
       <c r="AI601" s="4"/>
     </row>
-    <row r="602" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
         <v>857</v>
       </c>
@@ -61920,7 +61951,7 @@
       <c r="AH602" s="4"/>
       <c r="AI602" s="4"/>
     </row>
-    <row r="603" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
         <v>860</v>
       </c>
@@ -61981,7 +62012,7 @@
       <c r="AH603" s="4"/>
       <c r="AI603" s="4"/>
     </row>
-    <row r="604" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
         <v>861</v>
       </c>
@@ -62042,7 +62073,7 @@
       <c r="AH604" s="4"/>
       <c r="AI604" s="4"/>
     </row>
-    <row r="605" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
         <v>862</v>
       </c>
@@ -62103,7 +62134,7 @@
       <c r="AH605" s="4"/>
       <c r="AI605" s="4"/>
     </row>
-    <row r="606" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
         <v>865</v>
       </c>
@@ -62164,7 +62195,7 @@
       <c r="AH606" s="4"/>
       <c r="AI606" s="4"/>
     </row>
-    <row r="607" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
         <v>866</v>
       </c>
@@ -62225,7 +62256,7 @@
       <c r="AH607" s="4"/>
       <c r="AI607" s="4"/>
     </row>
-    <row r="608" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
         <v>867</v>
       </c>
@@ -62286,7 +62317,7 @@
       <c r="AH608" s="4"/>
       <c r="AI608" s="4"/>
     </row>
-    <row r="609" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
         <v>870</v>
       </c>
@@ -62347,7 +62378,7 @@
       <c r="AH609" s="4"/>
       <c r="AI609" s="4"/>
     </row>
-    <row r="610" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
         <v>871</v>
       </c>
@@ -62408,7 +62439,7 @@
       <c r="AH610" s="4"/>
       <c r="AI610" s="4"/>
     </row>
-    <row r="611" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
         <v>872</v>
       </c>
@@ -62469,7 +62500,7 @@
       <c r="AH611" s="4"/>
       <c r="AI611" s="4"/>
     </row>
-    <row r="612" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
         <v>875</v>
       </c>
@@ -62530,7 +62561,7 @@
       <c r="AH612" s="4"/>
       <c r="AI612" s="4"/>
     </row>
-    <row r="613" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
         <v>876</v>
       </c>
@@ -62591,7 +62622,7 @@
       <c r="AH613" s="4"/>
       <c r="AI613" s="4"/>
     </row>
-    <row r="614" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
         <v>877</v>
       </c>
@@ -62652,7 +62683,7 @@
       <c r="AH614" s="4"/>
       <c r="AI614" s="4"/>
     </row>
-    <row r="615" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
         <v>880</v>
       </c>
@@ -62713,7 +62744,7 @@
       <c r="AH615" s="4"/>
       <c r="AI615" s="4"/>
     </row>
-    <row r="616" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
         <v>881</v>
       </c>
@@ -62774,7 +62805,7 @@
       <c r="AH616" s="4"/>
       <c r="AI616" s="4"/>
     </row>
-    <row r="617" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
         <v>882</v>
       </c>
@@ -62835,7 +62866,7 @@
       <c r="AH617" s="4"/>
       <c r="AI617" s="4"/>
     </row>
-    <row r="618" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
         <v>885</v>
       </c>
@@ -62896,7 +62927,7 @@
       <c r="AH618" s="4"/>
       <c r="AI618" s="4"/>
     </row>
-    <row r="619" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
         <v>886</v>
       </c>
@@ -62957,7 +62988,7 @@
       <c r="AH619" s="4"/>
       <c r="AI619" s="4"/>
     </row>
-    <row r="620" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
         <v>887</v>
       </c>
@@ -63018,7 +63049,7 @@
       <c r="AH620" s="4"/>
       <c r="AI620" s="4"/>
     </row>
-    <row r="621" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
         <v>890</v>
       </c>
@@ -63079,7 +63110,7 @@
       <c r="AH621" s="4"/>
       <c r="AI621" s="4"/>
     </row>
-    <row r="622" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
         <v>891</v>
       </c>
@@ -63140,7 +63171,7 @@
       <c r="AH622" s="4"/>
       <c r="AI622" s="4"/>
     </row>
-    <row r="623" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
         <v>892</v>
       </c>
@@ -63201,7 +63232,7 @@
       <c r="AH623" s="4"/>
       <c r="AI623" s="4"/>
     </row>
-    <row r="624" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
         <v>895</v>
       </c>
@@ -63262,7 +63293,7 @@
       <c r="AH624" s="4"/>
       <c r="AI624" s="4"/>
     </row>
-    <row r="625" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
         <v>896</v>
       </c>
@@ -63323,7 +63354,7 @@
       <c r="AH625" s="4"/>
       <c r="AI625" s="4"/>
     </row>
-    <row r="626" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
         <v>897</v>
       </c>
@@ -63384,7 +63415,7 @@
       <c r="AH626" s="4"/>
       <c r="AI626" s="4"/>
     </row>
-    <row r="627" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
         <v>898</v>
       </c>
@@ -63445,7 +63476,7 @@
       <c r="AH627" s="4"/>
       <c r="AI627" s="4"/>
     </row>
-    <row r="628" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
         <v>901</v>
       </c>
@@ -63506,7 +63537,7 @@
       <c r="AH628" s="4"/>
       <c r="AI628" s="4"/>
     </row>
-    <row r="629" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
         <v>903</v>
       </c>
@@ -63567,7 +63598,7 @@
       <c r="AH629" s="4"/>
       <c r="AI629" s="4"/>
     </row>
-    <row r="630" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
         <v>905</v>
       </c>
@@ -63628,7 +63659,7 @@
       <c r="AH630" s="4"/>
       <c r="AI630" s="4"/>
     </row>
-    <row r="631" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
         <v>907</v>
       </c>
@@ -63689,7 +63720,7 @@
       <c r="AH631" s="4"/>
       <c r="AI631" s="4"/>
     </row>
-    <row r="632" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
         <v>911</v>
       </c>
@@ -63750,7 +63781,7 @@
       <c r="AH632" s="4"/>
       <c r="AI632" s="4"/>
     </row>
-    <row r="633" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
         <v>913</v>
       </c>
@@ -63811,7 +63842,7 @@
       <c r="AH633" s="4"/>
       <c r="AI633" s="4"/>
     </row>
-    <row r="634" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
         <v>915</v>
       </c>
@@ -63872,7 +63903,7 @@
       <c r="AH634" s="4"/>
       <c r="AI634" s="4"/>
     </row>
-    <row r="635" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
         <v>917</v>
       </c>
@@ -63933,7 +63964,7 @@
       <c r="AH635" s="4"/>
       <c r="AI635" s="4"/>
     </row>
-    <row r="636" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
         <v>919</v>
       </c>
@@ -63994,7 +64025,7 @@
       <c r="AH636" s="4"/>
       <c r="AI636" s="4"/>
     </row>
-    <row r="637" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
         <v>922</v>
       </c>
@@ -64055,7 +64086,7 @@
       <c r="AH637" s="4"/>
       <c r="AI637" s="4"/>
     </row>
-    <row r="638" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
         <v>923</v>
       </c>
@@ -64116,7 +64147,7 @@
       <c r="AH638" s="4"/>
       <c r="AI638" s="4"/>
     </row>
-    <row r="639" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
         <v>924</v>
       </c>
@@ -64177,7 +64208,7 @@
       <c r="AH639" s="4"/>
       <c r="AI639" s="4"/>
     </row>
-    <row r="640" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
         <v>925</v>
       </c>
@@ -64238,7 +64269,7 @@
       <c r="AH640" s="4"/>
       <c r="AI640" s="4"/>
     </row>
-    <row r="641" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
         <v>926</v>
       </c>
@@ -64299,7 +64330,7 @@
       <c r="AH641" s="4"/>
       <c r="AI641" s="4"/>
     </row>
-    <row r="642" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
         <v>929</v>
       </c>
@@ -64360,7 +64391,7 @@
       <c r="AH642" s="4"/>
       <c r="AI642" s="4"/>
     </row>
-    <row r="643" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
         <v>933</v>
       </c>
@@ -64421,7 +64452,7 @@
       <c r="AH643" s="4"/>
       <c r="AI643" s="4"/>
     </row>
-    <row r="644" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
         <v>934</v>
       </c>
@@ -64482,7 +64513,7 @@
       <c r="AH644" s="4"/>
       <c r="AI644" s="4"/>
     </row>
-    <row r="645" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
         <v>937</v>
       </c>
@@ -64543,7 +64574,7 @@
       <c r="AH645" s="4"/>
       <c r="AI645" s="4"/>
     </row>
-    <row r="646" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
         <v>938</v>
       </c>
@@ -64604,7 +64635,7 @@
       <c r="AH646" s="4"/>
       <c r="AI646" s="4"/>
     </row>
-    <row r="647" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
         <v>941</v>
       </c>
@@ -64665,7 +64696,7 @@
       <c r="AH647" s="4"/>
       <c r="AI647" s="4"/>
     </row>
-    <row r="648" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
         <v>944</v>
       </c>
@@ -64726,7 +64757,7 @@
       <c r="AH648" s="4"/>
       <c r="AI648" s="4"/>
     </row>
-    <row r="649" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
         <v>946</v>
       </c>
@@ -64787,7 +64818,7 @@
       <c r="AH649" s="4"/>
       <c r="AI649" s="4"/>
     </row>
-    <row r="650" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
         <v>949</v>
       </c>
@@ -64848,7 +64879,7 @@
       <c r="AH650" s="4"/>
       <c r="AI650" s="4"/>
     </row>
-    <row r="651" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
         <v>952</v>
       </c>
@@ -64909,7 +64940,7 @@
       <c r="AH651" s="4"/>
       <c r="AI651" s="4"/>
     </row>
-    <row r="652" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
         <v>955</v>
       </c>
@@ -64970,7 +65001,7 @@
       <c r="AH652" s="4"/>
       <c r="AI652" s="4"/>
     </row>
-    <row r="653" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
         <v>956</v>
       </c>
@@ -65031,7 +65062,7 @@
       <c r="AH653" s="4"/>
       <c r="AI653" s="4"/>
     </row>
-    <row r="654" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
         <v>957</v>
       </c>
@@ -65092,7 +65123,7 @@
       <c r="AH654" s="4"/>
       <c r="AI654" s="4"/>
     </row>
-    <row r="655" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
         <v>960</v>
       </c>
@@ -65153,7 +65184,7 @@
       <c r="AH655" s="4"/>
       <c r="AI655" s="4"/>
     </row>
-    <row r="656" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
         <v>962</v>
       </c>
@@ -65214,7 +65245,7 @@
       <c r="AH656" s="4"/>
       <c r="AI656" s="4"/>
     </row>
-    <row r="657" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
         <v>963</v>
       </c>
@@ -65275,7 +65306,7 @@
       <c r="AH657" s="4"/>
       <c r="AI657" s="4"/>
     </row>
-    <row r="658" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
         <v>964</v>
       </c>
@@ -65336,7 +65367,7 @@
       <c r="AH658" s="4"/>
       <c r="AI658" s="4"/>
     </row>
-    <row r="659" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
         <v>965</v>
       </c>
@@ -65397,7 +65428,7 @@
       <c r="AH659" s="4"/>
       <c r="AI659" s="4"/>
     </row>
-    <row r="660" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
         <v>968</v>
       </c>
@@ -65458,7 +65489,7 @@
       <c r="AH660" s="4"/>
       <c r="AI660" s="4"/>
     </row>
-    <row r="661" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
         <v>969</v>
       </c>
@@ -65519,7 +65550,7 @@
       <c r="AH661" s="4"/>
       <c r="AI661" s="4"/>
     </row>
-    <row r="662" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
         <v>971</v>
       </c>
@@ -65580,7 +65611,7 @@
       <c r="AH662" s="4"/>
       <c r="AI662" s="4"/>
     </row>
-    <row r="663" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
         <v>972</v>
       </c>
@@ -65641,7 +65672,7 @@
       <c r="AH663" s="4"/>
       <c r="AI663" s="4"/>
     </row>
-    <row r="664" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
         <v>973</v>
       </c>
@@ -65702,7 +65733,7 @@
       <c r="AH664" s="4"/>
       <c r="AI664" s="4"/>
     </row>
-    <row r="665" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
         <v>976</v>
       </c>
@@ -65763,7 +65794,7 @@
       <c r="AH665" s="4"/>
       <c r="AI665" s="4"/>
     </row>
-    <row r="666" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
         <v>978</v>
       </c>
@@ -65824,7 +65855,7 @@
       <c r="AH666" s="4"/>
       <c r="AI666" s="4"/>
     </row>
-    <row r="667" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
         <v>980</v>
       </c>
@@ -65885,7 +65916,7 @@
       <c r="AH667" s="4"/>
       <c r="AI667" s="4"/>
     </row>
-    <row r="668" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
         <v>983</v>
       </c>
@@ -65946,7 +65977,7 @@
       <c r="AH668" s="4"/>
       <c r="AI668" s="4"/>
     </row>
-    <row r="669" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
         <v>986</v>
       </c>
@@ -66007,7 +66038,7 @@
       <c r="AH669" s="4"/>
       <c r="AI669" s="4"/>
     </row>
-    <row r="670" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
         <v>989</v>
       </c>
@@ -66068,7 +66099,7 @@
       <c r="AH670" s="4"/>
       <c r="AI670" s="4"/>
     </row>
-    <row r="671" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
         <v>990</v>
       </c>
@@ -66129,7 +66160,7 @@
       <c r="AH671" s="4"/>
       <c r="AI671" s="4"/>
     </row>
-    <row r="672" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
         <v>993</v>
       </c>
@@ -66190,7 +66221,7 @@
       <c r="AH672" s="4"/>
       <c r="AI672" s="4"/>
     </row>
-    <row r="673" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
         <v>994</v>
       </c>
@@ -66251,7 +66282,7 @@
       <c r="AH673" s="4"/>
       <c r="AI673" s="4"/>
     </row>
-    <row r="674" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
         <v>995</v>
       </c>
@@ -66312,7 +66343,7 @@
       <c r="AH674" s="4"/>
       <c r="AI674" s="4"/>
     </row>
-    <row r="675" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
         <v>996</v>
       </c>
@@ -66373,7 +66404,7 @@
       <c r="AH675" s="4"/>
       <c r="AI675" s="4"/>
     </row>
-    <row r="676" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
         <v>999</v>
       </c>
@@ -66434,7 +66465,7 @@
       <c r="AH676" s="4"/>
       <c r="AI676" s="4"/>
     </row>
-    <row r="677" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
         <v>1000</v>
       </c>
@@ -66495,7 +66526,7 @@
       <c r="AH677" s="4"/>
       <c r="AI677" s="4"/>
     </row>
-    <row r="678" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
         <v>1001</v>
       </c>
@@ -66556,7 +66587,7 @@
       <c r="AH678" s="4"/>
       <c r="AI678" s="4"/>
     </row>
-    <row r="679" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
         <v>1002</v>
       </c>
@@ -66617,7 +66648,7 @@
       <c r="AH679" s="4"/>
       <c r="AI679" s="4"/>
     </row>
-    <row r="680" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
         <v>1005</v>
       </c>
@@ -66678,7 +66709,7 @@
       <c r="AH680" s="4"/>
       <c r="AI680" s="4"/>
     </row>
-    <row r="681" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
         <v>1008</v>
       </c>
@@ -66739,7 +66770,7 @@
       <c r="AH681" s="4"/>
       <c r="AI681" s="4"/>
     </row>
-    <row r="682" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
         <v>1009</v>
       </c>
@@ -66800,7 +66831,7 @@
       <c r="AH682" s="4"/>
       <c r="AI682" s="4"/>
     </row>
-    <row r="683" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
         <v>1010</v>
       </c>
@@ -66861,7 +66892,7 @@
       <c r="AH683" s="4"/>
       <c r="AI683" s="4"/>
     </row>
-    <row r="684" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
         <v>1011</v>
       </c>
@@ -66922,7 +66953,7 @@
       <c r="AH684" s="4"/>
       <c r="AI684" s="4"/>
     </row>
-    <row r="685" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
         <v>1012</v>
       </c>
@@ -66983,7 +67014,7 @@
       <c r="AH685" s="4"/>
       <c r="AI685" s="4"/>
     </row>
-    <row r="686" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
         <v>1015</v>
       </c>
@@ -67044,7 +67075,7 @@
       <c r="AH686" s="4"/>
       <c r="AI686" s="4"/>
     </row>
-    <row r="687" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
         <v>1016</v>
       </c>
@@ -67105,7 +67136,7 @@
       <c r="AH687" s="4"/>
       <c r="AI687" s="4"/>
     </row>
-    <row r="688" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
         <v>1019</v>
       </c>
@@ -67166,7 +67197,7 @@
       <c r="AH688" s="4"/>
       <c r="AI688" s="4"/>
     </row>
-    <row r="689" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
         <v>1020</v>
       </c>
@@ -67227,7 +67258,7 @@
       <c r="AH689" s="4"/>
       <c r="AI689" s="4"/>
     </row>
-    <row r="690" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
         <v>1022</v>
       </c>
@@ -67288,7 +67319,7 @@
       <c r="AH690" s="4"/>
       <c r="AI690" s="4"/>
     </row>
-    <row r="691" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
         <v>1027</v>
       </c>
@@ -67349,7 +67380,7 @@
       <c r="AH691" s="4"/>
       <c r="AI691" s="4"/>
     </row>
-    <row r="692" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
         <v>1029</v>
       </c>
@@ -67410,7 +67441,7 @@
       <c r="AH692" s="4"/>
       <c r="AI692" s="4"/>
     </row>
-    <row r="693" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
         <v>1033</v>
       </c>
@@ -67471,7 +67502,7 @@
       <c r="AH693" s="4"/>
       <c r="AI693" s="4"/>
     </row>
-    <row r="694" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
         <v>1034</v>
       </c>
@@ -67532,7 +67563,7 @@
       <c r="AH694" s="4"/>
       <c r="AI694" s="4"/>
     </row>
-    <row r="695" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
         <v>1036</v>
       </c>
@@ -67593,7 +67624,7 @@
       <c r="AH695" s="4"/>
       <c r="AI695" s="4"/>
     </row>
-    <row r="696" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
         <v>1039</v>
       </c>
@@ -67654,7 +67685,7 @@
       <c r="AH696" s="4"/>
       <c r="AI696" s="4"/>
     </row>
-    <row r="697" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
         <v>1040</v>
       </c>
@@ -67715,7 +67746,7 @@
       <c r="AH697" s="4"/>
       <c r="AI697" s="4"/>
     </row>
-    <row r="698" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
         <v>1041</v>
       </c>
@@ -67776,7 +67807,7 @@
       <c r="AH698" s="4"/>
       <c r="AI698" s="4"/>
     </row>
-    <row r="699" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
         <v>1043</v>
       </c>
@@ -67837,7 +67868,7 @@
       <c r="AH699" s="4"/>
       <c r="AI699" s="4"/>
     </row>
-    <row r="700" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
         <v>1047</v>
       </c>
@@ -67898,7 +67929,7 @@
       <c r="AH700" s="4"/>
       <c r="AI700" s="4"/>
     </row>
-    <row r="701" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
         <v>1049</v>
       </c>
@@ -67959,7 +67990,7 @@
       <c r="AH701" s="4"/>
       <c r="AI701" s="4"/>
     </row>
-    <row r="702" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
         <v>1052</v>
       </c>
@@ -68020,7 +68051,7 @@
       <c r="AH702" s="4"/>
       <c r="AI702" s="4"/>
     </row>
-    <row r="703" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
         <v>1053</v>
       </c>
@@ -68081,7 +68112,7 @@
       <c r="AH703" s="4"/>
       <c r="AI703" s="4"/>
     </row>
-    <row r="704" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
         <v>1056</v>
       </c>
@@ -68142,7 +68173,7 @@
       <c r="AH704" s="4"/>
       <c r="AI704" s="4"/>
     </row>
-    <row r="705" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
         <v>1057</v>
       </c>
@@ -68203,7 +68234,7 @@
       <c r="AH705" s="4"/>
       <c r="AI705" s="4"/>
     </row>
-    <row r="706" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
         <v>1058</v>
       </c>
@@ -68264,7 +68295,7 @@
       <c r="AH706" s="4"/>
       <c r="AI706" s="4"/>
     </row>
-    <row r="707" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
         <v>1060</v>
       </c>
@@ -68325,7 +68356,7 @@
       <c r="AH707" s="4"/>
       <c r="AI707" s="4"/>
     </row>
-    <row r="708" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
         <v>1061</v>
       </c>
@@ -68386,7 +68417,7 @@
       <c r="AH708" s="4"/>
       <c r="AI708" s="4"/>
     </row>
-    <row r="709" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
         <v>1062</v>
       </c>
@@ -68447,7 +68478,7 @@
       <c r="AH709" s="4"/>
       <c r="AI709" s="4"/>
     </row>
-    <row r="710" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
         <v>1066</v>
       </c>
@@ -68508,7 +68539,7 @@
       <c r="AH710" s="4"/>
       <c r="AI710" s="4"/>
     </row>
-    <row r="711" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
         <v>1068</v>
       </c>
@@ -68569,7 +68600,7 @@
       <c r="AH711" s="4"/>
       <c r="AI711" s="4"/>
     </row>
-    <row r="712" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
         <v>1070</v>
       </c>
@@ -68630,7 +68661,7 @@
       <c r="AH712" s="4"/>
       <c r="AI712" s="4"/>
     </row>
-    <row r="713" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
         <v>1071</v>
       </c>
@@ -68691,7 +68722,7 @@
       <c r="AH713" s="4"/>
       <c r="AI713" s="4"/>
     </row>
-    <row r="714" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
         <v>1074</v>
       </c>
@@ -68752,7 +68783,7 @@
       <c r="AH714" s="4"/>
       <c r="AI714" s="4"/>
     </row>
-    <row r="715" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
         <v>1077</v>
       </c>
@@ -68813,7 +68844,7 @@
       <c r="AH715" s="4"/>
       <c r="AI715" s="4"/>
     </row>
-    <row r="716" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
         <v>1078</v>
       </c>
@@ -68874,7 +68905,7 @@
       <c r="AH716" s="4"/>
       <c r="AI716" s="4"/>
     </row>
-    <row r="717" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
         <v>1081</v>
       </c>
@@ -68935,7 +68966,7 @@
       <c r="AH717" s="4"/>
       <c r="AI717" s="4"/>
     </row>
-    <row r="718" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
         <v>1085</v>
       </c>
@@ -68996,7 +69027,7 @@
       <c r="AH718" s="4"/>
       <c r="AI718" s="4"/>
     </row>
-    <row r="719" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
         <v>1086</v>
       </c>
@@ -69057,7 +69088,7 @@
       <c r="AH719" s="4"/>
       <c r="AI719" s="4"/>
     </row>
-    <row r="720" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
         <v>1087</v>
       </c>
@@ -69118,7 +69149,7 @@
       <c r="AH720" s="4"/>
       <c r="AI720" s="4"/>
     </row>
-    <row r="721" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
         <v>1089</v>
       </c>
@@ -69179,7 +69210,7 @@
       <c r="AH721" s="4"/>
       <c r="AI721" s="4"/>
     </row>
-    <row r="722" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
         <v>1092</v>
       </c>
@@ -69240,7 +69271,7 @@
       <c r="AH722" s="4"/>
       <c r="AI722" s="4"/>
     </row>
-    <row r="723" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
         <v>1093</v>
       </c>
@@ -69301,7 +69332,7 @@
       <c r="AH723" s="4"/>
       <c r="AI723" s="4"/>
     </row>
-    <row r="724" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
         <v>1094</v>
       </c>
@@ -69362,7 +69393,7 @@
       <c r="AH724" s="4"/>
       <c r="AI724" s="4"/>
     </row>
-    <row r="725" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
         <v>1096</v>
       </c>
@@ -69423,7 +69454,7 @@
       <c r="AH725" s="4"/>
       <c r="AI725" s="4"/>
     </row>
-    <row r="726" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
         <v>1097</v>
       </c>
@@ -69484,7 +69515,7 @@
       <c r="AH726" s="4"/>
       <c r="AI726" s="4"/>
     </row>
-    <row r="727" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
         <v>1098</v>
       </c>
@@ -69545,7 +69576,7 @@
       <c r="AH727" s="4"/>
       <c r="AI727" s="4"/>
     </row>
-    <row r="728" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="s">
         <v>1099</v>
       </c>
@@ -69606,7 +69637,7 @@
       <c r="AH728" s="4"/>
       <c r="AI728" s="4"/>
     </row>
-    <row r="729" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
         <v>1100</v>
       </c>
@@ -69667,7 +69698,7 @@
       <c r="AH729" s="4"/>
       <c r="AI729" s="4"/>
     </row>
-    <row r="730" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
         <v>1103</v>
       </c>
@@ -69728,7 +69759,7 @@
       <c r="AH730" s="4"/>
       <c r="AI730" s="4"/>
     </row>
-    <row r="731" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
         <v>1104</v>
       </c>
@@ -69789,7 +69820,7 @@
       <c r="AH731" s="4"/>
       <c r="AI731" s="4"/>
     </row>
-    <row r="732" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
         <v>1105</v>
       </c>
@@ -69850,7 +69881,7 @@
       <c r="AH732" s="4"/>
       <c r="AI732" s="4"/>
     </row>
-    <row r="733" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
         <v>1108</v>
       </c>
@@ -69911,7 +69942,7 @@
       <c r="AH733" s="4"/>
       <c r="AI733" s="4"/>
     </row>
-    <row r="734" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
         <v>1110</v>
       </c>
@@ -69972,7 +70003,7 @@
       <c r="AH734" s="4"/>
       <c r="AI734" s="4"/>
     </row>
-    <row r="735" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
         <v>1111</v>
       </c>
@@ -70033,7 +70064,7 @@
       <c r="AH735" s="4"/>
       <c r="AI735" s="4"/>
     </row>
-    <row r="736" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
         <v>1114</v>
       </c>
@@ -70094,7 +70125,7 @@
       <c r="AH736" s="4"/>
       <c r="AI736" s="4"/>
     </row>
-    <row r="737" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
         <v>1116</v>
       </c>
@@ -70155,7 +70186,7 @@
       <c r="AH737" s="4"/>
       <c r="AI737" s="4"/>
     </row>
-    <row r="738" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
         <v>1117</v>
       </c>
@@ -70216,7 +70247,7 @@
       <c r="AH738" s="4"/>
       <c r="AI738" s="4"/>
     </row>
-    <row r="739" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
         <v>1118</v>
       </c>
@@ -70277,7 +70308,7 @@
       <c r="AH739" s="4"/>
       <c r="AI739" s="4"/>
     </row>
-    <row r="740" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
         <v>1121</v>
       </c>
@@ -70338,7 +70369,7 @@
       <c r="AH740" s="4"/>
       <c r="AI740" s="4"/>
     </row>
-    <row r="741" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
         <v>1122</v>
       </c>
@@ -70399,7 +70430,7 @@
       <c r="AH741" s="4"/>
       <c r="AI741" s="4"/>
     </row>
-    <row r="742" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
         <v>1125</v>
       </c>
@@ -70460,7 +70491,7 @@
       <c r="AH742" s="4"/>
       <c r="AI742" s="4"/>
     </row>
-    <row r="743" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
         <v>1126</v>
       </c>
@@ -70521,7 +70552,7 @@
       <c r="AH743" s="4"/>
       <c r="AI743" s="4"/>
     </row>
-    <row r="744" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
         <v>1129</v>
       </c>
@@ -70582,7 +70613,7 @@
       <c r="AH744" s="4"/>
       <c r="AI744" s="4"/>
     </row>
-    <row r="745" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
         <v>1131</v>
       </c>
@@ -70643,7 +70674,7 @@
       <c r="AH745" s="4"/>
       <c r="AI745" s="4"/>
     </row>
-    <row r="746" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
         <v>1134</v>
       </c>
@@ -70704,7 +70735,7 @@
       <c r="AH746" s="4"/>
       <c r="AI746" s="4"/>
     </row>
-    <row r="747" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
         <v>1135</v>
       </c>
@@ -70765,7 +70796,7 @@
       <c r="AH747" s="4"/>
       <c r="AI747" s="4"/>
     </row>
-    <row r="748" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
         <v>1138</v>
       </c>
@@ -70826,7 +70857,7 @@
       <c r="AH748" s="4"/>
       <c r="AI748" s="4"/>
     </row>
-    <row r="749" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
         <v>1139</v>
       </c>
@@ -70887,7 +70918,7 @@
       <c r="AH749" s="4"/>
       <c r="AI749" s="4"/>
     </row>
-    <row r="750" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
         <v>1143</v>
       </c>
@@ -70948,7 +70979,7 @@
       <c r="AH750" s="4"/>
       <c r="AI750" s="4"/>
     </row>
-    <row r="751" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
         <v>1144</v>
       </c>
@@ -71009,7 +71040,7 @@
       <c r="AH751" s="4"/>
       <c r="AI751" s="4"/>
     </row>
-    <row r="752" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
         <v>1145</v>
       </c>
@@ -71070,7 +71101,7 @@
       <c r="AH752" s="4"/>
       <c r="AI752" s="4"/>
     </row>
-    <row r="753" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
         <v>1147</v>
       </c>
@@ -71131,7 +71162,7 @@
       <c r="AH753" s="4"/>
       <c r="AI753" s="4"/>
     </row>
-    <row r="754" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
         <v>1148</v>
       </c>
@@ -71192,7 +71223,7 @@
       <c r="AH754" s="4"/>
       <c r="AI754" s="4"/>
     </row>
-    <row r="755" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
         <v>1150</v>
       </c>
@@ -71253,7 +71284,7 @@
       <c r="AH755" s="4"/>
       <c r="AI755" s="4"/>
     </row>
-    <row r="756" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
         <v>1151</v>
       </c>
@@ -71314,7 +71345,7 @@
       <c r="AH756" s="4"/>
       <c r="AI756" s="4"/>
     </row>
-    <row r="757" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
         <v>1154</v>
       </c>
@@ -71375,7 +71406,7 @@
       <c r="AH757" s="4"/>
       <c r="AI757" s="4"/>
     </row>
-    <row r="758" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
         <v>1156</v>
       </c>
@@ -71436,7 +71467,7 @@
       <c r="AH758" s="4"/>
       <c r="AI758" s="4"/>
     </row>
-    <row r="759" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
         <v>1157</v>
       </c>
@@ -71497,7 +71528,7 @@
       <c r="AH759" s="4"/>
       <c r="AI759" s="4"/>
     </row>
-    <row r="760" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
         <v>1160</v>
       </c>
@@ -71558,7 +71589,7 @@
       <c r="AH760" s="4"/>
       <c r="AI760" s="4"/>
     </row>
-    <row r="761" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
         <v>1161</v>
       </c>
@@ -71619,7 +71650,7 @@
       <c r="AH761" s="4"/>
       <c r="AI761" s="4"/>
     </row>
-    <row r="762" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
         <v>1162</v>
       </c>
@@ -71680,7 +71711,7 @@
       <c r="AH762" s="4"/>
       <c r="AI762" s="4"/>
     </row>
-    <row r="763" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
         <v>1164</v>
       </c>
@@ -71741,7 +71772,7 @@
       <c r="AH763" s="4"/>
       <c r="AI763" s="4"/>
     </row>
-    <row r="764" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
         <v>1165</v>
       </c>
@@ -71802,7 +71833,7 @@
       <c r="AH764" s="4"/>
       <c r="AI764" s="4"/>
     </row>
-    <row r="765" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
         <v>1168</v>
       </c>
@@ -71863,7 +71894,7 @@
       <c r="AH765" s="4"/>
       <c r="AI765" s="4"/>
     </row>
-    <row r="766" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
         <v>1169</v>
       </c>
@@ -71924,7 +71955,7 @@
       <c r="AH766" s="4"/>
       <c r="AI766" s="4"/>
     </row>
-    <row r="767" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
         <v>1170</v>
       </c>
@@ -71985,7 +72016,7 @@
       <c r="AH767" s="4"/>
       <c r="AI767" s="4"/>
     </row>
-    <row r="768" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="s">
         <v>1172</v>
       </c>
@@ -72046,7 +72077,7 @@
       <c r="AH768" s="4"/>
       <c r="AI768" s="4"/>
     </row>
-    <row r="769" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
         <v>1173</v>
       </c>
@@ -72107,7 +72138,7 @@
       <c r="AH769" s="4"/>
       <c r="AI769" s="4"/>
     </row>
-    <row r="770" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
         <v>1174</v>
       </c>
@@ -72168,7 +72199,7 @@
       <c r="AH770" s="4"/>
       <c r="AI770" s="4"/>
     </row>
-    <row r="771" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
         <v>1177</v>
       </c>
@@ -72229,7 +72260,7 @@
       <c r="AH771" s="4"/>
       <c r="AI771" s="4"/>
     </row>
-    <row r="772" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
         <v>1178</v>
       </c>
@@ -72290,7 +72321,7 @@
       <c r="AH772" s="4"/>
       <c r="AI772" s="4"/>
     </row>
-    <row r="773" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
         <v>1179</v>
       </c>
@@ -72351,7 +72382,7 @@
       <c r="AH773" s="4"/>
       <c r="AI773" s="4"/>
     </row>
-    <row r="774" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
         <v>1180</v>
       </c>
@@ -72412,7 +72443,7 @@
       <c r="AH774" s="4"/>
       <c r="AI774" s="4"/>
     </row>
-    <row r="775" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
         <v>1183</v>
       </c>
@@ -72473,7 +72504,7 @@
       <c r="AH775" s="4"/>
       <c r="AI775" s="4"/>
     </row>
-    <row r="776" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
         <v>1184</v>
       </c>
@@ -72534,7 +72565,7 @@
       <c r="AH776" s="4"/>
       <c r="AI776" s="4"/>
     </row>
-    <row r="777" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
         <v>1185</v>
       </c>
@@ -72595,7 +72626,7 @@
       <c r="AH777" s="4"/>
       <c r="AI777" s="4"/>
     </row>
-    <row r="778" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
         <v>1186</v>
       </c>
@@ -72656,7 +72687,7 @@
       <c r="AH778" s="4"/>
       <c r="AI778" s="4"/>
     </row>
-    <row r="779" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
         <v>1187</v>
       </c>
@@ -72717,7 +72748,7 @@
       <c r="AH779" s="4"/>
       <c r="AI779" s="4"/>
     </row>
-    <row r="780" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
         <v>1188</v>
       </c>
@@ -72778,7 +72809,7 @@
       <c r="AH780" s="4"/>
       <c r="AI780" s="4"/>
     </row>
-    <row r="781" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
         <v>1191</v>
       </c>
@@ -72839,7 +72870,7 @@
       <c r="AH781" s="4"/>
       <c r="AI781" s="4"/>
     </row>
-    <row r="782" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
         <v>1194</v>
       </c>
@@ -72900,7 +72931,7 @@
       <c r="AH782" s="4"/>
       <c r="AI782" s="4"/>
     </row>
-    <row r="783" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
         <v>1195</v>
       </c>
@@ -72961,7 +72992,7 @@
       <c r="AH783" s="4"/>
       <c r="AI783" s="4"/>
     </row>
-    <row r="784" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784" s="2" t="s">
         <v>1196</v>
       </c>
@@ -73022,7 +73053,7 @@
       <c r="AH784" s="4"/>
       <c r="AI784" s="4"/>
     </row>
-    <row r="785" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
         <v>1197</v>
       </c>
@@ -73083,7 +73114,7 @@
       <c r="AH785" s="4"/>
       <c r="AI785" s="4"/>
     </row>
-    <row r="786" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
         <v>1200</v>
       </c>
@@ -73144,7 +73175,7 @@
       <c r="AH786" s="4"/>
       <c r="AI786" s="4"/>
     </row>
-    <row r="787" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
         <v>1201</v>
       </c>
@@ -73205,7 +73236,7 @@
       <c r="AH787" s="4"/>
       <c r="AI787" s="4"/>
     </row>
-    <row r="788" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="s">
         <v>1202</v>
       </c>
@@ -73266,7 +73297,7 @@
       <c r="AH788" s="4"/>
       <c r="AI788" s="4"/>
     </row>
-    <row r="789" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
         <v>1203</v>
       </c>
@@ -73327,7 +73358,7 @@
       <c r="AH789" s="4"/>
       <c r="AI789" s="4"/>
     </row>
-    <row r="790" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="s">
         <v>1206</v>
       </c>
@@ -73388,7 +73419,7 @@
       <c r="AH790" s="4"/>
       <c r="AI790" s="4"/>
     </row>
-    <row r="791" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="2" t="s">
         <v>1207</v>
       </c>
@@ -73449,7 +73480,7 @@
       <c r="AH791" s="4"/>
       <c r="AI791" s="4"/>
     </row>
-    <row r="792" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="2" t="s">
         <v>1210</v>
       </c>
@@ -73510,7 +73541,7 @@
       <c r="AH792" s="4"/>
       <c r="AI792" s="4"/>
     </row>
-    <row r="793" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="2" t="s">
         <v>1211</v>
       </c>
@@ -73571,7 +73602,7 @@
       <c r="AH793" s="4"/>
       <c r="AI793" s="4"/>
     </row>
-    <row r="794" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794" s="2" t="s">
         <v>1214</v>
       </c>
@@ -73632,7 +73663,7 @@
       <c r="AH794" s="4"/>
       <c r="AI794" s="4"/>
     </row>
-    <row r="795" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="2" t="s">
         <v>1217</v>
       </c>
@@ -73693,7 +73724,7 @@
       <c r="AH795" s="4"/>
       <c r="AI795" s="4"/>
     </row>
-    <row r="796" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796" s="2" t="s">
         <v>1218</v>
       </c>
@@ -73754,7 +73785,7 @@
       <c r="AH796" s="4"/>
       <c r="AI796" s="4"/>
     </row>
-    <row r="797" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A797" s="2" t="s">
         <v>1222</v>
       </c>
@@ -73815,7 +73846,7 @@
       <c r="AH797" s="4"/>
       <c r="AI797" s="4"/>
     </row>
-    <row r="798" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="2" t="s">
         <v>1223</v>
       </c>
@@ -73876,7 +73907,7 @@
       <c r="AH798" s="4"/>
       <c r="AI798" s="4"/>
     </row>
-    <row r="799" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="2" t="s">
         <v>1225</v>
       </c>
@@ -73937,7 +73968,7 @@
       <c r="AH799" s="4"/>
       <c r="AI799" s="4"/>
     </row>
-    <row r="800" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800" s="2" t="s">
         <v>1228</v>
       </c>
@@ -73998,7 +74029,7 @@
       <c r="AH800" s="4"/>
       <c r="AI800" s="4"/>
     </row>
-    <row r="801" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801" s="2" t="s">
         <v>1229</v>
       </c>
@@ -74059,7 +74090,7 @@
       <c r="AH801" s="4"/>
       <c r="AI801" s="4"/>
     </row>
-    <row r="802" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A802" s="2" t="s">
         <v>1230</v>
       </c>
@@ -74120,7 +74151,7 @@
       <c r="AH802" s="4"/>
       <c r="AI802" s="4"/>
     </row>
-    <row r="803" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803" s="2" t="s">
         <v>1231</v>
       </c>
@@ -74181,7 +74212,7 @@
       <c r="AH803" s="4"/>
       <c r="AI803" s="4"/>
     </row>
-    <row r="804" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="2" t="s">
         <v>1234</v>
       </c>
@@ -74242,7 +74273,7 @@
       <c r="AH804" s="4"/>
       <c r="AI804" s="4"/>
     </row>
-    <row r="805" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A805" s="2" t="s">
         <v>1235</v>
       </c>
@@ -74303,7 +74334,7 @@
       <c r="AH805" s="4"/>
       <c r="AI805" s="4"/>
     </row>
-    <row r="806" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806" s="2" t="s">
         <v>1236</v>
       </c>
@@ -74364,7 +74395,7 @@
       <c r="AH806" s="4"/>
       <c r="AI806" s="4"/>
     </row>
-    <row r="807" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807" s="2" t="s">
         <v>1239</v>
       </c>
@@ -74425,7 +74456,7 @@
       <c r="AH807" s="4"/>
       <c r="AI807" s="4"/>
     </row>
-    <row r="808" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A808" s="2" t="s">
         <v>1240</v>
       </c>
@@ -74486,7 +74517,7 @@
       <c r="AH808" s="4"/>
       <c r="AI808" s="4"/>
     </row>
-    <row r="809" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A809" s="2" t="s">
         <v>1241</v>
       </c>
@@ -74547,7 +74578,7 @@
       <c r="AH809" s="4"/>
       <c r="AI809" s="4"/>
     </row>
-    <row r="810" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A810" s="2" t="s">
         <v>1244</v>
       </c>
@@ -74608,7 +74639,7 @@
       <c r="AH810" s="4"/>
       <c r="AI810" s="4"/>
     </row>
-    <row r="811" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A811" s="2" t="s">
         <v>1245</v>
       </c>
@@ -74669,7 +74700,7 @@
       <c r="AH811" s="4"/>
       <c r="AI811" s="4"/>
     </row>
-    <row r="812" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A812" s="2" t="s">
         <v>1247</v>
       </c>
@@ -74730,7 +74761,7 @@
       <c r="AH812" s="4"/>
       <c r="AI812" s="4"/>
     </row>
-    <row r="813" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A813" s="2" t="s">
         <v>1248</v>
       </c>
@@ -74791,7 +74822,7 @@
       <c r="AH813" s="4"/>
       <c r="AI813" s="4"/>
     </row>
-    <row r="814" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A814" s="2" t="s">
         <v>1252</v>
       </c>
@@ -74852,7 +74883,7 @@
       <c r="AH814" s="4"/>
       <c r="AI814" s="4"/>
     </row>
-    <row r="815" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A815" s="2" t="s">
         <v>1253</v>
       </c>
@@ -74913,7 +74944,7 @@
       <c r="AH815" s="4"/>
       <c r="AI815" s="4"/>
     </row>
-    <row r="816" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="2" t="s">
         <v>1255</v>
       </c>
@@ -74974,7 +75005,7 @@
       <c r="AH816" s="4"/>
       <c r="AI816" s="4"/>
     </row>
-    <row r="817" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817" s="2" t="s">
         <v>1256</v>
       </c>
@@ -75035,7 +75066,7 @@
       <c r="AH817" s="4"/>
       <c r="AI817" s="4"/>
     </row>
-    <row r="818" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="2" t="s">
         <v>1257</v>
       </c>
@@ -75096,7 +75127,7 @@
       <c r="AH818" s="4"/>
       <c r="AI818" s="4"/>
     </row>
-    <row r="819" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A819" s="2" t="s">
         <v>1258</v>
       </c>
@@ -75157,7 +75188,7 @@
       <c r="AH819" s="4"/>
       <c r="AI819" s="4"/>
     </row>
-    <row r="820" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A820" s="2" t="s">
         <v>1261</v>
       </c>
@@ -75218,7 +75249,7 @@
       <c r="AH820" s="4"/>
       <c r="AI820" s="4"/>
     </row>
-    <row r="821" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A821" s="2" t="s">
         <v>1262</v>
       </c>
@@ -75279,7 +75310,7 @@
       <c r="AH821" s="4"/>
       <c r="AI821" s="4"/>
     </row>
-    <row r="822" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A822" s="2" t="s">
         <v>1263</v>
       </c>
@@ -75340,7 +75371,7 @@
       <c r="AH822" s="4"/>
       <c r="AI822" s="4"/>
     </row>
-    <row r="823" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="2" t="s">
         <v>1266</v>
       </c>
@@ -75401,7 +75432,7 @@
       <c r="AH823" s="4"/>
       <c r="AI823" s="4"/>
     </row>
-    <row r="824" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A824" s="2" t="s">
         <v>1268</v>
       </c>
@@ -75462,7 +75493,7 @@
       <c r="AH824" s="4"/>
       <c r="AI824" s="4"/>
     </row>
-    <row r="825" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A825" s="2" t="s">
         <v>1269</v>
       </c>
@@ -75523,7 +75554,7 @@
       <c r="AH825" s="4"/>
       <c r="AI825" s="4"/>
     </row>
-    <row r="826" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826" s="2" t="s">
         <v>1272</v>
       </c>
@@ -75584,7 +75615,7 @@
       <c r="AH826" s="4"/>
       <c r="AI826" s="4"/>
     </row>
-    <row r="827" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="2" t="s">
         <v>1273</v>
       </c>
@@ -75645,7 +75676,7 @@
       <c r="AH827" s="4"/>
       <c r="AI827" s="4"/>
     </row>
-    <row r="828" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="2" t="s">
         <v>1276</v>
       </c>
@@ -75706,7 +75737,7 @@
       <c r="AH828" s="4"/>
       <c r="AI828" s="4"/>
     </row>
-    <row r="829" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="2" t="s">
         <v>1277</v>
       </c>
@@ -75767,7 +75798,7 @@
       <c r="AH829" s="4"/>
       <c r="AI829" s="4"/>
     </row>
-    <row r="830" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830" s="2" t="s">
         <v>1279</v>
       </c>
@@ -75828,7 +75859,7 @@
       <c r="AH830" s="4"/>
       <c r="AI830" s="4"/>
     </row>
-    <row r="831" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A831" s="2" t="s">
         <v>1280</v>
       </c>
@@ -75889,7 +75920,7 @@
       <c r="AH831" s="4"/>
       <c r="AI831" s="4"/>
     </row>
-    <row r="832" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A832" s="2" t="s">
         <v>1281</v>
       </c>
@@ -75950,7 +75981,7 @@
       <c r="AH832" s="4"/>
       <c r="AI832" s="4"/>
     </row>
-    <row r="833" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A833" s="2" t="s">
         <v>1282</v>
       </c>
@@ -76011,7 +76042,7 @@
       <c r="AH833" s="4"/>
       <c r="AI833" s="4"/>
     </row>
-    <row r="834" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A834" s="2" t="s">
         <v>1283</v>
       </c>
@@ -76072,7 +76103,7 @@
       <c r="AH834" s="4"/>
       <c r="AI834" s="4"/>
     </row>
-    <row r="835" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835" s="2" t="s">
         <v>1286</v>
       </c>
@@ -76133,7 +76164,7 @@
       <c r="AH835" s="4"/>
       <c r="AI835" s="4"/>
     </row>
-    <row r="836" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A836" s="2" t="s">
         <v>1289</v>
       </c>
@@ -76194,7 +76225,7 @@
       <c r="AH836" s="4"/>
       <c r="AI836" s="4"/>
     </row>
-    <row r="837" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A837" s="2" t="s">
         <v>1290</v>
       </c>
@@ -76255,7 +76286,7 @@
       <c r="AH837" s="4"/>
       <c r="AI837" s="4"/>
     </row>
-    <row r="838" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="2" t="s">
         <v>1291</v>
       </c>
@@ -76316,7 +76347,7 @@
       <c r="AH838" s="4"/>
       <c r="AI838" s="4"/>
     </row>
-    <row r="839" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="2" t="s">
         <v>1292</v>
       </c>
@@ -76377,7 +76408,7 @@
       <c r="AH839" s="4"/>
       <c r="AI839" s="4"/>
     </row>
-    <row r="840" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="2" t="s">
         <v>1293</v>
       </c>
@@ -76438,7 +76469,7 @@
       <c r="AH840" s="4"/>
       <c r="AI840" s="4"/>
     </row>
-    <row r="841" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="2" t="s">
         <v>1297</v>
       </c>
@@ -76499,7 +76530,7 @@
       <c r="AH841" s="4"/>
       <c r="AI841" s="4"/>
     </row>
-    <row r="842" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="2" t="s">
         <v>1298</v>
       </c>
@@ -76560,7 +76591,7 @@
       <c r="AH842" s="4"/>
       <c r="AI842" s="4"/>
     </row>
-    <row r="843" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A843" s="2" t="s">
         <v>1299</v>
       </c>
@@ -76621,7 +76652,7 @@
       <c r="AH843" s="4"/>
       <c r="AI843" s="4"/>
     </row>
-    <row r="844" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A844" s="2" t="s">
         <v>1300</v>
       </c>
@@ -76682,7 +76713,7 @@
       <c r="AH844" s="4"/>
       <c r="AI844" s="4"/>
     </row>
-    <row r="845" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A845" s="2" t="s">
         <v>1301</v>
       </c>
@@ -76743,7 +76774,7 @@
       <c r="AH845" s="4"/>
       <c r="AI845" s="4"/>
     </row>
-    <row r="846" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="2" t="s">
         <v>1302</v>
       </c>
@@ -76804,7 +76835,7 @@
       <c r="AH846" s="4"/>
       <c r="AI846" s="4"/>
     </row>
-    <row r="847" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A847" s="2" t="s">
         <v>1303</v>
       </c>
@@ -76865,7 +76896,7 @@
       <c r="AH847" s="4"/>
       <c r="AI847" s="4"/>
     </row>
-    <row r="848" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A848" s="2" t="s">
         <v>1306</v>
       </c>
@@ -76926,7 +76957,7 @@
       <c r="AH848" s="4"/>
       <c r="AI848" s="4"/>
     </row>
-    <row r="849" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A849" s="2" t="s">
         <v>1308</v>
       </c>
@@ -76987,7 +77018,7 @@
       <c r="AH849" s="4"/>
       <c r="AI849" s="4"/>
     </row>
-    <row r="850" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850" s="2" t="s">
         <v>1309</v>
       </c>
@@ -77048,7 +77079,7 @@
       <c r="AH850" s="4"/>
       <c r="AI850" s="4"/>
     </row>
-    <row r="851" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A851" s="2" t="s">
         <v>1311</v>
       </c>
@@ -77109,7 +77140,7 @@
       <c r="AH851" s="4"/>
       <c r="AI851" s="4"/>
     </row>
-    <row r="852" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A852" s="2" t="s">
         <v>1312</v>
       </c>
@@ -77170,7 +77201,7 @@
       <c r="AH852" s="4"/>
       <c r="AI852" s="4"/>
     </row>
-    <row r="853" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A853" s="2" t="s">
         <v>1314</v>
       </c>
@@ -77353,7 +77384,7 @@
       <c r="AH855" s="4"/>
       <c r="AI855" s="4"/>
     </row>
-    <row r="856" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A856" s="2" t="s">
         <v>1319</v>
       </c>
@@ -77414,7 +77445,7 @@
       <c r="AH856" s="4"/>
       <c r="AI856" s="4"/>
     </row>
-    <row r="857" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A857" s="2" t="s">
         <v>1322</v>
       </c>
@@ -77475,7 +77506,7 @@
       <c r="AH857" s="4"/>
       <c r="AI857" s="4"/>
     </row>
-    <row r="858" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A858" s="2" t="s">
         <v>1324</v>
       </c>
@@ -77536,7 +77567,7 @@
       <c r="AH858" s="4"/>
       <c r="AI858" s="4"/>
     </row>
-    <row r="859" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859" s="2" t="s">
         <v>1326</v>
       </c>
@@ -77597,7 +77628,7 @@
       <c r="AH859" s="4"/>
       <c r="AI859" s="4"/>
     </row>
-    <row r="860" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860" s="2" t="s">
         <v>1327</v>
       </c>
@@ -77658,7 +77689,7 @@
       <c r="AH860" s="4"/>
       <c r="AI860" s="4"/>
     </row>
-    <row r="861" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A861" s="2" t="s">
         <v>1329</v>
       </c>
@@ -77719,7 +77750,7 @@
       <c r="AH861" s="4"/>
       <c r="AI861" s="4"/>
     </row>
-    <row r="862" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A862" s="2" t="s">
         <v>1330</v>
       </c>
@@ -77780,7 +77811,7 @@
       <c r="AH862" s="4"/>
       <c r="AI862" s="4"/>
     </row>
-    <row r="863" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A863" s="2" t="s">
         <v>1332</v>
       </c>
@@ -77841,7 +77872,7 @@
       <c r="AH863" s="4"/>
       <c r="AI863" s="4"/>
     </row>
-    <row r="864" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A864" s="2" t="s">
         <v>1334</v>
       </c>
@@ -77902,7 +77933,7 @@
       <c r="AH864" s="4"/>
       <c r="AI864" s="4"/>
     </row>
-    <row r="865" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865" s="2" t="s">
         <v>1337</v>
       </c>
@@ -77963,7 +77994,7 @@
       <c r="AH865" s="4"/>
       <c r="AI865" s="4"/>
     </row>
-    <row r="866" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A866" s="2" t="s">
         <v>1338</v>
       </c>
@@ -78024,7 +78055,7 @@
       <c r="AH866" s="4"/>
       <c r="AI866" s="4"/>
     </row>
-    <row r="867" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867" s="2" t="s">
         <v>1341</v>
       </c>
@@ -78085,7 +78116,7 @@
       <c r="AH867" s="4"/>
       <c r="AI867" s="4"/>
     </row>
-    <row r="868" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868" s="2" t="s">
         <v>1344</v>
       </c>
@@ -78146,7 +78177,7 @@
       <c r="AH868" s="4"/>
       <c r="AI868" s="4"/>
     </row>
-    <row r="869" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869" s="2" t="s">
         <v>1345</v>
       </c>
@@ -78207,7 +78238,7 @@
       <c r="AH869" s="4"/>
       <c r="AI869" s="4"/>
     </row>
-    <row r="870" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870" s="2" t="s">
         <v>1347</v>
       </c>
@@ -78268,7 +78299,7 @@
       <c r="AH870" s="4"/>
       <c r="AI870" s="4"/>
     </row>
-    <row r="871" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="2" t="s">
         <v>1349</v>
       </c>
@@ -78329,7 +78360,7 @@
       <c r="AH871" s="4"/>
       <c r="AI871" s="4"/>
     </row>
-    <row r="872" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872" s="2" t="s">
         <v>1352</v>
       </c>
@@ -78390,7 +78421,7 @@
       <c r="AH872" s="4"/>
       <c r="AI872" s="4"/>
     </row>
-    <row r="873" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873" s="2" t="s">
         <v>1353</v>
       </c>
@@ -78451,7 +78482,7 @@
       <c r="AH873" s="4"/>
       <c r="AI873" s="4"/>
     </row>
-    <row r="874" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A874" s="2" t="s">
         <v>1355</v>
       </c>
@@ -78512,7 +78543,7 @@
       <c r="AH874" s="4"/>
       <c r="AI874" s="4"/>
     </row>
-    <row r="875" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A875" s="2" t="s">
         <v>1357</v>
       </c>
@@ -78573,7 +78604,7 @@
       <c r="AH875" s="4"/>
       <c r="AI875" s="4"/>
     </row>
-    <row r="876" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876" s="2" t="s">
         <v>1359</v>
       </c>
@@ -78634,7 +78665,7 @@
       <c r="AH876" s="4"/>
       <c r="AI876" s="4"/>
     </row>
-    <row r="877" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="2" t="s">
         <v>1362</v>
       </c>
@@ -78695,7 +78726,7 @@
       <c r="AH877" s="4"/>
       <c r="AI877" s="4"/>
     </row>
-    <row r="878" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878" s="2" t="s">
         <v>1364</v>
       </c>
@@ -78756,7 +78787,7 @@
       <c r="AH878" s="4"/>
       <c r="AI878" s="4"/>
     </row>
-    <row r="879" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879" s="2" t="s">
         <v>1365</v>
       </c>
@@ -78817,7 +78848,7 @@
       <c r="AH879" s="4"/>
       <c r="AI879" s="4"/>
     </row>
-    <row r="880" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880" s="2" t="s">
         <v>1366</v>
       </c>
@@ -78878,7 +78909,7 @@
       <c r="AH880" s="4"/>
       <c r="AI880" s="4"/>
     </row>
-    <row r="881" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881" s="2" t="s">
         <v>1367</v>
       </c>
@@ -78939,7 +78970,7 @@
       <c r="AH881" s="4"/>
       <c r="AI881" s="4"/>
     </row>
-    <row r="882" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882" s="2" t="s">
         <v>1370</v>
       </c>
@@ -79000,7 +79031,7 @@
       <c r="AH882" s="4"/>
       <c r="AI882" s="4"/>
     </row>
-    <row r="883" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="2" t="s">
         <v>1371</v>
       </c>
@@ -79061,7 +79092,7 @@
       <c r="AH883" s="4"/>
       <c r="AI883" s="4"/>
     </row>
-    <row r="884" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A884" s="2" t="s">
         <v>1372</v>
       </c>
@@ -79122,7 +79153,7 @@
       <c r="AH884" s="4"/>
       <c r="AI884" s="4"/>
     </row>
-    <row r="885" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A885" s="2" t="s">
         <v>1373</v>
       </c>
@@ -79183,7 +79214,7 @@
       <c r="AH885" s="4"/>
       <c r="AI885" s="4"/>
     </row>
-    <row r="886" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="2" t="s">
         <v>1375</v>
       </c>
@@ -79244,7 +79275,7 @@
       <c r="AH886" s="4"/>
       <c r="AI886" s="4"/>
     </row>
-    <row r="887" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="2" t="s">
         <v>1378</v>
       </c>
@@ -79305,7 +79336,7 @@
       <c r="AH887" s="4"/>
       <c r="AI887" s="4"/>
     </row>
-    <row r="888" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="2" t="s">
         <v>1380</v>
       </c>
@@ -79366,7 +79397,7 @@
       <c r="AH888" s="4"/>
       <c r="AI888" s="4"/>
     </row>
-    <row r="889" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="2" t="s">
         <v>1383</v>
       </c>
@@ -79427,7 +79458,7 @@
       <c r="AH889" s="4"/>
       <c r="AI889" s="4"/>
     </row>
-    <row r="890" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A890" s="2" t="s">
         <v>1384</v>
       </c>
@@ -79488,7 +79519,7 @@
       <c r="AH890" s="4"/>
       <c r="AI890" s="4"/>
     </row>
-    <row r="891" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A891" s="2" t="s">
         <v>1385</v>
       </c>
@@ -79549,7 +79580,7 @@
       <c r="AH891" s="4"/>
       <c r="AI891" s="4"/>
     </row>
-    <row r="892" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892" s="2" t="s">
         <v>1387</v>
       </c>
@@ -79610,7 +79641,7 @@
       <c r="AH892" s="4"/>
       <c r="AI892" s="4"/>
     </row>
-    <row r="893" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893" s="2" t="s">
         <v>1390</v>
       </c>
@@ -79671,7 +79702,7 @@
       <c r="AH893" s="4"/>
       <c r="AI893" s="4"/>
     </row>
-    <row r="894" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894" s="2" t="s">
         <v>1391</v>
       </c>
@@ -79732,7 +79763,7 @@
       <c r="AH894" s="4"/>
       <c r="AI894" s="4"/>
     </row>
-    <row r="895" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895" s="2" t="s">
         <v>1394</v>
       </c>
@@ -79793,7 +79824,7 @@
       <c r="AH895" s="4"/>
       <c r="AI895" s="4"/>
     </row>
-    <row r="896" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896" s="2" t="s">
         <v>1396</v>
       </c>
@@ -79854,7 +79885,7 @@
       <c r="AH896" s="4"/>
       <c r="AI896" s="4"/>
     </row>
-    <row r="897" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897" s="2" t="s">
         <v>1399</v>
       </c>
@@ -79915,7 +79946,7 @@
       <c r="AH897" s="4"/>
       <c r="AI897" s="4"/>
     </row>
-    <row r="898" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898" s="2" t="s">
         <v>1401</v>
       </c>
@@ -79976,7 +80007,7 @@
       <c r="AH898" s="4"/>
       <c r="AI898" s="4"/>
     </row>
-    <row r="899" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="2" t="s">
         <v>1403</v>
       </c>
@@ -80037,7 +80068,7 @@
       <c r="AH899" s="4"/>
       <c r="AI899" s="4"/>
     </row>
-    <row r="900" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="2" t="s">
         <v>1404</v>
       </c>
@@ -80098,7 +80129,7 @@
       <c r="AH900" s="4"/>
       <c r="AI900" s="4"/>
     </row>
-    <row r="901" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="2" t="s">
         <v>1407</v>
       </c>
@@ -80159,7 +80190,7 @@
       <c r="AH901" s="4"/>
       <c r="AI901" s="4"/>
     </row>
-    <row r="902" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="2" t="s">
         <v>1408</v>
       </c>
@@ -80220,7 +80251,7 @@
       <c r="AH902" s="4"/>
       <c r="AI902" s="4"/>
     </row>
-    <row r="903" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="2" t="s">
         <v>1412</v>
       </c>
@@ -80281,7 +80312,7 @@
       <c r="AH903" s="4"/>
       <c r="AI903" s="4"/>
     </row>
-    <row r="904" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="2" t="s">
         <v>1414</v>
       </c>
@@ -80342,7 +80373,7 @@
       <c r="AH904" s="4"/>
       <c r="AI904" s="4"/>
     </row>
-    <row r="905" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="2" t="s">
         <v>1418</v>
       </c>
@@ -80403,7 +80434,7 @@
       <c r="AH905" s="4"/>
       <c r="AI905" s="4"/>
     </row>
-    <row r="906" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="2" t="s">
         <v>1420</v>
       </c>
@@ -80464,7 +80495,7 @@
       <c r="AH906" s="4"/>
       <c r="AI906" s="4"/>
     </row>
-    <row r="907" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="2" t="s">
         <v>1422</v>
       </c>
@@ -80525,7 +80556,7 @@
       <c r="AH907" s="4"/>
       <c r="AI907" s="4"/>
     </row>
-    <row r="908" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="2" t="s">
         <v>1426</v>
       </c>
@@ -80586,7 +80617,7 @@
       <c r="AH908" s="4"/>
       <c r="AI908" s="4"/>
     </row>
-    <row r="909" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="2" t="s">
         <v>1428</v>
       </c>
@@ -80647,7 +80678,7 @@
       <c r="AH909" s="4"/>
       <c r="AI909" s="4"/>
     </row>
-    <row r="910" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="2" t="s">
         <v>1430</v>
       </c>
@@ -80708,7 +80739,7 @@
       <c r="AH910" s="4"/>
       <c r="AI910" s="4"/>
     </row>
-    <row r="911" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="2" t="s">
         <v>1432</v>
       </c>
@@ -80769,7 +80800,7 @@
       <c r="AH911" s="4"/>
       <c r="AI911" s="4"/>
     </row>
-    <row r="912" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="2" t="s">
         <v>1435</v>
       </c>
@@ -80830,7 +80861,7 @@
       <c r="AH912" s="4"/>
       <c r="AI912" s="4"/>
     </row>
-    <row r="913" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
         <v>1436</v>
       </c>
@@ -80891,7 +80922,7 @@
       <c r="AH913" s="4"/>
       <c r="AI913" s="4"/>
     </row>
-    <row r="914" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="2" t="s">
         <v>1437</v>
       </c>
@@ -80952,7 +80983,7 @@
       <c r="AH914" s="4"/>
       <c r="AI914" s="4"/>
     </row>
-    <row r="915" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="2" t="s">
         <v>1438</v>
       </c>
@@ -81013,7 +81044,7 @@
       <c r="AH915" s="4"/>
       <c r="AI915" s="4"/>
     </row>
-    <row r="916" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="2" t="s">
         <v>1441</v>
       </c>
@@ -81074,7 +81105,7 @@
       <c r="AH916" s="4"/>
       <c r="AI916" s="4"/>
     </row>
-    <row r="917" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="2" t="s">
         <v>1442</v>
       </c>
@@ -81135,7 +81166,7 @@
       <c r="AH917" s="4"/>
       <c r="AI917" s="4"/>
     </row>
-    <row r="918" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="2" t="s">
         <v>1445</v>
       </c>
@@ -81196,7 +81227,7 @@
       <c r="AH918" s="4"/>
       <c r="AI918" s="4"/>
     </row>
-    <row r="919" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="2" t="s">
         <v>1446</v>
       </c>
@@ -81257,7 +81288,7 @@
       <c r="AH919" s="4"/>
       <c r="AI919" s="4"/>
     </row>
-    <row r="920" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="2" t="s">
         <v>1449</v>
       </c>
@@ -81318,7 +81349,7 @@
       <c r="AH920" s="4"/>
       <c r="AI920" s="4"/>
     </row>
-    <row r="921" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="2" t="s">
         <v>1450</v>
       </c>
@@ -81379,7 +81410,7 @@
       <c r="AH921" s="4"/>
       <c r="AI921" s="4"/>
     </row>
-    <row r="922" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A922" s="2" t="s">
         <v>1542</v>
       </c>
@@ -81438,7 +81469,7 @@
       <c r="AH922" s="4"/>
       <c r="AI922" s="4"/>
     </row>
-    <row r="923" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A923" s="2" t="s">
         <v>1543</v>
       </c>
@@ -81497,7 +81528,7 @@
       <c r="AH923" s="4"/>
       <c r="AI923" s="4"/>
     </row>
-    <row r="924" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A924" s="2" t="s">
         <v>1544</v>
       </c>
@@ -81556,7 +81587,7 @@
       <c r="AH924" s="4"/>
       <c r="AI924" s="4"/>
     </row>
-    <row r="925" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="2" t="s">
         <v>1545</v>
       </c>
@@ -81615,7 +81646,7 @@
       <c r="AH925" s="4"/>
       <c r="AI925" s="4"/>
     </row>
-    <row r="926" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A926" s="2" t="s">
         <v>1546</v>
       </c>
@@ -81674,7 +81705,7 @@
       <c r="AH926" s="4"/>
       <c r="AI926" s="4"/>
     </row>
-    <row r="927" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A927" s="2" t="s">
         <v>1547</v>
       </c>
@@ -81733,7 +81764,7 @@
       <c r="AH927" s="4"/>
       <c r="AI927" s="4"/>
     </row>
-    <row r="928" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A928" s="2" t="s">
         <v>1548</v>
       </c>
@@ -81792,7 +81823,7 @@
       <c r="AH928" s="4"/>
       <c r="AI928" s="4"/>
     </row>
-    <row r="929" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A929" s="2" t="s">
         <v>1549</v>
       </c>
@@ -81851,7 +81882,7 @@
       <c r="AH929" s="4"/>
       <c r="AI929" s="4"/>
     </row>
-    <row r="930" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="2" t="s">
         <v>1550</v>
       </c>
@@ -81910,7 +81941,7 @@
       <c r="AH930" s="4"/>
       <c r="AI930" s="4"/>
     </row>
-    <row r="931" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A931" s="2" t="s">
         <v>1551</v>
       </c>
@@ -81969,7 +82000,7 @@
       <c r="AH931" s="4"/>
       <c r="AI931" s="4"/>
     </row>
-    <row r="932" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A932" s="2" t="s">
         <v>1552</v>
       </c>
@@ -82028,7 +82059,7 @@
       <c r="AH932" s="4"/>
       <c r="AI932" s="4"/>
     </row>
-    <row r="933" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A933" s="2" t="s">
         <v>1553</v>
       </c>
@@ -82087,7 +82118,7 @@
       <c r="AH933" s="4"/>
       <c r="AI933" s="4"/>
     </row>
-    <row r="934" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A934" s="2" t="s">
         <v>1554</v>
       </c>
@@ -82146,7 +82177,7 @@
       <c r="AH934" s="4"/>
       <c r="AI934" s="4"/>
     </row>
-    <row r="935" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A935" s="2" t="s">
         <v>1555</v>
       </c>
@@ -82205,7 +82236,7 @@
       <c r="AH935" s="4"/>
       <c r="AI935" s="4"/>
     </row>
-    <row r="936" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A936" s="2" t="s">
         <v>1556</v>
       </c>
@@ -82264,7 +82295,7 @@
       <c r="AH936" s="4"/>
       <c r="AI936" s="4"/>
     </row>
-    <row r="937" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A937" s="2" t="s">
         <v>1557</v>
       </c>
@@ -82323,7 +82354,7 @@
       <c r="AH937" s="4"/>
       <c r="AI937" s="4"/>
     </row>
-    <row r="938" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A938" s="2" t="s">
         <v>1558</v>
       </c>
@@ -82382,7 +82413,7 @@
       <c r="AH938" s="4"/>
       <c r="AI938" s="4"/>
     </row>
-    <row r="939" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A939" s="2" t="s">
         <v>1559</v>
       </c>
@@ -82441,7 +82472,7 @@
       <c r="AH939" s="4"/>
       <c r="AI939" s="4"/>
     </row>
-    <row r="940" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A940" s="2" t="s">
         <v>1560</v>
       </c>
@@ -82500,7 +82531,7 @@
       <c r="AH940" s="4"/>
       <c r="AI940" s="4"/>
     </row>
-    <row r="941" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A941" s="2" t="s">
         <v>1561</v>
       </c>
@@ -82559,7 +82590,7 @@
       <c r="AH941" s="4"/>
       <c r="AI941" s="4"/>
     </row>
-    <row r="942" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A942" s="2" t="s">
         <v>1562</v>
       </c>
@@ -82618,7 +82649,7 @@
       <c r="AH942" s="4"/>
       <c r="AI942" s="4"/>
     </row>
-    <row r="943" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A943" s="2" t="s">
         <v>1563</v>
       </c>
@@ -82677,7 +82708,7 @@
       <c r="AH943" s="4"/>
       <c r="AI943" s="4"/>
     </row>
-    <row r="944" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A944" s="2" t="s">
         <v>1564</v>
       </c>
@@ -82736,7 +82767,7 @@
       <c r="AH944" s="4"/>
       <c r="AI944" s="4"/>
     </row>
-    <row r="945" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A945" s="2" t="s">
         <v>1565</v>
       </c>
@@ -82795,7 +82826,7 @@
       <c r="AH945" s="4"/>
       <c r="AI945" s="4"/>
     </row>
-    <row r="946" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A946" s="2" t="s">
         <v>1566</v>
       </c>
@@ -82854,7 +82885,7 @@
       <c r="AH946" s="4"/>
       <c r="AI946" s="4"/>
     </row>
-    <row r="947" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A947" s="2" t="s">
         <v>1567</v>
       </c>
@@ -82913,7 +82944,7 @@
       <c r="AH947" s="4"/>
       <c r="AI947" s="4"/>
     </row>
-    <row r="948" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A948" s="2" t="s">
         <v>1568</v>
       </c>
@@ -82972,7 +83003,7 @@
       <c r="AH948" s="4"/>
       <c r="AI948" s="4"/>
     </row>
-    <row r="949" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A949" s="2" t="s">
         <v>1569</v>
       </c>
@@ -83031,7 +83062,7 @@
       <c r="AH949" s="4"/>
       <c r="AI949" s="4"/>
     </row>
-    <row r="950" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A950" s="2" t="s">
         <v>1570</v>
       </c>
@@ -83090,7 +83121,7 @@
       <c r="AH950" s="4"/>
       <c r="AI950" s="4"/>
     </row>
-    <row r="951" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="2" t="s">
         <v>1571</v>
       </c>
@@ -83149,7 +83180,7 @@
       <c r="AH951" s="4"/>
       <c r="AI951" s="4"/>
     </row>
-    <row r="952" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="2" t="s">
         <v>1572</v>
       </c>
@@ -83208,7 +83239,7 @@
       <c r="AH952" s="4"/>
       <c r="AI952" s="4"/>
     </row>
-    <row r="953" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A953" s="2" t="s">
         <v>1573</v>
       </c>
@@ -83267,7 +83298,7 @@
       <c r="AH953" s="4"/>
       <c r="AI953" s="4"/>
     </row>
-    <row r="954" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="2" t="s">
         <v>1574</v>
       </c>
@@ -83326,7 +83357,7 @@
       <c r="AH954" s="4"/>
       <c r="AI954" s="4"/>
     </row>
-    <row r="955" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A955" s="2" t="s">
         <v>1575</v>
       </c>
@@ -83385,7 +83416,7 @@
       <c r="AH955" s="4"/>
       <c r="AI955" s="4"/>
     </row>
-    <row r="956" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A956" s="2" t="s">
         <v>1576</v>
       </c>
@@ -83444,7 +83475,7 @@
       <c r="AH956" s="4"/>
       <c r="AI956" s="4"/>
     </row>
-    <row r="957" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A957" s="2" t="s">
         <v>1577</v>
       </c>
@@ -83503,7 +83534,7 @@
       <c r="AH957" s="4"/>
       <c r="AI957" s="4"/>
     </row>
-    <row r="958" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A958" s="2" t="s">
         <v>1578</v>
       </c>
@@ -83562,7 +83593,7 @@
       <c r="AH958" s="4"/>
       <c r="AI958" s="4"/>
     </row>
-    <row r="959" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A959" s="2" t="s">
         <v>1579</v>
       </c>
@@ -83621,7 +83652,7 @@
       <c r="AH959" s="4"/>
       <c r="AI959" s="4"/>
     </row>
-    <row r="960" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A960" s="2" t="s">
         <v>1580</v>
       </c>
@@ -83680,7 +83711,7 @@
       <c r="AH960" s="4"/>
       <c r="AI960" s="4"/>
     </row>
-    <row r="961" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A961" s="2" t="s">
         <v>1581</v>
       </c>
@@ -83739,7 +83770,7 @@
       <c r="AH961" s="4"/>
       <c r="AI961" s="4"/>
     </row>
-    <row r="962" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A962" s="2" t="s">
         <v>1582</v>
       </c>
@@ -83798,7 +83829,7 @@
       <c r="AH962" s="4"/>
       <c r="AI962" s="4"/>
     </row>
-    <row r="963" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A963" s="2" t="s">
         <v>1583</v>
       </c>
@@ -83857,7 +83888,7 @@
       <c r="AH963" s="4"/>
       <c r="AI963" s="4"/>
     </row>
-    <row r="964" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A964" s="2" t="s">
         <v>1584</v>
       </c>
@@ -83916,7 +83947,7 @@
       <c r="AH964" s="4"/>
       <c r="AI964" s="4"/>
     </row>
-    <row r="965" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A965" s="2" t="s">
         <v>1585</v>
       </c>
@@ -83975,7 +84006,7 @@
       <c r="AH965" s="4"/>
       <c r="AI965" s="4"/>
     </row>
-    <row r="966" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A966" s="2" t="s">
         <v>1586</v>
       </c>
@@ -84034,7 +84065,7 @@
       <c r="AH966" s="4"/>
       <c r="AI966" s="4"/>
     </row>
-    <row r="967" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A967" s="2" t="s">
         <v>1587</v>
       </c>
@@ -84093,7 +84124,7 @@
       <c r="AH967" s="4"/>
       <c r="AI967" s="4"/>
     </row>
-    <row r="968" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A968" s="2" t="s">
         <v>1588</v>
       </c>
@@ -84152,7 +84183,7 @@
       <c r="AH968" s="4"/>
       <c r="AI968" s="4"/>
     </row>
-    <row r="969" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A969" s="2" t="s">
         <v>1589</v>
       </c>
@@ -84211,7 +84242,7 @@
       <c r="AH969" s="4"/>
       <c r="AI969" s="4"/>
     </row>
-    <row r="970" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A970" s="2" t="s">
         <v>1590</v>
       </c>
@@ -84268,7 +84299,7 @@
       <c r="AH970" s="4"/>
       <c r="AI970" s="4"/>
     </row>
-    <row r="971" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A971" s="2" t="s">
         <v>1591</v>
       </c>
@@ -84325,7 +84356,7 @@
       <c r="AH971" s="4"/>
       <c r="AI971" s="4"/>
     </row>
-    <row r="972" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A972" s="2" t="s">
         <v>1592</v>
       </c>
@@ -84382,7 +84413,7 @@
       <c r="AH972" s="4"/>
       <c r="AI972" s="4"/>
     </row>
-    <row r="973" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A973" s="2" t="s">
         <v>1593</v>
       </c>
@@ -84439,7 +84470,7 @@
       <c r="AH973" s="4"/>
       <c r="AI973" s="4"/>
     </row>
-    <row r="974" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A974" s="2" t="s">
         <v>1595</v>
       </c>
@@ -84496,7 +84527,7 @@
       <c r="AH974" s="4"/>
       <c r="AI974" s="4"/>
     </row>
-    <row r="975" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A975" s="2" t="s">
         <v>1596</v>
       </c>
@@ -84553,7 +84584,7 @@
       <c r="AH975" s="4"/>
       <c r="AI975" s="4"/>
     </row>
-    <row r="976" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A976" s="2" t="s">
         <v>1597</v>
       </c>
@@ -84610,7 +84641,7 @@
       <c r="AH976" s="4"/>
       <c r="AI976" s="4"/>
     </row>
-    <row r="977" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A977" s="2" t="s">
         <v>1598</v>
       </c>
@@ -84667,7 +84698,7 @@
       <c r="AH977" s="4"/>
       <c r="AI977" s="4"/>
     </row>
-    <row r="978" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A978" s="2" t="s">
         <v>1599</v>
       </c>
@@ -84724,7 +84755,7 @@
       <c r="AH978" s="4"/>
       <c r="AI978" s="4"/>
     </row>
-    <row r="979" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A979" s="2" t="s">
         <v>1600</v>
       </c>
@@ -84781,7 +84812,7 @@
       <c r="AH979" s="4"/>
       <c r="AI979" s="4"/>
     </row>
-    <row r="980" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A980" s="2" t="s">
         <v>1601</v>
       </c>
@@ -84838,7 +84869,7 @@
       <c r="AH980" s="4"/>
       <c r="AI980" s="4"/>
     </row>
-    <row r="981" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A981" s="2" t="s">
         <v>1602</v>
       </c>
@@ -84895,7 +84926,7 @@
       <c r="AH981" s="4"/>
       <c r="AI981" s="4"/>
     </row>
-    <row r="982" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A982" s="2" t="s">
         <v>1604</v>
       </c>
@@ -84952,7 +84983,7 @@
       <c r="AH982" s="4"/>
       <c r="AI982" s="4"/>
     </row>
-    <row r="983" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A983" s="2" t="s">
         <v>1605</v>
       </c>
@@ -85009,7 +85040,7 @@
       <c r="AH983" s="4"/>
       <c r="AI983" s="4"/>
     </row>
-    <row r="984" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A984" s="2" t="s">
         <v>1606</v>
       </c>
@@ -85066,7 +85097,7 @@
       <c r="AH984" s="4"/>
       <c r="AI984" s="4"/>
     </row>
-    <row r="985" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A985" s="2" t="s">
         <v>1607</v>
       </c>
@@ -85123,7 +85154,7 @@
       <c r="AH985" s="4"/>
       <c r="AI985" s="4"/>
     </row>
-    <row r="986" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A986" s="2" t="s">
         <v>1608</v>
       </c>
@@ -85180,7 +85211,7 @@
       <c r="AH986" s="4"/>
       <c r="AI986" s="4"/>
     </row>
-    <row r="987" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A987" s="2" t="s">
         <v>1609</v>
       </c>
@@ -85237,7 +85268,7 @@
       <c r="AH987" s="4"/>
       <c r="AI987" s="4"/>
     </row>
-    <row r="988" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A988" s="2" t="s">
         <v>1610</v>
       </c>
@@ -85294,7 +85325,7 @@
       <c r="AH988" s="4"/>
       <c r="AI988" s="4"/>
     </row>
-    <row r="989" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A989" s="2" t="s">
         <v>1612</v>
       </c>
@@ -85351,7 +85382,7 @@
       <c r="AH989" s="4"/>
       <c r="AI989" s="4"/>
     </row>
-    <row r="990" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A990" s="2" t="s">
         <v>1613</v>
       </c>
@@ -85408,7 +85439,7 @@
       <c r="AH990" s="4"/>
       <c r="AI990" s="4"/>
     </row>
-    <row r="991" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A991" s="2" t="s">
         <v>1614</v>
       </c>
@@ -85465,7 +85496,7 @@
       <c r="AH991" s="4"/>
       <c r="AI991" s="4"/>
     </row>
-    <row r="992" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A992" s="2" t="s">
         <v>1616</v>
       </c>
@@ -85522,7 +85553,7 @@
       <c r="AH992" s="4"/>
       <c r="AI992" s="4"/>
     </row>
-    <row r="993" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="2" t="s">
         <v>1618</v>
       </c>
@@ -85579,7 +85610,7 @@
       <c r="AH993" s="4"/>
       <c r="AI993" s="4"/>
     </row>
-    <row r="994" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A994" s="2" t="s">
         <v>1620</v>
       </c>
@@ -85638,7 +85669,7 @@
       <c r="AH994" s="4"/>
       <c r="AI994" s="4"/>
     </row>
-    <row r="995" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A995" s="2" t="s">
         <v>1621</v>
       </c>
@@ -85697,7 +85728,7 @@
       <c r="AH995" s="4"/>
       <c r="AI995" s="4"/>
     </row>
-    <row r="996" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A996" s="2" t="s">
         <v>1622</v>
       </c>
@@ -85754,7 +85785,7 @@
       <c r="AH996" s="4"/>
       <c r="AI996" s="4"/>
     </row>
-    <row r="997" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A997" s="2" t="s">
         <v>1623</v>
       </c>
@@ -85811,7 +85842,7 @@
       <c r="AH997" s="4"/>
       <c r="AI997" s="4"/>
     </row>
-    <row r="998" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A998" s="2" t="s">
         <v>1626</v>
       </c>
@@ -85868,7 +85899,7 @@
       <c r="AH998" s="4"/>
       <c r="AI998" s="4"/>
     </row>
-    <row r="999" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A999" s="2" t="s">
         <v>1630</v>
       </c>
@@ -85925,7 +85956,7 @@
       <c r="AH999" s="4"/>
       <c r="AI999" s="4"/>
     </row>
-    <row r="1000" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1000" s="2" t="s">
         <v>1631</v>
       </c>
@@ -85982,7 +86013,7 @@
       <c r="AH1000" s="4"/>
       <c r="AI1000" s="4"/>
     </row>
-    <row r="1001" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1001" s="2" t="s">
         <v>1632</v>
       </c>
@@ -86039,7 +86070,7 @@
       <c r="AH1001" s="4"/>
       <c r="AI1001" s="4"/>
     </row>
-    <row r="1002" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1002" s="2" t="s">
         <v>1635</v>
       </c>
@@ -86096,7 +86127,7 @@
       <c r="AH1002" s="4"/>
       <c r="AI1002" s="4"/>
     </row>
-    <row r="1003" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1003" s="2" t="s">
         <v>1636</v>
       </c>
@@ -86153,7 +86184,7 @@
       <c r="AH1003" s="4"/>
       <c r="AI1003" s="4"/>
     </row>
-    <row r="1004" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="2" t="s">
         <v>1637</v>
       </c>
@@ -86210,7 +86241,7 @@
       <c r="AH1004" s="4"/>
       <c r="AI1004" s="4"/>
     </row>
-    <row r="1005" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="2" t="s">
         <v>1640</v>
       </c>
@@ -86267,7 +86298,7 @@
       <c r="AH1005" s="4"/>
       <c r="AI1005" s="4"/>
     </row>
-    <row r="1006" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="2" t="s">
         <v>1641</v>
       </c>
@@ -86324,7 +86355,7 @@
       <c r="AH1006" s="4"/>
       <c r="AI1006" s="4"/>
     </row>
-    <row r="1007" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1007" s="2" t="s">
         <v>1644</v>
       </c>
@@ -86381,7 +86412,7 @@
       <c r="AH1007" s="4"/>
       <c r="AI1007" s="4"/>
     </row>
-    <row r="1008" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1008" s="2" t="s">
         <v>1645</v>
       </c>
@@ -86438,7 +86469,7 @@
       <c r="AH1008" s="4"/>
       <c r="AI1008" s="4"/>
     </row>
-    <row r="1009" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1009" s="2" t="s">
         <v>1648</v>
       </c>
@@ -86495,7 +86526,7 @@
       <c r="AH1009" s="4"/>
       <c r="AI1009" s="4"/>
     </row>
-    <row r="1010" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1010" s="2" t="s">
         <v>1652</v>
       </c>
@@ -86552,7 +86583,7 @@
       <c r="AH1010" s="4"/>
       <c r="AI1010" s="4"/>
     </row>
-    <row r="1011" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1011" s="2" t="s">
         <v>1653</v>
       </c>
@@ -86609,7 +86640,7 @@
       <c r="AH1011" s="4"/>
       <c r="AI1011" s="4"/>
     </row>
-    <row r="1012" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1012" s="2" t="s">
         <v>1655</v>
       </c>
@@ -86668,7 +86699,7 @@
       <c r="AH1012" s="4"/>
       <c r="AI1012" s="4"/>
     </row>
-    <row r="1013" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1013" s="2" t="s">
         <v>1656</v>
       </c>
@@ -86727,7 +86758,7 @@
       <c r="AH1013" s="4"/>
       <c r="AI1013" s="4"/>
     </row>
-    <row r="1014" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1014" s="2" t="s">
         <v>1657</v>
       </c>
@@ -86784,7 +86815,7 @@
       <c r="AH1014" s="4"/>
       <c r="AI1014" s="4"/>
     </row>
-    <row r="1015" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1015" s="2" t="s">
         <v>1660</v>
       </c>
@@ -86841,7 +86872,7 @@
       <c r="AH1015" s="4"/>
       <c r="AI1015" s="4"/>
     </row>
-    <row r="1016" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1016" s="2" t="s">
         <v>1661</v>
       </c>
@@ -86898,7 +86929,7 @@
       <c r="AH1016" s="4"/>
       <c r="AI1016" s="4"/>
     </row>
-    <row r="1017" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1017" s="2" t="s">
         <v>1662</v>
       </c>
@@ -86955,7 +86986,7 @@
       <c r="AH1017" s="4"/>
       <c r="AI1017" s="4"/>
     </row>
-    <row r="1018" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1018" s="2" t="s">
         <v>1663</v>
       </c>
@@ -87012,7 +87043,7 @@
       <c r="AH1018" s="4"/>
       <c r="AI1018" s="4"/>
     </row>
-    <row r="1019" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1019" s="2" t="s">
         <v>1664</v>
       </c>
@@ -87069,7 +87100,7 @@
       <c r="AH1019" s="4"/>
       <c r="AI1019" s="4"/>
     </row>
-    <row r="1020" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1020" s="2" t="s">
         <v>1665</v>
       </c>
@@ -87126,7 +87157,7 @@
       <c r="AH1020" s="4"/>
       <c r="AI1020" s="4"/>
     </row>
-    <row r="1021" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1021" s="2" t="s">
         <v>1667</v>
       </c>
@@ -87183,7 +87214,7 @@
       <c r="AH1021" s="4"/>
       <c r="AI1021" s="4"/>
     </row>
-    <row r="1022" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1022" s="2" t="s">
         <v>1669</v>
       </c>
@@ -87240,7 +87271,7 @@
       <c r="AH1022" s="4"/>
       <c r="AI1022" s="4"/>
     </row>
-    <row r="1023" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1023" s="2" t="s">
         <v>1672</v>
       </c>
@@ -87297,7 +87328,7 @@
       <c r="AH1023" s="4"/>
       <c r="AI1023" s="4"/>
     </row>
-    <row r="1024" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1024" s="2" t="s">
         <v>1673</v>
       </c>
@@ -87354,7 +87385,7 @@
       <c r="AH1024" s="4"/>
       <c r="AI1024" s="4"/>
     </row>
-    <row r="1025" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1025" s="2" t="s">
         <v>1675</v>
       </c>
@@ -87411,7 +87442,7 @@
       <c r="AH1025" s="4"/>
       <c r="AI1025" s="4"/>
     </row>
-    <row r="1026" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1026" s="2" t="s">
         <v>1677</v>
       </c>
@@ -87468,7 +87499,7 @@
       <c r="AH1026" s="4"/>
       <c r="AI1026" s="4"/>
     </row>
-    <row r="1027" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1027" s="9" t="s">
         <v>1686</v>
       </c>
@@ -87515,7 +87546,7 @@
       <c r="AH1027" s="4"/>
       <c r="AI1027" s="4"/>
     </row>
-    <row r="1028" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1028" s="9" t="s">
         <v>1687</v>
       </c>
@@ -87562,7 +87593,7 @@
       <c r="AH1028" s="4"/>
       <c r="AI1028" s="4"/>
     </row>
-    <row r="1029" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1029" s="9" t="s">
         <v>1688</v>
       </c>
@@ -87609,7 +87640,7 @@
       <c r="AH1029" s="4"/>
       <c r="AI1029" s="4"/>
     </row>
-    <row r="1030" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1030" s="9" t="s">
         <v>1689</v>
       </c>
@@ -87656,7 +87687,7 @@
       <c r="AH1030" s="4"/>
       <c r="AI1030" s="4"/>
     </row>
-    <row r="1031" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1031" s="9" t="s">
         <v>1690</v>
       </c>
@@ -87703,7 +87734,7 @@
       <c r="AH1031" s="4"/>
       <c r="AI1031" s="4"/>
     </row>
-    <row r="1032" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1032" s="9" t="s">
         <v>1691</v>
       </c>
@@ -87750,7 +87781,7 @@
       <c r="AH1032" s="4"/>
       <c r="AI1032" s="4"/>
     </row>
-    <row r="1033" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1033" s="9" t="s">
         <v>1692</v>
       </c>
@@ -87797,7 +87828,7 @@
       <c r="AH1033" s="4"/>
       <c r="AI1033" s="4"/>
     </row>
-    <row r="1034" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1034" s="9" t="s">
         <v>1693</v>
       </c>
@@ -87844,7 +87875,7 @@
       <c r="AH1034" s="4"/>
       <c r="AI1034" s="4"/>
     </row>
-    <row r="1035" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1035" s="9" t="s">
         <v>1694</v>
       </c>
@@ -87891,7 +87922,7 @@
       <c r="AH1035" s="4"/>
       <c r="AI1035" s="4"/>
     </row>
-    <row r="1036" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1036" s="9" t="s">
         <v>1695</v>
       </c>
@@ -87938,7 +87969,7 @@
       <c r="AH1036" s="4"/>
       <c r="AI1036" s="4"/>
     </row>
-    <row r="1037" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1037" s="9" t="s">
         <v>1696</v>
       </c>
@@ -87985,7 +88016,7 @@
       <c r="AH1037" s="4"/>
       <c r="AI1037" s="4"/>
     </row>
-    <row r="1038" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1038" s="9" t="s">
         <v>1697</v>
       </c>
@@ -88032,7 +88063,7 @@
       <c r="AH1038" s="4"/>
       <c r="AI1038" s="4"/>
     </row>
-    <row r="1039" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1039" s="9" t="s">
         <v>1698</v>
       </c>
@@ -88080,18 +88111,42 @@
       <c r="AI1039" s="4"/>
     </row>
     <row r="1040" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1040" s="2"/>
-      <c r="B1040" s="2"/>
-      <c r="C1040" s="2"/>
-      <c r="D1040" s="4"/>
-      <c r="E1040" s="5"/>
-      <c r="F1040" s="4"/>
-      <c r="G1040" s="4"/>
-      <c r="H1040" s="4"/>
-      <c r="I1040" s="4"/>
-      <c r="J1040" s="4"/>
-      <c r="K1040" s="4"/>
-      <c r="L1040" s="4"/>
+      <c r="A1040" s="2" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B1040" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1040" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D1040" s="4">
+        <v>43206446</v>
+      </c>
+      <c r="E1040" s="5" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F1040" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="G1040" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1040" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1040" s="4">
+        <v>599.99</v>
+      </c>
+      <c r="J1040" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1040" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1040" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="M1040" s="4"/>
       <c r="N1040" s="4"/>
       <c r="O1040" s="4"/>
@@ -88116,8 +88171,502 @@
       <c r="AH1040" s="4"/>
       <c r="AI1040" s="4"/>
     </row>
+    <row r="1041" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1041" s="2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B1041" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1041" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D1041" s="4">
+        <v>43206446</v>
+      </c>
+      <c r="E1041" s="5" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F1041" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="G1041" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1041" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1041" s="4">
+        <v>599.99</v>
+      </c>
+      <c r="J1041" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1041" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1041" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1041" s="4"/>
+      <c r="N1041" s="4"/>
+      <c r="O1041" s="4"/>
+      <c r="P1041" s="4"/>
+      <c r="Q1041" s="4"/>
+      <c r="R1041" s="4"/>
+      <c r="S1041" s="4"/>
+      <c r="T1041" s="4"/>
+      <c r="U1041" s="4"/>
+      <c r="V1041" s="4"/>
+      <c r="W1041" s="4"/>
+      <c r="X1041" s="4"/>
+      <c r="Y1041" s="4"/>
+      <c r="Z1041" s="4"/>
+      <c r="AA1041" s="4"/>
+      <c r="AB1041" s="4"/>
+      <c r="AC1041" s="4"/>
+      <c r="AD1041" s="4"/>
+      <c r="AE1041" s="4"/>
+      <c r="AF1041" s="4"/>
+      <c r="AG1041" s="4"/>
+      <c r="AH1041" s="4"/>
+      <c r="AI1041" s="4"/>
+    </row>
+    <row r="1042" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1042" s="2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B1042" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1042" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D1042" s="4">
+        <v>43206446</v>
+      </c>
+      <c r="E1042" s="5" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F1042" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="G1042" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1042" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1042" s="4">
+        <v>599.99</v>
+      </c>
+      <c r="J1042" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1042" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1042" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1042" s="4"/>
+      <c r="N1042" s="4"/>
+      <c r="O1042" s="4"/>
+      <c r="P1042" s="4"/>
+      <c r="Q1042" s="4"/>
+      <c r="R1042" s="4"/>
+      <c r="S1042" s="4"/>
+      <c r="T1042" s="4"/>
+      <c r="U1042" s="4"/>
+      <c r="V1042" s="4"/>
+      <c r="W1042" s="4"/>
+      <c r="X1042" s="4"/>
+      <c r="Y1042" s="4"/>
+      <c r="Z1042" s="4"/>
+      <c r="AA1042" s="4"/>
+      <c r="AB1042" s="4"/>
+      <c r="AC1042" s="4"/>
+      <c r="AD1042" s="4"/>
+      <c r="AE1042" s="4"/>
+      <c r="AF1042" s="4"/>
+      <c r="AG1042" s="4"/>
+      <c r="AH1042" s="4"/>
+      <c r="AI1042" s="4"/>
+    </row>
+    <row r="1043" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1043" s="2" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B1043" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1043" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D1043" s="4">
+        <v>43206446</v>
+      </c>
+      <c r="E1043" s="5" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F1043" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="G1043" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1043" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1043" s="4">
+        <v>599.99</v>
+      </c>
+      <c r="J1043" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1043" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1043" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1043" s="4"/>
+      <c r="N1043" s="4"/>
+      <c r="O1043" s="4"/>
+      <c r="P1043" s="4"/>
+      <c r="Q1043" s="4"/>
+      <c r="R1043" s="4"/>
+      <c r="S1043" s="4"/>
+      <c r="T1043" s="4"/>
+      <c r="U1043" s="4"/>
+      <c r="V1043" s="4"/>
+      <c r="W1043" s="4"/>
+      <c r="X1043" s="4"/>
+      <c r="Y1043" s="4"/>
+      <c r="Z1043" s="4"/>
+      <c r="AA1043" s="4"/>
+      <c r="AB1043" s="4"/>
+      <c r="AC1043" s="4"/>
+      <c r="AD1043" s="4"/>
+      <c r="AE1043" s="4"/>
+      <c r="AF1043" s="4"/>
+      <c r="AG1043" s="4"/>
+      <c r="AH1043" s="4"/>
+      <c r="AI1043" s="4"/>
+    </row>
+    <row r="1044" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1044" s="2" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B1044" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1044" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D1044" s="4">
+        <v>43206446</v>
+      </c>
+      <c r="E1044" s="5" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F1044" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="G1044" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1044" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1044" s="4">
+        <v>599.99</v>
+      </c>
+      <c r="J1044" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1044" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1044" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1044" s="4"/>
+      <c r="N1044" s="4"/>
+      <c r="O1044" s="4"/>
+      <c r="P1044" s="4"/>
+      <c r="Q1044" s="4"/>
+      <c r="R1044" s="4"/>
+      <c r="S1044" s="4"/>
+      <c r="T1044" s="4"/>
+      <c r="U1044" s="4"/>
+      <c r="V1044" s="4"/>
+      <c r="W1044" s="4"/>
+      <c r="X1044" s="4"/>
+      <c r="Y1044" s="4"/>
+      <c r="Z1044" s="4"/>
+      <c r="AA1044" s="4"/>
+      <c r="AB1044" s="4"/>
+      <c r="AC1044" s="4"/>
+      <c r="AD1044" s="4"/>
+      <c r="AE1044" s="4"/>
+      <c r="AF1044" s="4"/>
+      <c r="AG1044" s="4"/>
+      <c r="AH1044" s="4"/>
+      <c r="AI1044" s="4"/>
+    </row>
+    <row r="1045" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1045" s="2" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B1045" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C1045" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="D1045" s="4">
+        <v>54111405</v>
+      </c>
+      <c r="E1045" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="F1045" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="G1045" s="4" t="s">
+        <v>538</v>
+      </c>
+      <c r="H1045" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1045" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J1045" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1045" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1045" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1045" s="4"/>
+      <c r="N1045" s="4"/>
+      <c r="O1045" s="4"/>
+      <c r="P1045" s="4"/>
+      <c r="Q1045" s="4"/>
+      <c r="R1045" s="4"/>
+      <c r="S1045" s="4"/>
+      <c r="T1045" s="4"/>
+      <c r="U1045" s="4"/>
+      <c r="V1045" s="4"/>
+      <c r="W1045" s="4"/>
+      <c r="X1045" s="4"/>
+      <c r="Y1045" s="4"/>
+      <c r="Z1045" s="4"/>
+      <c r="AA1045" s="4"/>
+      <c r="AB1045" s="4"/>
+      <c r="AC1045" s="4"/>
+      <c r="AD1045" s="4"/>
+      <c r="AE1045" s="4"/>
+      <c r="AF1045" s="4"/>
+      <c r="AG1045" s="4"/>
+      <c r="AH1045" s="4"/>
+      <c r="AI1045" s="4"/>
+    </row>
+    <row r="1046" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1046" s="2" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B1046" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C1046" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="D1046" s="4">
+        <v>54111405</v>
+      </c>
+      <c r="E1046" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="F1046" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="G1046" s="4" t="s">
+        <v>1704</v>
+      </c>
+      <c r="H1046" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1046" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J1046" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1046" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1046" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1046" s="4"/>
+      <c r="N1046" s="4"/>
+      <c r="O1046" s="4"/>
+      <c r="P1046" s="4"/>
+      <c r="Q1046" s="4"/>
+      <c r="R1046" s="4"/>
+      <c r="S1046" s="4"/>
+      <c r="T1046" s="4"/>
+      <c r="U1046" s="4"/>
+      <c r="V1046" s="4"/>
+      <c r="W1046" s="4"/>
+      <c r="X1046" s="4"/>
+      <c r="Y1046" s="4"/>
+      <c r="Z1046" s="4"/>
+      <c r="AA1046" s="4"/>
+      <c r="AB1046" s="4"/>
+      <c r="AC1046" s="4"/>
+      <c r="AD1046" s="4"/>
+      <c r="AE1046" s="4"/>
+      <c r="AF1046" s="4"/>
+      <c r="AG1046" s="4"/>
+      <c r="AH1046" s="4"/>
+      <c r="AI1046" s="4"/>
+    </row>
+    <row r="1047" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1047" s="2" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B1047" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C1047" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="D1047" s="4">
+        <v>54111405</v>
+      </c>
+      <c r="E1047" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="F1047" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="G1047" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="H1047" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1047" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J1047" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1047" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1047" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1047" s="4"/>
+      <c r="N1047" s="4"/>
+      <c r="O1047" s="4"/>
+      <c r="P1047" s="4"/>
+      <c r="Q1047" s="4"/>
+      <c r="R1047" s="4"/>
+      <c r="S1047" s="4"/>
+      <c r="T1047" s="4"/>
+      <c r="U1047" s="4"/>
+      <c r="V1047" s="4"/>
+      <c r="W1047" s="4"/>
+      <c r="X1047" s="4"/>
+      <c r="Y1047" s="4"/>
+      <c r="Z1047" s="4"/>
+      <c r="AA1047" s="4"/>
+      <c r="AB1047" s="4"/>
+      <c r="AC1047" s="4"/>
+      <c r="AD1047" s="4"/>
+      <c r="AE1047" s="4"/>
+      <c r="AF1047" s="4"/>
+      <c r="AG1047" s="4"/>
+      <c r="AH1047" s="4"/>
+      <c r="AI1047" s="4"/>
+    </row>
+    <row r="1048" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1048" s="2" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B1048" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C1048" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="D1048" s="4">
+        <v>54111405</v>
+      </c>
+      <c r="E1048" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="F1048" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="G1048" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1048" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1048" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J1048" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1048" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1048" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1048" s="4"/>
+      <c r="N1048" s="4"/>
+      <c r="O1048" s="4"/>
+      <c r="P1048" s="4"/>
+      <c r="Q1048" s="4"/>
+      <c r="R1048" s="4"/>
+      <c r="S1048" s="4"/>
+      <c r="T1048" s="4"/>
+      <c r="U1048" s="4"/>
+      <c r="V1048" s="4"/>
+      <c r="W1048" s="4"/>
+      <c r="X1048" s="4"/>
+      <c r="Y1048" s="4"/>
+      <c r="Z1048" s="4"/>
+      <c r="AA1048" s="4"/>
+      <c r="AB1048" s="4"/>
+      <c r="AC1048" s="4"/>
+      <c r="AD1048" s="4"/>
+      <c r="AE1048" s="4"/>
+      <c r="AF1048" s="4"/>
+      <c r="AG1048" s="4"/>
+      <c r="AH1048" s="4"/>
+      <c r="AI1048" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R1026" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R1048" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="CORRE 5"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF474D8F-B84D-4929-82CE-0BFC68E604F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498574B8-27A2-4ACC-8265-195A5CB72AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12219" uniqueCount="1709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13245" uniqueCount="1709">
   <si>
     <t>IMAGEM</t>
   </si>
@@ -51495,7 +51495,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="455" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>620</v>
       </c>
@@ -51556,7 +51556,7 @@
       <c r="AH455" s="4"/>
       <c r="AI455" s="4"/>
     </row>
-    <row r="456" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>623</v>
       </c>
@@ -51617,7 +51617,7 @@
       <c r="AH456" s="4"/>
       <c r="AI456" s="4"/>
     </row>
-    <row r="457" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>625</v>
       </c>
@@ -51678,7 +51678,7 @@
       <c r="AH457" s="4"/>
       <c r="AI457" s="4"/>
     </row>
-    <row r="458" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>627</v>
       </c>
@@ -77262,7 +77262,7 @@
       <c r="AH853" s="4"/>
       <c r="AI853" s="4"/>
     </row>
-    <row r="854" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A854" s="2" t="s">
         <v>1315</v>
       </c>
@@ -77323,7 +77323,7 @@
       <c r="AH854" s="4"/>
       <c r="AI854" s="4"/>
     </row>
-    <row r="855" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A855" s="2" t="s">
         <v>1317</v>
       </c>
@@ -88110,7 +88110,7 @@
       <c r="AH1039" s="4"/>
       <c r="AI1039" s="4"/>
     </row>
-    <row r="1040" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1040" s="2" t="s">
         <v>1702</v>
       </c>
@@ -88171,7 +88171,7 @@
       <c r="AH1040" s="4"/>
       <c r="AI1040" s="4"/>
     </row>
-    <row r="1041" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1041" s="2" t="s">
         <v>1699</v>
       </c>
@@ -88232,7 +88232,7 @@
       <c r="AH1041" s="4"/>
       <c r="AI1041" s="4"/>
     </row>
-    <row r="1042" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1042" s="2" t="s">
         <v>1700</v>
       </c>
@@ -88293,7 +88293,7 @@
       <c r="AH1042" s="4"/>
       <c r="AI1042" s="4"/>
     </row>
-    <row r="1043" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1043" s="2" t="s">
         <v>1701</v>
       </c>
@@ -88354,7 +88354,7 @@
       <c r="AH1043" s="4"/>
       <c r="AI1043" s="4"/>
     </row>
-    <row r="1044" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1044" s="2" t="s">
         <v>1703</v>
       </c>
@@ -88415,7 +88415,7 @@
       <c r="AH1044" s="4"/>
       <c r="AI1044" s="4"/>
     </row>
-    <row r="1045" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1045" s="2" t="s">
         <v>1705</v>
       </c>
@@ -88476,7 +88476,7 @@
       <c r="AH1045" s="4"/>
       <c r="AI1045" s="4"/>
     </row>
-    <row r="1046" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1046" s="2" t="s">
         <v>1706</v>
       </c>
@@ -88537,7 +88537,7 @@
       <c r="AH1046" s="4"/>
       <c r="AI1046" s="4"/>
     </row>
-    <row r="1047" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1047" s="2" t="s">
         <v>1707</v>
       </c>
@@ -88598,7 +88598,7 @@
       <c r="AH1047" s="4"/>
       <c r="AI1047" s="4"/>
     </row>
-    <row r="1048" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1048" s="2" t="s">
         <v>1708</v>
       </c>
@@ -88663,7 +88663,7 @@
   <autoFilter ref="A1:R1048" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="4">
       <filters>
-        <filter val="CORRE 5"/>
+        <filter val="POS/CORRE"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498574B8-27A2-4ACC-8265-195A5CB72AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823094DE-B736-4094-8315-AE9803FE1368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="corre" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produtos!$A$1:$R$1048</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produtos!$A$1:$R$1051</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13245" uniqueCount="1709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13275" uniqueCount="1714">
   <si>
     <t>IMAGEM</t>
   </si>
@@ -5164,6 +5164,21 @@
   </si>
   <si>
     <t>54111405_VDEMLT</t>
+  </si>
+  <si>
+    <t>LUNMHO</t>
+  </si>
+  <si>
+    <t>CH/VMH</t>
+  </si>
+  <si>
+    <t>43447473_LUNMHO</t>
+  </si>
+  <si>
+    <t>43447473_MARBRI</t>
+  </si>
+  <si>
+    <t>43447473_CH_VMH</t>
   </si>
 </sst>
 </file>
@@ -5627,7 +5642,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:AI1048"/>
+  <dimension ref="A1:AI1051"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" style="6" customWidth="1"/>
@@ -51495,7 +51510,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="455" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>620</v>
       </c>
@@ -51556,7 +51571,7 @@
       <c r="AH455" s="4"/>
       <c r="AI455" s="4"/>
     </row>
-    <row r="456" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>623</v>
       </c>
@@ -51617,7 +51632,7 @@
       <c r="AH456" s="4"/>
       <c r="AI456" s="4"/>
     </row>
-    <row r="457" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>625</v>
       </c>
@@ -51678,7 +51693,7 @@
       <c r="AH457" s="4"/>
       <c r="AI457" s="4"/>
     </row>
-    <row r="458" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>627</v>
       </c>
@@ -77506,7 +77521,7 @@
       <c r="AH857" s="4"/>
       <c r="AI857" s="4"/>
     </row>
-    <row r="858" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A858" s="2" t="s">
         <v>1324</v>
       </c>
@@ -77567,7 +77582,7 @@
       <c r="AH858" s="4"/>
       <c r="AI858" s="4"/>
     </row>
-    <row r="859" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859" s="2" t="s">
         <v>1326</v>
       </c>
@@ -77628,7 +77643,7 @@
       <c r="AH859" s="4"/>
       <c r="AI859" s="4"/>
     </row>
-    <row r="860" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860" s="2" t="s">
         <v>1327</v>
       </c>
@@ -77689,7 +77704,7 @@
       <c r="AH860" s="4"/>
       <c r="AI860" s="4"/>
     </row>
-    <row r="861" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A861" s="2" t="s">
         <v>1329</v>
       </c>
@@ -77750,9 +77765,9 @@
       <c r="AH861" s="4"/>
       <c r="AI861" s="4"/>
     </row>
-    <row r="862" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A862" s="2" t="s">
-        <v>1330</v>
+        <v>1711</v>
       </c>
       <c r="B862" s="2" t="s">
         <v>36</v>
@@ -77770,7 +77785,7 @@
         <v>45</v>
       </c>
       <c r="G862" s="4" t="s">
-        <v>1331</v>
+        <v>1709</v>
       </c>
       <c r="H862" s="4" t="s">
         <v>46</v>
@@ -77779,13 +77794,13 @@
         <v>499.99</v>
       </c>
       <c r="J862" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K862" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L862" s="4" t="s">
-        <v>494</v>
+        <v>44</v>
       </c>
       <c r="M862" s="4"/>
       <c r="N862" s="4"/>
@@ -77811,9 +77826,9 @@
       <c r="AH862" s="4"/>
       <c r="AI862" s="4"/>
     </row>
-    <row r="863" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A863" s="2" t="s">
-        <v>1332</v>
+        <v>1712</v>
       </c>
       <c r="B863" s="2" t="s">
         <v>36</v>
@@ -77831,7 +77846,7 @@
         <v>45</v>
       </c>
       <c r="G863" s="4" t="s">
-        <v>1333</v>
+        <v>119</v>
       </c>
       <c r="H863" s="4" t="s">
         <v>46</v>
@@ -77840,13 +77855,13 @@
         <v>499.99</v>
       </c>
       <c r="J863" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K863" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L863" s="4" t="s">
-        <v>494</v>
+        <v>44</v>
       </c>
       <c r="M863" s="4"/>
       <c r="N863" s="4"/>
@@ -77872,39 +77887,39 @@
       <c r="AH863" s="4"/>
       <c r="AI863" s="4"/>
     </row>
-    <row r="864" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A864" s="2" t="s">
-        <v>1334</v>
+        <v>1713</v>
       </c>
       <c r="B864" s="2" t="s">
-        <v>698</v>
+        <v>36</v>
       </c>
       <c r="C864" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D864" s="4" t="s">
-        <v>958</v>
+        <v>1307</v>
+      </c>
+      <c r="D864" s="4">
+        <v>43447473</v>
       </c>
       <c r="E864" s="5" t="s">
-        <v>1335</v>
+        <v>1325</v>
       </c>
       <c r="F864" s="4" t="s">
-        <v>708</v>
+        <v>45</v>
       </c>
       <c r="G864" s="4" t="s">
-        <v>1336</v>
+        <v>1710</v>
       </c>
       <c r="H864" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I864" s="4">
-        <v>119.99</v>
+        <v>499.99</v>
       </c>
       <c r="J864" s="4" t="s">
         <v>43</v>
       </c>
       <c r="K864" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L864" s="4" t="s">
         <v>44</v>
@@ -77933,42 +77948,42 @@
       <c r="AH864" s="4"/>
       <c r="AI864" s="4"/>
     </row>
-    <row r="865" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865" s="2" t="s">
-        <v>1337</v>
+        <v>1330</v>
       </c>
       <c r="B865" s="2" t="s">
-        <v>698</v>
+        <v>36</v>
       </c>
       <c r="C865" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D865" s="4" t="s">
-        <v>966</v>
+        <v>1307</v>
+      </c>
+      <c r="D865" s="4">
+        <v>43447473</v>
       </c>
       <c r="E865" s="5" t="s">
-        <v>967</v>
+        <v>1325</v>
       </c>
       <c r="F865" s="4" t="s">
-        <v>708</v>
+        <v>45</v>
       </c>
       <c r="G865" s="4" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="H865" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I865" s="4">
-        <v>109.99</v>
+        <v>499.99</v>
       </c>
       <c r="J865" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K865" s="4" t="s">
         <v>42</v>
       </c>
       <c r="L865" s="4" t="s">
-        <v>44</v>
+        <v>494</v>
       </c>
       <c r="M865" s="4"/>
       <c r="N865" s="4"/>
@@ -77994,42 +78009,42 @@
       <c r="AH865" s="4"/>
       <c r="AI865" s="4"/>
     </row>
-    <row r="866" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A866" s="2" t="s">
-        <v>1338</v>
+        <v>1332</v>
       </c>
       <c r="B866" s="2" t="s">
-        <v>698</v>
+        <v>36</v>
       </c>
       <c r="C866" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D866" s="4" t="s">
-        <v>974</v>
+        <v>1307</v>
+      </c>
+      <c r="D866" s="4">
+        <v>43447473</v>
       </c>
       <c r="E866" s="5" t="s">
-        <v>1339</v>
+        <v>1325</v>
       </c>
       <c r="F866" s="4" t="s">
-        <v>708</v>
+        <v>45</v>
       </c>
       <c r="G866" s="4" t="s">
-        <v>1340</v>
+        <v>1333</v>
       </c>
       <c r="H866" s="4" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="I866" s="4">
-        <v>169.99</v>
+        <v>499.99</v>
       </c>
       <c r="J866" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K866" s="4" t="s">
         <v>42</v>
       </c>
       <c r="L866" s="4" t="s">
-        <v>44</v>
+        <v>494</v>
       </c>
       <c r="M866" s="4"/>
       <c r="N866" s="4"/>
@@ -78057,7 +78072,7 @@
     </row>
     <row r="867" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867" s="2" t="s">
-        <v>1341</v>
+        <v>1334</v>
       </c>
       <c r="B867" s="2" t="s">
         <v>698</v>
@@ -78066,19 +78081,19 @@
         <v>37</v>
       </c>
       <c r="D867" s="4" t="s">
-        <v>991</v>
+        <v>958</v>
       </c>
       <c r="E867" s="5" t="s">
-        <v>1342</v>
+        <v>1335</v>
       </c>
       <c r="F867" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G867" s="4" t="s">
-        <v>1343</v>
+        <v>1336</v>
       </c>
       <c r="H867" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I867" s="4">
         <v>119.99</v>
@@ -78118,7 +78133,7 @@
     </row>
     <row r="868" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868" s="2" t="s">
-        <v>1344</v>
+        <v>1337</v>
       </c>
       <c r="B868" s="2" t="s">
         <v>698</v>
@@ -78127,19 +78142,19 @@
         <v>37</v>
       </c>
       <c r="D868" s="4" t="s">
-        <v>997</v>
+        <v>966</v>
       </c>
       <c r="E868" s="5" t="s">
-        <v>998</v>
+        <v>967</v>
       </c>
       <c r="F868" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G868" s="4" t="s">
-        <v>1343</v>
+        <v>1336</v>
       </c>
       <c r="H868" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I868" s="4">
         <v>109.99</v>
@@ -78179,31 +78194,31 @@
     </row>
     <row r="869" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869" s="2" t="s">
-        <v>1345</v>
+        <v>1338</v>
       </c>
       <c r="B869" s="2" t="s">
         <v>698</v>
       </c>
       <c r="C869" s="2" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="D869" s="4" t="s">
-        <v>1072</v>
+        <v>974</v>
       </c>
       <c r="E869" s="5" t="s">
-        <v>1073</v>
+        <v>1339</v>
       </c>
       <c r="F869" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G869" s="4" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="H869" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I869" s="4">
-        <v>119.99</v>
+        <v>169.99</v>
       </c>
       <c r="J869" s="4" t="s">
         <v>43</v>
@@ -78240,28 +78255,28 @@
     </row>
     <row r="870" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870" s="2" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="B870" s="2" t="s">
         <v>698</v>
       </c>
       <c r="C870" s="2" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="D870" s="4" t="s">
-        <v>1072</v>
+        <v>991</v>
       </c>
       <c r="E870" s="5" t="s">
-        <v>1073</v>
+        <v>1342</v>
       </c>
       <c r="F870" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G870" s="4" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="H870" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I870" s="4">
         <v>119.99</v>
@@ -78301,31 +78316,31 @@
     </row>
     <row r="871" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="2" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
       <c r="B871" s="2" t="s">
         <v>698</v>
       </c>
       <c r="C871" s="2" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="D871" s="4" t="s">
-        <v>1350</v>
+        <v>997</v>
       </c>
       <c r="E871" s="5" t="s">
-        <v>1351</v>
+        <v>998</v>
       </c>
       <c r="F871" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G871" s="4" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="H871" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I871" s="4">
-        <v>149.99</v>
+        <v>109.99</v>
       </c>
       <c r="J871" s="4" t="s">
         <v>43</v>
@@ -78362,7 +78377,7 @@
     </row>
     <row r="872" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872" s="2" t="s">
-        <v>1352</v>
+        <v>1345</v>
       </c>
       <c r="B872" s="2" t="s">
         <v>698</v>
@@ -78371,10 +78386,10 @@
         <v>109</v>
       </c>
       <c r="D872" s="4" t="s">
-        <v>1079</v>
+        <v>1072</v>
       </c>
       <c r="E872" s="5" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="F872" s="4" t="s">
         <v>708</v>
@@ -78386,7 +78401,7 @@
         <v>41</v>
       </c>
       <c r="I872" s="4">
-        <v>159.99</v>
+        <v>119.99</v>
       </c>
       <c r="J872" s="4" t="s">
         <v>43</v>
@@ -78423,7 +78438,7 @@
     </row>
     <row r="873" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873" s="2" t="s">
-        <v>1353</v>
+        <v>1347</v>
       </c>
       <c r="B873" s="2" t="s">
         <v>698</v>
@@ -78432,22 +78447,22 @@
         <v>109</v>
       </c>
       <c r="D873" s="4" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="E873" s="5" t="s">
-        <v>1354</v>
+        <v>1073</v>
       </c>
       <c r="F873" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G873" s="4" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="H873" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I873" s="4">
-        <v>139.99</v>
+        <v>119.99</v>
       </c>
       <c r="J873" s="4" t="s">
         <v>43</v>
@@ -78484,7 +78499,7 @@
     </row>
     <row r="874" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A874" s="2" t="s">
-        <v>1355</v>
+        <v>1349</v>
       </c>
       <c r="B874" s="2" t="s">
         <v>698</v>
@@ -78493,22 +78508,22 @@
         <v>109</v>
       </c>
       <c r="D874" s="4" t="s">
-        <v>1082</v>
+        <v>1350</v>
       </c>
       <c r="E874" s="5" t="s">
-        <v>1083</v>
+        <v>1351</v>
       </c>
       <c r="F874" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G874" s="4" t="s">
-        <v>1356</v>
+        <v>1346</v>
       </c>
       <c r="H874" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I874" s="4">
-        <v>139.99</v>
+        <v>149.99</v>
       </c>
       <c r="J874" s="4" t="s">
         <v>43</v>
@@ -78545,7 +78560,7 @@
     </row>
     <row r="875" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A875" s="2" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="B875" s="2" t="s">
         <v>698</v>
@@ -78554,22 +78569,22 @@
         <v>109</v>
       </c>
       <c r="D875" s="4" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="E875" s="5" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="F875" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G875" s="4" t="s">
-        <v>1358</v>
+        <v>1346</v>
       </c>
       <c r="H875" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I875" s="4">
-        <v>139.99</v>
+        <v>159.99</v>
       </c>
       <c r="J875" s="4" t="s">
         <v>43</v>
@@ -78606,7 +78621,7 @@
     </row>
     <row r="876" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876" s="2" t="s">
-        <v>1359</v>
+        <v>1353</v>
       </c>
       <c r="B876" s="2" t="s">
         <v>698</v>
@@ -78615,13 +78630,13 @@
         <v>109</v>
       </c>
       <c r="D876" s="4" t="s">
-        <v>1090</v>
+        <v>1075</v>
       </c>
       <c r="E876" s="5" t="s">
-        <v>1360</v>
+        <v>1354</v>
       </c>
       <c r="F876" s="4" t="s">
-        <v>1361</v>
+        <v>708</v>
       </c>
       <c r="G876" s="4" t="s">
         <v>1346</v>
@@ -78630,7 +78645,7 @@
         <v>41</v>
       </c>
       <c r="I876" s="4">
-        <v>99.99</v>
+        <v>139.99</v>
       </c>
       <c r="J876" s="4" t="s">
         <v>43</v>
@@ -78667,7 +78682,7 @@
     </row>
     <row r="877" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="2" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B877" s="2" t="s">
         <v>698</v>
@@ -78676,22 +78691,22 @@
         <v>109</v>
       </c>
       <c r="D877" s="4" t="s">
-        <v>1101</v>
+        <v>1082</v>
       </c>
       <c r="E877" s="5" t="s">
-        <v>1363</v>
+        <v>1083</v>
       </c>
       <c r="F877" s="4" t="s">
-        <v>1361</v>
+        <v>708</v>
       </c>
       <c r="G877" s="4" t="s">
-        <v>76</v>
+        <v>1356</v>
       </c>
       <c r="H877" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I877" s="4">
-        <v>89.99</v>
+        <v>139.99</v>
       </c>
       <c r="J877" s="4" t="s">
         <v>43</v>
@@ -78728,7 +78743,7 @@
     </row>
     <row r="878" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878" s="2" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
       <c r="B878" s="2" t="s">
         <v>698</v>
@@ -78737,22 +78752,22 @@
         <v>109</v>
       </c>
       <c r="D878" s="4" t="s">
-        <v>1101</v>
+        <v>1082</v>
       </c>
       <c r="E878" s="5" t="s">
-        <v>1363</v>
+        <v>1083</v>
       </c>
       <c r="F878" s="4" t="s">
-        <v>1361</v>
+        <v>708</v>
       </c>
       <c r="G878" s="4" t="s">
-        <v>1346</v>
+        <v>1358</v>
       </c>
       <c r="H878" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I878" s="4">
-        <v>89.99</v>
+        <v>139.99</v>
       </c>
       <c r="J878" s="4" t="s">
         <v>43</v>
@@ -78789,7 +78804,7 @@
     </row>
     <row r="879" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879" s="2" t="s">
-        <v>1365</v>
+        <v>1359</v>
       </c>
       <c r="B879" s="2" t="s">
         <v>698</v>
@@ -78798,22 +78813,22 @@
         <v>109</v>
       </c>
       <c r="D879" s="4" t="s">
-        <v>1101</v>
+        <v>1090</v>
       </c>
       <c r="E879" s="5" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
       <c r="F879" s="4" t="s">
         <v>1361</v>
       </c>
       <c r="G879" s="4" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="H879" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I879" s="4">
-        <v>89.99</v>
+        <v>99.99</v>
       </c>
       <c r="J879" s="4" t="s">
         <v>43</v>
@@ -78850,7 +78865,7 @@
     </row>
     <row r="880" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880" s="2" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="B880" s="2" t="s">
         <v>698</v>
@@ -78865,10 +78880,10 @@
         <v>1363</v>
       </c>
       <c r="F880" s="4" t="s">
-        <v>708</v>
+        <v>1361</v>
       </c>
       <c r="G880" s="4" t="s">
-        <v>384</v>
+        <v>76</v>
       </c>
       <c r="H880" s="4" t="s">
         <v>41</v>
@@ -78911,7 +78926,7 @@
     </row>
     <row r="881" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881" s="2" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="B881" s="2" t="s">
         <v>698</v>
@@ -78920,10 +78935,10 @@
         <v>109</v>
       </c>
       <c r="D881" s="4" t="s">
-        <v>1368</v>
+        <v>1101</v>
       </c>
       <c r="E881" s="5" t="s">
-        <v>1369</v>
+        <v>1363</v>
       </c>
       <c r="F881" s="4" t="s">
         <v>1361</v>
@@ -78935,7 +78950,7 @@
         <v>41</v>
       </c>
       <c r="I881" s="4">
-        <v>79.989999999999995</v>
+        <v>89.99</v>
       </c>
       <c r="J881" s="4" t="s">
         <v>43</v>
@@ -78972,7 +78987,7 @@
     </row>
     <row r="882" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882" s="2" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="B882" s="2" t="s">
         <v>698</v>
@@ -78981,10 +78996,10 @@
         <v>109</v>
       </c>
       <c r="D882" s="4" t="s">
-        <v>1368</v>
+        <v>1101</v>
       </c>
       <c r="E882" s="5" t="s">
-        <v>1369</v>
+        <v>1363</v>
       </c>
       <c r="F882" s="4" t="s">
         <v>1361</v>
@@ -78996,7 +79011,7 @@
         <v>41</v>
       </c>
       <c r="I882" s="4">
-        <v>79.989999999999995</v>
+        <v>89.99</v>
       </c>
       <c r="J882" s="4" t="s">
         <v>43</v>
@@ -79033,7 +79048,7 @@
     </row>
     <row r="883" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="2" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
       <c r="B883" s="2" t="s">
         <v>698</v>
@@ -79042,22 +79057,22 @@
         <v>109</v>
       </c>
       <c r="D883" s="4" t="s">
-        <v>1123</v>
+        <v>1101</v>
       </c>
       <c r="E883" s="5" t="s">
-        <v>1124</v>
+        <v>1363</v>
       </c>
       <c r="F883" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G883" s="4" t="s">
-        <v>1346</v>
+        <v>384</v>
       </c>
       <c r="H883" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I883" s="4">
-        <v>169.99</v>
+        <v>89.99</v>
       </c>
       <c r="J883" s="4" t="s">
         <v>43</v>
@@ -79094,7 +79109,7 @@
     </row>
     <row r="884" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A884" s="2" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
       <c r="B884" s="2" t="s">
         <v>698</v>
@@ -79103,22 +79118,22 @@
         <v>109</v>
       </c>
       <c r="D884" s="4" t="s">
-        <v>1123</v>
+        <v>1368</v>
       </c>
       <c r="E884" s="5" t="s">
-        <v>1124</v>
+        <v>1369</v>
       </c>
       <c r="F884" s="4" t="s">
-        <v>708</v>
+        <v>1361</v>
       </c>
       <c r="G884" s="4" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="H884" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I884" s="4">
-        <v>169.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J884" s="4" t="s">
         <v>43</v>
@@ -79155,7 +79170,7 @@
     </row>
     <row r="885" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A885" s="2" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="B885" s="2" t="s">
         <v>698</v>
@@ -79164,22 +79179,22 @@
         <v>109</v>
       </c>
       <c r="D885" s="4" t="s">
-        <v>1132</v>
+        <v>1368</v>
       </c>
       <c r="E885" s="5" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
       <c r="F885" s="4" t="s">
-        <v>708</v>
+        <v>1361</v>
       </c>
       <c r="G885" s="4" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="H885" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I885" s="4">
-        <v>199.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J885" s="4" t="s">
         <v>43</v>
@@ -79216,7 +79231,7 @@
     </row>
     <row r="886" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="2" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="B886" s="2" t="s">
         <v>698</v>
@@ -79225,22 +79240,22 @@
         <v>109</v>
       </c>
       <c r="D886" s="4" t="s">
-        <v>1166</v>
+        <v>1123</v>
       </c>
       <c r="E886" s="5" t="s">
-        <v>1376</v>
+        <v>1124</v>
       </c>
       <c r="F886" s="4" t="s">
-        <v>1361</v>
+        <v>708</v>
       </c>
       <c r="G886" s="4" t="s">
-        <v>1377</v>
+        <v>1346</v>
       </c>
       <c r="H886" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I886" s="4">
-        <v>99.99</v>
+        <v>169.99</v>
       </c>
       <c r="J886" s="4" t="s">
         <v>43</v>
@@ -79277,7 +79292,7 @@
     </row>
     <row r="887" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="2" t="s">
-        <v>1378</v>
+        <v>1372</v>
       </c>
       <c r="B887" s="2" t="s">
         <v>698</v>
@@ -79286,22 +79301,22 @@
         <v>109</v>
       </c>
       <c r="D887" s="4" t="s">
-        <v>1181</v>
+        <v>1123</v>
       </c>
       <c r="E887" s="5" t="s">
-        <v>1379</v>
+        <v>1124</v>
       </c>
       <c r="F887" s="4" t="s">
-        <v>1361</v>
+        <v>708</v>
       </c>
       <c r="G887" s="4" t="s">
-        <v>1377</v>
+        <v>1348</v>
       </c>
       <c r="H887" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I887" s="4">
-        <v>89.99</v>
+        <v>169.99</v>
       </c>
       <c r="J887" s="4" t="s">
         <v>43</v>
@@ -79338,7 +79353,7 @@
     </row>
     <row r="888" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="2" t="s">
-        <v>1380</v>
+        <v>1373</v>
       </c>
       <c r="B888" s="2" t="s">
         <v>698</v>
@@ -79347,22 +79362,22 @@
         <v>109</v>
       </c>
       <c r="D888" s="4" t="s">
-        <v>1381</v>
+        <v>1132</v>
       </c>
       <c r="E888" s="5" t="s">
-        <v>1382</v>
+        <v>1374</v>
       </c>
       <c r="F888" s="4" t="s">
-        <v>1361</v>
+        <v>708</v>
       </c>
       <c r="G888" s="4" t="s">
-        <v>1377</v>
+        <v>1346</v>
       </c>
       <c r="H888" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I888" s="4">
-        <v>79.989999999999995</v>
+        <v>199.99</v>
       </c>
       <c r="J888" s="4" t="s">
         <v>43</v>
@@ -79399,7 +79414,7 @@
     </row>
     <row r="889" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="2" t="s">
-        <v>1383</v>
+        <v>1375</v>
       </c>
       <c r="B889" s="2" t="s">
         <v>698</v>
@@ -79408,10 +79423,10 @@
         <v>109</v>
       </c>
       <c r="D889" s="4" t="s">
-        <v>1198</v>
+        <v>1166</v>
       </c>
       <c r="E889" s="5" t="s">
-        <v>1199</v>
+        <v>1376</v>
       </c>
       <c r="F889" s="4" t="s">
         <v>1361</v>
@@ -79423,7 +79438,7 @@
         <v>95</v>
       </c>
       <c r="I889" s="4">
-        <v>119.99</v>
+        <v>99.99</v>
       </c>
       <c r="J889" s="4" t="s">
         <v>43</v>
@@ -79460,7 +79475,7 @@
     </row>
     <row r="890" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A890" s="2" t="s">
-        <v>1384</v>
+        <v>1378</v>
       </c>
       <c r="B890" s="2" t="s">
         <v>698</v>
@@ -79469,13 +79484,13 @@
         <v>109</v>
       </c>
       <c r="D890" s="4" t="s">
-        <v>1204</v>
+        <v>1181</v>
       </c>
       <c r="E890" s="5" t="s">
-        <v>1205</v>
+        <v>1379</v>
       </c>
       <c r="F890" s="4" t="s">
-        <v>708</v>
+        <v>1361</v>
       </c>
       <c r="G890" s="4" t="s">
         <v>1377</v>
@@ -79484,7 +79499,7 @@
         <v>95</v>
       </c>
       <c r="I890" s="4">
-        <v>109.99</v>
+        <v>89.99</v>
       </c>
       <c r="J890" s="4" t="s">
         <v>43</v>
@@ -79521,7 +79536,7 @@
     </row>
     <row r="891" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A891" s="2" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="B891" s="2" t="s">
         <v>698</v>
@@ -79530,13 +79545,13 @@
         <v>109</v>
       </c>
       <c r="D891" s="4" t="s">
-        <v>1208</v>
+        <v>1381</v>
       </c>
       <c r="E891" s="5" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="F891" s="4" t="s">
-        <v>708</v>
+        <v>1361</v>
       </c>
       <c r="G891" s="4" t="s">
         <v>1377</v>
@@ -79545,7 +79560,7 @@
         <v>95</v>
       </c>
       <c r="I891" s="4">
-        <v>199.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J891" s="4" t="s">
         <v>43</v>
@@ -79582,7 +79597,7 @@
     </row>
     <row r="892" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892" s="2" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="B892" s="2" t="s">
         <v>698</v>
@@ -79591,16 +79606,16 @@
         <v>109</v>
       </c>
       <c r="D892" s="4" t="s">
-        <v>1388</v>
+        <v>1198</v>
       </c>
       <c r="E892" s="5" t="s">
-        <v>1389</v>
+        <v>1199</v>
       </c>
       <c r="F892" s="4" t="s">
-        <v>708</v>
+        <v>1361</v>
       </c>
       <c r="G892" s="4" t="s">
-        <v>1346</v>
+        <v>1377</v>
       </c>
       <c r="H892" s="4" t="s">
         <v>95</v>
@@ -79643,7 +79658,7 @@
     </row>
     <row r="893" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893" s="2" t="s">
-        <v>1390</v>
+        <v>1384</v>
       </c>
       <c r="B893" s="2" t="s">
         <v>698</v>
@@ -79652,16 +79667,16 @@
         <v>109</v>
       </c>
       <c r="D893" s="4" t="s">
-        <v>1226</v>
+        <v>1204</v>
       </c>
       <c r="E893" s="5" t="s">
-        <v>1227</v>
+        <v>1205</v>
       </c>
       <c r="F893" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G893" s="4" t="s">
-        <v>1346</v>
+        <v>1377</v>
       </c>
       <c r="H893" s="4" t="s">
         <v>95</v>
@@ -79704,31 +79719,31 @@
     </row>
     <row r="894" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894" s="2" t="s">
-        <v>1391</v>
+        <v>1385</v>
       </c>
       <c r="B894" s="2" t="s">
-        <v>795</v>
+        <v>698</v>
       </c>
       <c r="C894" s="2" t="s">
-        <v>1023</v>
+        <v>109</v>
       </c>
       <c r="D894" s="4" t="s">
-        <v>1037</v>
+        <v>1208</v>
       </c>
       <c r="E894" s="5" t="s">
-        <v>1392</v>
+        <v>1386</v>
       </c>
       <c r="F894" s="4" t="s">
-        <v>798</v>
+        <v>708</v>
       </c>
       <c r="G894" s="4" t="s">
-        <v>1393</v>
+        <v>1377</v>
       </c>
       <c r="H894" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I894" s="4">
-        <v>59.99</v>
+        <v>199.99</v>
       </c>
       <c r="J894" s="4" t="s">
         <v>43</v>
@@ -79765,31 +79780,31 @@
     </row>
     <row r="895" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895" s="2" t="s">
-        <v>1394</v>
+        <v>1387</v>
       </c>
       <c r="B895" s="2" t="s">
-        <v>795</v>
+        <v>698</v>
       </c>
       <c r="C895" s="2" t="s">
-        <v>1023</v>
+        <v>109</v>
       </c>
       <c r="D895" s="4" t="s">
-        <v>1037</v>
+        <v>1388</v>
       </c>
       <c r="E895" s="5" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="F895" s="4" t="s">
-        <v>798</v>
+        <v>708</v>
       </c>
       <c r="G895" s="4" t="s">
-        <v>1395</v>
+        <v>1346</v>
       </c>
       <c r="H895" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I895" s="4">
-        <v>59.99</v>
+        <v>119.99</v>
       </c>
       <c r="J895" s="4" t="s">
         <v>43</v>
@@ -79826,31 +79841,31 @@
     </row>
     <row r="896" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896" s="2" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
       <c r="B896" s="2" t="s">
-        <v>795</v>
+        <v>698</v>
       </c>
       <c r="C896" s="2" t="s">
-        <v>1023</v>
+        <v>109</v>
       </c>
       <c r="D896" s="4" t="s">
-        <v>1044</v>
+        <v>1226</v>
       </c>
       <c r="E896" s="5" t="s">
-        <v>1397</v>
+        <v>1227</v>
       </c>
       <c r="F896" s="4" t="s">
-        <v>798</v>
+        <v>708</v>
       </c>
       <c r="G896" s="4" t="s">
-        <v>1398</v>
+        <v>1346</v>
       </c>
       <c r="H896" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I896" s="4">
-        <v>59.99</v>
+        <v>109.99</v>
       </c>
       <c r="J896" s="4" t="s">
         <v>43</v>
@@ -79887,7 +79902,7 @@
     </row>
     <row r="897" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897" s="2" t="s">
-        <v>1399</v>
+        <v>1391</v>
       </c>
       <c r="B897" s="2" t="s">
         <v>795</v>
@@ -79896,16 +79911,16 @@
         <v>1023</v>
       </c>
       <c r="D897" s="4" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
       <c r="E897" s="5" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="F897" s="4" t="s">
         <v>798</v>
       </c>
       <c r="G897" s="4" t="s">
-        <v>1400</v>
+        <v>1393</v>
       </c>
       <c r="H897" s="4" t="s">
         <v>41</v>
@@ -79948,7 +79963,7 @@
     </row>
     <row r="898" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898" s="2" t="s">
-        <v>1401</v>
+        <v>1394</v>
       </c>
       <c r="B898" s="2" t="s">
         <v>795</v>
@@ -79957,19 +79972,19 @@
         <v>1023</v>
       </c>
       <c r="D898" s="4" t="s">
-        <v>1059</v>
+        <v>1037</v>
       </c>
       <c r="E898" s="5" t="s">
-        <v>1402</v>
+        <v>1392</v>
       </c>
       <c r="F898" s="4" t="s">
-        <v>852</v>
+        <v>798</v>
       </c>
       <c r="G898" s="4" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="H898" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I898" s="4">
         <v>59.99</v>
@@ -80009,7 +80024,7 @@
     </row>
     <row r="899" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="2" t="s">
-        <v>1403</v>
+        <v>1396</v>
       </c>
       <c r="B899" s="2" t="s">
         <v>795</v>
@@ -80018,19 +80033,19 @@
         <v>1023</v>
       </c>
       <c r="D899" s="4" t="s">
-        <v>1059</v>
+        <v>1044</v>
       </c>
       <c r="E899" s="5" t="s">
-        <v>1402</v>
+        <v>1397</v>
       </c>
       <c r="F899" s="4" t="s">
-        <v>852</v>
+        <v>798</v>
       </c>
       <c r="G899" s="4" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="H899" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I899" s="4">
         <v>59.99</v>
@@ -80070,7 +80085,7 @@
     </row>
     <row r="900" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="2" t="s">
-        <v>1404</v>
+        <v>1399</v>
       </c>
       <c r="B900" s="2" t="s">
         <v>795</v>
@@ -80079,19 +80094,19 @@
         <v>1023</v>
       </c>
       <c r="D900" s="4" t="s">
-        <v>1063</v>
+        <v>1044</v>
       </c>
       <c r="E900" s="5" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="F900" s="4" t="s">
-        <v>852</v>
+        <v>798</v>
       </c>
       <c r="G900" s="4" t="s">
-        <v>1406</v>
+        <v>1400</v>
       </c>
       <c r="H900" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I900" s="4">
         <v>59.99</v>
@@ -80131,7 +80146,7 @@
     </row>
     <row r="901" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="2" t="s">
-        <v>1407</v>
+        <v>1401</v>
       </c>
       <c r="B901" s="2" t="s">
         <v>795</v>
@@ -80140,16 +80155,16 @@
         <v>1023</v>
       </c>
       <c r="D901" s="4" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="E901" s="5" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="F901" s="4" t="s">
         <v>852</v>
       </c>
       <c r="G901" s="4" t="s">
-        <v>1400</v>
+        <v>1393</v>
       </c>
       <c r="H901" s="4" t="s">
         <v>95</v>
@@ -80192,37 +80207,37 @@
     </row>
     <row r="902" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="2" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
       <c r="B902" s="2" t="s">
-        <v>729</v>
+        <v>795</v>
       </c>
       <c r="C902" s="2" t="s">
-        <v>37</v>
+        <v>1023</v>
       </c>
       <c r="D902" s="4" t="s">
-        <v>1409</v>
+        <v>1059</v>
       </c>
       <c r="E902" s="5" t="s">
-        <v>1410</v>
+        <v>1402</v>
       </c>
       <c r="F902" s="4" t="s">
-        <v>732</v>
+        <v>852</v>
       </c>
       <c r="G902" s="4" t="s">
-        <v>1411</v>
+        <v>1395</v>
       </c>
       <c r="H902" s="4" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="I902" s="4">
-        <v>119.99</v>
+        <v>59.99</v>
       </c>
       <c r="J902" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K902" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L902" s="4" t="s">
         <v>44</v>
@@ -80253,37 +80268,37 @@
     </row>
     <row r="903" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="2" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="B903" s="2" t="s">
-        <v>729</v>
+        <v>795</v>
       </c>
       <c r="C903" s="2" t="s">
-        <v>37</v>
+        <v>1023</v>
       </c>
       <c r="D903" s="4" t="s">
-        <v>1409</v>
+        <v>1063</v>
       </c>
       <c r="E903" s="5" t="s">
-        <v>1410</v>
+        <v>1405</v>
       </c>
       <c r="F903" s="4" t="s">
-        <v>732</v>
+        <v>852</v>
       </c>
       <c r="G903" s="4" t="s">
-        <v>1413</v>
+        <v>1406</v>
       </c>
       <c r="H903" s="4" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="I903" s="4">
-        <v>119.99</v>
+        <v>59.99</v>
       </c>
       <c r="J903" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K903" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L903" s="4" t="s">
         <v>44</v>
@@ -80314,37 +80329,37 @@
     </row>
     <row r="904" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="2" t="s">
-        <v>1414</v>
+        <v>1407</v>
       </c>
       <c r="B904" s="2" t="s">
         <v>795</v>
       </c>
       <c r="C904" s="2" t="s">
-        <v>37</v>
+        <v>1023</v>
       </c>
       <c r="D904" s="4" t="s">
-        <v>1415</v>
+        <v>1063</v>
       </c>
       <c r="E904" s="5" t="s">
-        <v>1416</v>
+        <v>1405</v>
       </c>
       <c r="F904" s="4" t="s">
-        <v>143</v>
+        <v>852</v>
       </c>
       <c r="G904" s="4" t="s">
-        <v>1417</v>
+        <v>1400</v>
       </c>
       <c r="H904" s="4" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="I904" s="4">
-        <v>99.99</v>
+        <v>59.99</v>
       </c>
       <c r="J904" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K904" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L904" s="4" t="s">
         <v>44</v>
@@ -80375,31 +80390,31 @@
     </row>
     <row r="905" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="2" t="s">
-        <v>1418</v>
+        <v>1408</v>
       </c>
       <c r="B905" s="2" t="s">
-        <v>795</v>
+        <v>729</v>
       </c>
       <c r="C905" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D905" s="4" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="E905" s="5" t="s">
-        <v>1416</v>
+        <v>1410</v>
       </c>
       <c r="F905" s="4" t="s">
-        <v>143</v>
+        <v>732</v>
       </c>
       <c r="G905" s="4" t="s">
-        <v>1419</v>
+        <v>1411</v>
       </c>
       <c r="H905" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I905" s="4">
-        <v>99.99</v>
+        <v>119.99</v>
       </c>
       <c r="J905" s="4" t="s">
         <v>42</v>
@@ -80436,31 +80451,31 @@
     </row>
     <row r="906" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="2" t="s">
-        <v>1420</v>
+        <v>1412</v>
       </c>
       <c r="B906" s="2" t="s">
-        <v>795</v>
+        <v>729</v>
       </c>
       <c r="C906" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D906" s="4" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="E906" s="5" t="s">
-        <v>1416</v>
+        <v>1410</v>
       </c>
       <c r="F906" s="4" t="s">
-        <v>143</v>
+        <v>732</v>
       </c>
       <c r="G906" s="4" t="s">
-        <v>1421</v>
+        <v>1413</v>
       </c>
       <c r="H906" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I906" s="4">
-        <v>99.99</v>
+        <v>119.99</v>
       </c>
       <c r="J906" s="4" t="s">
         <v>42</v>
@@ -80497,7 +80512,7 @@
     </row>
     <row r="907" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="2" t="s">
-        <v>1422</v>
+        <v>1414</v>
       </c>
       <c r="B907" s="2" t="s">
         <v>795</v>
@@ -80506,22 +80521,22 @@
         <v>37</v>
       </c>
       <c r="D907" s="4" t="s">
-        <v>1423</v>
+        <v>1415</v>
       </c>
       <c r="E907" s="5" t="s">
-        <v>1424</v>
+        <v>1416</v>
       </c>
       <c r="F907" s="4" t="s">
-        <v>798</v>
+        <v>143</v>
       </c>
       <c r="G907" s="4" t="s">
-        <v>1425</v>
+        <v>1417</v>
       </c>
       <c r="H907" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I907" s="4">
-        <v>59.99</v>
+        <v>99.99</v>
       </c>
       <c r="J907" s="4" t="s">
         <v>42</v>
@@ -80558,7 +80573,7 @@
     </row>
     <row r="908" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="2" t="s">
-        <v>1426</v>
+        <v>1418</v>
       </c>
       <c r="B908" s="2" t="s">
         <v>795</v>
@@ -80567,22 +80582,22 @@
         <v>37</v>
       </c>
       <c r="D908" s="4" t="s">
-        <v>1423</v>
+        <v>1415</v>
       </c>
       <c r="E908" s="5" t="s">
-        <v>1424</v>
+        <v>1416</v>
       </c>
       <c r="F908" s="4" t="s">
-        <v>798</v>
+        <v>143</v>
       </c>
       <c r="G908" s="4" t="s">
-        <v>1427</v>
+        <v>1419</v>
       </c>
       <c r="H908" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I908" s="4">
-        <v>59.99</v>
+        <v>99.99</v>
       </c>
       <c r="J908" s="4" t="s">
         <v>42</v>
@@ -80619,7 +80634,7 @@
     </row>
     <row r="909" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="2" t="s">
-        <v>1428</v>
+        <v>1420</v>
       </c>
       <c r="B909" s="2" t="s">
         <v>795</v>
@@ -80628,22 +80643,22 @@
         <v>37</v>
       </c>
       <c r="D909" s="4" t="s">
-        <v>1423</v>
+        <v>1415</v>
       </c>
       <c r="E909" s="5" t="s">
-        <v>1424</v>
+        <v>1416</v>
       </c>
       <c r="F909" s="4" t="s">
-        <v>798</v>
+        <v>143</v>
       </c>
       <c r="G909" s="4" t="s">
-        <v>1429</v>
+        <v>1421</v>
       </c>
       <c r="H909" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I909" s="4">
-        <v>59.99</v>
+        <v>99.99</v>
       </c>
       <c r="J909" s="4" t="s">
         <v>42</v>
@@ -80680,7 +80695,7 @@
     </row>
     <row r="910" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="2" t="s">
-        <v>1430</v>
+        <v>1422</v>
       </c>
       <c r="B910" s="2" t="s">
         <v>795</v>
@@ -80698,7 +80713,7 @@
         <v>798</v>
       </c>
       <c r="G910" s="4" t="s">
-        <v>1431</v>
+        <v>1425</v>
       </c>
       <c r="H910" s="4" t="s">
         <v>41</v>
@@ -80741,7 +80756,7 @@
     </row>
     <row r="911" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="2" t="s">
-        <v>1432</v>
+        <v>1426</v>
       </c>
       <c r="B911" s="2" t="s">
         <v>795</v>
@@ -80750,19 +80765,19 @@
         <v>37</v>
       </c>
       <c r="D911" s="4" t="s">
-        <v>1433</v>
+        <v>1423</v>
       </c>
       <c r="E911" s="5" t="s">
-        <v>1434</v>
+        <v>1424</v>
       </c>
       <c r="F911" s="4" t="s">
-        <v>852</v>
+        <v>798</v>
       </c>
       <c r="G911" s="4" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="H911" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I911" s="4">
         <v>59.99</v>
@@ -80802,7 +80817,7 @@
     </row>
     <row r="912" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="2" t="s">
-        <v>1435</v>
+        <v>1428</v>
       </c>
       <c r="B912" s="2" t="s">
         <v>795</v>
@@ -80811,19 +80826,19 @@
         <v>37</v>
       </c>
       <c r="D912" s="4" t="s">
-        <v>1433</v>
+        <v>1423</v>
       </c>
       <c r="E912" s="5" t="s">
-        <v>1434</v>
+        <v>1424</v>
       </c>
       <c r="F912" s="4" t="s">
-        <v>852</v>
+        <v>798</v>
       </c>
       <c r="G912" s="4" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="H912" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I912" s="4">
         <v>59.99</v>
@@ -80863,7 +80878,7 @@
     </row>
     <row r="913" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="B913" s="2" t="s">
         <v>795</v>
@@ -80872,19 +80887,19 @@
         <v>37</v>
       </c>
       <c r="D913" s="4" t="s">
-        <v>1433</v>
+        <v>1423</v>
       </c>
       <c r="E913" s="5" t="s">
-        <v>1434</v>
+        <v>1424</v>
       </c>
       <c r="F913" s="4" t="s">
-        <v>852</v>
+        <v>798</v>
       </c>
       <c r="G913" s="4" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="H913" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I913" s="4">
         <v>59.99</v>
@@ -80924,7 +80939,7 @@
     </row>
     <row r="914" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="2" t="s">
-        <v>1437</v>
+        <v>1432</v>
       </c>
       <c r="B914" s="2" t="s">
         <v>795</v>
@@ -80942,7 +80957,7 @@
         <v>852</v>
       </c>
       <c r="G914" s="4" t="s">
-        <v>1431</v>
+        <v>1425</v>
       </c>
       <c r="H914" s="4" t="s">
         <v>95</v>
@@ -80985,31 +81000,31 @@
     </row>
     <row r="915" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="2" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="B915" s="2" t="s">
-        <v>698</v>
+        <v>795</v>
       </c>
       <c r="C915" s="2" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="D915" s="4" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="E915" s="5" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="F915" s="4" t="s">
-        <v>1361</v>
+        <v>852</v>
       </c>
       <c r="G915" s="4" t="s">
-        <v>76</v>
+        <v>1427</v>
       </c>
       <c r="H915" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I915" s="4">
-        <v>159.99</v>
+        <v>59.99</v>
       </c>
       <c r="J915" s="4" t="s">
         <v>42</v>
@@ -81046,31 +81061,31 @@
     </row>
     <row r="916" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="2" t="s">
-        <v>1441</v>
+        <v>1436</v>
       </c>
       <c r="B916" s="2" t="s">
-        <v>698</v>
+        <v>795</v>
       </c>
       <c r="C916" s="2" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="D916" s="4" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="E916" s="5" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="F916" s="4" t="s">
-        <v>1361</v>
+        <v>852</v>
       </c>
       <c r="G916" s="4" t="s">
-        <v>1348</v>
+        <v>1429</v>
       </c>
       <c r="H916" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I916" s="4">
-        <v>159.99</v>
+        <v>59.99</v>
       </c>
       <c r="J916" s="4" t="s">
         <v>42</v>
@@ -81107,31 +81122,31 @@
     </row>
     <row r="917" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="2" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
       <c r="B917" s="2" t="s">
-        <v>698</v>
+        <v>795</v>
       </c>
       <c r="C917" s="2" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="D917" s="4" t="s">
-        <v>1443</v>
+        <v>1433</v>
       </c>
       <c r="E917" s="5" t="s">
-        <v>1444</v>
+        <v>1434</v>
       </c>
       <c r="F917" s="4" t="s">
-        <v>1361</v>
+        <v>852</v>
       </c>
       <c r="G917" s="4" t="s">
-        <v>76</v>
+        <v>1431</v>
       </c>
       <c r="H917" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I917" s="4">
-        <v>189.99</v>
+        <v>59.99</v>
       </c>
       <c r="J917" s="4" t="s">
         <v>42</v>
@@ -81168,7 +81183,7 @@
     </row>
     <row r="918" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="2" t="s">
-        <v>1445</v>
+        <v>1438</v>
       </c>
       <c r="B918" s="2" t="s">
         <v>698</v>
@@ -81177,22 +81192,22 @@
         <v>109</v>
       </c>
       <c r="D918" s="4" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="E918" s="5" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="F918" s="4" t="s">
         <v>1361</v>
       </c>
       <c r="G918" s="4" t="s">
-        <v>1348</v>
+        <v>76</v>
       </c>
       <c r="H918" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I918" s="4">
-        <v>189.99</v>
+        <v>159.99</v>
       </c>
       <c r="J918" s="4" t="s">
         <v>42</v>
@@ -81229,7 +81244,7 @@
     </row>
     <row r="919" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="2" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="B919" s="2" t="s">
         <v>698</v>
@@ -81238,22 +81253,22 @@
         <v>109</v>
       </c>
       <c r="D919" s="4" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="E919" s="5" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="F919" s="4" t="s">
-        <v>708</v>
+        <v>1361</v>
       </c>
       <c r="G919" s="4" t="s">
-        <v>76</v>
+        <v>1348</v>
       </c>
       <c r="H919" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I919" s="4">
-        <v>109.99</v>
+        <v>159.99</v>
       </c>
       <c r="J919" s="4" t="s">
         <v>42</v>
@@ -81290,7 +81305,7 @@
     </row>
     <row r="920" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="2" t="s">
-        <v>1449</v>
+        <v>1442</v>
       </c>
       <c r="B920" s="2" t="s">
         <v>698</v>
@@ -81299,22 +81314,22 @@
         <v>109</v>
       </c>
       <c r="D920" s="4" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="E920" s="5" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="F920" s="4" t="s">
-        <v>708</v>
+        <v>1361</v>
       </c>
       <c r="G920" s="4" t="s">
-        <v>1377</v>
+        <v>76</v>
       </c>
       <c r="H920" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I920" s="4">
-        <v>109.99</v>
+        <v>189.99</v>
       </c>
       <c r="J920" s="4" t="s">
         <v>42</v>
@@ -81351,7 +81366,7 @@
     </row>
     <row r="921" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="2" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="B921" s="2" t="s">
         <v>698</v>
@@ -81360,22 +81375,22 @@
         <v>109</v>
       </c>
       <c r="D921" s="4" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="E921" s="5" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="F921" s="4" t="s">
-        <v>708</v>
+        <v>1361</v>
       </c>
       <c r="G921" s="4" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="H921" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I921" s="4">
-        <v>109.99</v>
+        <v>189.99</v>
       </c>
       <c r="J921" s="4" t="s">
         <v>42</v>
@@ -81410,34 +81425,36 @@
       <c r="AH921" s="4"/>
       <c r="AI921" s="4"/>
     </row>
-    <row r="922" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A922" s="2" t="s">
-        <v>1542</v>
-      </c>
-      <c r="B922" s="2"/>
+        <v>1446</v>
+      </c>
+      <c r="B922" s="2" t="s">
+        <v>698</v>
+      </c>
       <c r="C922" s="2" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="D922" s="4" t="s">
-        <v>1487</v>
+        <v>1447</v>
       </c>
       <c r="E922" s="5" t="s">
-        <v>1488</v>
+        <v>1448</v>
       </c>
       <c r="F922" s="4" t="s">
-        <v>1142</v>
+        <v>708</v>
       </c>
       <c r="G922" s="4" t="s">
-        <v>1411</v>
+        <v>76</v>
       </c>
       <c r="H922" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I922" s="4">
-        <v>229.99</v>
+        <v>109.99</v>
       </c>
       <c r="J922" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K922" s="4" t="s">
         <v>43</v>
@@ -81469,34 +81486,36 @@
       <c r="AH922" s="4"/>
       <c r="AI922" s="4"/>
     </row>
-    <row r="923" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A923" s="2" t="s">
-        <v>1543</v>
-      </c>
-      <c r="B923" s="2"/>
+        <v>1449</v>
+      </c>
+      <c r="B923" s="2" t="s">
+        <v>698</v>
+      </c>
       <c r="C923" s="2" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="D923" s="4" t="s">
-        <v>1487</v>
+        <v>1447</v>
       </c>
       <c r="E923" s="5" t="s">
-        <v>1488</v>
+        <v>1448</v>
       </c>
       <c r="F923" s="4" t="s">
-        <v>1142</v>
+        <v>708</v>
       </c>
       <c r="G923" s="4" t="s">
-        <v>1340</v>
+        <v>1377</v>
       </c>
       <c r="H923" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I923" s="4">
-        <v>229.99</v>
+        <v>109.99</v>
       </c>
       <c r="J923" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K923" s="4" t="s">
         <v>43</v>
@@ -81528,34 +81547,36 @@
       <c r="AH923" s="4"/>
       <c r="AI923" s="4"/>
     </row>
-    <row r="924" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A924" s="2" t="s">
-        <v>1544</v>
-      </c>
-      <c r="B924" s="2"/>
+        <v>1450</v>
+      </c>
+      <c r="B924" s="2" t="s">
+        <v>698</v>
+      </c>
       <c r="C924" s="2" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="D924" s="4" t="s">
-        <v>1489</v>
+        <v>1447</v>
       </c>
       <c r="E924" s="5" t="s">
-        <v>1490</v>
+        <v>1448</v>
       </c>
       <c r="F924" s="4" t="s">
-        <v>1142</v>
+        <v>708</v>
       </c>
       <c r="G924" s="4" t="s">
-        <v>1411</v>
+        <v>1346</v>
       </c>
       <c r="H924" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I924" s="4">
-        <v>229.99</v>
+        <v>109.99</v>
       </c>
       <c r="J924" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K924" s="4" t="s">
         <v>43</v>
@@ -81589,23 +81610,23 @@
     </row>
     <row r="925" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="2" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="B925" s="2"/>
       <c r="C925" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D925" s="4" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="E925" s="5" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="F925" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G925" s="4" t="s">
-        <v>1491</v>
+        <v>1411</v>
       </c>
       <c r="H925" s="4" t="s">
         <v>41</v>
@@ -81648,29 +81669,29 @@
     </row>
     <row r="926" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A926" s="2" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="B926" s="2"/>
       <c r="C926" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D926" s="4" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="E926" s="5" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
       <c r="F926" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G926" s="4" t="s">
-        <v>1411</v>
+        <v>1340</v>
       </c>
       <c r="H926" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I926" s="4">
-        <v>199.99</v>
+        <v>229.99</v>
       </c>
       <c r="J926" s="4" t="s">
         <v>43</v>
@@ -81707,29 +81728,29 @@
     </row>
     <row r="927" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A927" s="2" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
       <c r="B927" s="2"/>
       <c r="C927" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D927" s="4" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
       <c r="E927" s="5" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="F927" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G927" s="4" t="s">
-        <v>1340</v>
+        <v>1411</v>
       </c>
       <c r="H927" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I927" s="4">
-        <v>199.99</v>
+        <v>229.99</v>
       </c>
       <c r="J927" s="4" t="s">
         <v>43</v>
@@ -81766,23 +81787,23 @@
     </row>
     <row r="928" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A928" s="2" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
       <c r="B928" s="2"/>
       <c r="C928" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D928" s="4" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="E928" s="5" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="F928" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G928" s="4" t="s">
-        <v>1421</v>
+        <v>1491</v>
       </c>
       <c r="H928" s="4" t="s">
         <v>41</v>
@@ -81825,29 +81846,29 @@
     </row>
     <row r="929" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A929" s="2" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="B929" s="2"/>
       <c r="C929" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D929" s="4" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="E929" s="5" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="F929" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G929" s="4" t="s">
-        <v>1340</v>
+        <v>1411</v>
       </c>
       <c r="H929" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I929" s="4">
-        <v>229.99</v>
+        <v>199.99</v>
       </c>
       <c r="J929" s="4" t="s">
         <v>43</v>
@@ -81884,23 +81905,23 @@
     </row>
     <row r="930" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="2" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="B930" s="2"/>
       <c r="C930" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D930" s="4" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="E930" s="5" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
       <c r="F930" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G930" s="4" t="s">
-        <v>1411</v>
+        <v>1340</v>
       </c>
       <c r="H930" s="4" t="s">
         <v>41</v>
@@ -81943,29 +81964,29 @@
     </row>
     <row r="931" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A931" s="2" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
       <c r="B931" s="2"/>
       <c r="C931" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D931" s="4" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="E931" s="5" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="F931" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G931" s="4" t="s">
-        <v>1491</v>
+        <v>1421</v>
       </c>
       <c r="H931" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I931" s="4">
-        <v>199.99</v>
+        <v>229.99</v>
       </c>
       <c r="J931" s="4" t="s">
         <v>43</v>
@@ -82002,17 +82023,17 @@
     </row>
     <row r="932" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A932" s="2" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="B932" s="2"/>
       <c r="C932" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D932" s="4" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="E932" s="5" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="F932" s="4" t="s">
         <v>1142</v>
@@ -82024,7 +82045,7 @@
         <v>41</v>
       </c>
       <c r="I932" s="4">
-        <v>199.99</v>
+        <v>229.99</v>
       </c>
       <c r="J932" s="4" t="s">
         <v>43</v>
@@ -82061,17 +82082,17 @@
     </row>
     <row r="933" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A933" s="2" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
       <c r="B933" s="2"/>
       <c r="C933" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D933" s="4" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="E933" s="5" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="F933" s="4" t="s">
         <v>1142</v>
@@ -82083,7 +82104,7 @@
         <v>41</v>
       </c>
       <c r="I933" s="4">
-        <v>259.99</v>
+        <v>199.99</v>
       </c>
       <c r="J933" s="4" t="s">
         <v>43</v>
@@ -82120,29 +82141,29 @@
     </row>
     <row r="934" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A934" s="2" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
       <c r="B934" s="2"/>
       <c r="C934" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D934" s="4" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="E934" s="5" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="F934" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G934" s="4" t="s">
-        <v>1340</v>
+        <v>1491</v>
       </c>
       <c r="H934" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I934" s="4">
-        <v>259.99</v>
+        <v>199.99</v>
       </c>
       <c r="J934" s="4" t="s">
         <v>43</v>
@@ -82179,29 +82200,29 @@
     </row>
     <row r="935" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A935" s="2" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
       <c r="B935" s="2"/>
       <c r="C935" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D935" s="4" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="E935" s="5" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="F935" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G935" s="4" t="s">
-        <v>1411</v>
+        <v>1340</v>
       </c>
       <c r="H935" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I935" s="4">
-        <v>249.99</v>
+        <v>199.99</v>
       </c>
       <c r="J935" s="4" t="s">
         <v>43</v>
@@ -82238,29 +82259,29 @@
     </row>
     <row r="936" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A936" s="2" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
       <c r="B936" s="2"/>
       <c r="C936" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D936" s="4" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="E936" s="5" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="F936" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G936" s="4" t="s">
-        <v>1491</v>
+        <v>1411</v>
       </c>
       <c r="H936" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I936" s="4">
-        <v>249.99</v>
+        <v>259.99</v>
       </c>
       <c r="J936" s="4" t="s">
         <v>43</v>
@@ -82297,29 +82318,29 @@
     </row>
     <row r="937" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A937" s="2" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
       <c r="B937" s="2"/>
       <c r="C937" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D937" s="4" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
       <c r="E937" s="5" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
       <c r="F937" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G937" s="4" t="s">
-        <v>1411</v>
+        <v>1340</v>
       </c>
       <c r="H937" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I937" s="4">
-        <v>229.99</v>
+        <v>259.99</v>
       </c>
       <c r="J937" s="4" t="s">
         <v>43</v>
@@ -82356,29 +82377,29 @@
     </row>
     <row r="938" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A938" s="2" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
       <c r="B938" s="2"/>
       <c r="C938" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D938" s="4" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="E938" s="5" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="F938" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G938" s="4" t="s">
-        <v>1340</v>
+        <v>1411</v>
       </c>
       <c r="H938" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I938" s="4">
-        <v>229.99</v>
+        <v>249.99</v>
       </c>
       <c r="J938" s="4" t="s">
         <v>43</v>
@@ -82415,29 +82436,29 @@
     </row>
     <row r="939" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A939" s="2" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="B939" s="2"/>
       <c r="C939" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D939" s="4" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
       <c r="E939" s="5" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
       <c r="F939" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G939" s="4" t="s">
-        <v>1340</v>
+        <v>1491</v>
       </c>
       <c r="H939" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I939" s="4">
-        <v>379.99</v>
+        <v>249.99</v>
       </c>
       <c r="J939" s="4" t="s">
         <v>43</v>
@@ -82474,26 +82495,26 @@
     </row>
     <row r="940" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A940" s="2" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
       <c r="B940" s="2"/>
       <c r="C940" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D940" s="4" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
       <c r="E940" s="5" t="s">
-        <v>1507</v>
+        <v>1503</v>
       </c>
       <c r="F940" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G940" s="4" t="s">
-        <v>1421</v>
+        <v>1411</v>
       </c>
       <c r="H940" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I940" s="4">
         <v>229.99</v>
@@ -82533,17 +82554,17 @@
     </row>
     <row r="941" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A941" s="2" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
       <c r="B941" s="2"/>
       <c r="C941" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D941" s="4" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
       <c r="E941" s="5" t="s">
-        <v>1507</v>
+        <v>1503</v>
       </c>
       <c r="F941" s="4" t="s">
         <v>1142</v>
@@ -82552,7 +82573,7 @@
         <v>1340</v>
       </c>
       <c r="H941" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I941" s="4">
         <v>229.99</v>
@@ -82592,29 +82613,29 @@
     </row>
     <row r="942" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A942" s="2" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
       <c r="B942" s="2"/>
       <c r="C942" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D942" s="4" t="s">
-        <v>1508</v>
+        <v>1504</v>
       </c>
       <c r="E942" s="5" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
       <c r="F942" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G942" s="4" t="s">
-        <v>76</v>
+        <v>1340</v>
       </c>
       <c r="H942" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I942" s="4">
-        <v>199.99</v>
+        <v>379.99</v>
       </c>
       <c r="J942" s="4" t="s">
         <v>43</v>
@@ -82651,29 +82672,29 @@
     </row>
     <row r="943" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A943" s="2" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="B943" s="2"/>
       <c r="C943" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D943" s="4" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="E943" s="5" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="F943" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G943" s="4" t="s">
-        <v>1340</v>
+        <v>1421</v>
       </c>
       <c r="H943" s="4" t="s">
         <v>95</v>
       </c>
       <c r="I943" s="4">
-        <v>199.99</v>
+        <v>229.99</v>
       </c>
       <c r="J943" s="4" t="s">
         <v>43</v>
@@ -82710,29 +82731,29 @@
     </row>
     <row r="944" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A944" s="2" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="B944" s="2"/>
       <c r="C944" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D944" s="4" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="E944" s="5" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="F944" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G944" s="4" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="H944" s="4" t="s">
         <v>95</v>
       </c>
       <c r="I944" s="4">
-        <v>199.99</v>
+        <v>229.99</v>
       </c>
       <c r="J944" s="4" t="s">
         <v>43</v>
@@ -82769,29 +82790,29 @@
     </row>
     <row r="945" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A945" s="2" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="B945" s="2"/>
       <c r="C945" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D945" s="4" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="E945" s="5" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="F945" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G945" s="4" t="s">
-        <v>1411</v>
+        <v>76</v>
       </c>
       <c r="H945" s="4" t="s">
         <v>95</v>
       </c>
       <c r="I945" s="4">
-        <v>259.99</v>
+        <v>199.99</v>
       </c>
       <c r="J945" s="4" t="s">
         <v>43</v>
@@ -82828,17 +82849,17 @@
     </row>
     <row r="946" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A946" s="2" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="B946" s="2"/>
       <c r="C946" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D946" s="4" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="E946" s="5" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="F946" s="4" t="s">
         <v>1142</v>
@@ -82850,7 +82871,7 @@
         <v>95</v>
       </c>
       <c r="I946" s="4">
-        <v>259.99</v>
+        <v>199.99</v>
       </c>
       <c r="J946" s="4" t="s">
         <v>43</v>
@@ -82887,29 +82908,29 @@
     </row>
     <row r="947" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A947" s="2" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="B947" s="2"/>
       <c r="C947" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D947" s="4" t="s">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="E947" s="5" t="s">
-        <v>1513</v>
+        <v>1509</v>
       </c>
       <c r="F947" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G947" s="4" t="s">
-        <v>1411</v>
+        <v>1343</v>
       </c>
       <c r="H947" s="4" t="s">
         <v>95</v>
       </c>
       <c r="I947" s="4">
-        <v>249.99</v>
+        <v>199.99</v>
       </c>
       <c r="J947" s="4" t="s">
         <v>43</v>
@@ -82946,29 +82967,29 @@
     </row>
     <row r="948" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A948" s="2" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="B948" s="2"/>
       <c r="C948" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D948" s="4" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="E948" s="5" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="F948" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G948" s="4" t="s">
-        <v>1340</v>
+        <v>1411</v>
       </c>
       <c r="H948" s="4" t="s">
         <v>95</v>
       </c>
       <c r="I948" s="4">
-        <v>249.99</v>
+        <v>259.99</v>
       </c>
       <c r="J948" s="4" t="s">
         <v>43</v>
@@ -83005,29 +83026,29 @@
     </row>
     <row r="949" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A949" s="2" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="B949" s="2"/>
       <c r="C949" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D949" s="4" t="s">
-        <v>1514</v>
+        <v>1510</v>
       </c>
       <c r="E949" s="5" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
       <c r="F949" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G949" s="4" t="s">
-        <v>1411</v>
+        <v>1340</v>
       </c>
       <c r="H949" s="4" t="s">
         <v>95</v>
       </c>
       <c r="I949" s="4">
-        <v>239.99</v>
+        <v>259.99</v>
       </c>
       <c r="J949" s="4" t="s">
         <v>43</v>
@@ -83064,29 +83085,29 @@
     </row>
     <row r="950" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A950" s="2" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
       <c r="B950" s="2"/>
       <c r="C950" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D950" s="4" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="E950" s="5" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="F950" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G950" s="4" t="s">
-        <v>1340</v>
+        <v>1411</v>
       </c>
       <c r="H950" s="4" t="s">
         <v>95</v>
       </c>
       <c r="I950" s="4">
-        <v>239.99</v>
+        <v>249.99</v>
       </c>
       <c r="J950" s="4" t="s">
         <v>43</v>
@@ -83123,29 +83144,29 @@
     </row>
     <row r="951" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="2" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="B951" s="2"/>
       <c r="C951" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D951" s="4" t="s">
-        <v>1516</v>
+        <v>1512</v>
       </c>
       <c r="E951" s="5" t="s">
-        <v>1517</v>
+        <v>1513</v>
       </c>
       <c r="F951" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G951" s="4" t="s">
-        <v>1411</v>
+        <v>1340</v>
       </c>
       <c r="H951" s="4" t="s">
         <v>95</v>
       </c>
       <c r="I951" s="4">
-        <v>219.99</v>
+        <v>249.99</v>
       </c>
       <c r="J951" s="4" t="s">
         <v>43</v>
@@ -83182,29 +83203,29 @@
     </row>
     <row r="952" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="2" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="B952" s="2"/>
       <c r="C952" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D952" s="4" t="s">
-        <v>1518</v>
+        <v>1514</v>
       </c>
       <c r="E952" s="5" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="F952" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G952" s="4" t="s">
-        <v>1340</v>
+        <v>1411</v>
       </c>
       <c r="H952" s="4" t="s">
         <v>95</v>
       </c>
       <c r="I952" s="4">
-        <v>379.99</v>
+        <v>239.99</v>
       </c>
       <c r="J952" s="4" t="s">
         <v>43</v>
@@ -83241,29 +83262,29 @@
     </row>
     <row r="953" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A953" s="2" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="B953" s="2"/>
       <c r="C953" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D953" s="4" t="s">
-        <v>1520</v>
+        <v>1514</v>
       </c>
       <c r="E953" s="5" t="s">
-        <v>1521</v>
+        <v>1515</v>
       </c>
       <c r="F953" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G953" s="4" t="s">
-        <v>1411</v>
+        <v>1340</v>
       </c>
       <c r="H953" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I953" s="4">
-        <v>169.99</v>
+        <v>239.99</v>
       </c>
       <c r="J953" s="4" t="s">
         <v>43</v>
@@ -83300,29 +83321,29 @@
     </row>
     <row r="954" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="2" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="B954" s="2"/>
       <c r="C954" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D954" s="4" t="s">
-        <v>1520</v>
+        <v>1516</v>
       </c>
       <c r="E954" s="5" t="s">
-        <v>1521</v>
+        <v>1517</v>
       </c>
       <c r="F954" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G954" s="4" t="s">
-        <v>1336</v>
+        <v>1411</v>
       </c>
       <c r="H954" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I954" s="4">
-        <v>169.99</v>
+        <v>219.99</v>
       </c>
       <c r="J954" s="4" t="s">
         <v>43</v>
@@ -83359,29 +83380,29 @@
     </row>
     <row r="955" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A955" s="2" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="B955" s="2"/>
       <c r="C955" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D955" s="4" t="s">
-        <v>1522</v>
+        <v>1518</v>
       </c>
       <c r="E955" s="5" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
       <c r="F955" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G955" s="4" t="s">
-        <v>1411</v>
+        <v>1340</v>
       </c>
       <c r="H955" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I955" s="4">
-        <v>149.99</v>
+        <v>379.99</v>
       </c>
       <c r="J955" s="4" t="s">
         <v>43</v>
@@ -83418,29 +83439,29 @@
     </row>
     <row r="956" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A956" s="2" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="B956" s="2"/>
       <c r="C956" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D956" s="4" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="E956" s="5" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="F956" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G956" s="4" t="s">
-        <v>1524</v>
+        <v>1411</v>
       </c>
       <c r="H956" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I956" s="4">
-        <v>149.99</v>
+        <v>169.99</v>
       </c>
       <c r="J956" s="4" t="s">
         <v>43</v>
@@ -83477,29 +83498,29 @@
     </row>
     <row r="957" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A957" s="2" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
       <c r="B957" s="2"/>
       <c r="C957" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D957" s="4" t="s">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="E957" s="5" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="F957" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G957" s="4" t="s">
-        <v>1411</v>
+        <v>1336</v>
       </c>
       <c r="H957" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I957" s="4">
-        <v>249.99</v>
+        <v>169.99</v>
       </c>
       <c r="J957" s="4" t="s">
         <v>43</v>
@@ -83536,29 +83557,29 @@
     </row>
     <row r="958" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A958" s="2" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="B958" s="2"/>
       <c r="C958" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D958" s="4" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="E958" s="5" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
       <c r="F958" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G958" s="4" t="s">
-        <v>1340</v>
+        <v>1411</v>
       </c>
       <c r="H958" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I958" s="4">
-        <v>249.99</v>
+        <v>149.99</v>
       </c>
       <c r="J958" s="4" t="s">
         <v>43</v>
@@ -83595,29 +83616,29 @@
     </row>
     <row r="959" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A959" s="2" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="B959" s="2"/>
       <c r="C959" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D959" s="4" t="s">
-        <v>1527</v>
+        <v>1522</v>
       </c>
       <c r="E959" s="5" t="s">
-        <v>1528</v>
+        <v>1523</v>
       </c>
       <c r="F959" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G959" s="4" t="s">
-        <v>1411</v>
+        <v>1524</v>
       </c>
       <c r="H959" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I959" s="4">
-        <v>179.99</v>
+        <v>149.99</v>
       </c>
       <c r="J959" s="4" t="s">
         <v>43</v>
@@ -83654,29 +83675,29 @@
     </row>
     <row r="960" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A960" s="2" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="B960" s="2"/>
       <c r="C960" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D960" s="4" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="E960" s="5" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="F960" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G960" s="4" t="s">
-        <v>1340</v>
+        <v>1411</v>
       </c>
       <c r="H960" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I960" s="4">
-        <v>179.99</v>
+        <v>249.99</v>
       </c>
       <c r="J960" s="4" t="s">
         <v>43</v>
@@ -83713,29 +83734,29 @@
     </row>
     <row r="961" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A961" s="2" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="B961" s="2"/>
       <c r="C961" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D961" s="4" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="E961" s="5" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="F961" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G961" s="4" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="H961" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I961" s="4">
-        <v>179.99</v>
+        <v>249.99</v>
       </c>
       <c r="J961" s="4" t="s">
         <v>43</v>
@@ -83772,17 +83793,17 @@
     </row>
     <row r="962" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A962" s="2" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="B962" s="2"/>
       <c r="C962" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D962" s="4" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="E962" s="5" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="F962" s="4" t="s">
         <v>1142</v>
@@ -83794,7 +83815,7 @@
         <v>41</v>
       </c>
       <c r="I962" s="4">
-        <v>249.99</v>
+        <v>179.99</v>
       </c>
       <c r="J962" s="4" t="s">
         <v>43</v>
@@ -83831,17 +83852,17 @@
     </row>
     <row r="963" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A963" s="2" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="B963" s="2"/>
       <c r="C963" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D963" s="4" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="E963" s="5" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="F963" s="4" t="s">
         <v>1142</v>
@@ -83853,7 +83874,7 @@
         <v>41</v>
       </c>
       <c r="I963" s="4">
-        <v>249.99</v>
+        <v>179.99</v>
       </c>
       <c r="J963" s="4" t="s">
         <v>43</v>
@@ -83890,29 +83911,29 @@
     </row>
     <row r="964" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A964" s="2" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="B964" s="2"/>
       <c r="C964" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D964" s="4" t="s">
-        <v>1531</v>
+        <v>1527</v>
       </c>
       <c r="E964" s="5" t="s">
-        <v>1532</v>
+        <v>1528</v>
       </c>
       <c r="F964" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G964" s="4" t="s">
-        <v>1411</v>
+        <v>1336</v>
       </c>
       <c r="H964" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I964" s="4">
-        <v>149.99</v>
+        <v>179.99</v>
       </c>
       <c r="J964" s="4" t="s">
         <v>43</v>
@@ -83949,29 +83970,29 @@
     </row>
     <row r="965" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A965" s="2" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="B965" s="2"/>
       <c r="C965" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D965" s="4" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="E965" s="5" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="F965" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G965" s="4" t="s">
-        <v>1524</v>
+        <v>1411</v>
       </c>
       <c r="H965" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I965" s="4">
-        <v>149.99</v>
+        <v>249.99</v>
       </c>
       <c r="J965" s="4" t="s">
         <v>43</v>
@@ -84008,29 +84029,29 @@
     </row>
     <row r="966" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A966" s="2" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="B966" s="2"/>
       <c r="C966" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D966" s="4" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
       <c r="E966" s="5" t="s">
-        <v>1534</v>
+        <v>1530</v>
       </c>
       <c r="F966" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G966" s="4" t="s">
-        <v>1411</v>
+        <v>1340</v>
       </c>
       <c r="H966" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I966" s="4">
-        <v>219.99</v>
+        <v>249.99</v>
       </c>
       <c r="J966" s="4" t="s">
         <v>43</v>
@@ -84067,29 +84088,29 @@
     </row>
     <row r="967" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A967" s="2" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="B967" s="2"/>
       <c r="C967" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D967" s="4" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="E967" s="5" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="F967" s="4" t="s">
         <v>1142</v>
       </c>
       <c r="G967" s="4" t="s">
-        <v>1340</v>
+        <v>1411</v>
       </c>
       <c r="H967" s="4" t="s">
         <v>95</v>
       </c>
       <c r="I967" s="4">
-        <v>219.99</v>
+        <v>149.99</v>
       </c>
       <c r="J967" s="4" t="s">
         <v>43</v>
@@ -84126,29 +84147,29 @@
     </row>
     <row r="968" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A968" s="2" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="B968" s="2"/>
       <c r="C968" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D968" s="4" t="s">
-        <v>1535</v>
+        <v>1531</v>
       </c>
       <c r="E968" s="5" t="s">
-        <v>1536</v>
+        <v>1532</v>
       </c>
       <c r="F968" s="4" t="s">
-        <v>732</v>
+        <v>1142</v>
       </c>
       <c r="G968" s="4" t="s">
-        <v>778</v>
+        <v>1524</v>
       </c>
       <c r="H968" s="4" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="I968" s="4">
-        <v>79.989999999999995</v>
+        <v>149.99</v>
       </c>
       <c r="J968" s="4" t="s">
         <v>43</v>
@@ -84185,29 +84206,29 @@
     </row>
     <row r="969" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A969" s="2" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="B969" s="2"/>
       <c r="C969" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D969" s="4" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="E969" s="5" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="F969" s="4" t="s">
-        <v>732</v>
+        <v>1142</v>
       </c>
       <c r="G969" s="4" t="s">
-        <v>76</v>
+        <v>1411</v>
       </c>
       <c r="H969" s="4" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="I969" s="4">
-        <v>79.989999999999995</v>
+        <v>219.99</v>
       </c>
       <c r="J969" s="4" t="s">
         <v>43</v>
@@ -84244,34 +84265,36 @@
     </row>
     <row r="970" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A970" s="2" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="B970" s="2"/>
       <c r="C970" s="2" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="D970" s="4" t="s">
-        <v>1350</v>
+        <v>1533</v>
       </c>
       <c r="E970" s="5" t="s">
-        <v>1351</v>
+        <v>1534</v>
       </c>
       <c r="F970" s="4" t="s">
-        <v>708</v>
+        <v>1142</v>
       </c>
       <c r="G970" s="4" t="s">
-        <v>76</v>
+        <v>1340</v>
       </c>
       <c r="H970" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I970" s="4">
-        <v>149.99</v>
+        <v>219.99</v>
       </c>
       <c r="J970" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K970" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="K970" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="L970" s="4" t="s">
         <v>44</v>
       </c>
@@ -84301,34 +84324,36 @@
     </row>
     <row r="971" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A971" s="2" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="B971" s="2"/>
       <c r="C971" s="2" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="D971" s="4" t="s">
-        <v>1090</v>
+        <v>1535</v>
       </c>
       <c r="E971" s="5" t="s">
-        <v>1360</v>
+        <v>1536</v>
       </c>
       <c r="F971" s="4" t="s">
-        <v>1361</v>
+        <v>732</v>
       </c>
       <c r="G971" s="4" t="s">
         <v>778</v>
       </c>
       <c r="H971" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I971" s="4">
-        <v>99.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J971" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K971" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="K971" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="L971" s="4" t="s">
         <v>44</v>
       </c>
@@ -84358,34 +84383,36 @@
     </row>
     <row r="972" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A972" s="2" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="B972" s="2"/>
       <c r="C972" s="2" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="D972" s="4" t="s">
-        <v>1101</v>
+        <v>1535</v>
       </c>
       <c r="E972" s="5" t="s">
-        <v>1363</v>
+        <v>1536</v>
       </c>
       <c r="F972" s="4" t="s">
-        <v>1361</v>
+        <v>732</v>
       </c>
       <c r="G972" s="4" t="s">
-        <v>778</v>
+        <v>76</v>
       </c>
       <c r="H972" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I972" s="4">
-        <v>89.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J972" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K972" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="K972" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="L972" s="4" t="s">
         <v>44</v>
       </c>
@@ -84415,29 +84442,29 @@
     </row>
     <row r="973" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A973" s="2" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="B973" s="2"/>
       <c r="C973" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D973" s="4" t="s">
-        <v>1594</v>
+        <v>1350</v>
       </c>
       <c r="E973" s="5" t="s">
-        <v>1363</v>
+        <v>1351</v>
       </c>
       <c r="F973" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G973" s="4" t="s">
-        <v>733</v>
+        <v>76</v>
       </c>
       <c r="H973" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I973" s="4">
-        <v>89.99</v>
+        <v>149.99</v>
       </c>
       <c r="J973" s="4" t="s">
         <v>42</v>
@@ -84472,29 +84499,29 @@
     </row>
     <row r="974" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A974" s="2" t="s">
-        <v>1595</v>
+        <v>1591</v>
       </c>
       <c r="B974" s="2"/>
       <c r="C974" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D974" s="4" t="s">
-        <v>1594</v>
+        <v>1090</v>
       </c>
       <c r="E974" s="5" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
       <c r="F974" s="4" t="s">
-        <v>708</v>
+        <v>1361</v>
       </c>
       <c r="G974" s="4" t="s">
-        <v>76</v>
+        <v>778</v>
       </c>
       <c r="H974" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I974" s="4">
-        <v>89.99</v>
+        <v>99.99</v>
       </c>
       <c r="J974" s="4" t="s">
         <v>42</v>
@@ -84529,23 +84556,23 @@
     </row>
     <row r="975" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A975" s="2" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="B975" s="2"/>
       <c r="C975" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D975" s="4" t="s">
-        <v>1594</v>
+        <v>1101</v>
       </c>
       <c r="E975" s="5" t="s">
         <v>1363</v>
       </c>
       <c r="F975" s="4" t="s">
-        <v>708</v>
+        <v>1361</v>
       </c>
       <c r="G975" s="4" t="s">
-        <v>932</v>
+        <v>778</v>
       </c>
       <c r="H975" s="4" t="s">
         <v>41</v>
@@ -84586,29 +84613,29 @@
     </row>
     <row r="976" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A976" s="2" t="s">
-        <v>1597</v>
+        <v>1593</v>
       </c>
       <c r="B976" s="2"/>
       <c r="C976" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D976" s="4" t="s">
-        <v>1368</v>
+        <v>1594</v>
       </c>
       <c r="E976" s="5" t="s">
-        <v>1369</v>
+        <v>1363</v>
       </c>
       <c r="F976" s="4" t="s">
-        <v>1361</v>
+        <v>708</v>
       </c>
       <c r="G976" s="4" t="s">
-        <v>76</v>
+        <v>733</v>
       </c>
       <c r="H976" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I976" s="4">
-        <v>79.989999999999995</v>
+        <v>89.99</v>
       </c>
       <c r="J976" s="4" t="s">
         <v>42</v>
@@ -84643,29 +84670,29 @@
     </row>
     <row r="977" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A977" s="2" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="B977" s="2"/>
       <c r="C977" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D977" s="4" t="s">
-        <v>1368</v>
+        <v>1594</v>
       </c>
       <c r="E977" s="5" t="s">
-        <v>1369</v>
+        <v>1363</v>
       </c>
       <c r="F977" s="4" t="s">
-        <v>1361</v>
+        <v>708</v>
       </c>
       <c r="G977" s="4" t="s">
-        <v>778</v>
+        <v>76</v>
       </c>
       <c r="H977" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I977" s="4">
-        <v>79.989999999999995</v>
+        <v>89.99</v>
       </c>
       <c r="J977" s="4" t="s">
         <v>42</v>
@@ -84700,29 +84727,29 @@
     </row>
     <row r="978" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A978" s="2" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="B978" s="2"/>
       <c r="C978" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D978" s="4" t="s">
-        <v>1368</v>
+        <v>1594</v>
       </c>
       <c r="E978" s="5" t="s">
-        <v>1369</v>
+        <v>1363</v>
       </c>
       <c r="F978" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G978" s="4" t="s">
-        <v>384</v>
+        <v>932</v>
       </c>
       <c r="H978" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I978" s="4">
-        <v>79.989999999999995</v>
+        <v>89.99</v>
       </c>
       <c r="J978" s="4" t="s">
         <v>42</v>
@@ -84757,7 +84784,7 @@
     </row>
     <row r="979" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A979" s="2" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="B979" s="2"/>
       <c r="C979" s="2" t="s">
@@ -84770,10 +84797,10 @@
         <v>1369</v>
       </c>
       <c r="F979" s="4" t="s">
-        <v>708</v>
+        <v>1361</v>
       </c>
       <c r="G979" s="4" t="s">
-        <v>979</v>
+        <v>76</v>
       </c>
       <c r="H979" s="4" t="s">
         <v>41</v>
@@ -84814,7 +84841,7 @@
     </row>
     <row r="980" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A980" s="2" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="B980" s="2"/>
       <c r="C980" s="2" t="s">
@@ -84827,10 +84854,10 @@
         <v>1369</v>
       </c>
       <c r="F980" s="4" t="s">
-        <v>708</v>
+        <v>1361</v>
       </c>
       <c r="G980" s="4" t="s">
-        <v>375</v>
+        <v>778</v>
       </c>
       <c r="H980" s="4" t="s">
         <v>41</v>
@@ -84871,14 +84898,14 @@
     </row>
     <row r="981" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A981" s="2" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="B981" s="2"/>
       <c r="C981" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D981" s="4" t="s">
-        <v>1603</v>
+        <v>1368</v>
       </c>
       <c r="E981" s="5" t="s">
         <v>1369</v>
@@ -84887,7 +84914,7 @@
         <v>708</v>
       </c>
       <c r="G981" s="4" t="s">
-        <v>76</v>
+        <v>384</v>
       </c>
       <c r="H981" s="4" t="s">
         <v>41</v>
@@ -84928,14 +84955,14 @@
     </row>
     <row r="982" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A982" s="2" t="s">
-        <v>1604</v>
+        <v>1600</v>
       </c>
       <c r="B982" s="2"/>
       <c r="C982" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D982" s="4" t="s">
-        <v>1603</v>
+        <v>1368</v>
       </c>
       <c r="E982" s="5" t="s">
         <v>1369</v>
@@ -84944,7 +84971,7 @@
         <v>708</v>
       </c>
       <c r="G982" s="4" t="s">
-        <v>733</v>
+        <v>979</v>
       </c>
       <c r="H982" s="4" t="s">
         <v>41</v>
@@ -84985,26 +85012,26 @@
     </row>
     <row r="983" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A983" s="2" t="s">
-        <v>1605</v>
+        <v>1601</v>
       </c>
       <c r="B983" s="2"/>
       <c r="C983" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D983" s="4" t="s">
-        <v>1381</v>
+        <v>1368</v>
       </c>
       <c r="E983" s="5" t="s">
-        <v>1382</v>
+        <v>1369</v>
       </c>
       <c r="F983" s="4" t="s">
-        <v>1361</v>
+        <v>708</v>
       </c>
       <c r="G983" s="4" t="s">
-        <v>76</v>
+        <v>375</v>
       </c>
       <c r="H983" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I983" s="4">
         <v>79.989999999999995</v>
@@ -85042,26 +85069,26 @@
     </row>
     <row r="984" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A984" s="2" t="s">
-        <v>1606</v>
+        <v>1602</v>
       </c>
       <c r="B984" s="2"/>
       <c r="C984" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D984" s="4" t="s">
-        <v>1381</v>
+        <v>1603</v>
       </c>
       <c r="E984" s="5" t="s">
-        <v>1382</v>
+        <v>1369</v>
       </c>
       <c r="F984" s="4" t="s">
-        <v>1361</v>
+        <v>708</v>
       </c>
       <c r="G984" s="4" t="s">
-        <v>778</v>
+        <v>76</v>
       </c>
       <c r="H984" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I984" s="4">
         <v>79.989999999999995</v>
@@ -85099,26 +85126,26 @@
     </row>
     <row r="985" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A985" s="2" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="B985" s="2"/>
       <c r="C985" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D985" s="4" t="s">
-        <v>1381</v>
+        <v>1603</v>
       </c>
       <c r="E985" s="5" t="s">
-        <v>1382</v>
+        <v>1369</v>
       </c>
       <c r="F985" s="4" t="s">
-        <v>1361</v>
+        <v>708</v>
       </c>
       <c r="G985" s="4" t="s">
-        <v>384</v>
+        <v>733</v>
       </c>
       <c r="H985" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I985" s="4">
         <v>79.989999999999995</v>
@@ -85156,7 +85183,7 @@
     </row>
     <row r="986" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A986" s="2" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="B986" s="2"/>
       <c r="C986" s="2" t="s">
@@ -85169,10 +85196,10 @@
         <v>1382</v>
       </c>
       <c r="F986" s="4" t="s">
-        <v>708</v>
+        <v>1361</v>
       </c>
       <c r="G986" s="4" t="s">
-        <v>375</v>
+        <v>76</v>
       </c>
       <c r="H986" s="4" t="s">
         <v>95</v>
@@ -85213,7 +85240,7 @@
     </row>
     <row r="987" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A987" s="2" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="B987" s="2"/>
       <c r="C987" s="2" t="s">
@@ -85226,10 +85253,10 @@
         <v>1382</v>
       </c>
       <c r="F987" s="4" t="s">
-        <v>708</v>
+        <v>1361</v>
       </c>
       <c r="G987" s="4" t="s">
-        <v>945</v>
+        <v>778</v>
       </c>
       <c r="H987" s="4" t="s">
         <v>95</v>
@@ -85270,23 +85297,23 @@
     </row>
     <row r="988" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A988" s="2" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="B988" s="2"/>
       <c r="C988" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D988" s="4" t="s">
-        <v>1611</v>
+        <v>1381</v>
       </c>
       <c r="E988" s="5" t="s">
         <v>1382</v>
       </c>
       <c r="F988" s="4" t="s">
-        <v>708</v>
+        <v>1361</v>
       </c>
       <c r="G988" s="4" t="s">
-        <v>1190</v>
+        <v>384</v>
       </c>
       <c r="H988" s="4" t="s">
         <v>95</v>
@@ -85327,14 +85354,14 @@
     </row>
     <row r="989" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A989" s="2" t="s">
-        <v>1612</v>
+        <v>1608</v>
       </c>
       <c r="B989" s="2"/>
       <c r="C989" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D989" s="4" t="s">
-        <v>1611</v>
+        <v>1381</v>
       </c>
       <c r="E989" s="5" t="s">
         <v>1382</v>
@@ -85343,7 +85370,7 @@
         <v>708</v>
       </c>
       <c r="G989" s="4" t="s">
-        <v>778</v>
+        <v>375</v>
       </c>
       <c r="H989" s="4" t="s">
         <v>95</v>
@@ -85384,29 +85411,29 @@
     </row>
     <row r="990" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A990" s="2" t="s">
-        <v>1613</v>
+        <v>1609</v>
       </c>
       <c r="B990" s="2"/>
       <c r="C990" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D990" s="4" t="s">
-        <v>1204</v>
+        <v>1381</v>
       </c>
       <c r="E990" s="5" t="s">
-        <v>1205</v>
+        <v>1382</v>
       </c>
       <c r="F990" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G990" s="4" t="s">
-        <v>76</v>
+        <v>945</v>
       </c>
       <c r="H990" s="4" t="s">
         <v>95</v>
       </c>
       <c r="I990" s="4">
-        <v>109.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J990" s="4" t="s">
         <v>42</v>
@@ -85441,29 +85468,29 @@
     </row>
     <row r="991" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A991" s="2" t="s">
-        <v>1614</v>
+        <v>1610</v>
       </c>
       <c r="B991" s="2"/>
       <c r="C991" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D991" s="4" t="s">
-        <v>1219</v>
+        <v>1611</v>
       </c>
       <c r="E991" s="5" t="s">
-        <v>1448</v>
+        <v>1382</v>
       </c>
       <c r="F991" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G991" s="4" t="s">
-        <v>1615</v>
+        <v>1190</v>
       </c>
       <c r="H991" s="4" t="s">
         <v>95</v>
       </c>
       <c r="I991" s="4">
-        <v>99.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J991" s="4" t="s">
         <v>42</v>
@@ -85498,29 +85525,29 @@
     </row>
     <row r="992" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A992" s="2" t="s">
-        <v>1616</v>
+        <v>1612</v>
       </c>
       <c r="B992" s="2"/>
       <c r="C992" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D992" s="4" t="s">
-        <v>1219</v>
+        <v>1611</v>
       </c>
       <c r="E992" s="5" t="s">
-        <v>1448</v>
+        <v>1382</v>
       </c>
       <c r="F992" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G992" s="4" t="s">
-        <v>1617</v>
+        <v>778</v>
       </c>
       <c r="H992" s="4" t="s">
         <v>95</v>
       </c>
       <c r="I992" s="4">
-        <v>99.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J992" s="4" t="s">
         <v>42</v>
@@ -85555,29 +85582,29 @@
     </row>
     <row r="993" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="2" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
       <c r="B993" s="2"/>
       <c r="C993" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D993" s="4" t="s">
-        <v>1388</v>
+        <v>1204</v>
       </c>
       <c r="E993" s="5" t="s">
-        <v>1389</v>
+        <v>1205</v>
       </c>
       <c r="F993" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G993" s="4" t="s">
-        <v>1619</v>
+        <v>76</v>
       </c>
       <c r="H993" s="4" t="s">
         <v>95</v>
       </c>
       <c r="I993" s="4">
-        <v>119.99</v>
+        <v>109.99</v>
       </c>
       <c r="J993" s="4" t="s">
         <v>42</v>
@@ -85612,36 +85639,34 @@
     </row>
     <row r="994" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A994" s="2" t="s">
-        <v>1620</v>
+        <v>1614</v>
       </c>
       <c r="B994" s="2"/>
       <c r="C994" s="2" t="s">
-        <v>591</v>
+        <v>109</v>
       </c>
       <c r="D994" s="4" t="s">
-        <v>1537</v>
+        <v>1219</v>
       </c>
       <c r="E994" s="5" t="s">
-        <v>1538</v>
+        <v>1448</v>
       </c>
       <c r="F994" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G994" s="4" t="s">
-        <v>76</v>
+        <v>1615</v>
       </c>
       <c r="H994" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I994" s="4">
-        <v>149.99</v>
+        <v>99.99</v>
       </c>
       <c r="J994" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="K994" s="4" t="s">
-        <v>43</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="K994" s="4"/>
       <c r="L994" s="4" t="s">
         <v>44</v>
       </c>
@@ -85671,36 +85696,34 @@
     </row>
     <row r="995" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A995" s="2" t="s">
-        <v>1621</v>
+        <v>1616</v>
       </c>
       <c r="B995" s="2"/>
       <c r="C995" s="2" t="s">
-        <v>591</v>
+        <v>109</v>
       </c>
       <c r="D995" s="4" t="s">
-        <v>1537</v>
+        <v>1219</v>
       </c>
       <c r="E995" s="5" t="s">
-        <v>1538</v>
+        <v>1448</v>
       </c>
       <c r="F995" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G995" s="4" t="s">
-        <v>762</v>
+        <v>1617</v>
       </c>
       <c r="H995" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I995" s="4">
-        <v>149.99</v>
+        <v>99.99</v>
       </c>
       <c r="J995" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="K995" s="4" t="s">
-        <v>43</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="K995" s="4"/>
       <c r="L995" s="4" t="s">
         <v>44</v>
       </c>
@@ -85730,29 +85753,29 @@
     </row>
     <row r="996" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A996" s="2" t="s">
-        <v>1622</v>
+        <v>1618</v>
       </c>
       <c r="B996" s="2"/>
       <c r="C996" s="2" t="s">
-        <v>591</v>
+        <v>109</v>
       </c>
       <c r="D996" s="4" t="s">
-        <v>1451</v>
+        <v>1388</v>
       </c>
       <c r="E996" s="5" t="s">
-        <v>1452</v>
+        <v>1389</v>
       </c>
       <c r="F996" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G996" s="4" t="s">
-        <v>709</v>
+        <v>1619</v>
       </c>
       <c r="H996" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I996" s="4">
-        <v>129.99</v>
+        <v>119.99</v>
       </c>
       <c r="J996" s="4" t="s">
         <v>42</v>
@@ -85787,17 +85810,17 @@
     </row>
     <row r="997" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A997" s="2" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="B997" s="2"/>
       <c r="C997" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D997" s="4" t="s">
-        <v>1624</v>
+        <v>1537</v>
       </c>
       <c r="E997" s="5" t="s">
-        <v>1625</v>
+        <v>1538</v>
       </c>
       <c r="F997" s="4" t="s">
         <v>708</v>
@@ -85809,12 +85832,14 @@
         <v>41</v>
       </c>
       <c r="I997" s="4">
-        <v>119.99</v>
+        <v>149.99</v>
       </c>
       <c r="J997" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K997" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="K997" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="L997" s="4" t="s">
         <v>44</v>
       </c>
@@ -85844,34 +85869,36 @@
     </row>
     <row r="998" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A998" s="2" t="s">
-        <v>1626</v>
+        <v>1621</v>
       </c>
       <c r="B998" s="2"/>
       <c r="C998" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D998" s="4" t="s">
-        <v>1627</v>
+        <v>1537</v>
       </c>
       <c r="E998" s="5" t="s">
-        <v>1628</v>
+        <v>1538</v>
       </c>
       <c r="F998" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G998" s="4" t="s">
-        <v>1629</v>
+        <v>762</v>
       </c>
       <c r="H998" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I998" s="4">
-        <v>169.99</v>
+        <v>149.99</v>
       </c>
       <c r="J998" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K998" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="K998" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="L998" s="4" t="s">
         <v>44</v>
       </c>
@@ -85901,29 +85928,29 @@
     </row>
     <row r="999" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A999" s="2" t="s">
-        <v>1630</v>
+        <v>1622</v>
       </c>
       <c r="B999" s="2"/>
       <c r="C999" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D999" s="4" t="s">
-        <v>1627</v>
+        <v>1451</v>
       </c>
       <c r="E999" s="5" t="s">
-        <v>1628</v>
+        <v>1452</v>
       </c>
       <c r="F999" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G999" s="4" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="H999" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I999" s="4">
-        <v>169.99</v>
+        <v>129.99</v>
       </c>
       <c r="J999" s="4" t="s">
         <v>42</v>
@@ -85958,17 +85985,17 @@
     </row>
     <row r="1000" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1000" s="2" t="s">
-        <v>1631</v>
+        <v>1623</v>
       </c>
       <c r="B1000" s="2"/>
       <c r="C1000" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1000" s="4" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="E1000" s="5" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="F1000" s="4" t="s">
         <v>708</v>
@@ -85980,7 +86007,7 @@
         <v>41</v>
       </c>
       <c r="I1000" s="4">
-        <v>169.99</v>
+        <v>119.99</v>
       </c>
       <c r="J1000" s="4" t="s">
         <v>42</v>
@@ -86015,17 +86042,17 @@
     </row>
     <row r="1001" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1001" s="2" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
       <c r="B1001" s="2"/>
       <c r="C1001" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1001" s="4" t="s">
-        <v>1633</v>
+        <v>1627</v>
       </c>
       <c r="E1001" s="5" t="s">
-        <v>1634</v>
+        <v>1628</v>
       </c>
       <c r="F1001" s="4" t="s">
         <v>708</v>
@@ -86037,7 +86064,7 @@
         <v>41</v>
       </c>
       <c r="I1001" s="4">
-        <v>149.99</v>
+        <v>169.99</v>
       </c>
       <c r="J1001" s="4" t="s">
         <v>42</v>
@@ -86072,17 +86099,17 @@
     </row>
     <row r="1002" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1002" s="2" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
       <c r="B1002" s="2"/>
       <c r="C1002" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1002" s="4" t="s">
-        <v>1633</v>
+        <v>1627</v>
       </c>
       <c r="E1002" s="5" t="s">
-        <v>1634</v>
+        <v>1628</v>
       </c>
       <c r="F1002" s="4" t="s">
         <v>708</v>
@@ -86094,7 +86121,7 @@
         <v>41</v>
       </c>
       <c r="I1002" s="4">
-        <v>149.99</v>
+        <v>169.99</v>
       </c>
       <c r="J1002" s="4" t="s">
         <v>42</v>
@@ -86129,17 +86156,17 @@
     </row>
     <row r="1003" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1003" s="2" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="B1003" s="2"/>
       <c r="C1003" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1003" s="4" t="s">
-        <v>1633</v>
+        <v>1627</v>
       </c>
       <c r="E1003" s="5" t="s">
-        <v>1634</v>
+        <v>1628</v>
       </c>
       <c r="F1003" s="4" t="s">
         <v>708</v>
@@ -86151,7 +86178,7 @@
         <v>41</v>
       </c>
       <c r="I1003" s="4">
-        <v>149.99</v>
+        <v>169.99</v>
       </c>
       <c r="J1003" s="4" t="s">
         <v>42</v>
@@ -86186,29 +86213,29 @@
     </row>
     <row r="1004" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="2" t="s">
-        <v>1637</v>
+        <v>1632</v>
       </c>
       <c r="B1004" s="2"/>
       <c r="C1004" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1004" s="4" t="s">
-        <v>1638</v>
+        <v>1633</v>
       </c>
       <c r="E1004" s="5" t="s">
-        <v>1639</v>
+        <v>1634</v>
       </c>
       <c r="F1004" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G1004" s="4" t="s">
-        <v>384</v>
+        <v>1629</v>
       </c>
       <c r="H1004" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I1004" s="4">
-        <v>119.99</v>
+        <v>149.99</v>
       </c>
       <c r="J1004" s="4" t="s">
         <v>42</v>
@@ -86243,29 +86270,29 @@
     </row>
     <row r="1005" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="2" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
       <c r="B1005" s="2"/>
       <c r="C1005" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1005" s="4" t="s">
-        <v>1638</v>
+        <v>1633</v>
       </c>
       <c r="E1005" s="5" t="s">
-        <v>1639</v>
+        <v>1634</v>
       </c>
       <c r="F1005" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G1005" s="4" t="s">
-        <v>76</v>
+        <v>702</v>
       </c>
       <c r="H1005" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I1005" s="4">
-        <v>119.99</v>
+        <v>149.99</v>
       </c>
       <c r="J1005" s="4" t="s">
         <v>42</v>
@@ -86300,29 +86327,29 @@
     </row>
     <row r="1006" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="2" t="s">
-        <v>1641</v>
+        <v>1636</v>
       </c>
       <c r="B1006" s="2"/>
       <c r="C1006" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1006" s="4" t="s">
-        <v>1642</v>
+        <v>1633</v>
       </c>
       <c r="E1006" s="5" t="s">
-        <v>1643</v>
+        <v>1634</v>
       </c>
       <c r="F1006" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G1006" s="4" t="s">
-        <v>760</v>
+        <v>76</v>
       </c>
       <c r="H1006" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I1006" s="4">
-        <v>179.99</v>
+        <v>149.99</v>
       </c>
       <c r="J1006" s="4" t="s">
         <v>42</v>
@@ -86357,29 +86384,29 @@
     </row>
     <row r="1007" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1007" s="2" t="s">
-        <v>1644</v>
+        <v>1637</v>
       </c>
       <c r="B1007" s="2"/>
       <c r="C1007" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1007" s="4" t="s">
-        <v>1642</v>
+        <v>1638</v>
       </c>
       <c r="E1007" s="5" t="s">
-        <v>1643</v>
+        <v>1639</v>
       </c>
       <c r="F1007" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G1007" s="4" t="s">
-        <v>76</v>
+        <v>384</v>
       </c>
       <c r="H1007" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I1007" s="4">
-        <v>179.99</v>
+        <v>119.99</v>
       </c>
       <c r="J1007" s="4" t="s">
         <v>42</v>
@@ -86414,29 +86441,29 @@
     </row>
     <row r="1008" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1008" s="2" t="s">
-        <v>1645</v>
+        <v>1640</v>
       </c>
       <c r="B1008" s="2"/>
       <c r="C1008" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1008" s="4" t="s">
-        <v>1646</v>
+        <v>1638</v>
       </c>
       <c r="E1008" s="5" t="s">
-        <v>1647</v>
+        <v>1639</v>
       </c>
       <c r="F1008" s="4" t="s">
         <v>708</v>
       </c>
       <c r="G1008" s="4" t="s">
-        <v>702</v>
+        <v>76</v>
       </c>
       <c r="H1008" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I1008" s="4">
-        <v>149.99</v>
+        <v>119.99</v>
       </c>
       <c r="J1008" s="4" t="s">
         <v>42</v>
@@ -86471,29 +86498,29 @@
     </row>
     <row r="1009" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1009" s="2" t="s">
-        <v>1648</v>
+        <v>1641</v>
       </c>
       <c r="B1009" s="2"/>
       <c r="C1009" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1009" s="4" t="s">
-        <v>1649</v>
+        <v>1642</v>
       </c>
       <c r="E1009" s="5" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="F1009" s="4" t="s">
-        <v>1142</v>
+        <v>708</v>
       </c>
       <c r="G1009" s="4" t="s">
-        <v>1651</v>
+        <v>760</v>
       </c>
       <c r="H1009" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I1009" s="4">
-        <v>119.99</v>
+        <v>179.99</v>
       </c>
       <c r="J1009" s="4" t="s">
         <v>42</v>
@@ -86528,29 +86555,29 @@
     </row>
     <row r="1010" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1010" s="2" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="B1010" s="2"/>
       <c r="C1010" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1010" s="4" t="s">
-        <v>1649</v>
+        <v>1642</v>
       </c>
       <c r="E1010" s="5" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
       <c r="F1010" s="4" t="s">
-        <v>1142</v>
+        <v>708</v>
       </c>
       <c r="G1010" s="4" t="s">
-        <v>1084</v>
+        <v>76</v>
       </c>
       <c r="H1010" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I1010" s="4">
-        <v>119.99</v>
+        <v>179.99</v>
       </c>
       <c r="J1010" s="4" t="s">
         <v>42</v>
@@ -86585,29 +86612,29 @@
     </row>
     <row r="1011" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1011" s="2" t="s">
-        <v>1653</v>
+        <v>1645</v>
       </c>
       <c r="B1011" s="2"/>
       <c r="C1011" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1011" s="4" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
       <c r="E1011" s="5" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
       <c r="F1011" s="4" t="s">
-        <v>1142</v>
+        <v>708</v>
       </c>
       <c r="G1011" s="4" t="s">
-        <v>1654</v>
+        <v>702</v>
       </c>
       <c r="H1011" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I1011" s="4">
-        <v>119.99</v>
+        <v>149.99</v>
       </c>
       <c r="J1011" s="4" t="s">
         <v>42</v>
@@ -86642,36 +86669,34 @@
     </row>
     <row r="1012" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1012" s="2" t="s">
-        <v>1655</v>
+        <v>1648</v>
       </c>
       <c r="B1012" s="2"/>
       <c r="C1012" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1012" s="4" t="s">
-        <v>1539</v>
+        <v>1649</v>
       </c>
       <c r="E1012" s="5" t="s">
-        <v>1540</v>
+        <v>1650</v>
       </c>
       <c r="F1012" s="4" t="s">
-        <v>708</v>
+        <v>1142</v>
       </c>
       <c r="G1012" s="4" t="s">
-        <v>76</v>
+        <v>1651</v>
       </c>
       <c r="H1012" s="4" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="I1012" s="4">
-        <v>149.99</v>
+        <v>119.99</v>
       </c>
       <c r="J1012" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1012" s="4" t="s">
-        <v>43</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="K1012" s="4"/>
       <c r="L1012" s="4" t="s">
         <v>44</v>
       </c>
@@ -86701,36 +86726,34 @@
     </row>
     <row r="1013" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1013" s="2" t="s">
-        <v>1656</v>
+        <v>1652</v>
       </c>
       <c r="B1013" s="2"/>
       <c r="C1013" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1013" s="4" t="s">
-        <v>1539</v>
+        <v>1649</v>
       </c>
       <c r="E1013" s="5" t="s">
-        <v>1540</v>
+        <v>1650</v>
       </c>
       <c r="F1013" s="4" t="s">
-        <v>708</v>
+        <v>1142</v>
       </c>
       <c r="G1013" s="4" t="s">
-        <v>762</v>
+        <v>1084</v>
       </c>
       <c r="H1013" s="4" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="I1013" s="4">
-        <v>149.99</v>
+        <v>119.99</v>
       </c>
       <c r="J1013" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1013" s="4" t="s">
-        <v>43</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="K1013" s="4"/>
       <c r="L1013" s="4" t="s">
         <v>44</v>
       </c>
@@ -86760,29 +86783,29 @@
     </row>
     <row r="1014" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1014" s="2" t="s">
-        <v>1657</v>
+        <v>1653</v>
       </c>
       <c r="B1014" s="2"/>
       <c r="C1014" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1014" s="4" t="s">
-        <v>1658</v>
+        <v>1649</v>
       </c>
       <c r="E1014" s="5" t="s">
-        <v>1659</v>
+        <v>1650</v>
       </c>
       <c r="F1014" s="4" t="s">
-        <v>708</v>
+        <v>1142</v>
       </c>
       <c r="G1014" s="4" t="s">
-        <v>702</v>
+        <v>1654</v>
       </c>
       <c r="H1014" s="4" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="I1014" s="4">
-        <v>179.99</v>
+        <v>119.99</v>
       </c>
       <c r="J1014" s="4" t="s">
         <v>42</v>
@@ -86817,17 +86840,17 @@
     </row>
     <row r="1015" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1015" s="2" t="s">
-        <v>1660</v>
+        <v>1655</v>
       </c>
       <c r="B1015" s="2"/>
       <c r="C1015" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1015" s="4" t="s">
-        <v>1658</v>
+        <v>1539</v>
       </c>
       <c r="E1015" s="5" t="s">
-        <v>1659</v>
+        <v>1540</v>
       </c>
       <c r="F1015" s="4" t="s">
         <v>708</v>
@@ -86839,12 +86862,14 @@
         <v>95</v>
       </c>
       <c r="I1015" s="4">
-        <v>179.99</v>
+        <v>149.99</v>
       </c>
       <c r="J1015" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1015" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="K1015" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="L1015" s="4" t="s">
         <v>44</v>
       </c>
@@ -86874,34 +86899,36 @@
     </row>
     <row r="1016" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1016" s="2" t="s">
-        <v>1661</v>
+        <v>1656</v>
       </c>
       <c r="B1016" s="2"/>
       <c r="C1016" s="2" t="s">
-        <v>109</v>
+        <v>591</v>
       </c>
       <c r="D1016" s="4" t="s">
-        <v>1237</v>
+        <v>1539</v>
       </c>
       <c r="E1016" s="5" t="s">
-        <v>1238</v>
+        <v>1540</v>
       </c>
       <c r="F1016" s="4" t="s">
-        <v>732</v>
+        <v>708</v>
       </c>
       <c r="G1016" s="4" t="s">
-        <v>778</v>
+        <v>762</v>
       </c>
       <c r="H1016" s="4" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="I1016" s="4">
-        <v>249.99</v>
+        <v>149.99</v>
       </c>
       <c r="J1016" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1016" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="K1016" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="L1016" s="4" t="s">
         <v>44</v>
       </c>
@@ -86931,29 +86958,29 @@
     </row>
     <row r="1017" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1017" s="2" t="s">
-        <v>1662</v>
+        <v>1657</v>
       </c>
       <c r="B1017" s="2"/>
       <c r="C1017" s="2" t="s">
-        <v>109</v>
+        <v>591</v>
       </c>
       <c r="D1017" s="4" t="s">
-        <v>1242</v>
+        <v>1658</v>
       </c>
       <c r="E1017" s="5" t="s">
-        <v>1243</v>
+        <v>1659</v>
       </c>
       <c r="F1017" s="4" t="s">
-        <v>732</v>
+        <v>708</v>
       </c>
       <c r="G1017" s="4" t="s">
-        <v>76</v>
+        <v>702</v>
       </c>
       <c r="H1017" s="4" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="I1017" s="4">
-        <v>199.99</v>
+        <v>179.99</v>
       </c>
       <c r="J1017" s="4" t="s">
         <v>42</v>
@@ -86988,26 +87015,26 @@
     </row>
     <row r="1018" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1018" s="2" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="B1018" s="2"/>
       <c r="C1018" s="2" t="s">
-        <v>109</v>
+        <v>591</v>
       </c>
       <c r="D1018" s="4" t="s">
-        <v>1249</v>
+        <v>1658</v>
       </c>
       <c r="E1018" s="5" t="s">
-        <v>1250</v>
+        <v>1659</v>
       </c>
       <c r="F1018" s="4" t="s">
-        <v>732</v>
+        <v>708</v>
       </c>
       <c r="G1018" s="4" t="s">
-        <v>1411</v>
+        <v>76</v>
       </c>
       <c r="H1018" s="4" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="I1018" s="4">
         <v>179.99</v>
@@ -87045,17 +87072,17 @@
     </row>
     <row r="1019" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1019" s="2" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
       <c r="B1019" s="2"/>
       <c r="C1019" s="2" t="s">
-        <v>591</v>
+        <v>109</v>
       </c>
       <c r="D1019" s="4" t="s">
-        <v>751</v>
+        <v>1237</v>
       </c>
       <c r="E1019" s="5" t="s">
-        <v>752</v>
+        <v>1238</v>
       </c>
       <c r="F1019" s="4" t="s">
         <v>732</v>
@@ -87067,7 +87094,7 @@
         <v>46</v>
       </c>
       <c r="I1019" s="4">
-        <v>169.99</v>
+        <v>249.99</v>
       </c>
       <c r="J1019" s="4" t="s">
         <v>42</v>
@@ -87102,29 +87129,29 @@
     </row>
     <row r="1020" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1020" s="2" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="B1020" s="2"/>
       <c r="C1020" s="2" t="s">
-        <v>1023</v>
+        <v>109</v>
       </c>
       <c r="D1020" s="4" t="s">
-        <v>1024</v>
+        <v>1242</v>
       </c>
       <c r="E1020" s="5" t="s">
-        <v>1666</v>
+        <v>1243</v>
       </c>
       <c r="F1020" s="4" t="s">
-        <v>798</v>
+        <v>732</v>
       </c>
       <c r="G1020" s="4" t="s">
-        <v>1421</v>
+        <v>76</v>
       </c>
       <c r="H1020" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I1020" s="4">
-        <v>69.989999999999995</v>
+        <v>199.99</v>
       </c>
       <c r="J1020" s="4" t="s">
         <v>42</v>
@@ -87159,29 +87186,29 @@
     </row>
     <row r="1021" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1021" s="2" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="B1021" s="2"/>
       <c r="C1021" s="2" t="s">
-        <v>1023</v>
+        <v>109</v>
       </c>
       <c r="D1021" s="4" t="s">
-        <v>1050</v>
+        <v>1249</v>
       </c>
       <c r="E1021" s="5" t="s">
-        <v>1668</v>
+        <v>1250</v>
       </c>
       <c r="F1021" s="4" t="s">
-        <v>852</v>
+        <v>732</v>
       </c>
       <c r="G1021" s="4" t="s">
-        <v>1421</v>
+        <v>1411</v>
       </c>
       <c r="H1021" s="4" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="I1021" s="4">
-        <v>69.989999999999995</v>
+        <v>179.99</v>
       </c>
       <c r="J1021" s="4" t="s">
         <v>42</v>
@@ -87216,29 +87243,29 @@
     </row>
     <row r="1022" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1022" s="2" t="s">
-        <v>1669</v>
+        <v>1664</v>
       </c>
       <c r="B1022" s="2"/>
       <c r="C1022" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1022" s="4" t="s">
-        <v>796</v>
+        <v>751</v>
       </c>
       <c r="E1022" s="5" t="s">
-        <v>1670</v>
+        <v>752</v>
       </c>
       <c r="F1022" s="4" t="s">
-        <v>798</v>
+        <v>732</v>
       </c>
       <c r="G1022" s="4" t="s">
-        <v>1671</v>
+        <v>778</v>
       </c>
       <c r="H1022" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I1022" s="4">
-        <v>24.99</v>
+        <v>169.99</v>
       </c>
       <c r="J1022" s="4" t="s">
         <v>42</v>
@@ -87273,29 +87300,29 @@
     </row>
     <row r="1023" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1023" s="2" t="s">
-        <v>1672</v>
+        <v>1665</v>
       </c>
       <c r="B1023" s="2"/>
       <c r="C1023" s="2" t="s">
-        <v>591</v>
+        <v>1023</v>
       </c>
       <c r="D1023" s="4" t="s">
-        <v>796</v>
+        <v>1024</v>
       </c>
       <c r="E1023" s="5" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="F1023" s="4" t="s">
         <v>798</v>
       </c>
       <c r="G1023" s="4" t="s">
-        <v>1619</v>
+        <v>1421</v>
       </c>
       <c r="H1023" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I1023" s="4">
-        <v>24.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="J1023" s="4" t="s">
         <v>42</v>
@@ -87330,29 +87357,29 @@
     </row>
     <row r="1024" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1024" s="2" t="s">
-        <v>1673</v>
+        <v>1667</v>
       </c>
       <c r="B1024" s="2"/>
       <c r="C1024" s="2" t="s">
-        <v>591</v>
+        <v>1023</v>
       </c>
       <c r="D1024" s="4" t="s">
-        <v>796</v>
+        <v>1050</v>
       </c>
       <c r="E1024" s="5" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="F1024" s="4" t="s">
-        <v>798</v>
+        <v>852</v>
       </c>
       <c r="G1024" s="4" t="s">
-        <v>1674</v>
+        <v>1421</v>
       </c>
       <c r="H1024" s="4" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="I1024" s="4">
-        <v>24.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="J1024" s="4" t="s">
         <v>42</v>
@@ -87387,26 +87414,26 @@
     </row>
     <row r="1025" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1025" s="2" t="s">
-        <v>1675</v>
+        <v>1669</v>
       </c>
       <c r="B1025" s="2"/>
       <c r="C1025" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1025" s="4" t="s">
-        <v>850</v>
+        <v>796</v>
       </c>
       <c r="E1025" s="5" t="s">
-        <v>1676</v>
+        <v>1670</v>
       </c>
       <c r="F1025" s="4" t="s">
-        <v>852</v>
+        <v>798</v>
       </c>
       <c r="G1025" s="4" t="s">
-        <v>1619</v>
+        <v>1671</v>
       </c>
       <c r="H1025" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I1025" s="4">
         <v>24.99</v>
@@ -87444,26 +87471,26 @@
     </row>
     <row r="1026" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1026" s="2" t="s">
-        <v>1677</v>
+        <v>1672</v>
       </c>
       <c r="B1026" s="2"/>
       <c r="C1026" s="2" t="s">
         <v>591</v>
       </c>
       <c r="D1026" s="4" t="s">
-        <v>850</v>
+        <v>796</v>
       </c>
       <c r="E1026" s="5" t="s">
-        <v>1676</v>
+        <v>1670</v>
       </c>
       <c r="F1026" s="4" t="s">
-        <v>852</v>
+        <v>798</v>
       </c>
       <c r="G1026" s="4" t="s">
-        <v>1674</v>
+        <v>1619</v>
       </c>
       <c r="H1026" s="4" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I1026" s="4">
         <v>24.99</v>
@@ -87500,28 +87527,38 @@
       <c r="AI1026" s="4"/>
     </row>
     <row r="1027" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1027" s="9" t="s">
-        <v>1686</v>
+      <c r="A1027" s="2" t="s">
+        <v>1673</v>
       </c>
       <c r="B1027" s="2"/>
-      <c r="C1027" s="2"/>
+      <c r="C1027" s="2" t="s">
+        <v>591</v>
+      </c>
       <c r="D1027" s="4" t="s">
-        <v>1494</v>
+        <v>796</v>
       </c>
       <c r="E1027" s="5" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F1027" s="4"/>
+        <v>1670</v>
+      </c>
+      <c r="F1027" s="4" t="s">
+        <v>798</v>
+      </c>
       <c r="G1027" s="4" t="s">
-        <v>1026</v>
-      </c>
-      <c r="H1027" s="4"/>
+        <v>1674</v>
+      </c>
+      <c r="H1027" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="I1027" s="4">
-        <v>229.99</v>
-      </c>
-      <c r="J1027" s="4"/>
+        <v>24.99</v>
+      </c>
+      <c r="J1027" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="K1027" s="4"/>
-      <c r="L1027" s="4"/>
+      <c r="L1027" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="M1027" s="4"/>
       <c r="N1027" s="4"/>
       <c r="O1027" s="4"/>
@@ -87547,28 +87584,38 @@
       <c r="AI1027" s="4"/>
     </row>
     <row r="1028" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1028" s="9" t="s">
-        <v>1687</v>
+      <c r="A1028" s="2" t="s">
+        <v>1675</v>
       </c>
       <c r="B1028" s="2"/>
-      <c r="C1028" s="2"/>
+      <c r="C1028" s="2" t="s">
+        <v>591</v>
+      </c>
       <c r="D1028" s="4" t="s">
-        <v>1498</v>
+        <v>850</v>
       </c>
       <c r="E1028" s="5" t="s">
-        <v>1499</v>
-      </c>
-      <c r="F1028" s="4"/>
+        <v>1676</v>
+      </c>
+      <c r="F1028" s="4" t="s">
+        <v>852</v>
+      </c>
       <c r="G1028" s="4" t="s">
-        <v>1251</v>
-      </c>
-      <c r="H1028" s="4"/>
+        <v>1619</v>
+      </c>
+      <c r="H1028" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="I1028" s="4">
-        <v>259.99</v>
-      </c>
-      <c r="J1028" s="4"/>
+        <v>24.99</v>
+      </c>
+      <c r="J1028" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="K1028" s="4"/>
-      <c r="L1028" s="4"/>
+      <c r="L1028" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="M1028" s="4"/>
       <c r="N1028" s="4"/>
       <c r="O1028" s="4"/>
@@ -87594,28 +87641,38 @@
       <c r="AI1028" s="4"/>
     </row>
     <row r="1029" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1029" s="9" t="s">
-        <v>1688</v>
+      <c r="A1029" s="2" t="s">
+        <v>1677</v>
       </c>
       <c r="B1029" s="2"/>
-      <c r="C1029" s="2"/>
+      <c r="C1029" s="2" t="s">
+        <v>591</v>
+      </c>
       <c r="D1029" s="4" t="s">
-        <v>1500</v>
+        <v>850</v>
       </c>
       <c r="E1029" s="5" t="s">
-        <v>1679</v>
-      </c>
-      <c r="F1029" s="4"/>
+        <v>1676</v>
+      </c>
+      <c r="F1029" s="4" t="s">
+        <v>852</v>
+      </c>
       <c r="G1029" s="4" t="s">
-        <v>1251</v>
-      </c>
-      <c r="H1029" s="4"/>
+        <v>1674</v>
+      </c>
+      <c r="H1029" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="I1029" s="4">
-        <v>249.99</v>
-      </c>
-      <c r="J1029" s="4"/>
+        <v>24.99</v>
+      </c>
+      <c r="J1029" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="K1029" s="4"/>
-      <c r="L1029" s="4"/>
+      <c r="L1029" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="M1029" s="4"/>
       <c r="N1029" s="4"/>
       <c r="O1029" s="4"/>
@@ -87642,19 +87699,19 @@
     </row>
     <row r="1030" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1030" s="9" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
       <c r="B1030" s="2"/>
       <c r="C1030" s="2"/>
       <c r="D1030" s="4" t="s">
-        <v>1487</v>
+        <v>1494</v>
       </c>
       <c r="E1030" s="5" t="s">
-        <v>1488</v>
+        <v>1495</v>
       </c>
       <c r="F1030" s="4"/>
       <c r="G1030" s="4" t="s">
-        <v>1251</v>
+        <v>1026</v>
       </c>
       <c r="H1030" s="4"/>
       <c r="I1030" s="4">
@@ -87689,15 +87746,15 @@
     </row>
     <row r="1031" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1031" s="9" t="s">
-        <v>1690</v>
+        <v>1687</v>
       </c>
       <c r="B1031" s="2"/>
       <c r="C1031" s="2"/>
       <c r="D1031" s="4" t="s">
-        <v>1489</v>
+        <v>1498</v>
       </c>
       <c r="E1031" s="5" t="s">
-        <v>1680</v>
+        <v>1499</v>
       </c>
       <c r="F1031" s="4"/>
       <c r="G1031" s="4" t="s">
@@ -87705,7 +87762,7 @@
       </c>
       <c r="H1031" s="4"/>
       <c r="I1031" s="4">
-        <v>229.99</v>
+        <v>259.99</v>
       </c>
       <c r="J1031" s="4"/>
       <c r="K1031" s="4"/>
@@ -87736,15 +87793,15 @@
     </row>
     <row r="1032" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1032" s="9" t="s">
-        <v>1691</v>
+        <v>1688</v>
       </c>
       <c r="B1032" s="2"/>
       <c r="C1032" s="2"/>
       <c r="D1032" s="4" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="E1032" s="5" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="F1032" s="4"/>
       <c r="G1032" s="4" t="s">
@@ -87752,7 +87809,7 @@
       </c>
       <c r="H1032" s="4"/>
       <c r="I1032" s="4">
-        <v>229.99</v>
+        <v>249.99</v>
       </c>
       <c r="J1032" s="4"/>
       <c r="K1032" s="4"/>
@@ -87783,15 +87840,15 @@
     </row>
     <row r="1033" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1033" s="9" t="s">
-        <v>1692</v>
+        <v>1689</v>
       </c>
       <c r="B1033" s="2"/>
       <c r="C1033" s="2"/>
       <c r="D1033" s="4" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="E1033" s="5" t="s">
-        <v>1682</v>
+        <v>1488</v>
       </c>
       <c r="F1033" s="4"/>
       <c r="G1033" s="4" t="s">
@@ -87799,7 +87856,7 @@
       </c>
       <c r="H1033" s="4"/>
       <c r="I1033" s="4">
-        <v>199.99</v>
+        <v>229.99</v>
       </c>
       <c r="J1033" s="4"/>
       <c r="K1033" s="4"/>
@@ -87830,15 +87887,15 @@
     </row>
     <row r="1034" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1034" s="9" t="s">
-        <v>1693</v>
+        <v>1690</v>
       </c>
       <c r="B1034" s="2"/>
       <c r="C1034" s="2"/>
       <c r="D1034" s="4" t="s">
-        <v>1496</v>
+        <v>1489</v>
       </c>
       <c r="E1034" s="5" t="s">
-        <v>1497</v>
+        <v>1680</v>
       </c>
       <c r="F1034" s="4"/>
       <c r="G1034" s="4" t="s">
@@ -87846,7 +87903,7 @@
       </c>
       <c r="H1034" s="4"/>
       <c r="I1034" s="4">
-        <v>199.99</v>
+        <v>229.99</v>
       </c>
       <c r="J1034" s="4"/>
       <c r="K1034" s="4"/>
@@ -87877,19 +87934,19 @@
     </row>
     <row r="1035" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1035" s="9" t="s">
-        <v>1694</v>
+        <v>1691</v>
       </c>
       <c r="B1035" s="2"/>
       <c r="C1035" s="2"/>
       <c r="D1035" s="4" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
       <c r="E1035" s="5" t="s">
-        <v>1507</v>
+        <v>1681</v>
       </c>
       <c r="F1035" s="4"/>
       <c r="G1035" s="4" t="s">
-        <v>1026</v>
+        <v>1251</v>
       </c>
       <c r="H1035" s="4"/>
       <c r="I1035" s="4">
@@ -87924,15 +87981,15 @@
     </row>
     <row r="1036" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1036" s="9" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
       <c r="B1036" s="2"/>
       <c r="C1036" s="2"/>
       <c r="D1036" s="4" t="s">
-        <v>1512</v>
+        <v>1492</v>
       </c>
       <c r="E1036" s="5" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="F1036" s="4"/>
       <c r="G1036" s="4" t="s">
@@ -87940,7 +87997,7 @@
       </c>
       <c r="H1036" s="4"/>
       <c r="I1036" s="4">
-        <v>249.99</v>
+        <v>199.99</v>
       </c>
       <c r="J1036" s="4"/>
       <c r="K1036" s="4"/>
@@ -87971,15 +88028,15 @@
     </row>
     <row r="1037" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1037" s="9" t="s">
-        <v>1696</v>
+        <v>1693</v>
       </c>
       <c r="B1037" s="2"/>
       <c r="C1037" s="2"/>
       <c r="D1037" s="4" t="s">
-        <v>1514</v>
+        <v>1496</v>
       </c>
       <c r="E1037" s="5" t="s">
-        <v>1515</v>
+        <v>1497</v>
       </c>
       <c r="F1037" s="4"/>
       <c r="G1037" s="4" t="s">
@@ -87987,7 +88044,7 @@
       </c>
       <c r="H1037" s="4"/>
       <c r="I1037" s="4">
-        <v>239.99</v>
+        <v>199.99</v>
       </c>
       <c r="J1037" s="4"/>
       <c r="K1037" s="4"/>
@@ -88018,23 +88075,23 @@
     </row>
     <row r="1038" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1038" s="9" t="s">
-        <v>1697</v>
+        <v>1694</v>
       </c>
       <c r="B1038" s="2"/>
       <c r="C1038" s="2"/>
       <c r="D1038" s="4" t="s">
-        <v>1516</v>
+        <v>1506</v>
       </c>
       <c r="E1038" s="5" t="s">
-        <v>1684</v>
+        <v>1507</v>
       </c>
       <c r="F1038" s="4"/>
       <c r="G1038" s="4" t="s">
-        <v>1251</v>
+        <v>1026</v>
       </c>
       <c r="H1038" s="4"/>
       <c r="I1038" s="4">
-        <v>219.99</v>
+        <v>229.99</v>
       </c>
       <c r="J1038" s="4"/>
       <c r="K1038" s="4"/>
@@ -88065,15 +88122,15 @@
     </row>
     <row r="1039" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1039" s="9" t="s">
-        <v>1698</v>
+        <v>1695</v>
       </c>
       <c r="B1039" s="2"/>
       <c r="C1039" s="2"/>
       <c r="D1039" s="4" t="s">
-        <v>1409</v>
+        <v>1512</v>
       </c>
       <c r="E1039" s="5" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="F1039" s="4"/>
       <c r="G1039" s="4" t="s">
@@ -88081,7 +88138,7 @@
       </c>
       <c r="H1039" s="4"/>
       <c r="I1039" s="4">
-        <v>119.99</v>
+        <v>249.99</v>
       </c>
       <c r="J1039" s="4"/>
       <c r="K1039" s="4"/>
@@ -88111,42 +88168,28 @@
       <c r="AI1039" s="4"/>
     </row>
     <row r="1040" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1040" s="2" t="s">
-        <v>1702</v>
-      </c>
-      <c r="B1040" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1040" s="2" t="s">
-        <v>1307</v>
-      </c>
-      <c r="D1040" s="4">
-        <v>43206446</v>
+      <c r="A1040" s="9" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B1040" s="2"/>
+      <c r="C1040" s="2"/>
+      <c r="D1040" s="4" t="s">
+        <v>1514</v>
       </c>
       <c r="E1040" s="5" t="s">
-        <v>1316</v>
-      </c>
-      <c r="F1040" s="4" t="s">
-        <v>652</v>
-      </c>
+        <v>1515</v>
+      </c>
+      <c r="F1040" s="4"/>
       <c r="G1040" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1040" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>1251</v>
+      </c>
+      <c r="H1040" s="4"/>
       <c r="I1040" s="4">
-        <v>599.99</v>
-      </c>
-      <c r="J1040" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1040" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="L1040" s="4" t="s">
-        <v>44</v>
-      </c>
+        <v>239.99</v>
+      </c>
+      <c r="J1040" s="4"/>
+      <c r="K1040" s="4"/>
+      <c r="L1040" s="4"/>
       <c r="M1040" s="4"/>
       <c r="N1040" s="4"/>
       <c r="O1040" s="4"/>
@@ -88172,42 +88215,28 @@
       <c r="AI1040" s="4"/>
     </row>
     <row r="1041" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1041" s="2" t="s">
-        <v>1699</v>
-      </c>
-      <c r="B1041" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1041" s="2" t="s">
-        <v>1307</v>
-      </c>
-      <c r="D1041" s="4">
-        <v>43206446</v>
+      <c r="A1041" s="9" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B1041" s="2"/>
+      <c r="C1041" s="2"/>
+      <c r="D1041" s="4" t="s">
+        <v>1516</v>
       </c>
       <c r="E1041" s="5" t="s">
-        <v>1316</v>
-      </c>
-      <c r="F1041" s="4" t="s">
-        <v>652</v>
-      </c>
+        <v>1684</v>
+      </c>
+      <c r="F1041" s="4"/>
       <c r="G1041" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1041" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>1251</v>
+      </c>
+      <c r="H1041" s="4"/>
       <c r="I1041" s="4">
-        <v>599.99</v>
-      </c>
-      <c r="J1041" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1041" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="L1041" s="4" t="s">
-        <v>44</v>
-      </c>
+        <v>219.99</v>
+      </c>
+      <c r="J1041" s="4"/>
+      <c r="K1041" s="4"/>
+      <c r="L1041" s="4"/>
       <c r="M1041" s="4"/>
       <c r="N1041" s="4"/>
       <c r="O1041" s="4"/>
@@ -88233,42 +88262,28 @@
       <c r="AI1041" s="4"/>
     </row>
     <row r="1042" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1042" s="2" t="s">
-        <v>1700</v>
-      </c>
-      <c r="B1042" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1042" s="2" t="s">
-        <v>1307</v>
-      </c>
-      <c r="D1042" s="4">
-        <v>43206446</v>
+      <c r="A1042" s="9" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B1042" s="2"/>
+      <c r="C1042" s="2"/>
+      <c r="D1042" s="4" t="s">
+        <v>1409</v>
       </c>
       <c r="E1042" s="5" t="s">
-        <v>1316</v>
-      </c>
-      <c r="F1042" s="4" t="s">
-        <v>652</v>
-      </c>
+        <v>1685</v>
+      </c>
+      <c r="F1042" s="4"/>
       <c r="G1042" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H1042" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>1251</v>
+      </c>
+      <c r="H1042" s="4"/>
       <c r="I1042" s="4">
-        <v>599.99</v>
-      </c>
-      <c r="J1042" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1042" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="L1042" s="4" t="s">
-        <v>44</v>
-      </c>
+        <v>119.99</v>
+      </c>
+      <c r="J1042" s="4"/>
+      <c r="K1042" s="4"/>
+      <c r="L1042" s="4"/>
       <c r="M1042" s="4"/>
       <c r="N1042" s="4"/>
       <c r="O1042" s="4"/>
@@ -88295,7 +88310,7 @@
     </row>
     <row r="1043" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1043" s="2" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1043" s="2" t="s">
         <v>36</v>
@@ -88313,7 +88328,7 @@
         <v>652</v>
       </c>
       <c r="G1043" s="4" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="H1043" s="4" t="s">
         <v>46</v>
@@ -88356,7 +88371,7 @@
     </row>
     <row r="1044" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1044" s="2" t="s">
-        <v>1703</v>
+        <v>1699</v>
       </c>
       <c r="B1044" s="2" t="s">
         <v>36</v>
@@ -88374,7 +88389,7 @@
         <v>652</v>
       </c>
       <c r="G1044" s="4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H1044" s="4" t="s">
         <v>46</v>
@@ -88415,33 +88430,33 @@
       <c r="AH1044" s="4"/>
       <c r="AI1044" s="4"/>
     </row>
-    <row r="1045" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1045" s="2" t="s">
-        <v>1705</v>
+        <v>1700</v>
       </c>
       <c r="B1045" s="2" t="s">
-        <v>450</v>
+        <v>36</v>
       </c>
       <c r="C1045" s="2" t="s">
-        <v>619</v>
+        <v>1307</v>
       </c>
       <c r="D1045" s="4">
-        <v>54111405</v>
+        <v>43206446</v>
       </c>
       <c r="E1045" s="5" t="s">
-        <v>621</v>
+        <v>1316</v>
       </c>
       <c r="F1045" s="4" t="s">
-        <v>622</v>
+        <v>652</v>
       </c>
       <c r="G1045" s="4" t="s">
-        <v>538</v>
+        <v>55</v>
       </c>
       <c r="H1045" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I1045" s="4">
-        <v>199.99</v>
+        <v>599.99</v>
       </c>
       <c r="J1045" s="4" t="s">
         <v>43</v>
@@ -88476,33 +88491,33 @@
       <c r="AH1045" s="4"/>
       <c r="AI1045" s="4"/>
     </row>
-    <row r="1046" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1046" s="2" t="s">
-        <v>1706</v>
+        <v>1701</v>
       </c>
       <c r="B1046" s="2" t="s">
-        <v>450</v>
+        <v>36</v>
       </c>
       <c r="C1046" s="2" t="s">
-        <v>619</v>
+        <v>1307</v>
       </c>
       <c r="D1046" s="4">
-        <v>54111405</v>
+        <v>43206446</v>
       </c>
       <c r="E1046" s="5" t="s">
-        <v>621</v>
+        <v>1316</v>
       </c>
       <c r="F1046" s="4" t="s">
-        <v>622</v>
+        <v>652</v>
       </c>
       <c r="G1046" s="4" t="s">
-        <v>1704</v>
+        <v>61</v>
       </c>
       <c r="H1046" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I1046" s="4">
-        <v>199.99</v>
+        <v>599.99</v>
       </c>
       <c r="J1046" s="4" t="s">
         <v>43</v>
@@ -88537,33 +88552,33 @@
       <c r="AH1046" s="4"/>
       <c r="AI1046" s="4"/>
     </row>
-    <row r="1047" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1047" s="2" t="s">
-        <v>1707</v>
+        <v>1703</v>
       </c>
       <c r="B1047" s="2" t="s">
-        <v>450</v>
+        <v>36</v>
       </c>
       <c r="C1047" s="2" t="s">
-        <v>619</v>
+        <v>1307</v>
       </c>
       <c r="D1047" s="4">
-        <v>54111405</v>
+        <v>43206446</v>
       </c>
       <c r="E1047" s="5" t="s">
-        <v>621</v>
+        <v>1316</v>
       </c>
       <c r="F1047" s="4" t="s">
-        <v>622</v>
+        <v>652</v>
       </c>
       <c r="G1047" s="4" t="s">
-        <v>375</v>
+        <v>63</v>
       </c>
       <c r="H1047" s="4" t="s">
         <v>46</v>
       </c>
       <c r="I1047" s="4">
-        <v>199.99</v>
+        <v>599.99</v>
       </c>
       <c r="J1047" s="4" t="s">
         <v>43</v>
@@ -88598,9 +88613,9 @@
       <c r="AH1047" s="4"/>
       <c r="AI1047" s="4"/>
     </row>
-    <row r="1048" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1048" s="2" t="s">
-        <v>1708</v>
+        <v>1705</v>
       </c>
       <c r="B1048" s="2" t="s">
         <v>450</v>
@@ -88618,7 +88633,7 @@
         <v>622</v>
       </c>
       <c r="G1048" s="4" t="s">
-        <v>171</v>
+        <v>538</v>
       </c>
       <c r="H1048" s="4" t="s">
         <v>46</v>
@@ -88659,11 +88674,194 @@
       <c r="AH1048" s="4"/>
       <c r="AI1048" s="4"/>
     </row>
+    <row r="1049" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1049" s="2" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B1049" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C1049" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="D1049" s="4">
+        <v>54111405</v>
+      </c>
+      <c r="E1049" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="F1049" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="G1049" s="4" t="s">
+        <v>1704</v>
+      </c>
+      <c r="H1049" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1049" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J1049" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1049" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1049" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1049" s="4"/>
+      <c r="N1049" s="4"/>
+      <c r="O1049" s="4"/>
+      <c r="P1049" s="4"/>
+      <c r="Q1049" s="4"/>
+      <c r="R1049" s="4"/>
+      <c r="S1049" s="4"/>
+      <c r="T1049" s="4"/>
+      <c r="U1049" s="4"/>
+      <c r="V1049" s="4"/>
+      <c r="W1049" s="4"/>
+      <c r="X1049" s="4"/>
+      <c r="Y1049" s="4"/>
+      <c r="Z1049" s="4"/>
+      <c r="AA1049" s="4"/>
+      <c r="AB1049" s="4"/>
+      <c r="AC1049" s="4"/>
+      <c r="AD1049" s="4"/>
+      <c r="AE1049" s="4"/>
+      <c r="AF1049" s="4"/>
+      <c r="AG1049" s="4"/>
+      <c r="AH1049" s="4"/>
+      <c r="AI1049" s="4"/>
+    </row>
+    <row r="1050" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1050" s="2" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B1050" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C1050" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="D1050" s="4">
+        <v>54111405</v>
+      </c>
+      <c r="E1050" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="F1050" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="G1050" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="H1050" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1050" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J1050" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1050" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1050" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1050" s="4"/>
+      <c r="N1050" s="4"/>
+      <c r="O1050" s="4"/>
+      <c r="P1050" s="4"/>
+      <c r="Q1050" s="4"/>
+      <c r="R1050" s="4"/>
+      <c r="S1050" s="4"/>
+      <c r="T1050" s="4"/>
+      <c r="U1050" s="4"/>
+      <c r="V1050" s="4"/>
+      <c r="W1050" s="4"/>
+      <c r="X1050" s="4"/>
+      <c r="Y1050" s="4"/>
+      <c r="Z1050" s="4"/>
+      <c r="AA1050" s="4"/>
+      <c r="AB1050" s="4"/>
+      <c r="AC1050" s="4"/>
+      <c r="AD1050" s="4"/>
+      <c r="AE1050" s="4"/>
+      <c r="AF1050" s="4"/>
+      <c r="AG1050" s="4"/>
+      <c r="AH1050" s="4"/>
+      <c r="AI1050" s="4"/>
+    </row>
+    <row r="1051" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1051" s="2" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B1051" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C1051" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="D1051" s="4">
+        <v>54111405</v>
+      </c>
+      <c r="E1051" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="F1051" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="G1051" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1051" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1051" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J1051" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1051" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1051" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1051" s="4"/>
+      <c r="N1051" s="4"/>
+      <c r="O1051" s="4"/>
+      <c r="P1051" s="4"/>
+      <c r="Q1051" s="4"/>
+      <c r="R1051" s="4"/>
+      <c r="S1051" s="4"/>
+      <c r="T1051" s="4"/>
+      <c r="U1051" s="4"/>
+      <c r="V1051" s="4"/>
+      <c r="W1051" s="4"/>
+      <c r="X1051" s="4"/>
+      <c r="Y1051" s="4"/>
+      <c r="Z1051" s="4"/>
+      <c r="AA1051" s="4"/>
+      <c r="AB1051" s="4"/>
+      <c r="AC1051" s="4"/>
+      <c r="AD1051" s="4"/>
+      <c r="AE1051" s="4"/>
+      <c r="AF1051" s="4"/>
+      <c r="AG1051" s="4"/>
+      <c r="AH1051" s="4"/>
+      <c r="AI1051" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R1048" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:R1051" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="4">
       <filters>
-        <filter val="POS/CORRE"/>
+        <filter val="CORRE VENTO 3"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823094DE-B736-4094-8315-AE9803FE1368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC6115D-D6D9-48BD-883B-24D19B608F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC6115D-D6D9-48BD-883B-24D19B608F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894340B1-DEB1-4E63-9282-2E9EF3ED8DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5641,7 +5641,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AI1051"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5763,7 +5762,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
@@ -5870,7 +5869,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1678</v>
       </c>
@@ -5977,7 +5976,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>47</v>
       </c>
@@ -6084,7 +6083,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>49</v>
       </c>
@@ -6191,7 +6190,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>51</v>
       </c>
@@ -6298,7 +6297,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>53</v>
       </c>
@@ -6405,7 +6404,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>56</v>
       </c>
@@ -6512,7 +6511,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>58</v>
       </c>
@@ -6619,7 +6618,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>60</v>
       </c>
@@ -6726,7 +6725,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>62</v>
       </c>
@@ -6833,7 +6832,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>64</v>
       </c>
@@ -6940,7 +6939,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>67</v>
       </c>
@@ -7047,7 +7046,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>69</v>
       </c>
@@ -7154,7 +7153,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>71</v>
       </c>
@@ -7261,7 +7260,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>73</v>
       </c>
@@ -7368,7 +7367,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>75</v>
       </c>
@@ -7475,7 +7474,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>77</v>
       </c>
@@ -7582,7 +7581,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>79</v>
       </c>
@@ -7689,7 +7688,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>82</v>
       </c>
@@ -7796,7 +7795,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>83</v>
       </c>
@@ -7903,7 +7902,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>85</v>
       </c>
@@ -8010,7 +8009,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>87</v>
       </c>
@@ -8117,7 +8116,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>88</v>
       </c>
@@ -8224,7 +8223,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>89</v>
       </c>
@@ -8331,7 +8330,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>93</v>
       </c>
@@ -8438,7 +8437,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>96</v>
       </c>
@@ -8545,7 +8544,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>98</v>
       </c>
@@ -8652,7 +8651,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="29" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>100</v>
       </c>
@@ -8759,7 +8758,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>101</v>
       </c>
@@ -8866,7 +8865,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>103</v>
       </c>
@@ -8973,7 +8972,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>105</v>
       </c>
@@ -9080,7 +9079,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="33" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>106</v>
       </c>
@@ -9187,7 +9186,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>108</v>
       </c>
@@ -9294,7 +9293,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>113</v>
       </c>
@@ -9401,7 +9400,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>114</v>
       </c>
@@ -9508,7 +9507,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="37" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>116</v>
       </c>
@@ -9615,7 +9614,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="38" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>117</v>
       </c>
@@ -9722,7 +9721,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="39" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>118</v>
       </c>
@@ -9829,7 +9828,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="40" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>120</v>
       </c>
@@ -9936,7 +9935,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="41" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>122</v>
       </c>
@@ -10043,7 +10042,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>126</v>
       </c>
@@ -10150,7 +10149,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="43" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>128</v>
       </c>
@@ -10257,7 +10256,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>129</v>
       </c>
@@ -10364,7 +10363,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="45" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>131</v>
       </c>
@@ -10471,7 +10470,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="46" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>132</v>
       </c>
@@ -10578,7 +10577,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>134</v>
       </c>
@@ -10685,7 +10684,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>136</v>
       </c>
@@ -10792,7 +10791,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="49" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>138</v>
       </c>
@@ -10899,7 +10898,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="50" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>140</v>
       </c>
@@ -11006,7 +11005,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>141</v>
       </c>
@@ -11113,7 +11112,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="52" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>145</v>
       </c>
@@ -11220,7 +11219,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>146</v>
       </c>
@@ -11327,7 +11326,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="54" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>147</v>
       </c>
@@ -11434,7 +11433,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="55" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>149</v>
       </c>
@@ -11541,7 +11540,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="56" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>150</v>
       </c>
@@ -11648,7 +11647,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="57" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>152</v>
       </c>
@@ -11755,7 +11754,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="58" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>154</v>
       </c>
@@ -11862,7 +11861,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>156</v>
       </c>
@@ -11969,7 +11968,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>158</v>
       </c>
@@ -12076,7 +12075,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>160</v>
       </c>
@@ -12183,7 +12182,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>161</v>
       </c>
@@ -12290,7 +12289,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>163</v>
       </c>
@@ -12397,7 +12396,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="64" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>166</v>
       </c>
@@ -12504,7 +12503,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>168</v>
       </c>
@@ -12611,7 +12610,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="66" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>170</v>
       </c>
@@ -12718,7 +12717,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="67" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>172</v>
       </c>
@@ -12825,7 +12824,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="68" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>173</v>
       </c>
@@ -12932,7 +12931,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>175</v>
       </c>
@@ -13039,7 +13038,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="70" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>178</v>
       </c>
@@ -13146,7 +13145,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="71" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>179</v>
       </c>
@@ -13253,7 +13252,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="72" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>180</v>
       </c>
@@ -13360,7 +13359,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="73" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>181</v>
       </c>
@@ -13467,7 +13466,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>184</v>
       </c>
@@ -13574,7 +13573,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>186</v>
       </c>
@@ -13681,7 +13680,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>188</v>
       </c>
@@ -13788,7 +13787,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>190</v>
       </c>
@@ -13895,7 +13894,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>191</v>
       </c>
@@ -14002,7 +14001,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>194</v>
       </c>
@@ -14109,7 +14108,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>196</v>
       </c>
@@ -14216,7 +14215,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>197</v>
       </c>
@@ -14323,7 +14322,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="82" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>200</v>
       </c>
@@ -14430,7 +14429,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>201</v>
       </c>
@@ -14537,7 +14536,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="84" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>202</v>
       </c>
@@ -14644,7 +14643,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="85" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>205</v>
       </c>
@@ -14751,7 +14750,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="86" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>206</v>
       </c>
@@ -14858,7 +14857,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="87" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>208</v>
       </c>
@@ -14965,7 +14964,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="88" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>210</v>
       </c>
@@ -15072,7 +15071,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="89" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>213</v>
       </c>
@@ -15179,7 +15178,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="90" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>215</v>
       </c>
@@ -15286,7 +15285,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="91" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>216</v>
       </c>
@@ -15393,7 +15392,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="92" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>217</v>
       </c>
@@ -15500,7 +15499,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="93" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>220</v>
       </c>
@@ -15607,7 +15606,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="94" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>221</v>
       </c>
@@ -15714,7 +15713,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="95" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>223</v>
       </c>
@@ -15821,7 +15820,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="96" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>225</v>
       </c>
@@ -15928,7 +15927,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>229</v>
       </c>
@@ -16035,7 +16034,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>231</v>
       </c>
@@ -16142,7 +16141,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>233</v>
       </c>
@@ -16249,7 +16248,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>234</v>
       </c>
@@ -16356,7 +16355,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>237</v>
       </c>
@@ -16463,7 +16462,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>239</v>
       </c>
@@ -16570,7 +16569,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>240</v>
       </c>
@@ -16677,7 +16676,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>241</v>
       </c>
@@ -16784,7 +16783,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>243</v>
       </c>
@@ -16891,7 +16890,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>245</v>
       </c>
@@ -16998,7 +16997,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="107" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>248</v>
       </c>
@@ -17105,7 +17104,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="108" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>249</v>
       </c>
@@ -17212,7 +17211,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="109" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>250</v>
       </c>
@@ -17319,7 +17318,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="110" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>252</v>
       </c>
@@ -17426,7 +17425,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="111" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>253</v>
       </c>
@@ -17533,7 +17532,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="112" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>255</v>
       </c>
@@ -17640,7 +17639,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="113" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>257</v>
       </c>
@@ -17747,7 +17746,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="114" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>259</v>
       </c>
@@ -17854,7 +17853,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="115" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>260</v>
       </c>
@@ -17961,7 +17960,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="116" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>262</v>
       </c>
@@ -18068,7 +18067,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="117" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>264</v>
       </c>
@@ -18175,7 +18174,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="118" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>266</v>
       </c>
@@ -18282,7 +18281,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="119" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>268</v>
       </c>
@@ -18389,7 +18388,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="120" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>270</v>
       </c>
@@ -18496,7 +18495,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="121" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>271</v>
       </c>
@@ -18603,7 +18602,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>273</v>
       </c>
@@ -18710,7 +18709,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>275</v>
       </c>
@@ -18817,7 +18816,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="124" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>277</v>
       </c>
@@ -18924,7 +18923,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>278</v>
       </c>
@@ -19031,7 +19030,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="126" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>281</v>
       </c>
@@ -19138,7 +19137,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="127" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>282</v>
       </c>
@@ -19245,7 +19244,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="128" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>283</v>
       </c>
@@ -19352,7 +19351,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>284</v>
       </c>
@@ -19459,7 +19458,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>286</v>
       </c>
@@ -19566,7 +19565,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>288</v>
       </c>
@@ -19673,7 +19672,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="132" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>290</v>
       </c>
@@ -19780,7 +19779,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="133" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>291</v>
       </c>
@@ -19887,7 +19886,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="134" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>293</v>
       </c>
@@ -19994,7 +19993,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="135" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>294</v>
       </c>
@@ -20101,7 +20100,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="136" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>295</v>
       </c>
@@ -20208,7 +20207,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="137" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>296</v>
       </c>
@@ -20315,7 +20314,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="138" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>299</v>
       </c>
@@ -20422,7 +20421,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="139" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>300</v>
       </c>
@@ -20529,7 +20528,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="140" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>301</v>
       </c>
@@ -20636,7 +20635,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>302</v>
       </c>
@@ -20743,7 +20742,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="142" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>305</v>
       </c>
@@ -20850,7 +20849,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>307</v>
       </c>
@@ -20957,7 +20956,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="144" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>308</v>
       </c>
@@ -21064,7 +21063,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="145" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>310</v>
       </c>
@@ -21171,7 +21170,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="146" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>312</v>
       </c>
@@ -21278,7 +21277,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="147" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>313</v>
       </c>
@@ -21385,7 +21384,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="148" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>314</v>
       </c>
@@ -21492,7 +21491,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="149" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>316</v>
       </c>
@@ -21599,7 +21598,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="150" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>317</v>
       </c>
@@ -21706,7 +21705,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="151" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>318</v>
       </c>
@@ -21813,7 +21812,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="152" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>321</v>
       </c>
@@ -21920,7 +21919,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="153" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>322</v>
       </c>
@@ -22027,7 +22026,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="154" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>324</v>
       </c>
@@ -22134,7 +22133,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="155" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>325</v>
       </c>
@@ -22241,7 +22240,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="156" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>327</v>
       </c>
@@ -22348,7 +22347,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="157" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>328</v>
       </c>
@@ -22455,7 +22454,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="158" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>329</v>
       </c>
@@ -22562,7 +22561,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="159" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>330</v>
       </c>
@@ -22669,7 +22668,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="160" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>332</v>
       </c>
@@ -22776,7 +22775,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="161" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>334</v>
       </c>
@@ -22883,7 +22882,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="162" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>336</v>
       </c>
@@ -22990,7 +22989,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="163" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>337</v>
       </c>
@@ -23097,7 +23096,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="164" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>340</v>
       </c>
@@ -23204,7 +23203,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="165" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>342</v>
       </c>
@@ -23311,7 +23310,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="166" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>344</v>
       </c>
@@ -23418,7 +23417,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="167" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>346</v>
       </c>
@@ -23525,7 +23524,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="168" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>348</v>
       </c>
@@ -23632,7 +23631,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="169" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>349</v>
       </c>
@@ -23739,7 +23738,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="170" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>351</v>
       </c>
@@ -23846,7 +23845,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="171" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>352</v>
       </c>
@@ -23953,7 +23952,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="172" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>355</v>
       </c>
@@ -24060,7 +24059,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="173" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>356</v>
       </c>
@@ -24167,7 +24166,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="174" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>357</v>
       </c>
@@ -24274,7 +24273,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="175" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>358</v>
       </c>
@@ -24381,7 +24380,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="176" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>360</v>
       </c>
@@ -24488,7 +24487,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="177" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>361</v>
       </c>
@@ -24595,7 +24594,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="178" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>362</v>
       </c>
@@ -24702,7 +24701,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="179" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>365</v>
       </c>
@@ -24809,7 +24808,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="180" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>367</v>
       </c>
@@ -24916,7 +24915,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="181" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>368</v>
       </c>
@@ -25023,7 +25022,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="182" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>369</v>
       </c>
@@ -25130,7 +25129,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="183" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>372</v>
       </c>
@@ -25237,7 +25236,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="184" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>374</v>
       </c>
@@ -25344,7 +25343,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="185" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>376</v>
       </c>
@@ -25451,7 +25450,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="186" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>379</v>
       </c>
@@ -25558,7 +25557,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="187" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>380</v>
       </c>
@@ -25665,7 +25664,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="188" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>381</v>
       </c>
@@ -25772,7 +25771,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="189" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>385</v>
       </c>
@@ -25879,7 +25878,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="190" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>387</v>
       </c>
@@ -25986,7 +25985,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="191" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>389</v>
       </c>
@@ -26093,7 +26092,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="192" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>391</v>
       </c>
@@ -26200,7 +26199,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="193" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>392</v>
       </c>
@@ -26307,7 +26306,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="194" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>393</v>
       </c>
@@ -26414,7 +26413,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>396</v>
       </c>
@@ -26521,7 +26520,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>397</v>
       </c>
@@ -26628,7 +26627,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>400</v>
       </c>
@@ -26735,7 +26734,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>401</v>
       </c>
@@ -26842,7 +26841,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>402</v>
       </c>
@@ -26949,7 +26948,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="200" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>403</v>
       </c>
@@ -27056,7 +27055,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="201" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>404</v>
       </c>
@@ -27163,7 +27162,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="202" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>406</v>
       </c>
@@ -27270,7 +27269,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="203" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>408</v>
       </c>
@@ -27377,7 +27376,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="204" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>409</v>
       </c>
@@ -27484,7 +27483,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="205" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>410</v>
       </c>
@@ -27591,7 +27590,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="206" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>411</v>
       </c>
@@ -27698,7 +27697,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="207" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>412</v>
       </c>
@@ -27805,7 +27804,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="208" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>413</v>
       </c>
@@ -27912,7 +27911,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="209" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>417</v>
       </c>
@@ -28019,7 +28018,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="210" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>418</v>
       </c>
@@ -28126,7 +28125,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="211" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>419</v>
       </c>
@@ -28233,7 +28232,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="212" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>420</v>
       </c>
@@ -28340,7 +28339,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="213" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>421</v>
       </c>
@@ -28447,7 +28446,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="214" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>423</v>
       </c>
@@ -28554,7 +28553,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="215" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>424</v>
       </c>
@@ -28661,7 +28660,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="216" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>425</v>
       </c>
@@ -28768,7 +28767,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="217" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>426</v>
       </c>
@@ -28875,7 +28874,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="218" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>427</v>
       </c>
@@ -28982,7 +28981,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="219" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>428</v>
       </c>
@@ -29089,7 +29088,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="220" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>430</v>
       </c>
@@ -29196,7 +29195,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="221" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>432</v>
       </c>
@@ -29303,7 +29302,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="222" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>434</v>
       </c>
@@ -29410,7 +29409,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="223" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>435</v>
       </c>
@@ -29517,7 +29516,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="224" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>436</v>
       </c>
@@ -29624,7 +29623,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="225" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>438</v>
       </c>
@@ -29731,7 +29730,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="226" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>439</v>
       </c>
@@ -29838,7 +29837,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="227" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>440</v>
       </c>
@@ -29945,7 +29944,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="228" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>441</v>
       </c>
@@ -30052,7 +30051,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="229" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>442</v>
       </c>
@@ -30159,7 +30158,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="230" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>443</v>
       </c>
@@ -30266,7 +30265,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="231" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>445</v>
       </c>
@@ -30373,7 +30372,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="232" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>446</v>
       </c>
@@ -30480,7 +30479,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="233" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>447</v>
       </c>
@@ -30587,7 +30586,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="234" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>448</v>
       </c>
@@ -30694,7 +30693,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="235" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>449</v>
       </c>
@@ -30801,7 +30800,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="236" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>455</v>
       </c>
@@ -30908,7 +30907,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="237" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>456</v>
       </c>
@@ -31015,7 +31014,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="238" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>458</v>
       </c>
@@ -31122,7 +31121,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="239" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>460</v>
       </c>
@@ -31229,7 +31228,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="240" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>461</v>
       </c>
@@ -31336,7 +31335,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="241" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>462</v>
       </c>
@@ -31443,7 +31442,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="242" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>465</v>
       </c>
@@ -31550,7 +31549,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="243" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>466</v>
       </c>
@@ -31657,7 +31656,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="244" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>468</v>
       </c>
@@ -31764,7 +31763,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="245" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>469</v>
       </c>
@@ -31871,7 +31870,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="246" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>471</v>
       </c>
@@ -31978,7 +31977,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="247" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>472</v>
       </c>
@@ -32085,7 +32084,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="248" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>473</v>
       </c>
@@ -32192,7 +32191,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="249" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>474</v>
       </c>
@@ -32299,7 +32298,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="250" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>475</v>
       </c>
@@ -32406,7 +32405,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="251" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>478</v>
       </c>
@@ -32513,7 +32512,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="252" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>479</v>
       </c>
@@ -32620,7 +32619,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="253" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>481</v>
       </c>
@@ -32727,7 +32726,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="254" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>482</v>
       </c>
@@ -32834,7 +32833,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="255" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>485</v>
       </c>
@@ -32941,7 +32940,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="256" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>487</v>
       </c>
@@ -33048,7 +33047,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="257" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>489</v>
       </c>
@@ -33155,7 +33154,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="258" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>490</v>
       </c>
@@ -33262,7 +33261,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="259" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>492</v>
       </c>
@@ -33357,7 +33356,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="260" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>495</v>
       </c>
@@ -33452,7 +33451,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="261" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>496</v>
       </c>
@@ -33547,7 +33546,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="262" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>498</v>
       </c>
@@ -33642,7 +33641,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="263" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>499</v>
       </c>
@@ -33737,7 +33736,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="264" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>501</v>
       </c>
@@ -33832,7 +33831,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="265" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>503</v>
       </c>
@@ -33927,7 +33926,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="266" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>505</v>
       </c>
@@ -34022,7 +34021,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="267" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>506</v>
       </c>
@@ -34117,7 +34116,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="268" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>507</v>
       </c>
@@ -34212,7 +34211,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="269" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>508</v>
       </c>
@@ -34307,7 +34306,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="270" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>510</v>
       </c>
@@ -34402,7 +34401,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="271" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>511</v>
       </c>
@@ -34497,7 +34496,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="272" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>512</v>
       </c>
@@ -34592,7 +34591,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="273" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>513</v>
       </c>
@@ -34653,7 +34652,7 @@
       <c r="AH273" s="4"/>
       <c r="AI273" s="4"/>
     </row>
-    <row r="274" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>515</v>
       </c>
@@ -34714,7 +34713,7 @@
       <c r="AH274" s="4"/>
       <c r="AI274" s="4"/>
     </row>
-    <row r="275" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>516</v>
       </c>
@@ -34775,7 +34774,7 @@
       <c r="AH275" s="4"/>
       <c r="AI275" s="4"/>
     </row>
-    <row r="276" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>517</v>
       </c>
@@ -34836,7 +34835,7 @@
       <c r="AH276" s="4"/>
       <c r="AI276" s="4"/>
     </row>
-    <row r="277" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>518</v>
       </c>
@@ -34897,7 +34896,7 @@
       <c r="AH277" s="4"/>
       <c r="AI277" s="4"/>
     </row>
-    <row r="278" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>520</v>
       </c>
@@ -34992,7 +34991,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="279" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>522</v>
       </c>
@@ -35087,7 +35086,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="280" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>524</v>
       </c>
@@ -35182,7 +35181,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="281" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>525</v>
       </c>
@@ -35277,7 +35276,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="282" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>180</v>
       </c>
@@ -35372,7 +35371,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="283" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>179</v>
       </c>
@@ -35467,7 +35466,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="284" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>178</v>
       </c>
@@ -35562,7 +35561,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="285" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>175</v>
       </c>
@@ -35657,7 +35656,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="286" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>190</v>
       </c>
@@ -35752,7 +35751,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>526</v>
       </c>
@@ -35847,7 +35846,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="288" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>186</v>
       </c>
@@ -35942,7 +35941,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="289" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>181</v>
       </c>
@@ -36037,7 +36036,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="290" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>184</v>
       </c>
@@ -36132,7 +36131,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="291" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>528</v>
       </c>
@@ -36227,7 +36226,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="292" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>530</v>
       </c>
@@ -36322,7 +36321,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="293" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>531</v>
       </c>
@@ -36417,7 +36416,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="294" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>533</v>
       </c>
@@ -36478,7 +36477,7 @@
       <c r="AH294" s="4"/>
       <c r="AI294" s="4"/>
     </row>
-    <row r="295" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>535</v>
       </c>
@@ -36539,7 +36538,7 @@
       <c r="AH295" s="4"/>
       <c r="AI295" s="4"/>
     </row>
-    <row r="296" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>536</v>
       </c>
@@ -36600,7 +36599,7 @@
       <c r="AH296" s="4"/>
       <c r="AI296" s="4"/>
     </row>
-    <row r="297" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>220</v>
       </c>
@@ -36695,7 +36694,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="298" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>221</v>
       </c>
@@ -36790,7 +36789,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="299" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>217</v>
       </c>
@@ -36885,7 +36884,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="300" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>223</v>
       </c>
@@ -36980,7 +36979,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="301" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>205</v>
       </c>
@@ -37075,7 +37074,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="302" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>202</v>
       </c>
@@ -37170,7 +37169,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="303" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>537</v>
       </c>
@@ -37265,7 +37264,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="304" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>539</v>
       </c>
@@ -37360,7 +37359,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="305" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>541</v>
       </c>
@@ -37455,7 +37454,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="306" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>252</v>
       </c>
@@ -37550,7 +37549,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="307" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>250</v>
       </c>
@@ -37645,7 +37644,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="308" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>248</v>
       </c>
@@ -37740,7 +37739,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="309" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>245</v>
       </c>
@@ -37835,7 +37834,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="310" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>249</v>
       </c>
@@ -37930,7 +37929,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="311" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>257</v>
       </c>
@@ -38025,7 +38024,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="312" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>259</v>
       </c>
@@ -38120,7 +38119,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="313" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>255</v>
       </c>
@@ -38215,7 +38214,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="314" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>253</v>
       </c>
@@ -38310,7 +38309,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="315" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>543</v>
       </c>
@@ -38405,7 +38404,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="316" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>282</v>
       </c>
@@ -38500,7 +38499,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="317" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>281</v>
       </c>
@@ -38595,7 +38594,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="318" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>278</v>
       </c>
@@ -38690,7 +38689,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="319" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>290</v>
       </c>
@@ -38785,7 +38784,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="320" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>286</v>
       </c>
@@ -38880,7 +38879,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="321" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>284</v>
       </c>
@@ -38975,7 +38974,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="322" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>288</v>
       </c>
@@ -39070,7 +39069,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="323" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>544</v>
       </c>
@@ -39165,7 +39164,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="324" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>546</v>
       </c>
@@ -39260,7 +39259,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="325" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>548</v>
       </c>
@@ -39355,7 +39354,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="326" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>550</v>
       </c>
@@ -39450,7 +39449,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="327" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>551</v>
       </c>
@@ -39545,7 +39544,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="328" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>554</v>
       </c>
@@ -39640,7 +39639,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="329" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>555</v>
       </c>
@@ -39735,7 +39734,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="330" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>294</v>
       </c>
@@ -39830,7 +39829,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="331" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>293</v>
       </c>
@@ -39925,7 +39924,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="332" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>291</v>
       </c>
@@ -40020,7 +40019,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="333" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>295</v>
       </c>
@@ -40115,7 +40114,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="334" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>329</v>
       </c>
@@ -40210,7 +40209,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="335" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>327</v>
       </c>
@@ -40305,7 +40304,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="336" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>325</v>
       </c>
@@ -40400,7 +40399,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="337" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>328</v>
       </c>
@@ -40495,7 +40494,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="338" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>318</v>
       </c>
@@ -40590,7 +40589,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="339" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>322</v>
       </c>
@@ -40685,7 +40684,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="340" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>321</v>
       </c>
@@ -40780,7 +40779,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="341" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>324</v>
       </c>
@@ -40875,7 +40874,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="342" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>330</v>
       </c>
@@ -40970,7 +40969,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="343" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>336</v>
       </c>
@@ -41065,7 +41064,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="344" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>332</v>
       </c>
@@ -41160,7 +41159,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="345" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>557</v>
       </c>
@@ -41255,7 +41254,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="346" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>340</v>
       </c>
@@ -41350,7 +41349,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="347" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>344</v>
       </c>
@@ -41445,7 +41444,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="348" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>342</v>
       </c>
@@ -41540,7 +41539,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="349" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>337</v>
       </c>
@@ -41635,7 +41634,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="350" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>559</v>
       </c>
@@ -41742,7 +41741,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="351" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>561</v>
       </c>
@@ -41849,7 +41848,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="352" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>562</v>
       </c>
@@ -41956,7 +41955,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="353" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>564</v>
       </c>
@@ -42051,7 +42050,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="354" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>369</v>
       </c>
@@ -42146,7 +42145,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="355" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>372</v>
       </c>
@@ -42241,7 +42240,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="356" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>565</v>
       </c>
@@ -42336,7 +42335,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="357" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>365</v>
       </c>
@@ -42431,7 +42430,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="358" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>566</v>
       </c>
@@ -42526,7 +42525,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="359" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>362</v>
       </c>
@@ -42621,7 +42620,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="360" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>567</v>
       </c>
@@ -42716,7 +42715,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="361" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>568</v>
       </c>
@@ -42811,7 +42810,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="362" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>376</v>
       </c>
@@ -42906,7 +42905,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="363" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>147</v>
       </c>
@@ -43001,7 +43000,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="364" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>570</v>
       </c>
@@ -43096,7 +43095,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="365" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>150</v>
       </c>
@@ -43191,7 +43190,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="366" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>149</v>
       </c>
@@ -43286,7 +43285,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="367" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>141</v>
       </c>
@@ -43381,7 +43380,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="368" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>145</v>
       </c>
@@ -43476,7 +43475,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="369" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>146</v>
       </c>
@@ -43571,7 +43570,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="370" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>154</v>
       </c>
@@ -43666,7 +43665,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="371" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>571</v>
       </c>
@@ -43761,7 +43760,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="372" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>572</v>
       </c>
@@ -43856,7 +43855,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="373" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>573</v>
       </c>
@@ -43951,7 +43950,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="374" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>575</v>
       </c>
@@ -44046,7 +44045,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="375" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>229</v>
       </c>
@@ -44141,7 +44140,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="376" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
         <v>233</v>
       </c>
@@ -44236,7 +44235,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="377" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
         <v>225</v>
       </c>
@@ -44331,7 +44330,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="378" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>231</v>
       </c>
@@ -44426,7 +44425,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="379" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>312</v>
       </c>
@@ -44521,7 +44520,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="380" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>313</v>
       </c>
@@ -44616,7 +44615,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="381" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>310</v>
       </c>
@@ -44711,7 +44710,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="382" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>308</v>
       </c>
@@ -44806,7 +44805,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="383" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>577</v>
       </c>
@@ -44901,7 +44900,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="384" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>579</v>
       </c>
@@ -44996,7 +44995,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="385" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>581</v>
       </c>
@@ -45091,7 +45090,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="386" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>583</v>
       </c>
@@ -45186,7 +45185,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="387" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>434</v>
       </c>
@@ -45281,7 +45280,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="388" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>432</v>
       </c>
@@ -45376,7 +45375,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="389" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>435</v>
       </c>
@@ -45471,7 +45470,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="390" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
         <v>428</v>
       </c>
@@ -45566,7 +45565,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="391" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
         <v>430</v>
       </c>
@@ -45661,7 +45660,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="392" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>447</v>
       </c>
@@ -45756,7 +45755,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="393" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>445</v>
       </c>
@@ -45851,7 +45850,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="394" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
         <v>443</v>
       </c>
@@ -45946,7 +45945,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="395" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
         <v>585</v>
       </c>
@@ -46041,7 +46040,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="396" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
         <v>587</v>
       </c>
@@ -46136,7 +46135,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="397" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>588</v>
       </c>
@@ -46231,7 +46230,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="398" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>589</v>
       </c>
@@ -46326,7 +46325,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="399" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
         <v>590</v>
       </c>
@@ -46387,7 +46386,7 @@
       <c r="AH399" s="4"/>
       <c r="AI399" s="4"/>
     </row>
-    <row r="400" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>594</v>
       </c>
@@ -46448,7 +46447,7 @@
       <c r="AH400" s="4"/>
       <c r="AI400" s="4"/>
     </row>
-    <row r="401" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>596</v>
       </c>
@@ -46509,7 +46508,7 @@
       <c r="AH401" s="4"/>
       <c r="AI401" s="4"/>
     </row>
-    <row r="402" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
         <v>598</v>
       </c>
@@ -46570,7 +46569,7 @@
       <c r="AH402" s="4"/>
       <c r="AI402" s="4"/>
     </row>
-    <row r="403" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>381</v>
       </c>
@@ -46665,7 +46664,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="404" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
         <v>392</v>
       </c>
@@ -46760,7 +46759,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="405" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
         <v>391</v>
       </c>
@@ -46855,7 +46854,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="406" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>389</v>
       </c>
@@ -46950,7 +46949,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="407" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>385</v>
       </c>
@@ -47045,7 +47044,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="408" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>387</v>
       </c>
@@ -47140,7 +47139,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="409" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
         <v>196</v>
       </c>
@@ -47235,7 +47234,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="410" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>191</v>
       </c>
@@ -47330,7 +47329,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>194</v>
       </c>
@@ -47425,7 +47424,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="412" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
         <v>600</v>
       </c>
@@ -47520,7 +47519,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="413" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
         <v>602</v>
       </c>
@@ -47615,7 +47614,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="414" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>603</v>
       </c>
@@ -47710,7 +47709,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="415" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>604</v>
       </c>
@@ -47805,7 +47804,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="416" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
         <v>605</v>
       </c>
@@ -47900,7 +47899,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="417" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>607</v>
       </c>
@@ -47995,7 +47994,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="418" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>608</v>
       </c>
@@ -48090,7 +48089,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="419" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>609</v>
       </c>
@@ -48185,7 +48184,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="420" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
         <v>361</v>
       </c>
@@ -48280,7 +48279,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="421" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>360</v>
       </c>
@@ -48375,7 +48374,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="422" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>358</v>
       </c>
@@ -48470,7 +48469,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="423" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
         <v>357</v>
       </c>
@@ -48565,7 +48564,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="424" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>356</v>
       </c>
@@ -48660,7 +48659,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="425" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>355</v>
       </c>
@@ -48755,7 +48754,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="426" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>352</v>
       </c>
@@ -48850,7 +48849,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="427" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>610</v>
       </c>
@@ -48945,7 +48944,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="428" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
         <v>613</v>
       </c>
@@ -49040,7 +49039,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="429" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>614</v>
       </c>
@@ -49135,7 +49134,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="430" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>616</v>
       </c>
@@ -49230,7 +49229,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="431" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>406</v>
       </c>
@@ -49325,7 +49324,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="432" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
         <v>412</v>
       </c>
@@ -49420,7 +49419,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="433" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>411</v>
       </c>
@@ -49515,7 +49514,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="434" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>409</v>
       </c>
@@ -49610,7 +49609,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="435" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>617</v>
       </c>
@@ -49705,7 +49704,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="436" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>410</v>
       </c>
@@ -49800,7 +49799,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="437" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>396</v>
       </c>
@@ -49895,7 +49894,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="438" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>393</v>
       </c>
@@ -49990,7 +49989,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="439" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>436</v>
       </c>
@@ -50085,7 +50084,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="440" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
         <v>442</v>
       </c>
@@ -50180,7 +50179,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="441" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>441</v>
       </c>
@@ -50275,7 +50274,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="442" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>439</v>
       </c>
@@ -50370,7 +50369,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="443" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>440</v>
       </c>
@@ -50465,7 +50464,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="444" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>490</v>
       </c>
@@ -50560,7 +50559,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="445" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>489</v>
       </c>
@@ -50655,7 +50654,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="446" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
         <v>487</v>
       </c>
@@ -50750,7 +50749,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="447" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>485</v>
       </c>
@@ -50845,7 +50844,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="448" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>482</v>
       </c>
@@ -50940,7 +50939,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="449" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>461</v>
       </c>
@@ -51035,7 +51034,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="450" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
         <v>460</v>
       </c>
@@ -51130,7 +51129,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="451" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>458</v>
       </c>
@@ -51225,7 +51224,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="452" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>455</v>
       </c>
@@ -51320,7 +51319,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="453" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>456</v>
       </c>
@@ -51415,7 +51414,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="454" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>449</v>
       </c>
@@ -51510,7 +51509,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="455" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>620</v>
       </c>
@@ -51571,7 +51570,7 @@
       <c r="AH455" s="4"/>
       <c r="AI455" s="4"/>
     </row>
-    <row r="456" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>623</v>
       </c>
@@ -51632,7 +51631,7 @@
       <c r="AH456" s="4"/>
       <c r="AI456" s="4"/>
     </row>
-    <row r="457" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>625</v>
       </c>
@@ -51693,7 +51692,7 @@
       <c r="AH457" s="4"/>
       <c r="AI457" s="4"/>
     </row>
-    <row r="458" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>627</v>
       </c>
@@ -51754,7 +51753,7 @@
       <c r="AH458" s="4"/>
       <c r="AI458" s="4"/>
     </row>
-    <row r="459" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
         <v>474</v>
       </c>
@@ -51849,7 +51848,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="460" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>473</v>
       </c>
@@ -51944,7 +51943,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="461" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>469</v>
       </c>
@@ -52039,7 +52038,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="462" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>471</v>
       </c>
@@ -52134,7 +52133,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="463" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
         <v>472</v>
       </c>
@@ -52229,7 +52228,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="464" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>628</v>
       </c>
@@ -52324,7 +52323,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="465" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>475</v>
       </c>
@@ -52419,7 +52418,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="466" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>630</v>
       </c>
@@ -52514,7 +52513,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="467" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>631</v>
       </c>
@@ -52609,7 +52608,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="468" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
         <v>632</v>
       </c>
@@ -52704,7 +52703,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="469" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
         <v>633</v>
       </c>
@@ -52799,7 +52798,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="470" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>635</v>
       </c>
@@ -52894,7 +52893,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="471" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
         <v>637</v>
       </c>
@@ -52989,7 +52988,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="472" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
         <v>639</v>
       </c>
@@ -53084,7 +53083,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="473" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
         <v>641</v>
       </c>
@@ -53145,7 +53144,7 @@
       <c r="AH473" s="4"/>
       <c r="AI473" s="4"/>
     </row>
-    <row r="474" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
         <v>644</v>
       </c>
@@ -53206,7 +53205,7 @@
       <c r="AH474" s="4"/>
       <c r="AI474" s="4"/>
     </row>
-    <row r="475" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
         <v>645</v>
       </c>
@@ -53267,7 +53266,7 @@
       <c r="AH475" s="4"/>
       <c r="AI475" s="4"/>
     </row>
-    <row r="476" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
         <v>647</v>
       </c>
@@ -53328,7 +53327,7 @@
       <c r="AH476" s="4"/>
       <c r="AI476" s="4"/>
     </row>
-    <row r="477" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
         <v>649</v>
       </c>
@@ -53389,7 +53388,7 @@
       <c r="AH477" s="4"/>
       <c r="AI477" s="4"/>
     </row>
-    <row r="478" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
         <v>650</v>
       </c>
@@ -53450,7 +53449,7 @@
       <c r="AH478" s="4"/>
       <c r="AI478" s="4"/>
     </row>
-    <row r="479" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
         <v>654</v>
       </c>
@@ -53511,7 +53510,7 @@
       <c r="AH479" s="4"/>
       <c r="AI479" s="4"/>
     </row>
-    <row r="480" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
         <v>657</v>
       </c>
@@ -53572,7 +53571,7 @@
       <c r="AH480" s="4"/>
       <c r="AI480" s="4"/>
     </row>
-    <row r="481" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
         <v>659</v>
       </c>
@@ -53633,7 +53632,7 @@
       <c r="AH481" s="4"/>
       <c r="AI481" s="4"/>
     </row>
-    <row r="482" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
         <v>661</v>
       </c>
@@ -53694,7 +53693,7 @@
       <c r="AH482" s="4"/>
       <c r="AI482" s="4"/>
     </row>
-    <row r="483" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
         <v>662</v>
       </c>
@@ -53755,7 +53754,7 @@
       <c r="AH483" s="4"/>
       <c r="AI483" s="4"/>
     </row>
-    <row r="484" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
         <v>77</v>
       </c>
@@ -53850,7 +53849,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="485" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
         <v>75</v>
       </c>
@@ -53945,7 +53944,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="486" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
         <v>73</v>
       </c>
@@ -54040,7 +54039,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="487" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
         <v>69</v>
       </c>
@@ -54135,7 +54134,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="488" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
         <v>64</v>
       </c>
@@ -54230,7 +54229,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="489" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
         <v>71</v>
       </c>
@@ -54325,7 +54324,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="490" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
         <v>67</v>
       </c>
@@ -54420,7 +54419,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="491" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
         <v>663</v>
       </c>
@@ -54481,7 +54480,7 @@
       <c r="AH491" s="4"/>
       <c r="AI491" s="4"/>
     </row>
-    <row r="492" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
         <v>665</v>
       </c>
@@ -54542,7 +54541,7 @@
       <c r="AH492" s="4"/>
       <c r="AI492" s="4"/>
     </row>
-    <row r="493" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
         <v>667</v>
       </c>
@@ -54603,7 +54602,7 @@
       <c r="AH493" s="4"/>
       <c r="AI493" s="4"/>
     </row>
-    <row r="494" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
         <v>668</v>
       </c>
@@ -54664,7 +54663,7 @@
       <c r="AH494" s="4"/>
       <c r="AI494" s="4"/>
     </row>
-    <row r="495" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
         <v>669</v>
       </c>
@@ -54725,7 +54724,7 @@
       <c r="AH495" s="4"/>
       <c r="AI495" s="4"/>
     </row>
-    <row r="496" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
         <v>670</v>
       </c>
@@ -54786,7 +54785,7 @@
       <c r="AH496" s="4"/>
       <c r="AI496" s="4"/>
     </row>
-    <row r="497" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
         <v>671</v>
       </c>
@@ -54847,7 +54846,7 @@
       <c r="AH497" s="4"/>
       <c r="AI497" s="4"/>
     </row>
-    <row r="498" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
         <v>673</v>
       </c>
@@ -54908,7 +54907,7 @@
       <c r="AH498" s="4"/>
       <c r="AI498" s="4"/>
     </row>
-    <row r="499" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
         <v>674</v>
       </c>
@@ -54969,7 +54968,7 @@
       <c r="AH499" s="4"/>
       <c r="AI499" s="4"/>
     </row>
-    <row r="500" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
         <v>675</v>
       </c>
@@ -55030,7 +55029,7 @@
       <c r="AH500" s="4"/>
       <c r="AI500" s="4"/>
     </row>
-    <row r="501" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
         <v>270</v>
       </c>
@@ -55125,7 +55124,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="502" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
         <v>266</v>
       </c>
@@ -55220,7 +55219,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="503" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
         <v>268</v>
       </c>
@@ -55315,7 +55314,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="504" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
         <v>262</v>
       </c>
@@ -55410,7 +55409,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="505" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
         <v>264</v>
       </c>
@@ -55505,7 +55504,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="506" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
         <v>676</v>
       </c>
@@ -55600,7 +55599,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="507" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
         <v>93</v>
       </c>
@@ -55695,7 +55694,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="508" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
         <v>89</v>
       </c>
@@ -55790,7 +55789,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="509" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
         <v>677</v>
       </c>
@@ -55885,7 +55884,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="510" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
         <v>679</v>
       </c>
@@ -55980,7 +55979,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="511" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
         <v>680</v>
       </c>
@@ -56075,7 +56074,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="512" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
         <v>681</v>
       </c>
@@ -56170,7 +56169,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="513" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
         <v>683</v>
       </c>
@@ -56265,7 +56264,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="514" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
         <v>685</v>
       </c>
@@ -56360,7 +56359,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="515" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
         <v>687</v>
       </c>
@@ -56455,7 +56454,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="516" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
         <v>688</v>
       </c>
@@ -56550,7 +56549,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="517" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
         <v>689</v>
       </c>
@@ -56645,7 +56644,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="518" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
         <v>691</v>
       </c>
@@ -56740,7 +56739,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="519" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
         <v>692</v>
       </c>
@@ -56835,7 +56834,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="520" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
         <v>694</v>
       </c>
@@ -56930,7 +56929,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="521" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
         <v>695</v>
       </c>
@@ -57025,7 +57024,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="522" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
         <v>697</v>
       </c>
@@ -57086,7 +57085,7 @@
       <c r="AH522" s="4"/>
       <c r="AI522" s="4"/>
     </row>
-    <row r="523" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
         <v>703</v>
       </c>
@@ -57147,7 +57146,7 @@
       <c r="AH523" s="4"/>
       <c r="AI523" s="4"/>
     </row>
-    <row r="524" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
         <v>705</v>
       </c>
@@ -57208,7 +57207,7 @@
       <c r="AH524" s="4"/>
       <c r="AI524" s="4"/>
     </row>
-    <row r="525" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
         <v>710</v>
       </c>
@@ -57269,7 +57268,7 @@
       <c r="AH525" s="4"/>
       <c r="AI525" s="4"/>
     </row>
-    <row r="526" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
         <v>711</v>
       </c>
@@ -57330,7 +57329,7 @@
       <c r="AH526" s="4"/>
       <c r="AI526" s="4"/>
     </row>
-    <row r="527" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
         <v>712</v>
       </c>
@@ -57391,7 +57390,7 @@
       <c r="AH527" s="4"/>
       <c r="AI527" s="4"/>
     </row>
-    <row r="528" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
         <v>715</v>
       </c>
@@ -57452,7 +57451,7 @@
       <c r="AH528" s="4"/>
       <c r="AI528" s="4"/>
     </row>
-    <row r="529" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
         <v>716</v>
       </c>
@@ -57513,7 +57512,7 @@
       <c r="AH529" s="4"/>
       <c r="AI529" s="4"/>
     </row>
-    <row r="530" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
         <v>719</v>
       </c>
@@ -57574,7 +57573,7 @@
       <c r="AH530" s="4"/>
       <c r="AI530" s="4"/>
     </row>
-    <row r="531" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
         <v>720</v>
       </c>
@@ -57635,7 +57634,7 @@
       <c r="AH531" s="4"/>
       <c r="AI531" s="4"/>
     </row>
-    <row r="532" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
         <v>722</v>
       </c>
@@ -57696,7 +57695,7 @@
       <c r="AH532" s="4"/>
       <c r="AI532" s="4"/>
     </row>
-    <row r="533" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
         <v>723</v>
       </c>
@@ -57757,7 +57756,7 @@
       <c r="AH533" s="4"/>
       <c r="AI533" s="4"/>
     </row>
-    <row r="534" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
         <v>726</v>
       </c>
@@ -57818,7 +57817,7 @@
       <c r="AH534" s="4"/>
       <c r="AI534" s="4"/>
     </row>
-    <row r="535" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
         <v>727</v>
       </c>
@@ -57879,7 +57878,7 @@
       <c r="AH535" s="4"/>
       <c r="AI535" s="4"/>
     </row>
-    <row r="536" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
         <v>728</v>
       </c>
@@ -57940,7 +57939,7 @@
       <c r="AH536" s="4"/>
       <c r="AI536" s="4"/>
     </row>
-    <row r="537" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
         <v>1541</v>
       </c>
@@ -58001,7 +58000,7 @@
       <c r="AH537" s="4"/>
       <c r="AI537" s="4"/>
     </row>
-    <row r="538" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
         <v>734</v>
       </c>
@@ -58062,7 +58061,7 @@
       <c r="AH538" s="4"/>
       <c r="AI538" s="4"/>
     </row>
-    <row r="539" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
         <v>735</v>
       </c>
@@ -58123,7 +58122,7 @@
       <c r="AH539" s="4"/>
       <c r="AI539" s="4"/>
     </row>
-    <row r="540" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
         <v>739</v>
       </c>
@@ -58184,7 +58183,7 @@
       <c r="AH540" s="4"/>
       <c r="AI540" s="4"/>
     </row>
-    <row r="541" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
         <v>742</v>
       </c>
@@ -58245,7 +58244,7 @@
       <c r="AH541" s="4"/>
       <c r="AI541" s="4"/>
     </row>
-    <row r="542" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
         <v>744</v>
       </c>
@@ -58306,7 +58305,7 @@
       <c r="AH542" s="4"/>
       <c r="AI542" s="4"/>
     </row>
-    <row r="543" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
         <v>746</v>
       </c>
@@ -58367,7 +58366,7 @@
       <c r="AH543" s="4"/>
       <c r="AI543" s="4"/>
     </row>
-    <row r="544" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
         <v>748</v>
       </c>
@@ -58428,7 +58427,7 @@
       <c r="AH544" s="4"/>
       <c r="AI544" s="4"/>
     </row>
-    <row r="545" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
         <v>749</v>
       </c>
@@ -58489,7 +58488,7 @@
       <c r="AH545" s="4"/>
       <c r="AI545" s="4"/>
     </row>
-    <row r="546" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
         <v>750</v>
       </c>
@@ -58550,7 +58549,7 @@
       <c r="AH546" s="4"/>
       <c r="AI546" s="4"/>
     </row>
-    <row r="547" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
         <v>753</v>
       </c>
@@ -58611,7 +58610,7 @@
       <c r="AH547" s="4"/>
       <c r="AI547" s="4"/>
     </row>
-    <row r="548" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
         <v>754</v>
       </c>
@@ -58672,7 +58671,7 @@
       <c r="AH548" s="4"/>
       <c r="AI548" s="4"/>
     </row>
-    <row r="549" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
         <v>756</v>
       </c>
@@ -58733,7 +58732,7 @@
       <c r="AH549" s="4"/>
       <c r="AI549" s="4"/>
     </row>
-    <row r="550" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
         <v>758</v>
       </c>
@@ -58794,7 +58793,7 @@
       <c r="AH550" s="4"/>
       <c r="AI550" s="4"/>
     </row>
-    <row r="551" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
         <v>759</v>
       </c>
@@ -58855,7 +58854,7 @@
       <c r="AH551" s="4"/>
       <c r="AI551" s="4"/>
     </row>
-    <row r="552" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
         <v>761</v>
       </c>
@@ -58916,7 +58915,7 @@
       <c r="AH552" s="4"/>
       <c r="AI552" s="4"/>
     </row>
-    <row r="553" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
         <v>763</v>
       </c>
@@ -58977,7 +58976,7 @@
       <c r="AH553" s="4"/>
       <c r="AI553" s="4"/>
     </row>
-    <row r="554" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
         <v>766</v>
       </c>
@@ -59038,7 +59037,7 @@
       <c r="AH554" s="4"/>
       <c r="AI554" s="4"/>
     </row>
-    <row r="555" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
         <v>768</v>
       </c>
@@ -59099,7 +59098,7 @@
       <c r="AH555" s="4"/>
       <c r="AI555" s="4"/>
     </row>
-    <row r="556" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
         <v>769</v>
       </c>
@@ -59160,7 +59159,7 @@
       <c r="AH556" s="4"/>
       <c r="AI556" s="4"/>
     </row>
-    <row r="557" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
         <v>772</v>
       </c>
@@ -59221,7 +59220,7 @@
       <c r="AH557" s="4"/>
       <c r="AI557" s="4"/>
     </row>
-    <row r="558" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
         <v>773</v>
       </c>
@@ -59282,7 +59281,7 @@
       <c r="AH558" s="4"/>
       <c r="AI558" s="4"/>
     </row>
-    <row r="559" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
         <v>776</v>
       </c>
@@ -59343,7 +59342,7 @@
       <c r="AH559" s="4"/>
       <c r="AI559" s="4"/>
     </row>
-    <row r="560" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
         <v>777</v>
       </c>
@@ -59404,7 +59403,7 @@
       <c r="AH560" s="4"/>
       <c r="AI560" s="4"/>
     </row>
-    <row r="561" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
         <v>779</v>
       </c>
@@ -59465,7 +59464,7 @@
       <c r="AH561" s="4"/>
       <c r="AI561" s="4"/>
     </row>
-    <row r="562" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
         <v>782</v>
       </c>
@@ -59526,7 +59525,7 @@
       <c r="AH562" s="4"/>
       <c r="AI562" s="4"/>
     </row>
-    <row r="563" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
         <v>783</v>
       </c>
@@ -59587,7 +59586,7 @@
       <c r="AH563" s="4"/>
       <c r="AI563" s="4"/>
     </row>
-    <row r="564" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
         <v>786</v>
       </c>
@@ -59648,7 +59647,7 @@
       <c r="AH564" s="4"/>
       <c r="AI564" s="4"/>
     </row>
-    <row r="565" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
         <v>787</v>
       </c>
@@ -59709,7 +59708,7 @@
       <c r="AH565" s="4"/>
       <c r="AI565" s="4"/>
     </row>
-    <row r="566" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
         <v>791</v>
       </c>
@@ -59770,7 +59769,7 @@
       <c r="AH566" s="4"/>
       <c r="AI566" s="4"/>
     </row>
-    <row r="567" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
         <v>794</v>
       </c>
@@ -59831,7 +59830,7 @@
       <c r="AH567" s="4"/>
       <c r="AI567" s="4"/>
     </row>
-    <row r="568" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
         <v>800</v>
       </c>
@@ -59892,7 +59891,7 @@
       <c r="AH568" s="4"/>
       <c r="AI568" s="4"/>
     </row>
-    <row r="569" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
         <v>801</v>
       </c>
@@ -59953,7 +59952,7 @@
       <c r="AH569" s="4"/>
       <c r="AI569" s="4"/>
     </row>
-    <row r="570" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
         <v>803</v>
       </c>
@@ -60014,7 +60013,7 @@
       <c r="AH570" s="4"/>
       <c r="AI570" s="4"/>
     </row>
-    <row r="571" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
         <v>805</v>
       </c>
@@ -60075,7 +60074,7 @@
       <c r="AH571" s="4"/>
       <c r="AI571" s="4"/>
     </row>
-    <row r="572" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
         <v>807</v>
       </c>
@@ -60136,7 +60135,7 @@
       <c r="AH572" s="4"/>
       <c r="AI572" s="4"/>
     </row>
-    <row r="573" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
         <v>810</v>
       </c>
@@ -60197,7 +60196,7 @@
       <c r="AH573" s="4"/>
       <c r="AI573" s="4"/>
     </row>
-    <row r="574" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
         <v>811</v>
       </c>
@@ -60258,7 +60257,7 @@
       <c r="AH574" s="4"/>
       <c r="AI574" s="4"/>
     </row>
-    <row r="575" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
         <v>812</v>
       </c>
@@ -60319,7 +60318,7 @@
       <c r="AH575" s="4"/>
       <c r="AI575" s="4"/>
     </row>
-    <row r="576" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
         <v>815</v>
       </c>
@@ -60380,7 +60379,7 @@
       <c r="AH576" s="4"/>
       <c r="AI576" s="4"/>
     </row>
-    <row r="577" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
         <v>816</v>
       </c>
@@ -60441,7 +60440,7 @@
       <c r="AH577" s="4"/>
       <c r="AI577" s="4"/>
     </row>
-    <row r="578" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
         <v>817</v>
       </c>
@@ -60502,7 +60501,7 @@
       <c r="AH578" s="4"/>
       <c r="AI578" s="4"/>
     </row>
-    <row r="579" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
         <v>820</v>
       </c>
@@ -60563,7 +60562,7 @@
       <c r="AH579" s="4"/>
       <c r="AI579" s="4"/>
     </row>
-    <row r="580" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
         <v>821</v>
       </c>
@@ -60624,7 +60623,7 @@
       <c r="AH580" s="4"/>
       <c r="AI580" s="4"/>
     </row>
-    <row r="581" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
         <v>822</v>
       </c>
@@ -60685,7 +60684,7 @@
       <c r="AH581" s="4"/>
       <c r="AI581" s="4"/>
     </row>
-    <row r="582" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
         <v>825</v>
       </c>
@@ -60746,7 +60745,7 @@
       <c r="AH582" s="4"/>
       <c r="AI582" s="4"/>
     </row>
-    <row r="583" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
         <v>826</v>
       </c>
@@ -60807,7 +60806,7 @@
       <c r="AH583" s="4"/>
       <c r="AI583" s="4"/>
     </row>
-    <row r="584" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
         <v>827</v>
       </c>
@@ -60868,7 +60867,7 @@
       <c r="AH584" s="4"/>
       <c r="AI584" s="4"/>
     </row>
-    <row r="585" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
         <v>831</v>
       </c>
@@ -60929,7 +60928,7 @@
       <c r="AH585" s="4"/>
       <c r="AI585" s="4"/>
     </row>
-    <row r="586" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
         <v>832</v>
       </c>
@@ -60990,7 +60989,7 @@
       <c r="AH586" s="4"/>
       <c r="AI586" s="4"/>
     </row>
-    <row r="587" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
         <v>833</v>
       </c>
@@ -61051,7 +61050,7 @@
       <c r="AH587" s="4"/>
       <c r="AI587" s="4"/>
     </row>
-    <row r="588" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
         <v>836</v>
       </c>
@@ -61112,7 +61111,7 @@
       <c r="AH588" s="4"/>
       <c r="AI588" s="4"/>
     </row>
-    <row r="589" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
         <v>837</v>
       </c>
@@ -61173,7 +61172,7 @@
       <c r="AH589" s="4"/>
       <c r="AI589" s="4"/>
     </row>
-    <row r="590" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
         <v>838</v>
       </c>
@@ -61234,7 +61233,7 @@
       <c r="AH590" s="4"/>
       <c r="AI590" s="4"/>
     </row>
-    <row r="591" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
         <v>841</v>
       </c>
@@ -61295,7 +61294,7 @@
       <c r="AH591" s="4"/>
       <c r="AI591" s="4"/>
     </row>
-    <row r="592" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
         <v>842</v>
       </c>
@@ -61356,7 +61355,7 @@
       <c r="AH592" s="4"/>
       <c r="AI592" s="4"/>
     </row>
-    <row r="593" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
         <v>843</v>
       </c>
@@ -61417,7 +61416,7 @@
       <c r="AH593" s="4"/>
       <c r="AI593" s="4"/>
     </row>
-    <row r="594" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
         <v>846</v>
       </c>
@@ -61478,7 +61477,7 @@
       <c r="AH594" s="4"/>
       <c r="AI594" s="4"/>
     </row>
-    <row r="595" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
         <v>847</v>
       </c>
@@ -61539,7 +61538,7 @@
       <c r="AH595" s="4"/>
       <c r="AI595" s="4"/>
     </row>
-    <row r="596" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
         <v>848</v>
       </c>
@@ -61600,7 +61599,7 @@
       <c r="AH596" s="4"/>
       <c r="AI596" s="4"/>
     </row>
-    <row r="597" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
         <v>849</v>
       </c>
@@ -61661,7 +61660,7 @@
       <c r="AH597" s="4"/>
       <c r="AI597" s="4"/>
     </row>
-    <row r="598" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
         <v>853</v>
       </c>
@@ -61722,7 +61721,7 @@
       <c r="AH598" s="4"/>
       <c r="AI598" s="4"/>
     </row>
-    <row r="599" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
         <v>854</v>
       </c>
@@ -61783,7 +61782,7 @@
       <c r="AH599" s="4"/>
       <c r="AI599" s="4"/>
     </row>
-    <row r="600" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
         <v>855</v>
       </c>
@@ -61844,7 +61843,7 @@
       <c r="AH600" s="4"/>
       <c r="AI600" s="4"/>
     </row>
-    <row r="601" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
         <v>856</v>
       </c>
@@ -61905,7 +61904,7 @@
       <c r="AH601" s="4"/>
       <c r="AI601" s="4"/>
     </row>
-    <row r="602" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
         <v>857</v>
       </c>
@@ -61966,7 +61965,7 @@
       <c r="AH602" s="4"/>
       <c r="AI602" s="4"/>
     </row>
-    <row r="603" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
         <v>860</v>
       </c>
@@ -62027,7 +62026,7 @@
       <c r="AH603" s="4"/>
       <c r="AI603" s="4"/>
     </row>
-    <row r="604" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
         <v>861</v>
       </c>
@@ -62088,7 +62087,7 @@
       <c r="AH604" s="4"/>
       <c r="AI604" s="4"/>
     </row>
-    <row r="605" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
         <v>862</v>
       </c>
@@ -62149,7 +62148,7 @@
       <c r="AH605" s="4"/>
       <c r="AI605" s="4"/>
     </row>
-    <row r="606" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
         <v>865</v>
       </c>
@@ -62210,7 +62209,7 @@
       <c r="AH606" s="4"/>
       <c r="AI606" s="4"/>
     </row>
-    <row r="607" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
         <v>866</v>
       </c>
@@ -62271,7 +62270,7 @@
       <c r="AH607" s="4"/>
       <c r="AI607" s="4"/>
     </row>
-    <row r="608" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
         <v>867</v>
       </c>
@@ -62332,7 +62331,7 @@
       <c r="AH608" s="4"/>
       <c r="AI608" s="4"/>
     </row>
-    <row r="609" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
         <v>870</v>
       </c>
@@ -62393,7 +62392,7 @@
       <c r="AH609" s="4"/>
       <c r="AI609" s="4"/>
     </row>
-    <row r="610" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
         <v>871</v>
       </c>
@@ -62454,7 +62453,7 @@
       <c r="AH610" s="4"/>
       <c r="AI610" s="4"/>
     </row>
-    <row r="611" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
         <v>872</v>
       </c>
@@ -62515,7 +62514,7 @@
       <c r="AH611" s="4"/>
       <c r="AI611" s="4"/>
     </row>
-    <row r="612" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
         <v>875</v>
       </c>
@@ -62576,7 +62575,7 @@
       <c r="AH612" s="4"/>
       <c r="AI612" s="4"/>
     </row>
-    <row r="613" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
         <v>876</v>
       </c>
@@ -62637,7 +62636,7 @@
       <c r="AH613" s="4"/>
       <c r="AI613" s="4"/>
     </row>
-    <row r="614" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
         <v>877</v>
       </c>
@@ -62698,7 +62697,7 @@
       <c r="AH614" s="4"/>
       <c r="AI614" s="4"/>
     </row>
-    <row r="615" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
         <v>880</v>
       </c>
@@ -62759,7 +62758,7 @@
       <c r="AH615" s="4"/>
       <c r="AI615" s="4"/>
     </row>
-    <row r="616" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
         <v>881</v>
       </c>
@@ -62820,7 +62819,7 @@
       <c r="AH616" s="4"/>
       <c r="AI616" s="4"/>
     </row>
-    <row r="617" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
         <v>882</v>
       </c>
@@ -62881,7 +62880,7 @@
       <c r="AH617" s="4"/>
       <c r="AI617" s="4"/>
     </row>
-    <row r="618" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
         <v>885</v>
       </c>
@@ -62942,7 +62941,7 @@
       <c r="AH618" s="4"/>
       <c r="AI618" s="4"/>
     </row>
-    <row r="619" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
         <v>886</v>
       </c>
@@ -63003,7 +63002,7 @@
       <c r="AH619" s="4"/>
       <c r="AI619" s="4"/>
     </row>
-    <row r="620" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
         <v>887</v>
       </c>
@@ -63064,7 +63063,7 @@
       <c r="AH620" s="4"/>
       <c r="AI620" s="4"/>
     </row>
-    <row r="621" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
         <v>890</v>
       </c>
@@ -63125,7 +63124,7 @@
       <c r="AH621" s="4"/>
       <c r="AI621" s="4"/>
     </row>
-    <row r="622" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
         <v>891</v>
       </c>
@@ -63186,7 +63185,7 @@
       <c r="AH622" s="4"/>
       <c r="AI622" s="4"/>
     </row>
-    <row r="623" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
         <v>892</v>
       </c>
@@ -63247,7 +63246,7 @@
       <c r="AH623" s="4"/>
       <c r="AI623" s="4"/>
     </row>
-    <row r="624" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
         <v>895</v>
       </c>
@@ -63308,7 +63307,7 @@
       <c r="AH624" s="4"/>
       <c r="AI624" s="4"/>
     </row>
-    <row r="625" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
         <v>896</v>
       </c>
@@ -63369,7 +63368,7 @@
       <c r="AH625" s="4"/>
       <c r="AI625" s="4"/>
     </row>
-    <row r="626" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
         <v>897</v>
       </c>
@@ -63430,7 +63429,7 @@
       <c r="AH626" s="4"/>
       <c r="AI626" s="4"/>
     </row>
-    <row r="627" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
         <v>898</v>
       </c>
@@ -63491,7 +63490,7 @@
       <c r="AH627" s="4"/>
       <c r="AI627" s="4"/>
     </row>
-    <row r="628" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
         <v>901</v>
       </c>
@@ -63552,7 +63551,7 @@
       <c r="AH628" s="4"/>
       <c r="AI628" s="4"/>
     </row>
-    <row r="629" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
         <v>903</v>
       </c>
@@ -63613,7 +63612,7 @@
       <c r="AH629" s="4"/>
       <c r="AI629" s="4"/>
     </row>
-    <row r="630" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
         <v>905</v>
       </c>
@@ -63674,7 +63673,7 @@
       <c r="AH630" s="4"/>
       <c r="AI630" s="4"/>
     </row>
-    <row r="631" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
         <v>907</v>
       </c>
@@ -63735,7 +63734,7 @@
       <c r="AH631" s="4"/>
       <c r="AI631" s="4"/>
     </row>
-    <row r="632" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
         <v>911</v>
       </c>
@@ -63796,7 +63795,7 @@
       <c r="AH632" s="4"/>
       <c r="AI632" s="4"/>
     </row>
-    <row r="633" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
         <v>913</v>
       </c>
@@ -63857,7 +63856,7 @@
       <c r="AH633" s="4"/>
       <c r="AI633" s="4"/>
     </row>
-    <row r="634" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
         <v>915</v>
       </c>
@@ -63918,7 +63917,7 @@
       <c r="AH634" s="4"/>
       <c r="AI634" s="4"/>
     </row>
-    <row r="635" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
         <v>917</v>
       </c>
@@ -63979,7 +63978,7 @@
       <c r="AH635" s="4"/>
       <c r="AI635" s="4"/>
     </row>
-    <row r="636" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
         <v>919</v>
       </c>
@@ -64040,7 +64039,7 @@
       <c r="AH636" s="4"/>
       <c r="AI636" s="4"/>
     </row>
-    <row r="637" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
         <v>922</v>
       </c>
@@ -64101,7 +64100,7 @@
       <c r="AH637" s="4"/>
       <c r="AI637" s="4"/>
     </row>
-    <row r="638" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
         <v>923</v>
       </c>
@@ -64162,7 +64161,7 @@
       <c r="AH638" s="4"/>
       <c r="AI638" s="4"/>
     </row>
-    <row r="639" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
         <v>924</v>
       </c>
@@ -64223,7 +64222,7 @@
       <c r="AH639" s="4"/>
       <c r="AI639" s="4"/>
     </row>
-    <row r="640" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
         <v>925</v>
       </c>
@@ -64284,7 +64283,7 @@
       <c r="AH640" s="4"/>
       <c r="AI640" s="4"/>
     </row>
-    <row r="641" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
         <v>926</v>
       </c>
@@ -64345,7 +64344,7 @@
       <c r="AH641" s="4"/>
       <c r="AI641" s="4"/>
     </row>
-    <row r="642" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
         <v>929</v>
       </c>
@@ -64406,7 +64405,7 @@
       <c r="AH642" s="4"/>
       <c r="AI642" s="4"/>
     </row>
-    <row r="643" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
         <v>933</v>
       </c>
@@ -64467,7 +64466,7 @@
       <c r="AH643" s="4"/>
       <c r="AI643" s="4"/>
     </row>
-    <row r="644" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
         <v>934</v>
       </c>
@@ -64528,7 +64527,7 @@
       <c r="AH644" s="4"/>
       <c r="AI644" s="4"/>
     </row>
-    <row r="645" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
         <v>937</v>
       </c>
@@ -64589,7 +64588,7 @@
       <c r="AH645" s="4"/>
       <c r="AI645" s="4"/>
     </row>
-    <row r="646" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
         <v>938</v>
       </c>
@@ -64650,7 +64649,7 @@
       <c r="AH646" s="4"/>
       <c r="AI646" s="4"/>
     </row>
-    <row r="647" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
         <v>941</v>
       </c>
@@ -64711,7 +64710,7 @@
       <c r="AH647" s="4"/>
       <c r="AI647" s="4"/>
     </row>
-    <row r="648" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
         <v>944</v>
       </c>
@@ -64772,7 +64771,7 @@
       <c r="AH648" s="4"/>
       <c r="AI648" s="4"/>
     </row>
-    <row r="649" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
         <v>946</v>
       </c>
@@ -64833,7 +64832,7 @@
       <c r="AH649" s="4"/>
       <c r="AI649" s="4"/>
     </row>
-    <row r="650" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
         <v>949</v>
       </c>
@@ -64894,7 +64893,7 @@
       <c r="AH650" s="4"/>
       <c r="AI650" s="4"/>
     </row>
-    <row r="651" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
         <v>952</v>
       </c>
@@ -64955,7 +64954,7 @@
       <c r="AH651" s="4"/>
       <c r="AI651" s="4"/>
     </row>
-    <row r="652" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
         <v>955</v>
       </c>
@@ -65016,7 +65015,7 @@
       <c r="AH652" s="4"/>
       <c r="AI652" s="4"/>
     </row>
-    <row r="653" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
         <v>956</v>
       </c>
@@ -65077,7 +65076,7 @@
       <c r="AH653" s="4"/>
       <c r="AI653" s="4"/>
     </row>
-    <row r="654" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
         <v>957</v>
       </c>
@@ -65138,7 +65137,7 @@
       <c r="AH654" s="4"/>
       <c r="AI654" s="4"/>
     </row>
-    <row r="655" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
         <v>960</v>
       </c>
@@ -65199,7 +65198,7 @@
       <c r="AH655" s="4"/>
       <c r="AI655" s="4"/>
     </row>
-    <row r="656" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
         <v>962</v>
       </c>
@@ -65260,7 +65259,7 @@
       <c r="AH656" s="4"/>
       <c r="AI656" s="4"/>
     </row>
-    <row r="657" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
         <v>963</v>
       </c>
@@ -65321,7 +65320,7 @@
       <c r="AH657" s="4"/>
       <c r="AI657" s="4"/>
     </row>
-    <row r="658" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
         <v>964</v>
       </c>
@@ -65382,7 +65381,7 @@
       <c r="AH658" s="4"/>
       <c r="AI658" s="4"/>
     </row>
-    <row r="659" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
         <v>965</v>
       </c>
@@ -65443,7 +65442,7 @@
       <c r="AH659" s="4"/>
       <c r="AI659" s="4"/>
     </row>
-    <row r="660" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
         <v>968</v>
       </c>
@@ -65504,7 +65503,7 @@
       <c r="AH660" s="4"/>
       <c r="AI660" s="4"/>
     </row>
-    <row r="661" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
         <v>969</v>
       </c>
@@ -65565,7 +65564,7 @@
       <c r="AH661" s="4"/>
       <c r="AI661" s="4"/>
     </row>
-    <row r="662" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
         <v>971</v>
       </c>
@@ -65626,7 +65625,7 @@
       <c r="AH662" s="4"/>
       <c r="AI662" s="4"/>
     </row>
-    <row r="663" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
         <v>972</v>
       </c>
@@ -65687,7 +65686,7 @@
       <c r="AH663" s="4"/>
       <c r="AI663" s="4"/>
     </row>
-    <row r="664" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
         <v>973</v>
       </c>
@@ -65748,7 +65747,7 @@
       <c r="AH664" s="4"/>
       <c r="AI664" s="4"/>
     </row>
-    <row r="665" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
         <v>976</v>
       </c>
@@ -65809,7 +65808,7 @@
       <c r="AH665" s="4"/>
       <c r="AI665" s="4"/>
     </row>
-    <row r="666" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
         <v>978</v>
       </c>
@@ -65870,7 +65869,7 @@
       <c r="AH666" s="4"/>
       <c r="AI666" s="4"/>
     </row>
-    <row r="667" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
         <v>980</v>
       </c>
@@ -65931,7 +65930,7 @@
       <c r="AH667" s="4"/>
       <c r="AI667" s="4"/>
     </row>
-    <row r="668" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
         <v>983</v>
       </c>
@@ -65992,7 +65991,7 @@
       <c r="AH668" s="4"/>
       <c r="AI668" s="4"/>
     </row>
-    <row r="669" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
         <v>986</v>
       </c>
@@ -66053,7 +66052,7 @@
       <c r="AH669" s="4"/>
       <c r="AI669" s="4"/>
     </row>
-    <row r="670" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
         <v>989</v>
       </c>
@@ -66114,7 +66113,7 @@
       <c r="AH670" s="4"/>
       <c r="AI670" s="4"/>
     </row>
-    <row r="671" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
         <v>990</v>
       </c>
@@ -66175,7 +66174,7 @@
       <c r="AH671" s="4"/>
       <c r="AI671" s="4"/>
     </row>
-    <row r="672" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
         <v>993</v>
       </c>
@@ -66236,7 +66235,7 @@
       <c r="AH672" s="4"/>
       <c r="AI672" s="4"/>
     </row>
-    <row r="673" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
         <v>994</v>
       </c>
@@ -66297,7 +66296,7 @@
       <c r="AH673" s="4"/>
       <c r="AI673" s="4"/>
     </row>
-    <row r="674" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
         <v>995</v>
       </c>
@@ -66358,7 +66357,7 @@
       <c r="AH674" s="4"/>
       <c r="AI674" s="4"/>
     </row>
-    <row r="675" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
         <v>996</v>
       </c>
@@ -66419,7 +66418,7 @@
       <c r="AH675" s="4"/>
       <c r="AI675" s="4"/>
     </row>
-    <row r="676" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
         <v>999</v>
       </c>
@@ -66480,7 +66479,7 @@
       <c r="AH676" s="4"/>
       <c r="AI676" s="4"/>
     </row>
-    <row r="677" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
         <v>1000</v>
       </c>
@@ -66541,7 +66540,7 @@
       <c r="AH677" s="4"/>
       <c r="AI677" s="4"/>
     </row>
-    <row r="678" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
         <v>1001</v>
       </c>
@@ -66602,7 +66601,7 @@
       <c r="AH678" s="4"/>
       <c r="AI678" s="4"/>
     </row>
-    <row r="679" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
         <v>1002</v>
       </c>
@@ -66663,7 +66662,7 @@
       <c r="AH679" s="4"/>
       <c r="AI679" s="4"/>
     </row>
-    <row r="680" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
         <v>1005</v>
       </c>
@@ -66724,7 +66723,7 @@
       <c r="AH680" s="4"/>
       <c r="AI680" s="4"/>
     </row>
-    <row r="681" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
         <v>1008</v>
       </c>
@@ -66785,7 +66784,7 @@
       <c r="AH681" s="4"/>
       <c r="AI681" s="4"/>
     </row>
-    <row r="682" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
         <v>1009</v>
       </c>
@@ -66846,7 +66845,7 @@
       <c r="AH682" s="4"/>
       <c r="AI682" s="4"/>
     </row>
-    <row r="683" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
         <v>1010</v>
       </c>
@@ -66907,7 +66906,7 @@
       <c r="AH683" s="4"/>
       <c r="AI683" s="4"/>
     </row>
-    <row r="684" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
         <v>1011</v>
       </c>
@@ -66968,7 +66967,7 @@
       <c r="AH684" s="4"/>
       <c r="AI684" s="4"/>
     </row>
-    <row r="685" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
         <v>1012</v>
       </c>
@@ -67029,7 +67028,7 @@
       <c r="AH685" s="4"/>
       <c r="AI685" s="4"/>
     </row>
-    <row r="686" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
         <v>1015</v>
       </c>
@@ -67090,7 +67089,7 @@
       <c r="AH686" s="4"/>
       <c r="AI686" s="4"/>
     </row>
-    <row r="687" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
         <v>1016</v>
       </c>
@@ -67151,7 +67150,7 @@
       <c r="AH687" s="4"/>
       <c r="AI687" s="4"/>
     </row>
-    <row r="688" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
         <v>1019</v>
       </c>
@@ -67212,7 +67211,7 @@
       <c r="AH688" s="4"/>
       <c r="AI688" s="4"/>
     </row>
-    <row r="689" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
         <v>1020</v>
       </c>
@@ -67273,7 +67272,7 @@
       <c r="AH689" s="4"/>
       <c r="AI689" s="4"/>
     </row>
-    <row r="690" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
         <v>1022</v>
       </c>
@@ -67334,7 +67333,7 @@
       <c r="AH690" s="4"/>
       <c r="AI690" s="4"/>
     </row>
-    <row r="691" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
         <v>1027</v>
       </c>
@@ -67395,7 +67394,7 @@
       <c r="AH691" s="4"/>
       <c r="AI691" s="4"/>
     </row>
-    <row r="692" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
         <v>1029</v>
       </c>
@@ -67456,7 +67455,7 @@
       <c r="AH692" s="4"/>
       <c r="AI692" s="4"/>
     </row>
-    <row r="693" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
         <v>1033</v>
       </c>
@@ -67517,7 +67516,7 @@
       <c r="AH693" s="4"/>
       <c r="AI693" s="4"/>
     </row>
-    <row r="694" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
         <v>1034</v>
       </c>
@@ -67578,7 +67577,7 @@
       <c r="AH694" s="4"/>
       <c r="AI694" s="4"/>
     </row>
-    <row r="695" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
         <v>1036</v>
       </c>
@@ -67639,7 +67638,7 @@
       <c r="AH695" s="4"/>
       <c r="AI695" s="4"/>
     </row>
-    <row r="696" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
         <v>1039</v>
       </c>
@@ -67700,7 +67699,7 @@
       <c r="AH696" s="4"/>
       <c r="AI696" s="4"/>
     </row>
-    <row r="697" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
         <v>1040</v>
       </c>
@@ -67761,7 +67760,7 @@
       <c r="AH697" s="4"/>
       <c r="AI697" s="4"/>
     </row>
-    <row r="698" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
         <v>1041</v>
       </c>
@@ -67822,7 +67821,7 @@
       <c r="AH698" s="4"/>
       <c r="AI698" s="4"/>
     </row>
-    <row r="699" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
         <v>1043</v>
       </c>
@@ -67883,7 +67882,7 @@
       <c r="AH699" s="4"/>
       <c r="AI699" s="4"/>
     </row>
-    <row r="700" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
         <v>1047</v>
       </c>
@@ -67944,7 +67943,7 @@
       <c r="AH700" s="4"/>
       <c r="AI700" s="4"/>
     </row>
-    <row r="701" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
         <v>1049</v>
       </c>
@@ -68005,7 +68004,7 @@
       <c r="AH701" s="4"/>
       <c r="AI701" s="4"/>
     </row>
-    <row r="702" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
         <v>1052</v>
       </c>
@@ -68066,7 +68065,7 @@
       <c r="AH702" s="4"/>
       <c r="AI702" s="4"/>
     </row>
-    <row r="703" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
         <v>1053</v>
       </c>
@@ -68127,7 +68126,7 @@
       <c r="AH703" s="4"/>
       <c r="AI703" s="4"/>
     </row>
-    <row r="704" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
         <v>1056</v>
       </c>
@@ -68188,7 +68187,7 @@
       <c r="AH704" s="4"/>
       <c r="AI704" s="4"/>
     </row>
-    <row r="705" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
         <v>1057</v>
       </c>
@@ -68249,7 +68248,7 @@
       <c r="AH705" s="4"/>
       <c r="AI705" s="4"/>
     </row>
-    <row r="706" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
         <v>1058</v>
       </c>
@@ -68310,7 +68309,7 @@
       <c r="AH706" s="4"/>
       <c r="AI706" s="4"/>
     </row>
-    <row r="707" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
         <v>1060</v>
       </c>
@@ -68371,7 +68370,7 @@
       <c r="AH707" s="4"/>
       <c r="AI707" s="4"/>
     </row>
-    <row r="708" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
         <v>1061</v>
       </c>
@@ -68432,7 +68431,7 @@
       <c r="AH708" s="4"/>
       <c r="AI708" s="4"/>
     </row>
-    <row r="709" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
         <v>1062</v>
       </c>
@@ -68493,7 +68492,7 @@
       <c r="AH709" s="4"/>
       <c r="AI709" s="4"/>
     </row>
-    <row r="710" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
         <v>1066</v>
       </c>
@@ -68554,7 +68553,7 @@
       <c r="AH710" s="4"/>
       <c r="AI710" s="4"/>
     </row>
-    <row r="711" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
         <v>1068</v>
       </c>
@@ -68615,7 +68614,7 @@
       <c r="AH711" s="4"/>
       <c r="AI711" s="4"/>
     </row>
-    <row r="712" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
         <v>1070</v>
       </c>
@@ -68676,7 +68675,7 @@
       <c r="AH712" s="4"/>
       <c r="AI712" s="4"/>
     </row>
-    <row r="713" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
         <v>1071</v>
       </c>
@@ -68737,7 +68736,7 @@
       <c r="AH713" s="4"/>
       <c r="AI713" s="4"/>
     </row>
-    <row r="714" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
         <v>1074</v>
       </c>
@@ -68798,7 +68797,7 @@
       <c r="AH714" s="4"/>
       <c r="AI714" s="4"/>
     </row>
-    <row r="715" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
         <v>1077</v>
       </c>
@@ -68859,7 +68858,7 @@
       <c r="AH715" s="4"/>
       <c r="AI715" s="4"/>
     </row>
-    <row r="716" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
         <v>1078</v>
       </c>
@@ -68920,7 +68919,7 @@
       <c r="AH716" s="4"/>
       <c r="AI716" s="4"/>
     </row>
-    <row r="717" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
         <v>1081</v>
       </c>
@@ -68981,7 +68980,7 @@
       <c r="AH717" s="4"/>
       <c r="AI717" s="4"/>
     </row>
-    <row r="718" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
         <v>1085</v>
       </c>
@@ -69042,7 +69041,7 @@
       <c r="AH718" s="4"/>
       <c r="AI718" s="4"/>
     </row>
-    <row r="719" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
         <v>1086</v>
       </c>
@@ -69103,7 +69102,7 @@
       <c r="AH719" s="4"/>
       <c r="AI719" s="4"/>
     </row>
-    <row r="720" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
         <v>1087</v>
       </c>
@@ -69164,7 +69163,7 @@
       <c r="AH720" s="4"/>
       <c r="AI720" s="4"/>
     </row>
-    <row r="721" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
         <v>1089</v>
       </c>
@@ -69225,7 +69224,7 @@
       <c r="AH721" s="4"/>
       <c r="AI721" s="4"/>
     </row>
-    <row r="722" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
         <v>1092</v>
       </c>
@@ -69286,7 +69285,7 @@
       <c r="AH722" s="4"/>
       <c r="AI722" s="4"/>
     </row>
-    <row r="723" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
         <v>1093</v>
       </c>
@@ -69347,7 +69346,7 @@
       <c r="AH723" s="4"/>
       <c r="AI723" s="4"/>
     </row>
-    <row r="724" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
         <v>1094</v>
       </c>
@@ -69408,7 +69407,7 @@
       <c r="AH724" s="4"/>
       <c r="AI724" s="4"/>
     </row>
-    <row r="725" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
         <v>1096</v>
       </c>
@@ -69469,7 +69468,7 @@
       <c r="AH725" s="4"/>
       <c r="AI725" s="4"/>
     </row>
-    <row r="726" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
         <v>1097</v>
       </c>
@@ -69530,7 +69529,7 @@
       <c r="AH726" s="4"/>
       <c r="AI726" s="4"/>
     </row>
-    <row r="727" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
         <v>1098</v>
       </c>
@@ -69591,7 +69590,7 @@
       <c r="AH727" s="4"/>
       <c r="AI727" s="4"/>
     </row>
-    <row r="728" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="s">
         <v>1099</v>
       </c>
@@ -69652,7 +69651,7 @@
       <c r="AH728" s="4"/>
       <c r="AI728" s="4"/>
     </row>
-    <row r="729" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
         <v>1100</v>
       </c>
@@ -69713,7 +69712,7 @@
       <c r="AH729" s="4"/>
       <c r="AI729" s="4"/>
     </row>
-    <row r="730" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
         <v>1103</v>
       </c>
@@ -69774,7 +69773,7 @@
       <c r="AH730" s="4"/>
       <c r="AI730" s="4"/>
     </row>
-    <row r="731" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
         <v>1104</v>
       </c>
@@ -69835,7 +69834,7 @@
       <c r="AH731" s="4"/>
       <c r="AI731" s="4"/>
     </row>
-    <row r="732" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
         <v>1105</v>
       </c>
@@ -69896,7 +69895,7 @@
       <c r="AH732" s="4"/>
       <c r="AI732" s="4"/>
     </row>
-    <row r="733" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
         <v>1108</v>
       </c>
@@ -69957,7 +69956,7 @@
       <c r="AH733" s="4"/>
       <c r="AI733" s="4"/>
     </row>
-    <row r="734" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
         <v>1110</v>
       </c>
@@ -70018,7 +70017,7 @@
       <c r="AH734" s="4"/>
       <c r="AI734" s="4"/>
     </row>
-    <row r="735" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
         <v>1111</v>
       </c>
@@ -70079,7 +70078,7 @@
       <c r="AH735" s="4"/>
       <c r="AI735" s="4"/>
     </row>
-    <row r="736" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
         <v>1114</v>
       </c>
@@ -70140,7 +70139,7 @@
       <c r="AH736" s="4"/>
       <c r="AI736" s="4"/>
     </row>
-    <row r="737" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
         <v>1116</v>
       </c>
@@ -70201,7 +70200,7 @@
       <c r="AH737" s="4"/>
       <c r="AI737" s="4"/>
     </row>
-    <row r="738" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
         <v>1117</v>
       </c>
@@ -70262,7 +70261,7 @@
       <c r="AH738" s="4"/>
       <c r="AI738" s="4"/>
     </row>
-    <row r="739" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
         <v>1118</v>
       </c>
@@ -70323,7 +70322,7 @@
       <c r="AH739" s="4"/>
       <c r="AI739" s="4"/>
     </row>
-    <row r="740" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
         <v>1121</v>
       </c>
@@ -70384,7 +70383,7 @@
       <c r="AH740" s="4"/>
       <c r="AI740" s="4"/>
     </row>
-    <row r="741" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
         <v>1122</v>
       </c>
@@ -70445,7 +70444,7 @@
       <c r="AH741" s="4"/>
       <c r="AI741" s="4"/>
     </row>
-    <row r="742" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
         <v>1125</v>
       </c>
@@ -70506,7 +70505,7 @@
       <c r="AH742" s="4"/>
       <c r="AI742" s="4"/>
     </row>
-    <row r="743" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
         <v>1126</v>
       </c>
@@ -70567,7 +70566,7 @@
       <c r="AH743" s="4"/>
       <c r="AI743" s="4"/>
     </row>
-    <row r="744" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
         <v>1129</v>
       </c>
@@ -70628,7 +70627,7 @@
       <c r="AH744" s="4"/>
       <c r="AI744" s="4"/>
     </row>
-    <row r="745" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
         <v>1131</v>
       </c>
@@ -70689,7 +70688,7 @@
       <c r="AH745" s="4"/>
       <c r="AI745" s="4"/>
     </row>
-    <row r="746" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
         <v>1134</v>
       </c>
@@ -70750,7 +70749,7 @@
       <c r="AH746" s="4"/>
       <c r="AI746" s="4"/>
     </row>
-    <row r="747" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
         <v>1135</v>
       </c>
@@ -70811,7 +70810,7 @@
       <c r="AH747" s="4"/>
       <c r="AI747" s="4"/>
     </row>
-    <row r="748" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
         <v>1138</v>
       </c>
@@ -70872,7 +70871,7 @@
       <c r="AH748" s="4"/>
       <c r="AI748" s="4"/>
     </row>
-    <row r="749" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
         <v>1139</v>
       </c>
@@ -70933,7 +70932,7 @@
       <c r="AH749" s="4"/>
       <c r="AI749" s="4"/>
     </row>
-    <row r="750" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
         <v>1143</v>
       </c>
@@ -70994,7 +70993,7 @@
       <c r="AH750" s="4"/>
       <c r="AI750" s="4"/>
     </row>
-    <row r="751" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
         <v>1144</v>
       </c>
@@ -71055,7 +71054,7 @@
       <c r="AH751" s="4"/>
       <c r="AI751" s="4"/>
     </row>
-    <row r="752" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
         <v>1145</v>
       </c>
@@ -71116,7 +71115,7 @@
       <c r="AH752" s="4"/>
       <c r="AI752" s="4"/>
     </row>
-    <row r="753" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
         <v>1147</v>
       </c>
@@ -71177,7 +71176,7 @@
       <c r="AH753" s="4"/>
       <c r="AI753" s="4"/>
     </row>
-    <row r="754" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
         <v>1148</v>
       </c>
@@ -71238,7 +71237,7 @@
       <c r="AH754" s="4"/>
       <c r="AI754" s="4"/>
     </row>
-    <row r="755" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
         <v>1150</v>
       </c>
@@ -71299,7 +71298,7 @@
       <c r="AH755" s="4"/>
       <c r="AI755" s="4"/>
     </row>
-    <row r="756" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
         <v>1151</v>
       </c>
@@ -71360,7 +71359,7 @@
       <c r="AH756" s="4"/>
       <c r="AI756" s="4"/>
     </row>
-    <row r="757" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
         <v>1154</v>
       </c>
@@ -71421,7 +71420,7 @@
       <c r="AH757" s="4"/>
       <c r="AI757" s="4"/>
     </row>
-    <row r="758" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
         <v>1156</v>
       </c>
@@ -71482,7 +71481,7 @@
       <c r="AH758" s="4"/>
       <c r="AI758" s="4"/>
     </row>
-    <row r="759" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
         <v>1157</v>
       </c>
@@ -71543,7 +71542,7 @@
       <c r="AH759" s="4"/>
       <c r="AI759" s="4"/>
     </row>
-    <row r="760" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
         <v>1160</v>
       </c>
@@ -71604,7 +71603,7 @@
       <c r="AH760" s="4"/>
       <c r="AI760" s="4"/>
     </row>
-    <row r="761" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
         <v>1161</v>
       </c>
@@ -71665,7 +71664,7 @@
       <c r="AH761" s="4"/>
       <c r="AI761" s="4"/>
     </row>
-    <row r="762" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
         <v>1162</v>
       </c>
@@ -71726,7 +71725,7 @@
       <c r="AH762" s="4"/>
       <c r="AI762" s="4"/>
     </row>
-    <row r="763" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
         <v>1164</v>
       </c>
@@ -71787,7 +71786,7 @@
       <c r="AH763" s="4"/>
       <c r="AI763" s="4"/>
     </row>
-    <row r="764" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
         <v>1165</v>
       </c>
@@ -71848,7 +71847,7 @@
       <c r="AH764" s="4"/>
       <c r="AI764" s="4"/>
     </row>
-    <row r="765" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
         <v>1168</v>
       </c>
@@ -71909,7 +71908,7 @@
       <c r="AH765" s="4"/>
       <c r="AI765" s="4"/>
     </row>
-    <row r="766" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
         <v>1169</v>
       </c>
@@ -71970,7 +71969,7 @@
       <c r="AH766" s="4"/>
       <c r="AI766" s="4"/>
     </row>
-    <row r="767" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
         <v>1170</v>
       </c>
@@ -72031,7 +72030,7 @@
       <c r="AH767" s="4"/>
       <c r="AI767" s="4"/>
     </row>
-    <row r="768" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="s">
         <v>1172</v>
       </c>
@@ -72092,7 +72091,7 @@
       <c r="AH768" s="4"/>
       <c r="AI768" s="4"/>
     </row>
-    <row r="769" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
         <v>1173</v>
       </c>
@@ -72153,7 +72152,7 @@
       <c r="AH769" s="4"/>
       <c r="AI769" s="4"/>
     </row>
-    <row r="770" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
         <v>1174</v>
       </c>
@@ -72214,7 +72213,7 @@
       <c r="AH770" s="4"/>
       <c r="AI770" s="4"/>
     </row>
-    <row r="771" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
         <v>1177</v>
       </c>
@@ -72275,7 +72274,7 @@
       <c r="AH771" s="4"/>
       <c r="AI771" s="4"/>
     </row>
-    <row r="772" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
         <v>1178</v>
       </c>
@@ -72336,7 +72335,7 @@
       <c r="AH772" s="4"/>
       <c r="AI772" s="4"/>
     </row>
-    <row r="773" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
         <v>1179</v>
       </c>
@@ -72397,7 +72396,7 @@
       <c r="AH773" s="4"/>
       <c r="AI773" s="4"/>
     </row>
-    <row r="774" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
         <v>1180</v>
       </c>
@@ -72458,7 +72457,7 @@
       <c r="AH774" s="4"/>
       <c r="AI774" s="4"/>
     </row>
-    <row r="775" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
         <v>1183</v>
       </c>
@@ -72519,7 +72518,7 @@
       <c r="AH775" s="4"/>
       <c r="AI775" s="4"/>
     </row>
-    <row r="776" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
         <v>1184</v>
       </c>
@@ -72580,7 +72579,7 @@
       <c r="AH776" s="4"/>
       <c r="AI776" s="4"/>
     </row>
-    <row r="777" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
         <v>1185</v>
       </c>
@@ -72641,7 +72640,7 @@
       <c r="AH777" s="4"/>
       <c r="AI777" s="4"/>
     </row>
-    <row r="778" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
         <v>1186</v>
       </c>
@@ -72702,7 +72701,7 @@
       <c r="AH778" s="4"/>
       <c r="AI778" s="4"/>
     </row>
-    <row r="779" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
         <v>1187</v>
       </c>
@@ -72763,7 +72762,7 @@
       <c r="AH779" s="4"/>
       <c r="AI779" s="4"/>
     </row>
-    <row r="780" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
         <v>1188</v>
       </c>
@@ -72824,7 +72823,7 @@
       <c r="AH780" s="4"/>
       <c r="AI780" s="4"/>
     </row>
-    <row r="781" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
         <v>1191</v>
       </c>
@@ -72885,7 +72884,7 @@
       <c r="AH781" s="4"/>
       <c r="AI781" s="4"/>
     </row>
-    <row r="782" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
         <v>1194</v>
       </c>
@@ -72946,7 +72945,7 @@
       <c r="AH782" s="4"/>
       <c r="AI782" s="4"/>
     </row>
-    <row r="783" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
         <v>1195</v>
       </c>
@@ -73007,7 +73006,7 @@
       <c r="AH783" s="4"/>
       <c r="AI783" s="4"/>
     </row>
-    <row r="784" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784" s="2" t="s">
         <v>1196</v>
       </c>
@@ -73068,7 +73067,7 @@
       <c r="AH784" s="4"/>
       <c r="AI784" s="4"/>
     </row>
-    <row r="785" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
         <v>1197</v>
       </c>
@@ -73129,7 +73128,7 @@
       <c r="AH785" s="4"/>
       <c r="AI785" s="4"/>
     </row>
-    <row r="786" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
         <v>1200</v>
       </c>
@@ -73190,7 +73189,7 @@
       <c r="AH786" s="4"/>
       <c r="AI786" s="4"/>
     </row>
-    <row r="787" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
         <v>1201</v>
       </c>
@@ -73251,7 +73250,7 @@
       <c r="AH787" s="4"/>
       <c r="AI787" s="4"/>
     </row>
-    <row r="788" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="s">
         <v>1202</v>
       </c>
@@ -73312,7 +73311,7 @@
       <c r="AH788" s="4"/>
       <c r="AI788" s="4"/>
     </row>
-    <row r="789" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
         <v>1203</v>
       </c>
@@ -73373,7 +73372,7 @@
       <c r="AH789" s="4"/>
       <c r="AI789" s="4"/>
     </row>
-    <row r="790" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="s">
         <v>1206</v>
       </c>
@@ -73434,7 +73433,7 @@
       <c r="AH790" s="4"/>
       <c r="AI790" s="4"/>
     </row>
-    <row r="791" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="2" t="s">
         <v>1207</v>
       </c>
@@ -73495,7 +73494,7 @@
       <c r="AH791" s="4"/>
       <c r="AI791" s="4"/>
     </row>
-    <row r="792" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="2" t="s">
         <v>1210</v>
       </c>
@@ -73556,7 +73555,7 @@
       <c r="AH792" s="4"/>
       <c r="AI792" s="4"/>
     </row>
-    <row r="793" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="2" t="s">
         <v>1211</v>
       </c>
@@ -73617,7 +73616,7 @@
       <c r="AH793" s="4"/>
       <c r="AI793" s="4"/>
     </row>
-    <row r="794" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794" s="2" t="s">
         <v>1214</v>
       </c>
@@ -73678,7 +73677,7 @@
       <c r="AH794" s="4"/>
       <c r="AI794" s="4"/>
     </row>
-    <row r="795" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="2" t="s">
         <v>1217</v>
       </c>
@@ -73739,7 +73738,7 @@
       <c r="AH795" s="4"/>
       <c r="AI795" s="4"/>
     </row>
-    <row r="796" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796" s="2" t="s">
         <v>1218</v>
       </c>
@@ -73800,7 +73799,7 @@
       <c r="AH796" s="4"/>
       <c r="AI796" s="4"/>
     </row>
-    <row r="797" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A797" s="2" t="s">
         <v>1222</v>
       </c>
@@ -73861,7 +73860,7 @@
       <c r="AH797" s="4"/>
       <c r="AI797" s="4"/>
     </row>
-    <row r="798" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="2" t="s">
         <v>1223</v>
       </c>
@@ -73922,7 +73921,7 @@
       <c r="AH798" s="4"/>
       <c r="AI798" s="4"/>
     </row>
-    <row r="799" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="2" t="s">
         <v>1225</v>
       </c>
@@ -73983,7 +73982,7 @@
       <c r="AH799" s="4"/>
       <c r="AI799" s="4"/>
     </row>
-    <row r="800" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800" s="2" t="s">
         <v>1228</v>
       </c>
@@ -74044,7 +74043,7 @@
       <c r="AH800" s="4"/>
       <c r="AI800" s="4"/>
     </row>
-    <row r="801" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801" s="2" t="s">
         <v>1229</v>
       </c>
@@ -74105,7 +74104,7 @@
       <c r="AH801" s="4"/>
       <c r="AI801" s="4"/>
     </row>
-    <row r="802" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A802" s="2" t="s">
         <v>1230</v>
       </c>
@@ -74166,7 +74165,7 @@
       <c r="AH802" s="4"/>
       <c r="AI802" s="4"/>
     </row>
-    <row r="803" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803" s="2" t="s">
         <v>1231</v>
       </c>
@@ -74227,7 +74226,7 @@
       <c r="AH803" s="4"/>
       <c r="AI803" s="4"/>
     </row>
-    <row r="804" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="2" t="s">
         <v>1234</v>
       </c>
@@ -74288,7 +74287,7 @@
       <c r="AH804" s="4"/>
       <c r="AI804" s="4"/>
     </row>
-    <row r="805" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A805" s="2" t="s">
         <v>1235</v>
       </c>
@@ -74349,7 +74348,7 @@
       <c r="AH805" s="4"/>
       <c r="AI805" s="4"/>
     </row>
-    <row r="806" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806" s="2" t="s">
         <v>1236</v>
       </c>
@@ -74410,7 +74409,7 @@
       <c r="AH806" s="4"/>
       <c r="AI806" s="4"/>
     </row>
-    <row r="807" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807" s="2" t="s">
         <v>1239</v>
       </c>
@@ -74471,7 +74470,7 @@
       <c r="AH807" s="4"/>
       <c r="AI807" s="4"/>
     </row>
-    <row r="808" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A808" s="2" t="s">
         <v>1240</v>
       </c>
@@ -74532,7 +74531,7 @@
       <c r="AH808" s="4"/>
       <c r="AI808" s="4"/>
     </row>
-    <row r="809" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A809" s="2" t="s">
         <v>1241</v>
       </c>
@@ -74593,7 +74592,7 @@
       <c r="AH809" s="4"/>
       <c r="AI809" s="4"/>
     </row>
-    <row r="810" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A810" s="2" t="s">
         <v>1244</v>
       </c>
@@ -74654,7 +74653,7 @@
       <c r="AH810" s="4"/>
       <c r="AI810" s="4"/>
     </row>
-    <row r="811" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A811" s="2" t="s">
         <v>1245</v>
       </c>
@@ -74715,7 +74714,7 @@
       <c r="AH811" s="4"/>
       <c r="AI811" s="4"/>
     </row>
-    <row r="812" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A812" s="2" t="s">
         <v>1247</v>
       </c>
@@ -74776,7 +74775,7 @@
       <c r="AH812" s="4"/>
       <c r="AI812" s="4"/>
     </row>
-    <row r="813" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A813" s="2" t="s">
         <v>1248</v>
       </c>
@@ -74837,7 +74836,7 @@
       <c r="AH813" s="4"/>
       <c r="AI813" s="4"/>
     </row>
-    <row r="814" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A814" s="2" t="s">
         <v>1252</v>
       </c>
@@ -74898,7 +74897,7 @@
       <c r="AH814" s="4"/>
       <c r="AI814" s="4"/>
     </row>
-    <row r="815" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A815" s="2" t="s">
         <v>1253</v>
       </c>
@@ -74959,7 +74958,7 @@
       <c r="AH815" s="4"/>
       <c r="AI815" s="4"/>
     </row>
-    <row r="816" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="2" t="s">
         <v>1255</v>
       </c>
@@ -75020,7 +75019,7 @@
       <c r="AH816" s="4"/>
       <c r="AI816" s="4"/>
     </row>
-    <row r="817" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817" s="2" t="s">
         <v>1256</v>
       </c>
@@ -75081,7 +75080,7 @@
       <c r="AH817" s="4"/>
       <c r="AI817" s="4"/>
     </row>
-    <row r="818" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="2" t="s">
         <v>1257</v>
       </c>
@@ -75142,7 +75141,7 @@
       <c r="AH818" s="4"/>
       <c r="AI818" s="4"/>
     </row>
-    <row r="819" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A819" s="2" t="s">
         <v>1258</v>
       </c>
@@ -75203,7 +75202,7 @@
       <c r="AH819" s="4"/>
       <c r="AI819" s="4"/>
     </row>
-    <row r="820" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A820" s="2" t="s">
         <v>1261</v>
       </c>
@@ -75264,7 +75263,7 @@
       <c r="AH820" s="4"/>
       <c r="AI820" s="4"/>
     </row>
-    <row r="821" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A821" s="2" t="s">
         <v>1262</v>
       </c>
@@ -75325,7 +75324,7 @@
       <c r="AH821" s="4"/>
       <c r="AI821" s="4"/>
     </row>
-    <row r="822" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A822" s="2" t="s">
         <v>1263</v>
       </c>
@@ -75386,7 +75385,7 @@
       <c r="AH822" s="4"/>
       <c r="AI822" s="4"/>
     </row>
-    <row r="823" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="2" t="s">
         <v>1266</v>
       </c>
@@ -75447,7 +75446,7 @@
       <c r="AH823" s="4"/>
       <c r="AI823" s="4"/>
     </row>
-    <row r="824" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A824" s="2" t="s">
         <v>1268</v>
       </c>
@@ -75508,7 +75507,7 @@
       <c r="AH824" s="4"/>
       <c r="AI824" s="4"/>
     </row>
-    <row r="825" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A825" s="2" t="s">
         <v>1269</v>
       </c>
@@ -75569,7 +75568,7 @@
       <c r="AH825" s="4"/>
       <c r="AI825" s="4"/>
     </row>
-    <row r="826" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826" s="2" t="s">
         <v>1272</v>
       </c>
@@ -75630,7 +75629,7 @@
       <c r="AH826" s="4"/>
       <c r="AI826" s="4"/>
     </row>
-    <row r="827" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="2" t="s">
         <v>1273</v>
       </c>
@@ -75691,7 +75690,7 @@
       <c r="AH827" s="4"/>
       <c r="AI827" s="4"/>
     </row>
-    <row r="828" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="2" t="s">
         <v>1276</v>
       </c>
@@ -75752,7 +75751,7 @@
       <c r="AH828" s="4"/>
       <c r="AI828" s="4"/>
     </row>
-    <row r="829" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="2" t="s">
         <v>1277</v>
       </c>
@@ -75813,7 +75812,7 @@
       <c r="AH829" s="4"/>
       <c r="AI829" s="4"/>
     </row>
-    <row r="830" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830" s="2" t="s">
         <v>1279</v>
       </c>
@@ -75874,7 +75873,7 @@
       <c r="AH830" s="4"/>
       <c r="AI830" s="4"/>
     </row>
-    <row r="831" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A831" s="2" t="s">
         <v>1280</v>
       </c>
@@ -75935,7 +75934,7 @@
       <c r="AH831" s="4"/>
       <c r="AI831" s="4"/>
     </row>
-    <row r="832" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A832" s="2" t="s">
         <v>1281</v>
       </c>
@@ -75996,7 +75995,7 @@
       <c r="AH832" s="4"/>
       <c r="AI832" s="4"/>
     </row>
-    <row r="833" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A833" s="2" t="s">
         <v>1282</v>
       </c>
@@ -76057,7 +76056,7 @@
       <c r="AH833" s="4"/>
       <c r="AI833" s="4"/>
     </row>
-    <row r="834" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A834" s="2" t="s">
         <v>1283</v>
       </c>
@@ -76118,7 +76117,7 @@
       <c r="AH834" s="4"/>
       <c r="AI834" s="4"/>
     </row>
-    <row r="835" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835" s="2" t="s">
         <v>1286</v>
       </c>
@@ -76179,7 +76178,7 @@
       <c r="AH835" s="4"/>
       <c r="AI835" s="4"/>
     </row>
-    <row r="836" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A836" s="2" t="s">
         <v>1289</v>
       </c>
@@ -76240,7 +76239,7 @@
       <c r="AH836" s="4"/>
       <c r="AI836" s="4"/>
     </row>
-    <row r="837" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A837" s="2" t="s">
         <v>1290</v>
       </c>
@@ -76301,7 +76300,7 @@
       <c r="AH837" s="4"/>
       <c r="AI837" s="4"/>
     </row>
-    <row r="838" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="2" t="s">
         <v>1291</v>
       </c>
@@ -76362,7 +76361,7 @@
       <c r="AH838" s="4"/>
       <c r="AI838" s="4"/>
     </row>
-    <row r="839" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="2" t="s">
         <v>1292</v>
       </c>
@@ -76423,7 +76422,7 @@
       <c r="AH839" s="4"/>
       <c r="AI839" s="4"/>
     </row>
-    <row r="840" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="2" t="s">
         <v>1293</v>
       </c>
@@ -76484,7 +76483,7 @@
       <c r="AH840" s="4"/>
       <c r="AI840" s="4"/>
     </row>
-    <row r="841" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="2" t="s">
         <v>1297</v>
       </c>
@@ -76545,7 +76544,7 @@
       <c r="AH841" s="4"/>
       <c r="AI841" s="4"/>
     </row>
-    <row r="842" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="2" t="s">
         <v>1298</v>
       </c>
@@ -76606,7 +76605,7 @@
       <c r="AH842" s="4"/>
       <c r="AI842" s="4"/>
     </row>
-    <row r="843" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A843" s="2" t="s">
         <v>1299</v>
       </c>
@@ -76667,7 +76666,7 @@
       <c r="AH843" s="4"/>
       <c r="AI843" s="4"/>
     </row>
-    <row r="844" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A844" s="2" t="s">
         <v>1300</v>
       </c>
@@ -76728,7 +76727,7 @@
       <c r="AH844" s="4"/>
       <c r="AI844" s="4"/>
     </row>
-    <row r="845" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A845" s="2" t="s">
         <v>1301</v>
       </c>
@@ -76789,7 +76788,7 @@
       <c r="AH845" s="4"/>
       <c r="AI845" s="4"/>
     </row>
-    <row r="846" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="2" t="s">
         <v>1302</v>
       </c>
@@ -76850,7 +76849,7 @@
       <c r="AH846" s="4"/>
       <c r="AI846" s="4"/>
     </row>
-    <row r="847" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A847" s="2" t="s">
         <v>1303</v>
       </c>
@@ -76911,7 +76910,7 @@
       <c r="AH847" s="4"/>
       <c r="AI847" s="4"/>
     </row>
-    <row r="848" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A848" s="2" t="s">
         <v>1306</v>
       </c>
@@ -76972,7 +76971,7 @@
       <c r="AH848" s="4"/>
       <c r="AI848" s="4"/>
     </row>
-    <row r="849" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A849" s="2" t="s">
         <v>1308</v>
       </c>
@@ -77033,7 +77032,7 @@
       <c r="AH849" s="4"/>
       <c r="AI849" s="4"/>
     </row>
-    <row r="850" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850" s="2" t="s">
         <v>1309</v>
       </c>
@@ -77094,7 +77093,7 @@
       <c r="AH850" s="4"/>
       <c r="AI850" s="4"/>
     </row>
-    <row r="851" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A851" s="2" t="s">
         <v>1311</v>
       </c>
@@ -77155,7 +77154,7 @@
       <c r="AH851" s="4"/>
       <c r="AI851" s="4"/>
     </row>
-    <row r="852" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A852" s="2" t="s">
         <v>1312</v>
       </c>
@@ -77216,7 +77215,7 @@
       <c r="AH852" s="4"/>
       <c r="AI852" s="4"/>
     </row>
-    <row r="853" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A853" s="2" t="s">
         <v>1314</v>
       </c>
@@ -77277,7 +77276,7 @@
       <c r="AH853" s="4"/>
       <c r="AI853" s="4"/>
     </row>
-    <row r="854" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A854" s="2" t="s">
         <v>1315</v>
       </c>
@@ -77338,7 +77337,7 @@
       <c r="AH854" s="4"/>
       <c r="AI854" s="4"/>
     </row>
-    <row r="855" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A855" s="2" t="s">
         <v>1317</v>
       </c>
@@ -77399,7 +77398,7 @@
       <c r="AH855" s="4"/>
       <c r="AI855" s="4"/>
     </row>
-    <row r="856" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A856" s="2" t="s">
         <v>1319</v>
       </c>
@@ -77460,7 +77459,7 @@
       <c r="AH856" s="4"/>
       <c r="AI856" s="4"/>
     </row>
-    <row r="857" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A857" s="2" t="s">
         <v>1322</v>
       </c>
@@ -78070,7 +78069,7 @@
       <c r="AH866" s="4"/>
       <c r="AI866" s="4"/>
     </row>
-    <row r="867" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867" s="2" t="s">
         <v>1334</v>
       </c>
@@ -78131,7 +78130,7 @@
       <c r="AH867" s="4"/>
       <c r="AI867" s="4"/>
     </row>
-    <row r="868" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868" s="2" t="s">
         <v>1337</v>
       </c>
@@ -78192,7 +78191,7 @@
       <c r="AH868" s="4"/>
       <c r="AI868" s="4"/>
     </row>
-    <row r="869" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869" s="2" t="s">
         <v>1338</v>
       </c>
@@ -78253,7 +78252,7 @@
       <c r="AH869" s="4"/>
       <c r="AI869" s="4"/>
     </row>
-    <row r="870" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870" s="2" t="s">
         <v>1341</v>
       </c>
@@ -78314,7 +78313,7 @@
       <c r="AH870" s="4"/>
       <c r="AI870" s="4"/>
     </row>
-    <row r="871" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="2" t="s">
         <v>1344</v>
       </c>
@@ -78375,7 +78374,7 @@
       <c r="AH871" s="4"/>
       <c r="AI871" s="4"/>
     </row>
-    <row r="872" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872" s="2" t="s">
         <v>1345</v>
       </c>
@@ -78436,7 +78435,7 @@
       <c r="AH872" s="4"/>
       <c r="AI872" s="4"/>
     </row>
-    <row r="873" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873" s="2" t="s">
         <v>1347</v>
       </c>
@@ -78497,7 +78496,7 @@
       <c r="AH873" s="4"/>
       <c r="AI873" s="4"/>
     </row>
-    <row r="874" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A874" s="2" t="s">
         <v>1349</v>
       </c>
@@ -78558,7 +78557,7 @@
       <c r="AH874" s="4"/>
       <c r="AI874" s="4"/>
     </row>
-    <row r="875" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A875" s="2" t="s">
         <v>1352</v>
       </c>
@@ -78619,7 +78618,7 @@
       <c r="AH875" s="4"/>
       <c r="AI875" s="4"/>
     </row>
-    <row r="876" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876" s="2" t="s">
         <v>1353</v>
       </c>
@@ -78680,7 +78679,7 @@
       <c r="AH876" s="4"/>
       <c r="AI876" s="4"/>
     </row>
-    <row r="877" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="2" t="s">
         <v>1355</v>
       </c>
@@ -78741,7 +78740,7 @@
       <c r="AH877" s="4"/>
       <c r="AI877" s="4"/>
     </row>
-    <row r="878" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878" s="2" t="s">
         <v>1357</v>
       </c>
@@ -78802,7 +78801,7 @@
       <c r="AH878" s="4"/>
       <c r="AI878" s="4"/>
     </row>
-    <row r="879" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879" s="2" t="s">
         <v>1359</v>
       </c>
@@ -78863,7 +78862,7 @@
       <c r="AH879" s="4"/>
       <c r="AI879" s="4"/>
     </row>
-    <row r="880" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880" s="2" t="s">
         <v>1362</v>
       </c>
@@ -78924,7 +78923,7 @@
       <c r="AH880" s="4"/>
       <c r="AI880" s="4"/>
     </row>
-    <row r="881" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881" s="2" t="s">
         <v>1364</v>
       </c>
@@ -78985,7 +78984,7 @@
       <c r="AH881" s="4"/>
       <c r="AI881" s="4"/>
     </row>
-    <row r="882" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882" s="2" t="s">
         <v>1365</v>
       </c>
@@ -79046,7 +79045,7 @@
       <c r="AH882" s="4"/>
       <c r="AI882" s="4"/>
     </row>
-    <row r="883" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="2" t="s">
         <v>1366</v>
       </c>
@@ -79107,7 +79106,7 @@
       <c r="AH883" s="4"/>
       <c r="AI883" s="4"/>
     </row>
-    <row r="884" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A884" s="2" t="s">
         <v>1367</v>
       </c>
@@ -79168,7 +79167,7 @@
       <c r="AH884" s="4"/>
       <c r="AI884" s="4"/>
     </row>
-    <row r="885" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A885" s="2" t="s">
         <v>1370</v>
       </c>
@@ -79229,7 +79228,7 @@
       <c r="AH885" s="4"/>
       <c r="AI885" s="4"/>
     </row>
-    <row r="886" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="2" t="s">
         <v>1371</v>
       </c>
@@ -79290,7 +79289,7 @@
       <c r="AH886" s="4"/>
       <c r="AI886" s="4"/>
     </row>
-    <row r="887" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="2" t="s">
         <v>1372</v>
       </c>
@@ -79351,7 +79350,7 @@
       <c r="AH887" s="4"/>
       <c r="AI887" s="4"/>
     </row>
-    <row r="888" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="2" t="s">
         <v>1373</v>
       </c>
@@ -79412,7 +79411,7 @@
       <c r="AH888" s="4"/>
       <c r="AI888" s="4"/>
     </row>
-    <row r="889" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="2" t="s">
         <v>1375</v>
       </c>
@@ -79473,7 +79472,7 @@
       <c r="AH889" s="4"/>
       <c r="AI889" s="4"/>
     </row>
-    <row r="890" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A890" s="2" t="s">
         <v>1378</v>
       </c>
@@ -79534,7 +79533,7 @@
       <c r="AH890" s="4"/>
       <c r="AI890" s="4"/>
     </row>
-    <row r="891" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A891" s="2" t="s">
         <v>1380</v>
       </c>
@@ -79595,7 +79594,7 @@
       <c r="AH891" s="4"/>
       <c r="AI891" s="4"/>
     </row>
-    <row r="892" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892" s="2" t="s">
         <v>1383</v>
       </c>
@@ -79656,7 +79655,7 @@
       <c r="AH892" s="4"/>
       <c r="AI892" s="4"/>
     </row>
-    <row r="893" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893" s="2" t="s">
         <v>1384</v>
       </c>
@@ -79717,7 +79716,7 @@
       <c r="AH893" s="4"/>
       <c r="AI893" s="4"/>
     </row>
-    <row r="894" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894" s="2" t="s">
         <v>1385</v>
       </c>
@@ -79778,7 +79777,7 @@
       <c r="AH894" s="4"/>
       <c r="AI894" s="4"/>
     </row>
-    <row r="895" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895" s="2" t="s">
         <v>1387</v>
       </c>
@@ -79839,7 +79838,7 @@
       <c r="AH895" s="4"/>
       <c r="AI895" s="4"/>
     </row>
-    <row r="896" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896" s="2" t="s">
         <v>1390</v>
       </c>
@@ -79900,7 +79899,7 @@
       <c r="AH896" s="4"/>
       <c r="AI896" s="4"/>
     </row>
-    <row r="897" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897" s="2" t="s">
         <v>1391</v>
       </c>
@@ -79961,7 +79960,7 @@
       <c r="AH897" s="4"/>
       <c r="AI897" s="4"/>
     </row>
-    <row r="898" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898" s="2" t="s">
         <v>1394</v>
       </c>
@@ -80022,7 +80021,7 @@
       <c r="AH898" s="4"/>
       <c r="AI898" s="4"/>
     </row>
-    <row r="899" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="2" t="s">
         <v>1396</v>
       </c>
@@ -80083,7 +80082,7 @@
       <c r="AH899" s="4"/>
       <c r="AI899" s="4"/>
     </row>
-    <row r="900" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="2" t="s">
         <v>1399</v>
       </c>
@@ -80144,7 +80143,7 @@
       <c r="AH900" s="4"/>
       <c r="AI900" s="4"/>
     </row>
-    <row r="901" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="2" t="s">
         <v>1401</v>
       </c>
@@ -80205,7 +80204,7 @@
       <c r="AH901" s="4"/>
       <c r="AI901" s="4"/>
     </row>
-    <row r="902" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="2" t="s">
         <v>1403</v>
       </c>
@@ -80266,7 +80265,7 @@
       <c r="AH902" s="4"/>
       <c r="AI902" s="4"/>
     </row>
-    <row r="903" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="2" t="s">
         <v>1404</v>
       </c>
@@ -80327,7 +80326,7 @@
       <c r="AH903" s="4"/>
       <c r="AI903" s="4"/>
     </row>
-    <row r="904" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="2" t="s">
         <v>1407</v>
       </c>
@@ -80388,7 +80387,7 @@
       <c r="AH904" s="4"/>
       <c r="AI904" s="4"/>
     </row>
-    <row r="905" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="2" t="s">
         <v>1408</v>
       </c>
@@ -80449,7 +80448,7 @@
       <c r="AH905" s="4"/>
       <c r="AI905" s="4"/>
     </row>
-    <row r="906" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="2" t="s">
         <v>1412</v>
       </c>
@@ -80510,7 +80509,7 @@
       <c r="AH906" s="4"/>
       <c r="AI906" s="4"/>
     </row>
-    <row r="907" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="2" t="s">
         <v>1414</v>
       </c>
@@ -80571,7 +80570,7 @@
       <c r="AH907" s="4"/>
       <c r="AI907" s="4"/>
     </row>
-    <row r="908" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="2" t="s">
         <v>1418</v>
       </c>
@@ -80632,7 +80631,7 @@
       <c r="AH908" s="4"/>
       <c r="AI908" s="4"/>
     </row>
-    <row r="909" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="2" t="s">
         <v>1420</v>
       </c>
@@ -80693,7 +80692,7 @@
       <c r="AH909" s="4"/>
       <c r="AI909" s="4"/>
     </row>
-    <row r="910" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="2" t="s">
         <v>1422</v>
       </c>
@@ -80754,7 +80753,7 @@
       <c r="AH910" s="4"/>
       <c r="AI910" s="4"/>
     </row>
-    <row r="911" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="2" t="s">
         <v>1426</v>
       </c>
@@ -80815,7 +80814,7 @@
       <c r="AH911" s="4"/>
       <c r="AI911" s="4"/>
     </row>
-    <row r="912" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="2" t="s">
         <v>1428</v>
       </c>
@@ -80876,7 +80875,7 @@
       <c r="AH912" s="4"/>
       <c r="AI912" s="4"/>
     </row>
-    <row r="913" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
         <v>1430</v>
       </c>
@@ -80937,7 +80936,7 @@
       <c r="AH913" s="4"/>
       <c r="AI913" s="4"/>
     </row>
-    <row r="914" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="2" t="s">
         <v>1432</v>
       </c>
@@ -80998,7 +80997,7 @@
       <c r="AH914" s="4"/>
       <c r="AI914" s="4"/>
     </row>
-    <row r="915" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="2" t="s">
         <v>1435</v>
       </c>
@@ -81059,7 +81058,7 @@
       <c r="AH915" s="4"/>
       <c r="AI915" s="4"/>
     </row>
-    <row r="916" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="2" t="s">
         <v>1436</v>
       </c>
@@ -81120,7 +81119,7 @@
       <c r="AH916" s="4"/>
       <c r="AI916" s="4"/>
     </row>
-    <row r="917" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="2" t="s">
         <v>1437</v>
       </c>
@@ -81181,7 +81180,7 @@
       <c r="AH917" s="4"/>
       <c r="AI917" s="4"/>
     </row>
-    <row r="918" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="2" t="s">
         <v>1438</v>
       </c>
@@ -81242,7 +81241,7 @@
       <c r="AH918" s="4"/>
       <c r="AI918" s="4"/>
     </row>
-    <row r="919" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="2" t="s">
         <v>1441</v>
       </c>
@@ -81303,7 +81302,7 @@
       <c r="AH919" s="4"/>
       <c r="AI919" s="4"/>
     </row>
-    <row r="920" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="2" t="s">
         <v>1442</v>
       </c>
@@ -81364,7 +81363,7 @@
       <c r="AH920" s="4"/>
       <c r="AI920" s="4"/>
     </row>
-    <row r="921" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="2" t="s">
         <v>1445</v>
       </c>
@@ -81425,7 +81424,7 @@
       <c r="AH921" s="4"/>
       <c r="AI921" s="4"/>
     </row>
-    <row r="922" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A922" s="2" t="s">
         <v>1446</v>
       </c>
@@ -81486,7 +81485,7 @@
       <c r="AH922" s="4"/>
       <c r="AI922" s="4"/>
     </row>
-    <row r="923" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A923" s="2" t="s">
         <v>1449</v>
       </c>
@@ -81547,7 +81546,7 @@
       <c r="AH923" s="4"/>
       <c r="AI923" s="4"/>
     </row>
-    <row r="924" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A924" s="2" t="s">
         <v>1450</v>
       </c>
@@ -81608,7 +81607,7 @@
       <c r="AH924" s="4"/>
       <c r="AI924" s="4"/>
     </row>
-    <row r="925" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="2" t="s">
         <v>1542</v>
       </c>
@@ -81667,7 +81666,7 @@
       <c r="AH925" s="4"/>
       <c r="AI925" s="4"/>
     </row>
-    <row r="926" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A926" s="2" t="s">
         <v>1543</v>
       </c>
@@ -81726,7 +81725,7 @@
       <c r="AH926" s="4"/>
       <c r="AI926" s="4"/>
     </row>
-    <row r="927" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A927" s="2" t="s">
         <v>1544</v>
       </c>
@@ -81785,7 +81784,7 @@
       <c r="AH927" s="4"/>
       <c r="AI927" s="4"/>
     </row>
-    <row r="928" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A928" s="2" t="s">
         <v>1545</v>
       </c>
@@ -81844,7 +81843,7 @@
       <c r="AH928" s="4"/>
       <c r="AI928" s="4"/>
     </row>
-    <row r="929" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A929" s="2" t="s">
         <v>1546</v>
       </c>
@@ -81903,7 +81902,7 @@
       <c r="AH929" s="4"/>
       <c r="AI929" s="4"/>
     </row>
-    <row r="930" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="2" t="s">
         <v>1547</v>
       </c>
@@ -81962,7 +81961,7 @@
       <c r="AH930" s="4"/>
       <c r="AI930" s="4"/>
     </row>
-    <row r="931" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A931" s="2" t="s">
         <v>1548</v>
       </c>
@@ -82021,7 +82020,7 @@
       <c r="AH931" s="4"/>
       <c r="AI931" s="4"/>
     </row>
-    <row r="932" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A932" s="2" t="s">
         <v>1549</v>
       </c>
@@ -82080,7 +82079,7 @@
       <c r="AH932" s="4"/>
       <c r="AI932" s="4"/>
     </row>
-    <row r="933" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A933" s="2" t="s">
         <v>1550</v>
       </c>
@@ -82139,7 +82138,7 @@
       <c r="AH933" s="4"/>
       <c r="AI933" s="4"/>
     </row>
-    <row r="934" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A934" s="2" t="s">
         <v>1551</v>
       </c>
@@ -82198,7 +82197,7 @@
       <c r="AH934" s="4"/>
       <c r="AI934" s="4"/>
     </row>
-    <row r="935" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A935" s="2" t="s">
         <v>1552</v>
       </c>
@@ -82257,7 +82256,7 @@
       <c r="AH935" s="4"/>
       <c r="AI935" s="4"/>
     </row>
-    <row r="936" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A936" s="2" t="s">
         <v>1553</v>
       </c>
@@ -82316,7 +82315,7 @@
       <c r="AH936" s="4"/>
       <c r="AI936" s="4"/>
     </row>
-    <row r="937" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A937" s="2" t="s">
         <v>1554</v>
       </c>
@@ -82375,7 +82374,7 @@
       <c r="AH937" s="4"/>
       <c r="AI937" s="4"/>
     </row>
-    <row r="938" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A938" s="2" t="s">
         <v>1555</v>
       </c>
@@ -82434,7 +82433,7 @@
       <c r="AH938" s="4"/>
       <c r="AI938" s="4"/>
     </row>
-    <row r="939" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A939" s="2" t="s">
         <v>1556</v>
       </c>
@@ -82493,7 +82492,7 @@
       <c r="AH939" s="4"/>
       <c r="AI939" s="4"/>
     </row>
-    <row r="940" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A940" s="2" t="s">
         <v>1557</v>
       </c>
@@ -82552,7 +82551,7 @@
       <c r="AH940" s="4"/>
       <c r="AI940" s="4"/>
     </row>
-    <row r="941" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A941" s="2" t="s">
         <v>1558</v>
       </c>
@@ -82611,7 +82610,7 @@
       <c r="AH941" s="4"/>
       <c r="AI941" s="4"/>
     </row>
-    <row r="942" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A942" s="2" t="s">
         <v>1559</v>
       </c>
@@ -82670,7 +82669,7 @@
       <c r="AH942" s="4"/>
       <c r="AI942" s="4"/>
     </row>
-    <row r="943" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A943" s="2" t="s">
         <v>1560</v>
       </c>
@@ -82729,7 +82728,7 @@
       <c r="AH943" s="4"/>
       <c r="AI943" s="4"/>
     </row>
-    <row r="944" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A944" s="2" t="s">
         <v>1561</v>
       </c>
@@ -82788,7 +82787,7 @@
       <c r="AH944" s="4"/>
       <c r="AI944" s="4"/>
     </row>
-    <row r="945" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A945" s="2" t="s">
         <v>1562</v>
       </c>
@@ -82847,7 +82846,7 @@
       <c r="AH945" s="4"/>
       <c r="AI945" s="4"/>
     </row>
-    <row r="946" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A946" s="2" t="s">
         <v>1563</v>
       </c>
@@ -82906,7 +82905,7 @@
       <c r="AH946" s="4"/>
       <c r="AI946" s="4"/>
     </row>
-    <row r="947" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A947" s="2" t="s">
         <v>1564</v>
       </c>
@@ -82965,7 +82964,7 @@
       <c r="AH947" s="4"/>
       <c r="AI947" s="4"/>
     </row>
-    <row r="948" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A948" s="2" t="s">
         <v>1565</v>
       </c>
@@ -83024,7 +83023,7 @@
       <c r="AH948" s="4"/>
       <c r="AI948" s="4"/>
     </row>
-    <row r="949" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A949" s="2" t="s">
         <v>1566</v>
       </c>
@@ -83083,7 +83082,7 @@
       <c r="AH949" s="4"/>
       <c r="AI949" s="4"/>
     </row>
-    <row r="950" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A950" s="2" t="s">
         <v>1567</v>
       </c>
@@ -83142,7 +83141,7 @@
       <c r="AH950" s="4"/>
       <c r="AI950" s="4"/>
     </row>
-    <row r="951" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="2" t="s">
         <v>1568</v>
       </c>
@@ -83201,7 +83200,7 @@
       <c r="AH951" s="4"/>
       <c r="AI951" s="4"/>
     </row>
-    <row r="952" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="2" t="s">
         <v>1569</v>
       </c>
@@ -83260,7 +83259,7 @@
       <c r="AH952" s="4"/>
       <c r="AI952" s="4"/>
     </row>
-    <row r="953" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A953" s="2" t="s">
         <v>1570</v>
       </c>
@@ -83319,7 +83318,7 @@
       <c r="AH953" s="4"/>
       <c r="AI953" s="4"/>
     </row>
-    <row r="954" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="2" t="s">
         <v>1571</v>
       </c>
@@ -83378,7 +83377,7 @@
       <c r="AH954" s="4"/>
       <c r="AI954" s="4"/>
     </row>
-    <row r="955" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A955" s="2" t="s">
         <v>1572</v>
       </c>
@@ -83437,7 +83436,7 @@
       <c r="AH955" s="4"/>
       <c r="AI955" s="4"/>
     </row>
-    <row r="956" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A956" s="2" t="s">
         <v>1573</v>
       </c>
@@ -83496,7 +83495,7 @@
       <c r="AH956" s="4"/>
       <c r="AI956" s="4"/>
     </row>
-    <row r="957" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A957" s="2" t="s">
         <v>1574</v>
       </c>
@@ -83555,7 +83554,7 @@
       <c r="AH957" s="4"/>
       <c r="AI957" s="4"/>
     </row>
-    <row r="958" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A958" s="2" t="s">
         <v>1575</v>
       </c>
@@ -83614,7 +83613,7 @@
       <c r="AH958" s="4"/>
       <c r="AI958" s="4"/>
     </row>
-    <row r="959" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A959" s="2" t="s">
         <v>1576</v>
       </c>
@@ -83673,7 +83672,7 @@
       <c r="AH959" s="4"/>
       <c r="AI959" s="4"/>
     </row>
-    <row r="960" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A960" s="2" t="s">
         <v>1577</v>
       </c>
@@ -83732,7 +83731,7 @@
       <c r="AH960" s="4"/>
       <c r="AI960" s="4"/>
     </row>
-    <row r="961" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A961" s="2" t="s">
         <v>1578</v>
       </c>
@@ -83791,7 +83790,7 @@
       <c r="AH961" s="4"/>
       <c r="AI961" s="4"/>
     </row>
-    <row r="962" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A962" s="2" t="s">
         <v>1579</v>
       </c>
@@ -83850,7 +83849,7 @@
       <c r="AH962" s="4"/>
       <c r="AI962" s="4"/>
     </row>
-    <row r="963" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A963" s="2" t="s">
         <v>1580</v>
       </c>
@@ -83909,7 +83908,7 @@
       <c r="AH963" s="4"/>
       <c r="AI963" s="4"/>
     </row>
-    <row r="964" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A964" s="2" t="s">
         <v>1581</v>
       </c>
@@ -83968,7 +83967,7 @@
       <c r="AH964" s="4"/>
       <c r="AI964" s="4"/>
     </row>
-    <row r="965" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A965" s="2" t="s">
         <v>1582</v>
       </c>
@@ -84027,7 +84026,7 @@
       <c r="AH965" s="4"/>
       <c r="AI965" s="4"/>
     </row>
-    <row r="966" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A966" s="2" t="s">
         <v>1583</v>
       </c>
@@ -84086,7 +84085,7 @@
       <c r="AH966" s="4"/>
       <c r="AI966" s="4"/>
     </row>
-    <row r="967" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A967" s="2" t="s">
         <v>1584</v>
       </c>
@@ -84145,7 +84144,7 @@
       <c r="AH967" s="4"/>
       <c r="AI967" s="4"/>
     </row>
-    <row r="968" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A968" s="2" t="s">
         <v>1585</v>
       </c>
@@ -84204,7 +84203,7 @@
       <c r="AH968" s="4"/>
       <c r="AI968" s="4"/>
     </row>
-    <row r="969" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A969" s="2" t="s">
         <v>1586</v>
       </c>
@@ -84263,7 +84262,7 @@
       <c r="AH969" s="4"/>
       <c r="AI969" s="4"/>
     </row>
-    <row r="970" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A970" s="2" t="s">
         <v>1587</v>
       </c>
@@ -84322,7 +84321,7 @@
       <c r="AH970" s="4"/>
       <c r="AI970" s="4"/>
     </row>
-    <row r="971" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A971" s="2" t="s">
         <v>1588</v>
       </c>
@@ -84381,7 +84380,7 @@
       <c r="AH971" s="4"/>
       <c r="AI971" s="4"/>
     </row>
-    <row r="972" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A972" s="2" t="s">
         <v>1589</v>
       </c>
@@ -84440,7 +84439,7 @@
       <c r="AH972" s="4"/>
       <c r="AI972" s="4"/>
     </row>
-    <row r="973" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A973" s="2" t="s">
         <v>1590</v>
       </c>
@@ -84497,7 +84496,7 @@
       <c r="AH973" s="4"/>
       <c r="AI973" s="4"/>
     </row>
-    <row r="974" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A974" s="2" t="s">
         <v>1591</v>
       </c>
@@ -84554,7 +84553,7 @@
       <c r="AH974" s="4"/>
       <c r="AI974" s="4"/>
     </row>
-    <row r="975" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A975" s="2" t="s">
         <v>1592</v>
       </c>
@@ -84611,7 +84610,7 @@
       <c r="AH975" s="4"/>
       <c r="AI975" s="4"/>
     </row>
-    <row r="976" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A976" s="2" t="s">
         <v>1593</v>
       </c>
@@ -84668,7 +84667,7 @@
       <c r="AH976" s="4"/>
       <c r="AI976" s="4"/>
     </row>
-    <row r="977" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A977" s="2" t="s">
         <v>1595</v>
       </c>
@@ -84725,7 +84724,7 @@
       <c r="AH977" s="4"/>
       <c r="AI977" s="4"/>
     </row>
-    <row r="978" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A978" s="2" t="s">
         <v>1596</v>
       </c>
@@ -84782,7 +84781,7 @@
       <c r="AH978" s="4"/>
       <c r="AI978" s="4"/>
     </row>
-    <row r="979" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A979" s="2" t="s">
         <v>1597</v>
       </c>
@@ -84839,7 +84838,7 @@
       <c r="AH979" s="4"/>
       <c r="AI979" s="4"/>
     </row>
-    <row r="980" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A980" s="2" t="s">
         <v>1598</v>
       </c>
@@ -84896,7 +84895,7 @@
       <c r="AH980" s="4"/>
       <c r="AI980" s="4"/>
     </row>
-    <row r="981" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A981" s="2" t="s">
         <v>1599</v>
       </c>
@@ -84953,7 +84952,7 @@
       <c r="AH981" s="4"/>
       <c r="AI981" s="4"/>
     </row>
-    <row r="982" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A982" s="2" t="s">
         <v>1600</v>
       </c>
@@ -85010,7 +85009,7 @@
       <c r="AH982" s="4"/>
       <c r="AI982" s="4"/>
     </row>
-    <row r="983" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A983" s="2" t="s">
         <v>1601</v>
       </c>
@@ -85067,7 +85066,7 @@
       <c r="AH983" s="4"/>
       <c r="AI983" s="4"/>
     </row>
-    <row r="984" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A984" s="2" t="s">
         <v>1602</v>
       </c>
@@ -85124,7 +85123,7 @@
       <c r="AH984" s="4"/>
       <c r="AI984" s="4"/>
     </row>
-    <row r="985" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A985" s="2" t="s">
         <v>1604</v>
       </c>
@@ -85181,7 +85180,7 @@
       <c r="AH985" s="4"/>
       <c r="AI985" s="4"/>
     </row>
-    <row r="986" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A986" s="2" t="s">
         <v>1605</v>
       </c>
@@ -85238,7 +85237,7 @@
       <c r="AH986" s="4"/>
       <c r="AI986" s="4"/>
     </row>
-    <row r="987" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A987" s="2" t="s">
         <v>1606</v>
       </c>
@@ -85295,7 +85294,7 @@
       <c r="AH987" s="4"/>
       <c r="AI987" s="4"/>
     </row>
-    <row r="988" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A988" s="2" t="s">
         <v>1607</v>
       </c>
@@ -85352,7 +85351,7 @@
       <c r="AH988" s="4"/>
       <c r="AI988" s="4"/>
     </row>
-    <row r="989" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A989" s="2" t="s">
         <v>1608</v>
       </c>
@@ -85409,7 +85408,7 @@
       <c r="AH989" s="4"/>
       <c r="AI989" s="4"/>
     </row>
-    <row r="990" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A990" s="2" t="s">
         <v>1609</v>
       </c>
@@ -85466,7 +85465,7 @@
       <c r="AH990" s="4"/>
       <c r="AI990" s="4"/>
     </row>
-    <row r="991" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A991" s="2" t="s">
         <v>1610</v>
       </c>
@@ -85523,7 +85522,7 @@
       <c r="AH991" s="4"/>
       <c r="AI991" s="4"/>
     </row>
-    <row r="992" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A992" s="2" t="s">
         <v>1612</v>
       </c>
@@ -85580,7 +85579,7 @@
       <c r="AH992" s="4"/>
       <c r="AI992" s="4"/>
     </row>
-    <row r="993" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="2" t="s">
         <v>1613</v>
       </c>
@@ -85637,7 +85636,7 @@
       <c r="AH993" s="4"/>
       <c r="AI993" s="4"/>
     </row>
-    <row r="994" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A994" s="2" t="s">
         <v>1614</v>
       </c>
@@ -85694,7 +85693,7 @@
       <c r="AH994" s="4"/>
       <c r="AI994" s="4"/>
     </row>
-    <row r="995" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A995" s="2" t="s">
         <v>1616</v>
       </c>
@@ -85751,7 +85750,7 @@
       <c r="AH995" s="4"/>
       <c r="AI995" s="4"/>
     </row>
-    <row r="996" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A996" s="2" t="s">
         <v>1618</v>
       </c>
@@ -85808,7 +85807,7 @@
       <c r="AH996" s="4"/>
       <c r="AI996" s="4"/>
     </row>
-    <row r="997" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A997" s="2" t="s">
         <v>1620</v>
       </c>
@@ -85867,7 +85866,7 @@
       <c r="AH997" s="4"/>
       <c r="AI997" s="4"/>
     </row>
-    <row r="998" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A998" s="2" t="s">
         <v>1621</v>
       </c>
@@ -85926,7 +85925,7 @@
       <c r="AH998" s="4"/>
       <c r="AI998" s="4"/>
     </row>
-    <row r="999" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A999" s="2" t="s">
         <v>1622</v>
       </c>
@@ -85983,7 +85982,7 @@
       <c r="AH999" s="4"/>
       <c r="AI999" s="4"/>
     </row>
-    <row r="1000" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1000" s="2" t="s">
         <v>1623</v>
       </c>
@@ -86040,7 +86039,7 @@
       <c r="AH1000" s="4"/>
       <c r="AI1000" s="4"/>
     </row>
-    <row r="1001" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1001" s="2" t="s">
         <v>1626</v>
       </c>
@@ -86097,7 +86096,7 @@
       <c r="AH1001" s="4"/>
       <c r="AI1001" s="4"/>
     </row>
-    <row r="1002" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1002" s="2" t="s">
         <v>1630</v>
       </c>
@@ -86154,7 +86153,7 @@
       <c r="AH1002" s="4"/>
       <c r="AI1002" s="4"/>
     </row>
-    <row r="1003" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1003" s="2" t="s">
         <v>1631</v>
       </c>
@@ -86211,7 +86210,7 @@
       <c r="AH1003" s="4"/>
       <c r="AI1003" s="4"/>
     </row>
-    <row r="1004" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="2" t="s">
         <v>1632</v>
       </c>
@@ -86268,7 +86267,7 @@
       <c r="AH1004" s="4"/>
       <c r="AI1004" s="4"/>
     </row>
-    <row r="1005" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="2" t="s">
         <v>1635</v>
       </c>
@@ -86325,7 +86324,7 @@
       <c r="AH1005" s="4"/>
       <c r="AI1005" s="4"/>
     </row>
-    <row r="1006" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="2" t="s">
         <v>1636</v>
       </c>
@@ -86382,7 +86381,7 @@
       <c r="AH1006" s="4"/>
       <c r="AI1006" s="4"/>
     </row>
-    <row r="1007" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1007" s="2" t="s">
         <v>1637</v>
       </c>
@@ -86439,7 +86438,7 @@
       <c r="AH1007" s="4"/>
       <c r="AI1007" s="4"/>
     </row>
-    <row r="1008" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1008" s="2" t="s">
         <v>1640</v>
       </c>
@@ -86496,7 +86495,7 @@
       <c r="AH1008" s="4"/>
       <c r="AI1008" s="4"/>
     </row>
-    <row r="1009" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1009" s="2" t="s">
         <v>1641</v>
       </c>
@@ -86553,7 +86552,7 @@
       <c r="AH1009" s="4"/>
       <c r="AI1009" s="4"/>
     </row>
-    <row r="1010" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1010" s="2" t="s">
         <v>1644</v>
       </c>
@@ -86610,7 +86609,7 @@
       <c r="AH1010" s="4"/>
       <c r="AI1010" s="4"/>
     </row>
-    <row r="1011" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1011" s="2" t="s">
         <v>1645</v>
       </c>
@@ -86667,7 +86666,7 @@
       <c r="AH1011" s="4"/>
       <c r="AI1011" s="4"/>
     </row>
-    <row r="1012" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1012" s="2" t="s">
         <v>1648</v>
       </c>
@@ -86724,7 +86723,7 @@
       <c r="AH1012" s="4"/>
       <c r="AI1012" s="4"/>
     </row>
-    <row r="1013" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1013" s="2" t="s">
         <v>1652</v>
       </c>
@@ -86781,7 +86780,7 @@
       <c r="AH1013" s="4"/>
       <c r="AI1013" s="4"/>
     </row>
-    <row r="1014" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1014" s="2" t="s">
         <v>1653</v>
       </c>
@@ -86838,7 +86837,7 @@
       <c r="AH1014" s="4"/>
       <c r="AI1014" s="4"/>
     </row>
-    <row r="1015" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1015" s="2" t="s">
         <v>1655</v>
       </c>
@@ -86897,7 +86896,7 @@
       <c r="AH1015" s="4"/>
       <c r="AI1015" s="4"/>
     </row>
-    <row r="1016" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1016" s="2" t="s">
         <v>1656</v>
       </c>
@@ -86956,7 +86955,7 @@
       <c r="AH1016" s="4"/>
       <c r="AI1016" s="4"/>
     </row>
-    <row r="1017" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1017" s="2" t="s">
         <v>1657</v>
       </c>
@@ -87013,7 +87012,7 @@
       <c r="AH1017" s="4"/>
       <c r="AI1017" s="4"/>
     </row>
-    <row r="1018" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1018" s="2" t="s">
         <v>1660</v>
       </c>
@@ -87070,7 +87069,7 @@
       <c r="AH1018" s="4"/>
       <c r="AI1018" s="4"/>
     </row>
-    <row r="1019" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1019" s="2" t="s">
         <v>1661</v>
       </c>
@@ -87127,7 +87126,7 @@
       <c r="AH1019" s="4"/>
       <c r="AI1019" s="4"/>
     </row>
-    <row r="1020" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1020" s="2" t="s">
         <v>1662</v>
       </c>
@@ -87184,7 +87183,7 @@
       <c r="AH1020" s="4"/>
       <c r="AI1020" s="4"/>
     </row>
-    <row r="1021" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1021" s="2" t="s">
         <v>1663</v>
       </c>
@@ -87241,7 +87240,7 @@
       <c r="AH1021" s="4"/>
       <c r="AI1021" s="4"/>
     </row>
-    <row r="1022" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1022" s="2" t="s">
         <v>1664</v>
       </c>
@@ -87298,7 +87297,7 @@
       <c r="AH1022" s="4"/>
       <c r="AI1022" s="4"/>
     </row>
-    <row r="1023" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1023" s="2" t="s">
         <v>1665</v>
       </c>
@@ -87355,7 +87354,7 @@
       <c r="AH1023" s="4"/>
       <c r="AI1023" s="4"/>
     </row>
-    <row r="1024" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1024" s="2" t="s">
         <v>1667</v>
       </c>
@@ -87412,7 +87411,7 @@
       <c r="AH1024" s="4"/>
       <c r="AI1024" s="4"/>
     </row>
-    <row r="1025" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1025" s="2" t="s">
         <v>1669</v>
       </c>
@@ -87469,7 +87468,7 @@
       <c r="AH1025" s="4"/>
       <c r="AI1025" s="4"/>
     </row>
-    <row r="1026" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1026" s="2" t="s">
         <v>1672</v>
       </c>
@@ -87526,7 +87525,7 @@
       <c r="AH1026" s="4"/>
       <c r="AI1026" s="4"/>
     </row>
-    <row r="1027" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1027" s="2" t="s">
         <v>1673</v>
       </c>
@@ -87583,7 +87582,7 @@
       <c r="AH1027" s="4"/>
       <c r="AI1027" s="4"/>
     </row>
-    <row r="1028" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1028" s="2" t="s">
         <v>1675</v>
       </c>
@@ -87640,7 +87639,7 @@
       <c r="AH1028" s="4"/>
       <c r="AI1028" s="4"/>
     </row>
-    <row r="1029" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1029" s="2" t="s">
         <v>1677</v>
       </c>
@@ -87697,7 +87696,7 @@
       <c r="AH1029" s="4"/>
       <c r="AI1029" s="4"/>
     </row>
-    <row r="1030" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1030" s="9" t="s">
         <v>1686</v>
       </c>
@@ -87744,7 +87743,7 @@
       <c r="AH1030" s="4"/>
       <c r="AI1030" s="4"/>
     </row>
-    <row r="1031" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1031" s="9" t="s">
         <v>1687</v>
       </c>
@@ -87791,7 +87790,7 @@
       <c r="AH1031" s="4"/>
       <c r="AI1031" s="4"/>
     </row>
-    <row r="1032" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1032" s="9" t="s">
         <v>1688</v>
       </c>
@@ -87838,7 +87837,7 @@
       <c r="AH1032" s="4"/>
       <c r="AI1032" s="4"/>
     </row>
-    <row r="1033" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1033" s="9" t="s">
         <v>1689</v>
       </c>
@@ -87885,7 +87884,7 @@
       <c r="AH1033" s="4"/>
       <c r="AI1033" s="4"/>
     </row>
-    <row r="1034" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1034" s="9" t="s">
         <v>1690</v>
       </c>
@@ -87932,7 +87931,7 @@
       <c r="AH1034" s="4"/>
       <c r="AI1034" s="4"/>
     </row>
-    <row r="1035" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1035" s="9" t="s">
         <v>1691</v>
       </c>
@@ -87979,7 +87978,7 @@
       <c r="AH1035" s="4"/>
       <c r="AI1035" s="4"/>
     </row>
-    <row r="1036" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1036" s="9" t="s">
         <v>1692</v>
       </c>
@@ -88026,7 +88025,7 @@
       <c r="AH1036" s="4"/>
       <c r="AI1036" s="4"/>
     </row>
-    <row r="1037" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1037" s="9" t="s">
         <v>1693</v>
       </c>
@@ -88073,7 +88072,7 @@
       <c r="AH1037" s="4"/>
       <c r="AI1037" s="4"/>
     </row>
-    <row r="1038" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1038" s="9" t="s">
         <v>1694</v>
       </c>
@@ -88120,7 +88119,7 @@
       <c r="AH1038" s="4"/>
       <c r="AI1038" s="4"/>
     </row>
-    <row r="1039" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1039" s="9" t="s">
         <v>1695</v>
       </c>
@@ -88167,7 +88166,7 @@
       <c r="AH1039" s="4"/>
       <c r="AI1039" s="4"/>
     </row>
-    <row r="1040" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1040" s="9" t="s">
         <v>1696</v>
       </c>
@@ -88214,7 +88213,7 @@
       <c r="AH1040" s="4"/>
       <c r="AI1040" s="4"/>
     </row>
-    <row r="1041" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1041" s="9" t="s">
         <v>1697</v>
       </c>
@@ -88261,7 +88260,7 @@
       <c r="AH1041" s="4"/>
       <c r="AI1041" s="4"/>
     </row>
-    <row r="1042" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1042" s="9" t="s">
         <v>1698</v>
       </c>
@@ -88308,7 +88307,7 @@
       <c r="AH1042" s="4"/>
       <c r="AI1042" s="4"/>
     </row>
-    <row r="1043" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1043" s="2" t="s">
         <v>1702</v>
       </c>
@@ -88369,7 +88368,7 @@
       <c r="AH1043" s="4"/>
       <c r="AI1043" s="4"/>
     </row>
-    <row r="1044" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1044" s="2" t="s">
         <v>1699</v>
       </c>
@@ -88430,7 +88429,7 @@
       <c r="AH1044" s="4"/>
       <c r="AI1044" s="4"/>
     </row>
-    <row r="1045" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1045" s="2" t="s">
         <v>1700</v>
       </c>
@@ -88491,7 +88490,7 @@
       <c r="AH1045" s="4"/>
       <c r="AI1045" s="4"/>
     </row>
-    <row r="1046" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1046" s="2" t="s">
         <v>1701</v>
       </c>
@@ -88552,7 +88551,7 @@
       <c r="AH1046" s="4"/>
       <c r="AI1046" s="4"/>
     </row>
-    <row r="1047" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1047" s="2" t="s">
         <v>1703</v>
       </c>
@@ -88613,7 +88612,7 @@
       <c r="AH1047" s="4"/>
       <c r="AI1047" s="4"/>
     </row>
-    <row r="1048" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1048" s="2" t="s">
         <v>1705</v>
       </c>
@@ -88674,7 +88673,7 @@
       <c r="AH1048" s="4"/>
       <c r="AI1048" s="4"/>
     </row>
-    <row r="1049" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1049" s="2" t="s">
         <v>1706</v>
       </c>
@@ -88735,7 +88734,7 @@
       <c r="AH1049" s="4"/>
       <c r="AI1049" s="4"/>
     </row>
-    <row r="1050" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1050" s="2" t="s">
         <v>1707</v>
       </c>
@@ -88796,7 +88795,7 @@
       <c r="AH1050" s="4"/>
       <c r="AI1050" s="4"/>
     </row>
-    <row r="1051" spans="1:35" s="6" customFormat="1" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:35" s="6" customFormat="1" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1051" s="2" t="s">
         <v>1708</v>
       </c>
@@ -88858,13 +88857,7 @@
       <c r="AI1051" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R1051" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="CORRE VENTO 3"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:R1051" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrativo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5F7323-2A36-4B4E-80D2-5FEEE03C0FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DA9931-594E-4D33-8FE2-6BB515E1C882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77676,7 +77676,7 @@
         <v>46</v>
       </c>
       <c r="I860" s="4">
-        <v>499.99</v>
+        <v>399.99</v>
       </c>
       <c r="J860" s="4" t="s">
         <v>42</v>
@@ -77737,7 +77737,7 @@
         <v>46</v>
       </c>
       <c r="I861" s="4">
-        <v>499.99</v>
+        <v>399.99</v>
       </c>
       <c r="J861" s="4" t="s">
         <v>42</v>
@@ -77798,7 +77798,7 @@
         <v>46</v>
       </c>
       <c r="I862" s="4">
-        <v>499.99</v>
+        <v>399.99</v>
       </c>
       <c r="J862" s="4" t="s">
         <v>42</v>
@@ -77859,7 +77859,7 @@
         <v>46</v>
       </c>
       <c r="I863" s="4">
-        <v>499.99</v>
+        <v>399.99</v>
       </c>
       <c r="J863" s="4" t="s">
         <v>42</v>
@@ -77920,7 +77920,7 @@
         <v>46</v>
       </c>
       <c r="I864" s="4">
-        <v>499.99</v>
+        <v>399.99</v>
       </c>
       <c r="J864" s="4" t="s">
         <v>43</v>
@@ -77981,7 +77981,7 @@
         <v>46</v>
       </c>
       <c r="I865" s="4">
-        <v>499.99</v>
+        <v>399.99</v>
       </c>
       <c r="J865" s="4" t="s">
         <v>43</v>
@@ -78042,7 +78042,7 @@
         <v>46</v>
       </c>
       <c r="I866" s="4">
-        <v>499.99</v>
+        <v>399.99</v>
       </c>
       <c r="J866" s="4" t="s">
         <v>43</v>
@@ -78103,7 +78103,7 @@
         <v>46</v>
       </c>
       <c r="I867" s="4">
-        <v>499.99</v>
+        <v>399.99</v>
       </c>
       <c r="J867" s="4" t="s">
         <v>42</v>
@@ -78164,7 +78164,7 @@
         <v>46</v>
       </c>
       <c r="I868" s="4">
-        <v>499.99</v>
+        <v>399.99</v>
       </c>
       <c r="J868" s="4" t="s">
         <v>42</v>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrativo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30568873-55E8-4FD8-8EEA-1D4C8D0248E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C34284-1849-4947-8F22-76BA70815D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="corre" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produtos!$A$1:$R$1055</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produtos!$A$1:$R$1057</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13284" uniqueCount="1720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13304" uniqueCount="1723">
   <si>
     <t>IMAGEM</t>
   </si>
@@ -5197,6 +5197,15 @@
   </si>
   <si>
     <t>43304478_MUSGO</t>
+  </si>
+  <si>
+    <t>AREAML</t>
+  </si>
+  <si>
+    <t>43206446_LIMATL</t>
+  </si>
+  <si>
+    <t>43206446_AREAML</t>
   </si>
 </sst>
 </file>
@@ -5659,7 +5668,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:AI1055"/>
+  <dimension ref="A1:AI1057"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
@@ -76570,7 +76579,7 @@
       <c r="AH845" s="4"/>
       <c r="AI845" s="4"/>
     </row>
-    <row r="846" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="2" t="s">
         <v>1714</v>
       </c>
@@ -76631,7 +76640,7 @@
       <c r="AH846" s="4"/>
       <c r="AI846" s="4"/>
     </row>
-    <row r="847" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A847" s="2" t="s">
         <v>1715</v>
       </c>
@@ -76692,7 +76701,7 @@
       <c r="AH847" s="4"/>
       <c r="AI847" s="4"/>
     </row>
-    <row r="848" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A848" s="2" t="s">
         <v>1716</v>
       </c>
@@ -76753,7 +76762,7 @@
       <c r="AH848" s="4"/>
       <c r="AI848" s="4"/>
     </row>
-    <row r="849" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A849" s="2" t="s">
         <v>1717</v>
       </c>
@@ -76814,7 +76823,7 @@
       <c r="AH849" s="4"/>
       <c r="AI849" s="4"/>
     </row>
-    <row r="850" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850" s="2" t="s">
         <v>1718</v>
       </c>
@@ -76875,7 +76884,7 @@
       <c r="AH850" s="4"/>
       <c r="AI850" s="4"/>
     </row>
-    <row r="851" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A851" s="2" t="s">
         <v>1719</v>
       </c>
@@ -77241,7 +77250,7 @@
       <c r="AH856" s="4"/>
       <c r="AI856" s="4"/>
     </row>
-    <row r="857" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A857" s="2" t="s">
         <v>1308</v>
       </c>
@@ -77302,7 +77311,7 @@
       <c r="AH857" s="4"/>
       <c r="AI857" s="4"/>
     </row>
-    <row r="858" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A858" s="2" t="s">
         <v>1310</v>
       </c>
@@ -88272,7 +88281,7 @@
       <c r="AH1045" s="4"/>
       <c r="AI1045" s="4"/>
     </row>
-    <row r="1046" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1046" s="2" t="s">
         <v>1694</v>
       </c>
@@ -88333,7 +88342,7 @@
       <c r="AH1046" s="4"/>
       <c r="AI1046" s="4"/>
     </row>
-    <row r="1047" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1047" s="2" t="s">
         <v>1691</v>
       </c>
@@ -88394,9 +88403,9 @@
       <c r="AH1047" s="4"/>
       <c r="AI1047" s="4"/>
     </row>
-    <row r="1048" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1048" s="2" t="s">
-        <v>1692</v>
+        <v>1721</v>
       </c>
       <c r="B1048" s="2" t="s">
         <v>35</v>
@@ -88414,7 +88423,7 @@
         <v>645</v>
       </c>
       <c r="G1048" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H1048" s="4" t="s">
         <v>44</v>
@@ -88455,9 +88464,9 @@
       <c r="AH1048" s="4"/>
       <c r="AI1048" s="4"/>
     </row>
-    <row r="1049" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1049" s="2" t="s">
-        <v>1693</v>
+        <v>1722</v>
       </c>
       <c r="B1049" s="2" t="s">
         <v>35</v>
@@ -88475,7 +88484,7 @@
         <v>645</v>
       </c>
       <c r="G1049" s="4" t="s">
-        <v>54</v>
+        <v>1720</v>
       </c>
       <c r="H1049" s="4" t="s">
         <v>44</v>
@@ -88516,9 +88525,9 @@
       <c r="AH1049" s="4"/>
       <c r="AI1049" s="4"/>
     </row>
-    <row r="1050" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1050" s="2" t="s">
-        <v>1711</v>
+        <v>1692</v>
       </c>
       <c r="B1050" s="2" t="s">
         <v>35</v>
@@ -88536,7 +88545,7 @@
         <v>645</v>
       </c>
       <c r="G1050" s="4" t="s">
-        <v>377</v>
+        <v>48</v>
       </c>
       <c r="H1050" s="4" t="s">
         <v>44</v>
@@ -88577,9 +88586,9 @@
       <c r="AH1050" s="4"/>
       <c r="AI1050" s="4"/>
     </row>
-    <row r="1051" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1051" s="2" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="B1051" s="2" t="s">
         <v>35</v>
@@ -88597,7 +88606,7 @@
         <v>645</v>
       </c>
       <c r="G1051" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H1051" s="4" t="s">
         <v>44</v>
@@ -88638,33 +88647,33 @@
       <c r="AH1051" s="4"/>
       <c r="AI1051" s="4"/>
     </row>
-    <row r="1052" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1052" s="2" t="s">
-        <v>1697</v>
+        <v>1711</v>
       </c>
       <c r="B1052" s="2" t="s">
-        <v>443</v>
+        <v>35</v>
       </c>
       <c r="C1052" s="2" t="s">
-        <v>612</v>
+        <v>1300</v>
       </c>
       <c r="D1052" s="4">
-        <v>54111405</v>
+        <v>43206446</v>
       </c>
       <c r="E1052" s="5" t="s">
-        <v>614</v>
+        <v>1309</v>
       </c>
       <c r="F1052" s="4" t="s">
-        <v>615</v>
+        <v>645</v>
       </c>
       <c r="G1052" s="4" t="s">
-        <v>531</v>
+        <v>377</v>
       </c>
       <c r="H1052" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I1052" s="4">
-        <v>199.99</v>
+        <v>599.99</v>
       </c>
       <c r="J1052" s="4" t="s">
         <v>41</v>
@@ -88699,33 +88708,33 @@
       <c r="AH1052" s="4"/>
       <c r="AI1052" s="4"/>
     </row>
-    <row r="1053" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1053" s="2" t="s">
-        <v>1698</v>
+        <v>1695</v>
       </c>
       <c r="B1053" s="2" t="s">
-        <v>443</v>
+        <v>35</v>
       </c>
       <c r="C1053" s="2" t="s">
-        <v>612</v>
+        <v>1300</v>
       </c>
       <c r="D1053" s="4">
-        <v>54111405</v>
+        <v>43206446</v>
       </c>
       <c r="E1053" s="5" t="s">
-        <v>614</v>
+        <v>1309</v>
       </c>
       <c r="F1053" s="4" t="s">
-        <v>615</v>
+        <v>645</v>
       </c>
       <c r="G1053" s="4" t="s">
-        <v>1696</v>
+        <v>56</v>
       </c>
       <c r="H1053" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I1053" s="4">
-        <v>199.99</v>
+        <v>599.99</v>
       </c>
       <c r="J1053" s="4" t="s">
         <v>41</v>
@@ -88762,7 +88771,7 @@
     </row>
     <row r="1054" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1054" s="2" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="B1054" s="2" t="s">
         <v>443</v>
@@ -88780,7 +88789,7 @@
         <v>615</v>
       </c>
       <c r="G1054" s="4" t="s">
-        <v>368</v>
+        <v>531</v>
       </c>
       <c r="H1054" s="4" t="s">
         <v>44</v>
@@ -88823,7 +88832,7 @@
     </row>
     <row r="1055" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1055" s="2" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="B1055" s="2" t="s">
         <v>443</v>
@@ -88841,7 +88850,7 @@
         <v>615</v>
       </c>
       <c r="G1055" s="4" t="s">
-        <v>164</v>
+        <v>1696</v>
       </c>
       <c r="H1055" s="4" t="s">
         <v>44</v>
@@ -88882,11 +88891,133 @@
       <c r="AH1055" s="4"/>
       <c r="AI1055" s="4"/>
     </row>
+    <row r="1056" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1056" s="2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B1056" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C1056" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="D1056" s="4">
+        <v>54111405</v>
+      </c>
+      <c r="E1056" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="F1056" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="G1056" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="H1056" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1056" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J1056" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1056" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1056" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1056" s="4"/>
+      <c r="N1056" s="4"/>
+      <c r="O1056" s="4"/>
+      <c r="P1056" s="4"/>
+      <c r="Q1056" s="4"/>
+      <c r="R1056" s="4"/>
+      <c r="S1056" s="4"/>
+      <c r="T1056" s="4"/>
+      <c r="U1056" s="4"/>
+      <c r="V1056" s="4"/>
+      <c r="W1056" s="4"/>
+      <c r="X1056" s="4"/>
+      <c r="Y1056" s="4"/>
+      <c r="Z1056" s="4"/>
+      <c r="AA1056" s="4"/>
+      <c r="AB1056" s="4"/>
+      <c r="AC1056" s="4"/>
+      <c r="AD1056" s="4"/>
+      <c r="AE1056" s="4"/>
+      <c r="AF1056" s="4"/>
+      <c r="AG1056" s="4"/>
+      <c r="AH1056" s="4"/>
+      <c r="AI1056" s="4"/>
+    </row>
+    <row r="1057" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1057" s="2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B1057" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C1057" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="D1057" s="4">
+        <v>54111405</v>
+      </c>
+      <c r="E1057" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="F1057" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="G1057" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1057" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1057" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J1057" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1057" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1057" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1057" s="4"/>
+      <c r="N1057" s="4"/>
+      <c r="O1057" s="4"/>
+      <c r="P1057" s="4"/>
+      <c r="Q1057" s="4"/>
+      <c r="R1057" s="4"/>
+      <c r="S1057" s="4"/>
+      <c r="T1057" s="4"/>
+      <c r="U1057" s="4"/>
+      <c r="V1057" s="4"/>
+      <c r="W1057" s="4"/>
+      <c r="X1057" s="4"/>
+      <c r="Y1057" s="4"/>
+      <c r="Z1057" s="4"/>
+      <c r="AA1057" s="4"/>
+      <c r="AB1057" s="4"/>
+      <c r="AC1057" s="4"/>
+      <c r="AD1057" s="4"/>
+      <c r="AE1057" s="4"/>
+      <c r="AF1057" s="4"/>
+      <c r="AG1057" s="4"/>
+      <c r="AH1057" s="4"/>
+      <c r="AI1057" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R1055" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:R1057" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="4">
       <filters>
-        <filter val="CORRE MAX 2"/>
+        <filter val="CORRE 5"/>
       </filters>
     </filterColumn>
   </autoFilter>
